--- a/Översikt JÖNKÖPING.xlsx
+++ b/Översikt JÖNKÖPING.xlsx
@@ -567,7 +567,7 @@
         <v>45856.56684027778</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -665,7 +665,7 @@
         <v>45856.57200231482</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
         <v>45777</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>45609</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         <v>45348</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         <v>44111</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>45698.48634259259</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>45275</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>44083</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>44992</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>45788.88578703703</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>45846.47335648148</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>45751.53178240741</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>44530</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>44974</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>44512.62668981482</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         <v>44602</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>45604.53402777778</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>44991</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>45751.60517361111</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2412,7 +2412,7 @@
         <v>45539</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         <v>45373.44148148148</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>45790.83706018519</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         <v>45358.52763888889</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         <v>45679.98452546296</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>45302</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>44278</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>44419</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         <v>44463</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
         <v>44095</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>44083</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         <v>44469</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
         <v>44347.63069444444</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>44467</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>45751</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         <v>44404.71972222222</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3796,7 +3796,7 @@
         <v>44840</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3881,7 +3881,7 @@
         <v>45783</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         <v>45580.46207175926</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4051,7 +4051,7 @@
         <v>45740.58743055556</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>45841.4303125</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         <v>45295.3942824074</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4311,7 +4311,7 @@
         <v>45343</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>45587</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
         <v>45758</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>45846</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
         <v>45302</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4741,7 +4741,7 @@
         <v>45856.55965277777</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4830,7 +4830,7 @@
         <v>45819.60131944445</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
         <v>45205</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>45538.45523148148</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         <v>45846</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         <v>44879</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5268,7 +5268,7 @@
         <v>45876.69954861111</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         <v>45616</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5442,7 +5442,7 @@
         <v>45569.41550925926</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5527,7 +5527,7 @@
         <v>44943</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5612,7 +5612,7 @@
         <v>44260</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5669,7 +5669,7 @@
         <v>44188</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5726,7 +5726,7 @@
         <v>44137</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5783,7 +5783,7 @@
         <v>44147</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>44306</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5897,7 +5897,7 @@
         <v>44308</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5959,7 +5959,7 @@
         <v>44066</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6016,7 +6016,7 @@
         <v>44144</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6073,7 +6073,7 @@
         <v>44328.35063657408</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6130,7 +6130,7 @@
         <v>44239.33525462963</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         <v>44496</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6244,7 +6244,7 @@
         <v>44404.84280092592</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6301,7 +6301,7 @@
         <v>44404.84659722223</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6358,7 +6358,7 @@
         <v>44278.3859375</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         <v>44575.80925925926</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>44662</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>44487</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6586,7 +6586,7 @@
         <v>44749.55936342593</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         <v>44749.55703703704</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6700,7 +6700,7 @@
         <v>44273.62572916667</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6757,7 +6757,7 @@
         <v>44454.35472222222</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6814,7 +6814,7 @@
         <v>44308</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6876,7 +6876,7 @@
         <v>44225</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6933,7 +6933,7 @@
         <v>44308</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6995,7 +6995,7 @@
         <v>44349</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7052,7 +7052,7 @@
         <v>44792.53711805555</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7109,7 +7109,7 @@
         <v>44411</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7166,7 +7166,7 @@
         <v>44194</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         <v>44225</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7280,7 +7280,7 @@
         <v>44809</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7337,7 +7337,7 @@
         <v>44442</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7394,7 +7394,7 @@
         <v>44487.49392361111</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7451,7 +7451,7 @@
         <v>44487</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7508,7 +7508,7 @@
         <v>44749.32716435185</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7565,7 +7565,7 @@
         <v>44420.68987268519</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7622,7 +7622,7 @@
         <v>44404.84138888889</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7679,7 +7679,7 @@
         <v>44266</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7736,7 +7736,7 @@
         <v>44881.81052083334</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7793,7 +7793,7 @@
         <v>44665.60081018518</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7850,7 +7850,7 @@
         <v>44869.49265046296</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>44734</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7974,7 +7974,7 @@
         <v>44792</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
         <v>44054</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8093,7 +8093,7 @@
         <v>44365</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8150,7 +8150,7 @@
         <v>44259</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         <v>44538</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8264,7 +8264,7 @@
         <v>44263</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8326,7 +8326,7 @@
         <v>44113</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         <v>44487</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8440,7 +8440,7 @@
         <v>44487</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8497,7 +8497,7 @@
         <v>44272</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8554,7 +8554,7 @@
         <v>44875.59231481481</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         <v>44852.74376157407</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8673,7 +8673,7 @@
         <v>44200</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8730,7 +8730,7 @@
         <v>44292</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         <v>44498.56373842592</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8844,7 +8844,7 @@
         <v>44111</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8901,7 +8901,7 @@
         <v>44881.79847222222</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8958,7 +8958,7 @@
         <v>44286.34827546297</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9015,7 +9015,7 @@
         <v>44273</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9072,7 +9072,7 @@
         <v>44673</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9129,7 +9129,7 @@
         <v>44298.46462962963</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         <v>44298.46582175926</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9253,7 +9253,7 @@
         <v>44278.38752314815</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         <v>44279.37552083333</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         <v>44347.61920138889</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>44754.47359953704</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         <v>44855.3080787037</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9543,7 +9543,7 @@
         <v>44476</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9600,7 +9600,7 @@
         <v>44373.75251157407</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9657,7 +9657,7 @@
         <v>44347.6287962963</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9714,7 +9714,7 @@
         <v>44511</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9771,7 +9771,7 @@
         <v>44466.4425</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9828,7 +9828,7 @@
         <v>44377</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9885,7 +9885,7 @@
         <v>44440.71997685185</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9942,7 +9942,7 @@
         <v>44840</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9999,7 +9999,7 @@
         <v>44104</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10056,7 +10056,7 @@
         <v>44280</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10113,7 +10113,7 @@
         <v>44613</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10170,7 +10170,7 @@
         <v>44456.46952546296</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10227,7 +10227,7 @@
         <v>44537</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10284,7 +10284,7 @@
         <v>44360</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10341,7 +10341,7 @@
         <v>44356</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10398,7 +10398,7 @@
         <v>44476</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10455,7 +10455,7 @@
         <v>44575</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10512,7 +10512,7 @@
         <v>44298.44060185185</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10574,7 +10574,7 @@
         <v>44711</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10631,7 +10631,7 @@
         <v>44711</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10688,7 +10688,7 @@
         <v>44428.596875</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10750,7 +10750,7 @@
         <v>44659.57226851852</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10812,7 +10812,7 @@
         <v>44659</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10874,7 +10874,7 @@
         <v>44819</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10931,7 +10931,7 @@
         <v>44819.28449074074</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10988,7 +10988,7 @@
         <v>44292</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11045,7 +11045,7 @@
         <v>44846.66688657407</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11102,7 +11102,7 @@
         <v>44605.44909722222</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11159,7 +11159,7 @@
         <v>44151</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11216,7 +11216,7 @@
         <v>44523.65311342593</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11273,7 +11273,7 @@
         <v>44454.4800925926</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11330,7 +11330,7 @@
         <v>44578</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11387,7 +11387,7 @@
         <v>44344</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11444,7 +11444,7 @@
         <v>44474.25150462963</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11501,7 +11501,7 @@
         <v>44596</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11558,7 +11558,7 @@
         <v>44498.57181712963</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11615,7 +11615,7 @@
         <v>44628</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11672,7 +11672,7 @@
         <v>44711</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11729,7 +11729,7 @@
         <v>44711</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11786,7 +11786,7 @@
         <v>44082.79793981482</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11843,7 +11843,7 @@
         <v>44082</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11900,7 +11900,7 @@
         <v>44841.31997685185</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11957,7 +11957,7 @@
         <v>44579.41064814815</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12014,7 +12014,7 @@
         <v>44532.30398148148</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12071,7 +12071,7 @@
         <v>44467.68283564815</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12128,7 +12128,7 @@
         <v>44557.71989583333</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12185,7 +12185,7 @@
         <v>44792.53936342592</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12242,7 +12242,7 @@
         <v>44616.39256944445</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12299,7 +12299,7 @@
         <v>44593</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12356,7 +12356,7 @@
         <v>44373</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12413,7 +12413,7 @@
         <v>44056</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12470,7 +12470,7 @@
         <v>44428.34821759259</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12532,7 +12532,7 @@
         <v>44272</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12589,7 +12589,7 @@
         <v>44259</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12646,7 +12646,7 @@
         <v>44239</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12703,7 +12703,7 @@
         <v>44239</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12760,7 +12760,7 @@
         <v>44088</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12817,7 +12817,7 @@
         <v>44464.40523148148</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12874,7 +12874,7 @@
         <v>44294</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12931,7 +12931,7 @@
         <v>44412</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12988,7 +12988,7 @@
         <v>44830.90146990741</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13045,7 +13045,7 @@
         <v>44787.80010416666</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13102,7 +13102,7 @@
         <v>44575</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13159,7 +13159,7 @@
         <v>44428.58511574074</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13221,7 +13221,7 @@
         <v>44729</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13278,7 +13278,7 @@
         <v>44308</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13340,7 +13340,7 @@
         <v>44272</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13397,7 +13397,7 @@
         <v>44161.31023148148</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13454,7 +13454,7 @@
         <v>44825.40940972222</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13516,7 +13516,7 @@
         <v>44279.61517361111</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13573,7 +13573,7 @@
         <v>44614</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13635,7 +13635,7 @@
         <v>44805</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13697,7 +13697,7 @@
         <v>44811</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13754,7 +13754,7 @@
         <v>44585.30171296297</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13811,7 +13811,7 @@
         <v>44428</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13873,7 +13873,7 @@
         <v>44536</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13935,7 +13935,7 @@
         <v>44075</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13992,7 +13992,7 @@
         <v>44464.42415509259</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14049,7 +14049,7 @@
         <v>44488</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14106,7 +14106,7 @@
         <v>44579</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14163,7 +14163,7 @@
         <v>44074</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14220,7 +14220,7 @@
         <v>44412.7071875</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14277,7 +14277,7 @@
         <v>44998</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14334,7 +14334,7 @@
         <v>44361</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14391,7 +14391,7 @@
         <v>44252</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14448,7 +14448,7 @@
         <v>45673.71842592592</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14505,7 +14505,7 @@
         <v>45621.52488425926</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14562,7 +14562,7 @@
         <v>45621.5278125</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14619,7 +14619,7 @@
         <v>45758</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14681,7 +14681,7 @@
         <v>45008</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14738,7 +14738,7 @@
         <v>45338.69246527777</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14800,7 +14800,7 @@
         <v>45747.30204861111</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14857,7 +14857,7 @@
         <v>45152</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14914,7 +14914,7 @@
         <v>45401</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14976,7 +14976,7 @@
         <v>45373.60802083334</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15033,7 +15033,7 @@
         <v>45341</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15090,7 +15090,7 @@
         <v>45272.42149305555</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15147,7 +15147,7 @@
         <v>44326</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15204,7 +15204,7 @@
         <v>44575.8194212963</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15261,7 +15261,7 @@
         <v>45260.85619212963</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15318,7 +15318,7 @@
         <v>45772.45813657407</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15375,7 +15375,7 @@
         <v>45775.4219212963</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15432,7 +15432,7 @@
         <v>45127</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15489,7 +15489,7 @@
         <v>45197.61039351852</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15551,7 +15551,7 @@
         <v>44886.3340625</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15608,7 +15608,7 @@
         <v>44967.6228125</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15665,7 +15665,7 @@
         <v>45697.26537037037</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15722,7 +15722,7 @@
         <v>45043.67869212963</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15779,7 +15779,7 @@
         <v>45751.5153125</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15841,7 +15841,7 @@
         <v>45605.84435185185</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15898,7 +15898,7 @@
         <v>45152</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15955,7 +15955,7 @@
         <v>45092</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16012,7 +16012,7 @@
         <v>44273</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16069,7 +16069,7 @@
         <v>44741.69432870371</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16126,7 +16126,7 @@
         <v>45756</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16183,7 +16183,7 @@
         <v>45757.29700231482</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16240,7 +16240,7 @@
         <v>45615.90662037037</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16297,7 +16297,7 @@
         <v>45750.50650462963</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>44631</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16411,7 +16411,7 @@
         <v>44082</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16468,7 +16468,7 @@
         <v>45567</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16525,7 +16525,7 @@
         <v>45628</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16582,7 +16582,7 @@
         <v>45630.6993287037</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16639,7 +16639,7 @@
         <v>45240</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16696,7 +16696,7 @@
         <v>45642.92393518519</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16753,7 +16753,7 @@
         <v>45531</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16810,7 +16810,7 @@
         <v>45735.81920138889</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16867,7 +16867,7 @@
         <v>44229</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16924,7 +16924,7 @@
         <v>45112</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16981,7 +16981,7 @@
         <v>44735</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17038,7 +17038,7 @@
         <v>45775.4233912037</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17095,7 +17095,7 @@
         <v>45749.67842592593</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17152,7 +17152,7 @@
         <v>44325.76335648148</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>45406</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>45324.64579861111</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17328,7 +17328,7 @@
         <v>45324.64745370371</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17390,7 +17390,7 @@
         <v>45012</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17447,7 +17447,7 @@
         <v>45300</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17504,7 +17504,7 @@
         <v>45092.39466435185</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17561,7 +17561,7 @@
         <v>45751.62381944444</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17623,7 +17623,7 @@
         <v>45588</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17680,7 +17680,7 @@
         <v>45588</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17737,7 +17737,7 @@
         <v>45587</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17794,7 +17794,7 @@
         <v>44468</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17851,7 +17851,7 @@
         <v>44148</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17908,7 +17908,7 @@
         <v>44804</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17965,7 +17965,7 @@
         <v>44985</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18022,7 +18022,7 @@
         <v>45706.69090277778</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18084,7 +18084,7 @@
         <v>45099</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18141,7 +18141,7 @@
         <v>45363.45982638889</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18198,7 +18198,7 @@
         <v>45764.53915509259</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18255,7 +18255,7 @@
         <v>45757</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18312,7 +18312,7 @@
         <v>44449</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18369,7 +18369,7 @@
         <v>45177.5462962963</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18426,7 +18426,7 @@
         <v>45223.65527777778</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18483,7 +18483,7 @@
         <v>45181</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18540,7 +18540,7 @@
         <v>44904</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18602,7 +18602,7 @@
         <v>45769.60440972223</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18659,7 +18659,7 @@
         <v>44882</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18716,7 +18716,7 @@
         <v>45321</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18773,7 +18773,7 @@
         <v>45107</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18830,7 +18830,7 @@
         <v>45299</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18887,7 +18887,7 @@
         <v>44433</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18944,7 +18944,7 @@
         <v>45037.67510416666</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19001,7 +19001,7 @@
         <v>45270.42966435185</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19058,7 +19058,7 @@
         <v>44840</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19115,7 +19115,7 @@
         <v>45474.70864583334</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19172,7 +19172,7 @@
         <v>45079</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19229,7 +19229,7 @@
         <v>45252.58925925926</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19286,7 +19286,7 @@
         <v>44151</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19343,7 +19343,7 @@
         <v>44056</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19400,7 +19400,7 @@
         <v>44487</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19457,7 +19457,7 @@
         <v>44414</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19514,7 +19514,7 @@
         <v>45356.65395833334</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19576,7 +19576,7 @@
         <v>45764.30016203703</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19633,7 +19633,7 @@
         <v>44882</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19690,7 +19690,7 @@
         <v>45558.51949074074</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19752,7 +19752,7 @@
         <v>45764.30391203704</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19809,7 +19809,7 @@
         <v>45107</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19866,7 +19866,7 @@
         <v>44588.50104166667</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19923,7 +19923,7 @@
         <v>44893</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19985,7 +19985,7 @@
         <v>45355.56604166667</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20042,7 +20042,7 @@
         <v>45324.64302083333</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20104,7 +20104,7 @@
         <v>45747.44508101852</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20161,7 +20161,7 @@
         <v>45747.45177083334</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20218,7 +20218,7 @@
         <v>44979</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20275,7 +20275,7 @@
         <v>44368.64017361111</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20332,7 +20332,7 @@
         <v>45740.59871527777</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20389,7 +20389,7 @@
         <v>45243</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20451,7 +20451,7 @@
         <v>45763.38354166667</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20528,7 +20528,7 @@
         <v>45114.55280092593</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20585,7 +20585,7 @@
         <v>45201</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20647,7 +20647,7 @@
         <v>45545.53883101852</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20704,7 +20704,7 @@
         <v>45169</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20761,7 +20761,7 @@
         <v>44837</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20818,7 +20818,7 @@
         <v>45468.44574074074</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20875,7 +20875,7 @@
         <v>45775.32407407407</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20932,7 +20932,7 @@
         <v>45477.48771990741</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20989,7 +20989,7 @@
         <v>45597.53744212963</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21046,7 +21046,7 @@
         <v>45183</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21103,7 +21103,7 @@
         <v>45056.6438425926</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21160,7 +21160,7 @@
         <v>45436.68626157408</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21217,7 +21217,7 @@
         <v>45314</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21274,7 +21274,7 @@
         <v>45757.30554398148</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21331,7 +21331,7 @@
         <v>45755.70262731481</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21388,7 +21388,7 @@
         <v>45455.42533564815</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21450,7 +21450,7 @@
         <v>45455.42981481482</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21512,7 +21512,7 @@
         <v>45447.55340277778</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21569,7 +21569,7 @@
         <v>45201.59743055556</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21626,7 +21626,7 @@
         <v>45644.62243055556</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21683,7 +21683,7 @@
         <v>44963.66563657407</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21740,7 +21740,7 @@
         <v>45761.41857638889</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21797,7 +21797,7 @@
         <v>44904.49826388889</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21854,7 +21854,7 @@
         <v>44904</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21911,7 +21911,7 @@
         <v>44449</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21968,7 +21968,7 @@
         <v>44923.55936342593</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22025,7 +22025,7 @@
         <v>45359.54100694445</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22082,7 +22082,7 @@
         <v>44483.58045138889</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22139,7 +22139,7 @@
         <v>45414</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22196,7 +22196,7 @@
         <v>45477.38181712963</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22253,7 +22253,7 @@
         <v>45377.42784722222</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22310,7 +22310,7 @@
         <v>45533.46368055556</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22367,7 +22367,7 @@
         <v>45351.65180555556</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22429,7 +22429,7 @@
         <v>45617.48947916667</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22486,7 +22486,7 @@
         <v>45539.34539351852</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22543,7 +22543,7 @@
         <v>45462.37888888889</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22600,7 +22600,7 @@
         <v>45219</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22657,7 +22657,7 @@
         <v>45477.33712962963</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22714,7 +22714,7 @@
         <v>45775.32163194445</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22771,7 +22771,7 @@
         <v>45502.32021990741</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22828,7 +22828,7 @@
         <v>45502.33179398148</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22885,7 +22885,7 @@
         <v>45406.89703703704</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22942,7 +22942,7 @@
         <v>44853</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23004,7 +23004,7 @@
         <v>45751.52445601852</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23066,7 +23066,7 @@
         <v>45751.59875</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23128,7 +23128,7 @@
         <v>45751.61236111111</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23190,7 +23190,7 @@
         <v>45751.61556712963</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23252,7 +23252,7 @@
         <v>45547.43793981482</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23314,7 +23314,7 @@
         <v>45748</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23376,7 +23376,7 @@
         <v>45092.42630787037</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23433,7 +23433,7 @@
         <v>45446.56622685185</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23490,7 +23490,7 @@
         <v>45049</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23547,7 +23547,7 @@
         <v>45051</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23604,7 +23604,7 @@
         <v>44355.60153935185</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23661,7 +23661,7 @@
         <v>45716.7125</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23718,7 +23718,7 @@
         <v>45111</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23775,7 +23775,7 @@
         <v>45112</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23832,7 +23832,7 @@
         <v>44950</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23889,7 +23889,7 @@
         <v>44950</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23946,7 +23946,7 @@
         <v>45349</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24003,7 +24003,7 @@
         <v>45119.54038194445</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24060,7 +24060,7 @@
         <v>44893</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24122,7 +24122,7 @@
         <v>45145.47684027778</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24179,7 +24179,7 @@
         <v>45492.70833333334</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24236,7 +24236,7 @@
         <v>44488</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24293,7 +24293,7 @@
         <v>45566</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24350,7 +24350,7 @@
         <v>45331</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24407,7 +24407,7 @@
         <v>44966.57471064815</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24469,7 +24469,7 @@
         <v>44936</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24526,7 +24526,7 @@
         <v>44411</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24583,7 +24583,7 @@
         <v>45706.68554398148</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24645,7 +24645,7 @@
         <v>45645.88440972222</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24702,7 +24702,7 @@
         <v>44853</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24759,7 +24759,7 @@
         <v>45734.59972222222</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24816,7 +24816,7 @@
         <v>44083</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24873,7 +24873,7 @@
         <v>45497</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24930,7 +24930,7 @@
         <v>45615.89965277778</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24987,7 +24987,7 @@
         <v>45747.45038194444</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25044,7 +25044,7 @@
         <v>45701.38606481482</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25101,7 +25101,7 @@
         <v>45116.44680555556</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25158,7 +25158,7 @@
         <v>45169.38410879629</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25215,7 +25215,7 @@
         <v>44935.37284722222</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25272,7 +25272,7 @@
         <v>45758</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25334,7 +25334,7 @@
         <v>45758.64109953704</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25391,7 +25391,7 @@
         <v>45587.49814814814</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25448,7 +25448,7 @@
         <v>44957.36059027778</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25505,7 +25505,7 @@
         <v>45118</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25562,7 +25562,7 @@
         <v>44063</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25624,7 +25624,7 @@
         <v>45770</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25681,7 +25681,7 @@
         <v>45338</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25743,7 +25743,7 @@
         <v>44944.40825231482</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25800,7 +25800,7 @@
         <v>45562.38306712963</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25857,7 +25857,7 @@
         <v>45630.39188657407</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25919,7 +25919,7 @@
         <v>45012.47533564815</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25976,7 +25976,7 @@
         <v>44482</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26033,7 +26033,7 @@
         <v>45704</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26090,7 +26090,7 @@
         <v>45557.35435185185</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26147,7 +26147,7 @@
         <v>45358</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26204,7 +26204,7 @@
         <v>45358.61696759259</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26261,7 +26261,7 @@
         <v>44484.49586805556</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26318,7 +26318,7 @@
         <v>45764.3996412037</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26375,7 +26375,7 @@
         <v>45635.28104166667</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26432,7 +26432,7 @@
         <v>45643.47644675926</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26489,7 +26489,7 @@
         <v>45281.57759259259</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26551,7 +26551,7 @@
         <v>45295.40646990741</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26613,7 +26613,7 @@
         <v>45307.72520833334</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26670,7 +26670,7 @@
         <v>45275</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26727,7 +26727,7 @@
         <v>45455.4374537037</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26789,7 +26789,7 @@
         <v>45099.74195601852</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26846,7 +26846,7 @@
         <v>44628</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26903,7 +26903,7 @@
         <v>44090</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26960,7 +26960,7 @@
         <v>45335.76891203703</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27022,7 +27022,7 @@
         <v>45541.37402777778</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27079,7 +27079,7 @@
         <v>45618</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27136,7 +27136,7 @@
         <v>45414</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27193,7 +27193,7 @@
         <v>45667.63950231481</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27250,7 +27250,7 @@
         <v>44507.82581018518</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27307,7 +27307,7 @@
         <v>44589.74348379629</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27364,7 +27364,7 @@
         <v>45777.60824074074</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27421,7 +27421,7 @@
         <v>45777.50512731481</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27478,7 +27478,7 @@
         <v>44893.50922453704</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27540,7 +27540,7 @@
         <v>45545.59315972222</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27602,7 +27602,7 @@
         <v>45779.62363425926</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27659,7 +27659,7 @@
         <v>45538</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27716,7 +27716,7 @@
         <v>45646.67994212963</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27773,7 +27773,7 @@
         <v>44648.61840277778</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27830,7 +27830,7 @@
         <v>45560.35501157407</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27887,7 +27887,7 @@
         <v>45586.62837962963</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27944,7 +27944,7 @@
         <v>45519.48550925926</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28001,7 +28001,7 @@
         <v>45785.65899305556</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28058,7 +28058,7 @@
         <v>44109</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28115,7 +28115,7 @@
         <v>44097</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28172,7 +28172,7 @@
         <v>44550.30402777778</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28229,7 +28229,7 @@
         <v>44118</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28291,7 +28291,7 @@
         <v>44589.73825231481</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28348,7 +28348,7 @@
         <v>44557</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28405,7 +28405,7 @@
         <v>44904</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28462,7 +28462,7 @@
         <v>45124.59594907407</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28519,7 +28519,7 @@
         <v>44056</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28576,7 +28576,7 @@
         <v>45267.62943287037</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28633,7 +28633,7 @@
         <v>44943</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28690,7 +28690,7 @@
         <v>45747.73295138889</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28747,7 +28747,7 @@
         <v>45720.70986111111</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28804,7 +28804,7 @@
         <v>45216.47443287037</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28861,7 +28861,7 @@
         <v>45460.42804398148</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28918,7 +28918,7 @@
         <v>45588</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28975,7 +28975,7 @@
         <v>45009</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29032,7 +29032,7 @@
         <v>45784.84850694444</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29089,7 +29089,7 @@
         <v>44605.45792824074</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29146,7 +29146,7 @@
         <v>45175.44625</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29203,7 +29203,7 @@
         <v>45401.34349537037</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29260,7 +29260,7 @@
         <v>44172</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29317,7 +29317,7 @@
         <v>45750.40476851852</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29374,7 +29374,7 @@
         <v>45586</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29431,7 +29431,7 @@
         <v>45789.54226851852</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29488,7 +29488,7 @@
         <v>45764.42304398148</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29545,7 +29545,7 @@
         <v>45566</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29602,7 +29602,7 @@
         <v>45105.34402777778</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29659,7 +29659,7 @@
         <v>45405</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29716,7 +29716,7 @@
         <v>45405</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29773,7 +29773,7 @@
         <v>45184</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29830,7 +29830,7 @@
         <v>45547.83950231481</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29892,7 +29892,7 @@
         <v>44578.52657407407</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29949,7 +29949,7 @@
         <v>45788.88399305556</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30006,7 +30006,7 @@
         <v>44592.28611111111</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30063,7 +30063,7 @@
         <v>45541</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30120,7 +30120,7 @@
         <v>45545.65415509259</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30182,7 +30182,7 @@
         <v>45412</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30244,7 +30244,7 @@
         <v>45194</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30301,7 +30301,7 @@
         <v>45552.48335648148</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30358,7 +30358,7 @@
         <v>45462.38087962963</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30415,7 +30415,7 @@
         <v>44585</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30472,7 +30472,7 @@
         <v>45788.3231712963</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30529,7 +30529,7 @@
         <v>45763.49402777778</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30586,7 +30586,7 @@
         <v>45177</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30643,7 +30643,7 @@
         <v>45788.32225694445</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30700,7 +30700,7 @@
         <v>45197</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30757,7 +30757,7 @@
         <v>45670.66061342593</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30814,7 +30814,7 @@
         <v>45021</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30871,7 +30871,7 @@
         <v>45646.5796412037</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30928,7 +30928,7 @@
         <v>45519.49606481481</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30985,7 +30985,7 @@
         <v>44950</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31042,7 +31042,7 @@
         <v>45600.47958333333</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31099,7 +31099,7 @@
         <v>45560.35614583334</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31156,7 +31156,7 @@
         <v>45043</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31213,7 +31213,7 @@
         <v>45790.82361111111</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31270,7 +31270,7 @@
         <v>45205</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31327,7 +31327,7 @@
         <v>44938</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31389,7 +31389,7 @@
         <v>45645.57626157408</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31446,7 +31446,7 @@
         <v>44187</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31508,7 +31508,7 @@
         <v>45551.36004629629</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31565,7 +31565,7 @@
         <v>44977.26300925926</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31622,7 +31622,7 @@
         <v>45541.38644675926</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31679,7 +31679,7 @@
         <v>45587</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31736,7 +31736,7 @@
         <v>45790.81799768518</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31793,7 +31793,7 @@
         <v>45791.85732638889</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31850,7 +31850,7 @@
         <v>45184</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31907,7 +31907,7 @@
         <v>45350.56959490741</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31964,7 +31964,7 @@
         <v>44252</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32021,7 +32021,7 @@
         <v>45701.31962962963</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32078,7 +32078,7 @@
         <v>44943.4652199074</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32135,7 +32135,7 @@
         <v>44943.46980324074</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32192,7 +32192,7 @@
         <v>45681.48793981481</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32249,7 +32249,7 @@
         <v>45681.53460648148</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32306,7 +32306,7 @@
         <v>45622.35340277778</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32363,7 +32363,7 @@
         <v>45558.63807870371</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32425,7 +32425,7 @@
         <v>44591</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32482,7 +32482,7 @@
         <v>44608</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32539,7 +32539,7 @@
         <v>45169</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32596,7 +32596,7 @@
         <v>45637.51090277778</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32653,7 +32653,7 @@
         <v>45112.3174074074</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32710,7 +32710,7 @@
         <v>45112</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32767,7 +32767,7 @@
         <v>44930</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32824,7 +32824,7 @@
         <v>45759.74934027778</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32881,7 +32881,7 @@
         <v>45587.47273148148</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32938,7 +32938,7 @@
         <v>45701.37818287037</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32995,7 +32995,7 @@
         <v>44626</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33052,7 +33052,7 @@
         <v>45646.39016203704</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33109,7 +33109,7 @@
         <v>45628</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33171,7 +33171,7 @@
         <v>45628</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33233,7 +33233,7 @@
         <v>45570.58934027778</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33290,7 +33290,7 @@
         <v>44575.80709490741</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33347,7 +33347,7 @@
         <v>44950</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33404,7 +33404,7 @@
         <v>44249</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33461,7 +33461,7 @@
         <v>44225</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33518,7 +33518,7 @@
         <v>45793</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33575,7 +33575,7 @@
         <v>44249.66673611111</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33632,7 +33632,7 @@
         <v>45581.52885416667</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33689,7 +33689,7 @@
         <v>45363.91521990741</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33746,7 +33746,7 @@
         <v>45364.40862268519</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33803,7 +33803,7 @@
         <v>45435</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33865,7 +33865,7 @@
         <v>44966.52741898148</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33927,7 +33927,7 @@
         <v>45030</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33984,7 +33984,7 @@
         <v>45371.60959490741</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34041,7 +34041,7 @@
         <v>45630.70101851852</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34103,7 +34103,7 @@
         <v>45182.36129629629</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34160,7 +34160,7 @@
         <v>44988</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34217,7 +34217,7 @@
         <v>45617.92190972222</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34274,7 +34274,7 @@
         <v>45056</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34331,7 +34331,7 @@
         <v>45600.48127314815</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34388,7 +34388,7 @@
         <v>45600.48347222222</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34445,7 +34445,7 @@
         <v>45736</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34502,7 +34502,7 @@
         <v>45740.59474537037</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34559,7 +34559,7 @@
         <v>44564.8419212963</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34616,7 +34616,7 @@
         <v>45839.71761574074</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34673,7 +34673,7 @@
         <v>45174</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34730,7 +34730,7 @@
         <v>45727.55315972222</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34787,7 +34787,7 @@
         <v>45736.67693287037</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34844,7 +34844,7 @@
         <v>45727.3134375</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34901,7 +34901,7 @@
         <v>45727.36650462963</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34958,7 +34958,7 @@
         <v>45735</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35015,7 +35015,7 @@
         <v>45734.35039351852</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35072,7 +35072,7 @@
         <v>45740.91412037037</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35129,7 +35129,7 @@
         <v>45741.65699074074</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35186,7 +35186,7 @@
         <v>45741.69303240741</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35243,7 +35243,7 @@
         <v>45726.44835648148</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35300,7 +35300,7 @@
         <v>45735.65969907407</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35357,7 +35357,7 @@
         <v>45797.56770833334</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35414,7 +35414,7 @@
         <v>44571</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35471,7 +35471,7 @@
         <v>45764.40184027778</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35528,7 +35528,7 @@
         <v>45755</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35585,7 +35585,7 @@
         <v>45728</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35642,7 +35642,7 @@
         <v>45727.35745370371</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35699,7 +35699,7 @@
         <v>45727.36243055556</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35756,7 +35756,7 @@
         <v>45734.3584837963</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35813,7 +35813,7 @@
         <v>44711</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35870,7 +35870,7 @@
         <v>45730.44528935185</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35932,7 +35932,7 @@
         <v>45201</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35989,7 +35989,7 @@
         <v>45372.34530092592</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36046,7 +36046,7 @@
         <v>45179.9259375</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36103,7 +36103,7 @@
         <v>45736</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36160,7 +36160,7 @@
         <v>44261</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36217,7 +36217,7 @@
         <v>45743.59641203703</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36274,7 +36274,7 @@
         <v>45797.67148148148</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36331,7 +36331,7 @@
         <v>45734.35122685185</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36388,7 +36388,7 @@
         <v>45726.52925925926</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36445,7 +36445,7 @@
         <v>45624.41041666667</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36502,7 +36502,7 @@
         <v>44998.8734837963</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36559,7 +36559,7 @@
         <v>45730.65831018519</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36616,7 +36616,7 @@
         <v>45547.84315972222</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36678,7 +36678,7 @@
         <v>45737.67416666666</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36735,7 +36735,7 @@
         <v>45730.3782175926</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36797,7 +36797,7 @@
         <v>45799.50931712963</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36854,7 +36854,7 @@
         <v>45799.52318287037</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36911,7 +36911,7 @@
         <v>45799.58894675926</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36968,7 +36968,7 @@
         <v>45799.5803125</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37025,7 +37025,7 @@
         <v>45182.71081018518</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37082,7 +37082,7 @@
         <v>44894</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37139,7 +37139,7 @@
         <v>45763.49306712963</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37196,7 +37196,7 @@
         <v>45751.51961805556</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37258,7 +37258,7 @@
         <v>45841.4390625</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37315,7 +37315,7 @@
         <v>45295.4037962963</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37377,7 +37377,7 @@
         <v>45799.50469907407</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37434,7 +37434,7 @@
         <v>45547.42313657407</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37496,7 +37496,7 @@
         <v>45547.53320601852</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37553,7 +37553,7 @@
         <v>45842.49056712963</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37610,7 +37610,7 @@
         <v>45671.44894675926</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37667,7 +37667,7 @@
         <v>45842.49457175926</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37724,7 +37724,7 @@
         <v>45842.5059375</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37781,7 +37781,7 @@
         <v>45440.3712037037</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37838,7 +37838,7 @@
         <v>45617.4922337963</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37895,7 +37895,7 @@
         <v>45799.51578703704</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37952,7 +37952,7 @@
         <v>45113.31806712963</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38009,7 +38009,7 @@
         <v>44614.68596064814</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38066,7 +38066,7 @@
         <v>45435.51875</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38123,7 +38123,7 @@
         <v>45841.71503472222</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38180,7 +38180,7 @@
         <v>45621.52203703704</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38237,7 +38237,7 @@
         <v>45691.5603125</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38294,7 +38294,7 @@
         <v>45316</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38351,7 +38351,7 @@
         <v>45761.40570601852</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38408,7 +38408,7 @@
         <v>44839</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38470,7 +38470,7 @@
         <v>45693.67859953704</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38527,7 +38527,7 @@
         <v>45803.70234953704</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38584,7 +38584,7 @@
         <v>45603.60537037037</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38641,7 +38641,7 @@
         <v>45700.60138888889</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38698,7 +38698,7 @@
         <v>44659</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38760,7 +38760,7 @@
         <v>45804.31922453704</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38817,7 +38817,7 @@
         <v>45623.4970949074</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38874,7 +38874,7 @@
         <v>45705</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38931,7 +38931,7 @@
         <v>45845.60700231481</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38988,7 +38988,7 @@
         <v>45804</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39045,7 +39045,7 @@
         <v>45803.48614583333</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39102,7 +39102,7 @@
         <v>44272</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39159,7 +39159,7 @@
         <v>45434.58377314815</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39216,7 +39216,7 @@
         <v>44992.66236111111</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39273,7 +39273,7 @@
         <v>45846.48190972222</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39330,7 +39330,7 @@
         <v>45846.73861111111</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39387,7 +39387,7 @@
         <v>45687</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39444,7 +39444,7 @@
         <v>45687</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39501,7 +39501,7 @@
         <v>45630.3944675926</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39563,7 +39563,7 @@
         <v>45805</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39620,7 +39620,7 @@
         <v>44360.54226851852</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39677,7 +39677,7 @@
         <v>45806.26452546296</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39734,7 +39734,7 @@
         <v>45806.28703703704</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39791,7 +39791,7 @@
         <v>44965</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39848,7 +39848,7 @@
         <v>45701</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39905,7 +39905,7 @@
         <v>45706.66618055556</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39967,7 +39967,7 @@
         <v>44734</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40029,7 +40029,7 @@
         <v>45671.44716435186</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40086,7 +40086,7 @@
         <v>45733</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40143,7 +40143,7 @@
         <v>45805.58325231481</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40200,7 +40200,7 @@
         <v>45805.60481481482</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40257,7 +40257,7 @@
         <v>45643</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40314,7 +40314,7 @@
         <v>45015</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40371,7 +40371,7 @@
         <v>45617.91424768518</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40428,7 +40428,7 @@
         <v>45456.66137731481</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40485,7 +40485,7 @@
         <v>45215.72212962963</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40542,7 +40542,7 @@
         <v>45404.58408564814</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40599,7 +40599,7 @@
         <v>45806.2833912037</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40656,7 +40656,7 @@
         <v>45523.5090625</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40718,7 +40718,7 @@
         <v>45523.58461805555</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40780,7 +40780,7 @@
         <v>45392.63664351852</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40837,7 +40837,7 @@
         <v>45846</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40899,7 +40899,7 @@
         <v>45846</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40961,7 +40961,7 @@
         <v>44064</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41018,7 +41018,7 @@
         <v>45805.58372685185</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41075,7 +41075,7 @@
         <v>44704.65815972222</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41132,7 +41132,7 @@
         <v>45198.59607638889</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41189,7 +41189,7 @@
         <v>45706.67424768519</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41251,7 +41251,7 @@
         <v>45630.39777777778</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41313,7 +41313,7 @@
         <v>45630.4022337963</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41375,7 +41375,7 @@
         <v>45198.60034722222</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41432,7 +41432,7 @@
         <v>45764.42006944444</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41489,7 +41489,7 @@
         <v>45764.42517361111</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41546,7 +41546,7 @@
         <v>44655.48328703704</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41603,7 +41603,7 @@
         <v>45211</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41660,7 +41660,7 @@
         <v>45679.36950231482</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41717,7 +41717,7 @@
         <v>44321</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41779,7 +41779,7 @@
         <v>45644.62803240741</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41836,7 +41836,7 @@
         <v>45751</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41898,7 +41898,7 @@
         <v>44734</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41960,7 +41960,7 @@
         <v>44734</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42022,7 +42022,7 @@
         <v>45194</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42079,7 +42079,7 @@
         <v>45194</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42136,7 +42136,7 @@
         <v>45210.34773148148</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42193,7 +42193,7 @@
         <v>45681.57949074074</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42250,7 +42250,7 @@
         <v>45810</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42307,7 +42307,7 @@
         <v>44750</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42364,7 +42364,7 @@
         <v>45708.52121527777</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42421,7 +42421,7 @@
         <v>45597.43615740741</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42478,7 +42478,7 @@
         <v>45642.60125</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42535,7 +42535,7 @@
         <v>45617.45760416667</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42592,7 +42592,7 @@
         <v>45642.8053125</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42654,7 +42654,7 @@
         <v>45736</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42711,7 +42711,7 @@
         <v>44614</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42768,7 +42768,7 @@
         <v>45756</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42825,7 +42825,7 @@
         <v>45169</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42882,7 +42882,7 @@
         <v>45197.38018518518</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42939,7 +42939,7 @@
         <v>45769.43446759259</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42996,7 +42996,7 @@
         <v>45693</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43053,7 +43053,7 @@
         <v>44729</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43110,7 +43110,7 @@
         <v>44423.87825231482</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43167,7 +43167,7 @@
         <v>45469.43982638889</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43224,7 +43224,7 @@
         <v>45811</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43281,7 +43281,7 @@
         <v>45759.5549537037</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43338,7 +43338,7 @@
         <v>45751</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43400,7 +43400,7 @@
         <v>45314</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43457,7 +43457,7 @@
         <v>45706.66388888889</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43519,7 +43519,7 @@
         <v>45706.67943287037</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43581,7 +43581,7 @@
         <v>45303.63494212963</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43643,7 +43643,7 @@
         <v>45245.46393518519</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43700,7 +43700,7 @@
         <v>45189</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43757,7 +43757,7 @@
         <v>45294</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43819,7 +43819,7 @@
         <v>44904.59393518518</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43881,7 +43881,7 @@
         <v>44897</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43938,7 +43938,7 @@
         <v>44904.61212962963</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44000,7 +44000,7 @@
         <v>45246.50074074074</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44062,7 +44062,7 @@
         <v>45149</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44119,7 +44119,7 @@
         <v>45268</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44176,7 +44176,7 @@
         <v>45201</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44233,7 +44233,7 @@
         <v>45761.49107638889</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44290,7 +44290,7 @@
         <v>45679.98971064815</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44347,7 +44347,7 @@
         <v>45679.99299768519</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44404,7 +44404,7 @@
         <v>45272</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44461,7 +44461,7 @@
         <v>45643.89232638889</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44518,7 +44518,7 @@
         <v>45561.87885416667</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44575,7 +44575,7 @@
         <v>45226.3731712963</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44632,7 +44632,7 @@
         <v>45726.42344907407</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44694,7 +44694,7 @@
         <v>45769.60498842593</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44751,7 +44751,7 @@
         <v>44719.43577546296</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44808,7 +44808,7 @@
         <v>45860.54674768518</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44865,7 +44865,7 @@
         <v>45035</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44922,7 +44922,7 @@
         <v>45861.46241898148</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44979,7 +44979,7 @@
         <v>45861.68065972222</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45036,7 +45036,7 @@
         <v>45240</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45093,7 +45093,7 @@
         <v>44076</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45150,7 +45150,7 @@
         <v>44090</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45207,7 +45207,7 @@
         <v>45764.53740740741</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45264,7 +45264,7 @@
         <v>45188.3012037037</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45321,7 +45321,7 @@
         <v>45819.53688657407</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45378,7 +45378,7 @@
         <v>45819.53980324074</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45435,7 +45435,7 @@
         <v>45819.5429050926</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45492,7 +45492,7 @@
         <v>44103</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45549,7 +45549,7 @@
         <v>45862.63645833333</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45606,7 +45606,7 @@
         <v>44803.44065972222</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45663,7 +45663,7 @@
         <v>44882</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45720,7 +45720,7 @@
         <v>45621</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45777,7 +45777,7 @@
         <v>45182</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45834,7 +45834,7 @@
         <v>45271</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45891,7 +45891,7 @@
         <v>44137</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45948,7 +45948,7 @@
         <v>44063.68225694444</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46005,7 +46005,7 @@
         <v>45708.50255787037</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46062,7 +46062,7 @@
         <v>45715.65605324074</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46119,7 +46119,7 @@
         <v>45867.66349537037</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46176,7 +46176,7 @@
         <v>44077</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46233,7 +46233,7 @@
         <v>44627.41212962963</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46290,7 +46290,7 @@
         <v>44054</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46347,7 +46347,7 @@
         <v>44985.35407407407</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46404,7 +46404,7 @@
         <v>45852</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46461,7 +46461,7 @@
         <v>45826</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46518,7 +46518,7 @@
         <v>45870.62511574074</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46580,7 +46580,7 @@
         <v>45870.62930555556</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46642,7 +46642,7 @@
         <v>45681.57619212963</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46699,7 +46699,7 @@
         <v>45682.47550925926</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46756,7 +46756,7 @@
         <v>44889</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46813,7 +46813,7 @@
         <v>45198.41381944445</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46870,7 +46870,7 @@
         <v>45198.41887731481</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46927,7 +46927,7 @@
         <v>45735.82282407407</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46984,7 +46984,7 @@
         <v>45201.45827546297</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47041,7 +47041,7 @@
         <v>45534.36645833333</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47098,7 +47098,7 @@
         <v>45831.51019675926</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47155,7 +47155,7 @@
         <v>45831.50266203703</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47212,7 +47212,7 @@
         <v>45253.73424768518</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47269,7 +47269,7 @@
         <v>45300</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47326,7 +47326,7 @@
         <v>45215.71418981482</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47383,7 +47383,7 @@
         <v>45392.58569444445</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47440,7 +47440,7 @@
         <v>44540.57753472222</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47497,7 +47497,7 @@
         <v>45846</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47559,7 +47559,7 @@
         <v>45674.47359953704</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47616,7 +47616,7 @@
         <v>44867</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47673,7 +47673,7 @@
         <v>45477.38554398148</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47730,7 +47730,7 @@
         <v>45477.38663194444</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47787,7 +47787,7 @@
         <v>44904</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47844,7 +47844,7 @@
         <v>45875.57328703703</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47906,7 +47906,7 @@
         <v>45875.60922453704</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47963,7 +47963,7 @@
         <v>45777.50238425926</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48020,7 +48020,7 @@
         <v>45534.43841435185</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48077,7 +48077,7 @@
         <v>45876.6799537037</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48134,7 +48134,7 @@
         <v>45833.65434027778</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48191,7 +48191,7 @@
         <v>45833.63770833334</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48248,7 +48248,7 @@
         <v>44308.520625</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48305,7 +48305,7 @@
         <v>45684</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48362,7 +48362,7 @@
         <v>45834.48820601852</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48419,7 +48419,7 @@
         <v>44130</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48476,7 +48476,7 @@
         <v>44113</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48533,7 +48533,7 @@
         <v>45302</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48590,7 +48590,7 @@
         <v>44175</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48647,7 +48647,7 @@
         <v>44893</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48704,7 +48704,7 @@
         <v>44082</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48761,7 +48761,7 @@
         <v>45547.43438657407</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48823,7 +48823,7 @@
         <v>45406.89568287037</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48880,7 +48880,7 @@
         <v>45406.89640046296</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48937,7 +48937,7 @@
         <v>44853</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48994,7 +48994,7 @@
         <v>44484</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49051,7 +49051,7 @@
         <v>44949</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49108,7 +49108,7 @@
         <v>44648</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49165,7 +49165,7 @@
         <v>44861.62300925926</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49222,7 +49222,7 @@
         <v>44938.53719907408</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49284,7 +49284,7 @@
         <v>44084.61673611111</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49341,7 +49341,7 @@
         <v>44056</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49398,7 +49398,7 @@
         <v>45375</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49455,7 +49455,7 @@
         <v>45180</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49512,7 +49512,7 @@
         <v>44943.44811342593</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49569,7 +49569,7 @@
         <v>44614.56209490741</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49626,7 +49626,7 @@
         <v>44074</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49688,7 +49688,7 @@
         <v>44711</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49745,7 +49745,7 @@
         <v>44622</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49802,7 +49802,7 @@
         <v>45058</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49859,7 +49859,7 @@
         <v>44173</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49916,7 +49916,7 @@
         <v>44662</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49973,7 +49973,7 @@
         <v>45184</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50030,7 +50030,7 @@
         <v>45751.58130787037</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50087,7 +50087,7 @@
         <v>45706.69384259259</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50149,7 +50149,7 @@
         <v>45271</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50206,7 +50206,7 @@
         <v>44861.6108912037</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50263,7 +50263,7 @@
         <v>44861</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50320,7 +50320,7 @@
         <v>44211</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50377,7 +50377,7 @@
         <v>45461.65380787037</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50434,7 +50434,7 @@
         <v>45541.36828703704</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50491,7 +50491,7 @@
         <v>45043.43777777778</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50548,7 +50548,7 @@
         <v>44897.3564699074</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50610,7 +50610,7 @@
         <v>45455.40401620371</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50672,7 +50672,7 @@
         <v>44507.43497685185</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50729,7 +50729,7 @@
         <v>44943.44532407408</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50786,7 +50786,7 @@
         <v>44943.48144675926</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50843,7 +50843,7 @@
         <v>45580.46572916667</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50900,7 +50900,7 @@
         <v>44963</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50957,7 +50957,7 @@
         <v>45770.51686342592</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51014,7 +51014,7 @@
         <v>45477.48915509259</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51071,7 +51071,7 @@
         <v>45408.67427083333</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51133,7 +51133,7 @@
         <v>45547.83519675926</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51195,7 +51195,7 @@
         <v>44158</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51252,7 +51252,7 @@
         <v>45034</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51309,7 +51309,7 @@
         <v>44677</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51366,7 +51366,7 @@
         <v>44231</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51423,7 +51423,7 @@
         <v>45758</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51485,7 +51485,7 @@
         <v>44295.31922453704</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51542,7 +51542,7 @@
         <v>45470.6672337963</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51599,7 +51599,7 @@
         <v>44992.67101851852</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51676,7 +51676,7 @@
         <v>44658</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51733,7 +51733,7 @@
         <v>45048</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51790,7 +51790,7 @@
         <v>44959.36028935185</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -51852,7 +51852,7 @@
         <v>45051.37461805555</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -51909,7 +51909,7 @@
         <v>45764.4140162037</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -51966,7 +51966,7 @@
         <v>44846.68375</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52023,7 +52023,7 @@
         <v>45130</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52080,7 +52080,7 @@
         <v>45764.31284722222</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52137,7 +52137,7 @@
         <v>45471.4034837963</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52194,7 +52194,7 @@
         <v>44977.26482638889</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45878</v>
+        <v>45879</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>

--- a/Översikt JÖNKÖPING.xlsx
+++ b/Översikt JÖNKÖPING.xlsx
@@ -567,7 +567,7 @@
         <v>45856.56684027778</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -665,7 +665,7 @@
         <v>45856.57200231482</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
         <v>45777</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>45609</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         <v>45348</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         <v>44111</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>45698.48634259259</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>45275</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>44083</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>44992</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>45788.88578703703</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>45846.47335648148</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>45751.53178240741</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>44530</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>44974</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>44512.62668981482</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2052,7 +2052,7 @@
         <v>44602</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>45604.53402777778</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>44991</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>45751.60517361111</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2412,7 +2412,7 @@
         <v>45539</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2498,7 +2498,7 @@
         <v>45373.44148148148</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2584,7 +2584,7 @@
         <v>45790.83706018519</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2670,7 +2670,7 @@
         <v>45358.52763888889</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2756,7 +2756,7 @@
         <v>45679.98452546296</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>45302</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>44278</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>44419</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         <v>44463</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
         <v>44095</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>44083</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         <v>44469</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3447,7 +3447,7 @@
         <v>44347.63069444444</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3532,7 +3532,7 @@
         <v>44467</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>45751</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3711,7 +3711,7 @@
         <v>44404.71972222222</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3796,7 +3796,7 @@
         <v>44840</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3881,7 +3881,7 @@
         <v>45783</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3966,7 +3966,7 @@
         <v>45580.46207175926</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4051,7 +4051,7 @@
         <v>45740.58743055556</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>45841.4303125</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4221,7 +4221,7 @@
         <v>45295.3942824074</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4311,7 +4311,7 @@
         <v>45343</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
         <v>45587</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4481,7 +4481,7 @@
         <v>45758</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4571,7 +4571,7 @@
         <v>45846</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4656,7 +4656,7 @@
         <v>45302</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4741,7 +4741,7 @@
         <v>45856.55965277777</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4830,7 +4830,7 @@
         <v>45819.60131944445</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4915,7 +4915,7 @@
         <v>45205</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5000,7 +5000,7 @@
         <v>45538.45523148148</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5085,7 +5085,7 @@
         <v>45846</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5179,7 +5179,7 @@
         <v>44879</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5268,7 +5268,7 @@
         <v>45876.69954861111</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5353,7 +5353,7 @@
         <v>45616</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5442,7 +5442,7 @@
         <v>45569.41550925926</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5527,7 +5527,7 @@
         <v>44943</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5612,7 +5612,7 @@
         <v>44260</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5669,7 +5669,7 @@
         <v>44188</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5726,7 +5726,7 @@
         <v>44137</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5783,7 +5783,7 @@
         <v>44147</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>44306</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5897,7 +5897,7 @@
         <v>44308</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5959,7 +5959,7 @@
         <v>44066</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6016,7 +6016,7 @@
         <v>44144</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6073,7 +6073,7 @@
         <v>44328.35063657408</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6130,7 +6130,7 @@
         <v>44239.33525462963</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         <v>44496</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6244,7 +6244,7 @@
         <v>44404.84280092592</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6301,7 +6301,7 @@
         <v>44404.84659722223</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6358,7 +6358,7 @@
         <v>44278.3859375</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         <v>44575.80925925926</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>44662</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>44487</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6586,7 +6586,7 @@
         <v>44749.55936342593</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         <v>44749.55703703704</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6700,7 +6700,7 @@
         <v>44273.62572916667</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6757,7 +6757,7 @@
         <v>44454.35472222222</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6814,7 +6814,7 @@
         <v>44308</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6876,7 +6876,7 @@
         <v>44225</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6933,7 +6933,7 @@
         <v>44308</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6995,7 +6995,7 @@
         <v>44349</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7052,7 +7052,7 @@
         <v>44792.53711805555</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7109,7 +7109,7 @@
         <v>44411</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7166,7 +7166,7 @@
         <v>44194</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         <v>44225</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7280,7 +7280,7 @@
         <v>44809</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7337,7 +7337,7 @@
         <v>44442</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7394,7 +7394,7 @@
         <v>44487.49392361111</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7451,7 +7451,7 @@
         <v>44487</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7508,7 +7508,7 @@
         <v>44749.32716435185</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7565,7 +7565,7 @@
         <v>44420.68987268519</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7622,7 +7622,7 @@
         <v>44404.84138888889</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7679,7 +7679,7 @@
         <v>44266</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7736,7 +7736,7 @@
         <v>44881.81052083334</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7793,7 +7793,7 @@
         <v>44665.60081018518</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7850,7 +7850,7 @@
         <v>44869.49265046296</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>44734</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7974,7 +7974,7 @@
         <v>44792</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
         <v>44054</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8093,7 +8093,7 @@
         <v>44365</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8150,7 +8150,7 @@
         <v>44259</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         <v>44538</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8264,7 +8264,7 @@
         <v>44263</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8326,7 +8326,7 @@
         <v>44113</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8383,7 +8383,7 @@
         <v>44487</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8440,7 +8440,7 @@
         <v>44487</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8497,7 +8497,7 @@
         <v>44272</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8554,7 +8554,7 @@
         <v>44875.59231481481</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         <v>44852.74376157407</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8673,7 +8673,7 @@
         <v>44200</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8730,7 +8730,7 @@
         <v>44292</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8787,7 +8787,7 @@
         <v>44498.56373842592</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8844,7 +8844,7 @@
         <v>44111</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8901,7 +8901,7 @@
         <v>44881.79847222222</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8958,7 +8958,7 @@
         <v>44286.34827546297</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9015,7 +9015,7 @@
         <v>44273</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9072,7 +9072,7 @@
         <v>44673</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9129,7 +9129,7 @@
         <v>44298.46462962963</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         <v>44298.46582175926</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9253,7 +9253,7 @@
         <v>44278.38752314815</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9310,7 +9310,7 @@
         <v>44279.37552083333</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9367,7 +9367,7 @@
         <v>44347.61920138889</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>44754.47359953704</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9486,7 +9486,7 @@
         <v>44855.3080787037</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9543,7 +9543,7 @@
         <v>44476</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9600,7 +9600,7 @@
         <v>44373.75251157407</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9657,7 +9657,7 @@
         <v>44347.6287962963</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9714,7 +9714,7 @@
         <v>44511</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9771,7 +9771,7 @@
         <v>44466.4425</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9828,7 +9828,7 @@
         <v>44377</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9885,7 +9885,7 @@
         <v>44440.71997685185</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9942,7 +9942,7 @@
         <v>44840</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9999,7 +9999,7 @@
         <v>44104</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10056,7 +10056,7 @@
         <v>44280</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10113,7 +10113,7 @@
         <v>44613</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10170,7 +10170,7 @@
         <v>44456.46952546296</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10227,7 +10227,7 @@
         <v>44537</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10284,7 +10284,7 @@
         <v>44360</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10341,7 +10341,7 @@
         <v>44356</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10398,7 +10398,7 @@
         <v>44476</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10455,7 +10455,7 @@
         <v>44575</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10512,7 +10512,7 @@
         <v>44298.44060185185</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10574,7 +10574,7 @@
         <v>44711</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10631,7 +10631,7 @@
         <v>44711</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10688,7 +10688,7 @@
         <v>44428.596875</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10750,7 +10750,7 @@
         <v>44659.57226851852</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10812,7 +10812,7 @@
         <v>44659</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10874,7 +10874,7 @@
         <v>44819</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10931,7 +10931,7 @@
         <v>44819.28449074074</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10988,7 +10988,7 @@
         <v>44292</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11045,7 +11045,7 @@
         <v>44846.66688657407</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11102,7 +11102,7 @@
         <v>44605.44909722222</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11159,7 +11159,7 @@
         <v>44151</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11216,7 +11216,7 @@
         <v>44523.65311342593</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11273,7 +11273,7 @@
         <v>44454.4800925926</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11330,7 +11330,7 @@
         <v>44578</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11387,7 +11387,7 @@
         <v>44344</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11444,7 +11444,7 @@
         <v>44474.25150462963</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11501,7 +11501,7 @@
         <v>44596</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11558,7 +11558,7 @@
         <v>44498.57181712963</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11615,7 +11615,7 @@
         <v>44628</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11672,7 +11672,7 @@
         <v>44711</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11729,7 +11729,7 @@
         <v>44711</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11786,7 +11786,7 @@
         <v>44082.79793981482</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11843,7 +11843,7 @@
         <v>44082</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11900,7 +11900,7 @@
         <v>44841.31997685185</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11957,7 +11957,7 @@
         <v>44579.41064814815</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12014,7 +12014,7 @@
         <v>44532.30398148148</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12071,7 +12071,7 @@
         <v>44467.68283564815</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12128,7 +12128,7 @@
         <v>44557.71989583333</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12185,7 +12185,7 @@
         <v>44792.53936342592</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12242,7 +12242,7 @@
         <v>44616.39256944445</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12299,7 +12299,7 @@
         <v>44593</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12356,7 +12356,7 @@
         <v>44373</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12413,7 +12413,7 @@
         <v>44056</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12470,7 +12470,7 @@
         <v>44428.34821759259</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12532,7 +12532,7 @@
         <v>44272</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12589,7 +12589,7 @@
         <v>44259</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12646,7 +12646,7 @@
         <v>44239</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12703,7 +12703,7 @@
         <v>44239</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12760,7 +12760,7 @@
         <v>44088</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12817,7 +12817,7 @@
         <v>44464.40523148148</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12874,7 +12874,7 @@
         <v>44294</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12931,7 +12931,7 @@
         <v>44412</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12988,7 +12988,7 @@
         <v>44830.90146990741</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13045,7 +13045,7 @@
         <v>44787.80010416666</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13102,7 +13102,7 @@
         <v>44575</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13159,7 +13159,7 @@
         <v>44428.58511574074</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13221,7 +13221,7 @@
         <v>44729</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13278,7 +13278,7 @@
         <v>44308</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13340,7 +13340,7 @@
         <v>44272</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13397,7 +13397,7 @@
         <v>44161.31023148148</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13454,7 +13454,7 @@
         <v>44825.40940972222</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13516,7 +13516,7 @@
         <v>44279.61517361111</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13573,7 +13573,7 @@
         <v>44614</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13635,7 +13635,7 @@
         <v>44805</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13697,7 +13697,7 @@
         <v>44811</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13754,7 +13754,7 @@
         <v>44585.30171296297</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13811,7 +13811,7 @@
         <v>44428</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13873,7 +13873,7 @@
         <v>44536</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13935,7 +13935,7 @@
         <v>44075</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13992,7 +13992,7 @@
         <v>44464.42415509259</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14049,7 +14049,7 @@
         <v>44488</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14106,7 +14106,7 @@
         <v>44579</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14163,7 +14163,7 @@
         <v>44074</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14220,7 +14220,7 @@
         <v>44412.7071875</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14277,7 +14277,7 @@
         <v>44998</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14334,7 +14334,7 @@
         <v>44361</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14391,7 +14391,7 @@
         <v>44252</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14448,7 +14448,7 @@
         <v>45673.71842592592</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14505,7 +14505,7 @@
         <v>45621.52488425926</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14562,7 +14562,7 @@
         <v>45621.5278125</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14619,7 +14619,7 @@
         <v>45758</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14681,7 +14681,7 @@
         <v>45008</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14738,7 +14738,7 @@
         <v>45338.69246527777</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14800,7 +14800,7 @@
         <v>45747.30204861111</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14857,7 +14857,7 @@
         <v>45152</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14914,7 +14914,7 @@
         <v>45401</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14976,7 +14976,7 @@
         <v>45373.60802083334</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15033,7 +15033,7 @@
         <v>45341</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15090,7 +15090,7 @@
         <v>45272.42149305555</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15147,7 +15147,7 @@
         <v>44326</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15204,7 +15204,7 @@
         <v>44575.8194212963</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15261,7 +15261,7 @@
         <v>45260.85619212963</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15318,7 +15318,7 @@
         <v>45772.45813657407</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15375,7 +15375,7 @@
         <v>45775.4219212963</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15432,7 +15432,7 @@
         <v>45127</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15489,7 +15489,7 @@
         <v>45197.61039351852</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15551,7 +15551,7 @@
         <v>44886.3340625</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15608,7 +15608,7 @@
         <v>44967.6228125</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15665,7 +15665,7 @@
         <v>45697.26537037037</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15722,7 +15722,7 @@
         <v>45043.67869212963</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15779,7 +15779,7 @@
         <v>45751.5153125</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15841,7 +15841,7 @@
         <v>45605.84435185185</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15898,7 +15898,7 @@
         <v>45152</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15955,7 +15955,7 @@
         <v>45092</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16012,7 +16012,7 @@
         <v>44273</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16069,7 +16069,7 @@
         <v>44741.69432870371</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16126,7 +16126,7 @@
         <v>45756</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16183,7 +16183,7 @@
         <v>45757.29700231482</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16240,7 +16240,7 @@
         <v>45615.90662037037</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16297,7 +16297,7 @@
         <v>45750.50650462963</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>44631</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16411,7 +16411,7 @@
         <v>44082</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16468,7 +16468,7 @@
         <v>45567</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16525,7 +16525,7 @@
         <v>45628</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16582,7 +16582,7 @@
         <v>45630.6993287037</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16639,7 +16639,7 @@
         <v>45240</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16696,7 +16696,7 @@
         <v>45642.92393518519</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16753,7 +16753,7 @@
         <v>45531</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16810,7 +16810,7 @@
         <v>45735.81920138889</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16867,7 +16867,7 @@
         <v>44229</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16924,7 +16924,7 @@
         <v>45112</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16981,7 +16981,7 @@
         <v>44735</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17038,7 +17038,7 @@
         <v>45775.4233912037</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17095,7 +17095,7 @@
         <v>45749.67842592593</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17152,7 +17152,7 @@
         <v>44325.76335648148</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17209,7 +17209,7 @@
         <v>45406</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17266,7 +17266,7 @@
         <v>45324.64579861111</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17328,7 +17328,7 @@
         <v>45324.64745370371</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17390,7 +17390,7 @@
         <v>45012</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17447,7 +17447,7 @@
         <v>45300</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17504,7 +17504,7 @@
         <v>45092.39466435185</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17561,7 +17561,7 @@
         <v>45751.62381944444</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17623,7 +17623,7 @@
         <v>45588</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17680,7 +17680,7 @@
         <v>45588</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17737,7 +17737,7 @@
         <v>45587</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17794,7 +17794,7 @@
         <v>44468</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17851,7 +17851,7 @@
         <v>44148</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17908,7 +17908,7 @@
         <v>44804</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17965,7 +17965,7 @@
         <v>44985</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18022,7 +18022,7 @@
         <v>45706.69090277778</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18084,7 +18084,7 @@
         <v>45099</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18141,7 +18141,7 @@
         <v>45363.45982638889</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18198,7 +18198,7 @@
         <v>45764.53915509259</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18255,7 +18255,7 @@
         <v>45757</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18312,7 +18312,7 @@
         <v>44449</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18369,7 +18369,7 @@
         <v>45177.5462962963</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18426,7 +18426,7 @@
         <v>45223.65527777778</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18483,7 +18483,7 @@
         <v>45181</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18540,7 +18540,7 @@
         <v>44904</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18602,7 +18602,7 @@
         <v>45769.60440972223</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18659,7 +18659,7 @@
         <v>44882</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18716,7 +18716,7 @@
         <v>45321</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18773,7 +18773,7 @@
         <v>45107</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18830,7 +18830,7 @@
         <v>45299</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18887,7 +18887,7 @@
         <v>44433</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18944,7 +18944,7 @@
         <v>45037.67510416666</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19001,7 +19001,7 @@
         <v>45270.42966435185</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19058,7 +19058,7 @@
         <v>44840</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19115,7 +19115,7 @@
         <v>45474.70864583334</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19172,7 +19172,7 @@
         <v>45079</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19229,7 +19229,7 @@
         <v>45252.58925925926</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19286,7 +19286,7 @@
         <v>44151</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19343,7 +19343,7 @@
         <v>44056</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19400,7 +19400,7 @@
         <v>44487</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19457,7 +19457,7 @@
         <v>44414</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19514,7 +19514,7 @@
         <v>45356.65395833334</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19576,7 +19576,7 @@
         <v>45764.30016203703</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19633,7 +19633,7 @@
         <v>44882</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19690,7 +19690,7 @@
         <v>45558.51949074074</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19752,7 +19752,7 @@
         <v>45764.30391203704</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19809,7 +19809,7 @@
         <v>45107</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19866,7 +19866,7 @@
         <v>44588.50104166667</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19923,7 +19923,7 @@
         <v>44893</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19985,7 +19985,7 @@
         <v>45355.56604166667</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20042,7 +20042,7 @@
         <v>45324.64302083333</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20104,7 +20104,7 @@
         <v>45747.44508101852</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20161,7 +20161,7 @@
         <v>45747.45177083334</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20218,7 +20218,7 @@
         <v>44979</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20275,7 +20275,7 @@
         <v>44368.64017361111</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20332,7 +20332,7 @@
         <v>45740.59871527777</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20389,7 +20389,7 @@
         <v>45243</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20451,7 +20451,7 @@
         <v>45763.38354166667</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20528,7 +20528,7 @@
         <v>45114.55280092593</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20585,7 +20585,7 @@
         <v>45201</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20647,7 +20647,7 @@
         <v>45545.53883101852</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20704,7 +20704,7 @@
         <v>45169</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20761,7 +20761,7 @@
         <v>44837</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20818,7 +20818,7 @@
         <v>45468.44574074074</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20875,7 +20875,7 @@
         <v>45775.32407407407</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20932,7 +20932,7 @@
         <v>45477.48771990741</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20989,7 +20989,7 @@
         <v>45597.53744212963</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21046,7 +21046,7 @@
         <v>45183</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21103,7 +21103,7 @@
         <v>45056.6438425926</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21160,7 +21160,7 @@
         <v>45436.68626157408</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21217,7 +21217,7 @@
         <v>45314</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21274,7 +21274,7 @@
         <v>45757.30554398148</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21331,7 +21331,7 @@
         <v>45755.70262731481</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21388,7 +21388,7 @@
         <v>45455.42533564815</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21450,7 +21450,7 @@
         <v>45455.42981481482</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21512,7 +21512,7 @@
         <v>45447.55340277778</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21569,7 +21569,7 @@
         <v>45201.59743055556</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21626,7 +21626,7 @@
         <v>45644.62243055556</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21683,7 +21683,7 @@
         <v>44963.66563657407</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21740,7 +21740,7 @@
         <v>45761.41857638889</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21797,7 +21797,7 @@
         <v>44904.49826388889</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21854,7 +21854,7 @@
         <v>44904</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21911,7 +21911,7 @@
         <v>44449</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21968,7 +21968,7 @@
         <v>44923.55936342593</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22025,7 +22025,7 @@
         <v>45359.54100694445</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22082,7 +22082,7 @@
         <v>44483.58045138889</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22139,7 +22139,7 @@
         <v>45414</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22196,7 +22196,7 @@
         <v>45477.38181712963</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22253,7 +22253,7 @@
         <v>45377.42784722222</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22310,7 +22310,7 @@
         <v>45533.46368055556</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22367,7 +22367,7 @@
         <v>45351.65180555556</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22429,7 +22429,7 @@
         <v>45617.48947916667</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22486,7 +22486,7 @@
         <v>45539.34539351852</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22543,7 +22543,7 @@
         <v>45462.37888888889</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22600,7 +22600,7 @@
         <v>45219</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22657,7 +22657,7 @@
         <v>45477.33712962963</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22714,7 +22714,7 @@
         <v>45775.32163194445</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22771,7 +22771,7 @@
         <v>45502.32021990741</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22828,7 +22828,7 @@
         <v>45502.33179398148</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22885,7 +22885,7 @@
         <v>45406.89703703704</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22942,7 +22942,7 @@
         <v>44853</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -23004,7 +23004,7 @@
         <v>45751.52445601852</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23066,7 +23066,7 @@
         <v>45751.59875</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23128,7 +23128,7 @@
         <v>45751.61236111111</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23190,7 +23190,7 @@
         <v>45751.61556712963</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23252,7 +23252,7 @@
         <v>45547.43793981482</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23314,7 +23314,7 @@
         <v>45748</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23376,7 +23376,7 @@
         <v>45092.42630787037</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23433,7 +23433,7 @@
         <v>45446.56622685185</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23490,7 +23490,7 @@
         <v>45049</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23547,7 +23547,7 @@
         <v>45051</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23604,7 +23604,7 @@
         <v>44355.60153935185</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23661,7 +23661,7 @@
         <v>45716.7125</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23718,7 +23718,7 @@
         <v>45111</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23775,7 +23775,7 @@
         <v>45112</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23832,7 +23832,7 @@
         <v>44950</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23889,7 +23889,7 @@
         <v>44950</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23946,7 +23946,7 @@
         <v>45349</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -24003,7 +24003,7 @@
         <v>45119.54038194445</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24060,7 +24060,7 @@
         <v>44893</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24122,7 +24122,7 @@
         <v>45145.47684027778</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24179,7 +24179,7 @@
         <v>45492.70833333334</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24236,7 +24236,7 @@
         <v>44488</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24293,7 +24293,7 @@
         <v>45566</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24350,7 +24350,7 @@
         <v>45331</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24407,7 +24407,7 @@
         <v>44966.57471064815</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24469,7 +24469,7 @@
         <v>44936</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24526,7 +24526,7 @@
         <v>44411</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24583,7 +24583,7 @@
         <v>45706.68554398148</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24645,7 +24645,7 @@
         <v>45645.88440972222</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24702,7 +24702,7 @@
         <v>44853</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24759,7 +24759,7 @@
         <v>45734.59972222222</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24816,7 +24816,7 @@
         <v>44083</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24873,7 +24873,7 @@
         <v>45497</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24930,7 +24930,7 @@
         <v>45615.89965277778</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24987,7 +24987,7 @@
         <v>45747.45038194444</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25044,7 +25044,7 @@
         <v>45701.38606481482</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25101,7 +25101,7 @@
         <v>45116.44680555556</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25158,7 +25158,7 @@
         <v>45169.38410879629</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25215,7 +25215,7 @@
         <v>44935.37284722222</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25272,7 +25272,7 @@
         <v>45758</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25334,7 +25334,7 @@
         <v>45758.64109953704</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25391,7 +25391,7 @@
         <v>45587.49814814814</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25448,7 +25448,7 @@
         <v>44957.36059027778</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25505,7 +25505,7 @@
         <v>45118</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25562,7 +25562,7 @@
         <v>44063</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25624,7 +25624,7 @@
         <v>45770</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25681,7 +25681,7 @@
         <v>45338</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25743,7 +25743,7 @@
         <v>44944.40825231482</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25800,7 +25800,7 @@
         <v>45562.38306712963</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25857,7 +25857,7 @@
         <v>45630.39188657407</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25919,7 +25919,7 @@
         <v>45012.47533564815</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25976,7 +25976,7 @@
         <v>44482</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -26033,7 +26033,7 @@
         <v>45704</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26090,7 +26090,7 @@
         <v>45557.35435185185</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26147,7 +26147,7 @@
         <v>45358</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26204,7 +26204,7 @@
         <v>45358.61696759259</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26261,7 +26261,7 @@
         <v>44484.49586805556</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26318,7 +26318,7 @@
         <v>45764.3996412037</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26375,7 +26375,7 @@
         <v>45635.28104166667</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26432,7 +26432,7 @@
         <v>45643.47644675926</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26489,7 +26489,7 @@
         <v>45281.57759259259</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26551,7 +26551,7 @@
         <v>45295.40646990741</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26613,7 +26613,7 @@
         <v>45307.72520833334</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26670,7 +26670,7 @@
         <v>45275</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26727,7 +26727,7 @@
         <v>45455.4374537037</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26789,7 +26789,7 @@
         <v>45099.74195601852</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26846,7 +26846,7 @@
         <v>44628</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26903,7 +26903,7 @@
         <v>44090</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26960,7 +26960,7 @@
         <v>45335.76891203703</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -27022,7 +27022,7 @@
         <v>45541.37402777778</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27079,7 +27079,7 @@
         <v>45618</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27136,7 +27136,7 @@
         <v>45414</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27193,7 +27193,7 @@
         <v>45667.63950231481</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27250,7 +27250,7 @@
         <v>44507.82581018518</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27307,7 +27307,7 @@
         <v>44589.74348379629</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27364,7 +27364,7 @@
         <v>45777.60824074074</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27421,7 +27421,7 @@
         <v>45777.50512731481</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27478,7 +27478,7 @@
         <v>44893.50922453704</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27540,7 +27540,7 @@
         <v>45545.59315972222</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27602,7 +27602,7 @@
         <v>45779.62363425926</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27659,7 +27659,7 @@
         <v>45538</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27716,7 +27716,7 @@
         <v>45646.67994212963</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27773,7 +27773,7 @@
         <v>44648.61840277778</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27830,7 +27830,7 @@
         <v>45560.35501157407</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27887,7 +27887,7 @@
         <v>45586.62837962963</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27944,7 +27944,7 @@
         <v>45519.48550925926</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -28001,7 +28001,7 @@
         <v>45785.65899305556</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28058,7 +28058,7 @@
         <v>44109</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28115,7 +28115,7 @@
         <v>44097</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28172,7 +28172,7 @@
         <v>44550.30402777778</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28229,7 +28229,7 @@
         <v>44118</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28291,7 +28291,7 @@
         <v>44589.73825231481</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28348,7 +28348,7 @@
         <v>44557</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28405,7 +28405,7 @@
         <v>44904</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28462,7 +28462,7 @@
         <v>45124.59594907407</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28519,7 +28519,7 @@
         <v>44056</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28576,7 +28576,7 @@
         <v>45267.62943287037</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28633,7 +28633,7 @@
         <v>44943</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28690,7 +28690,7 @@
         <v>45747.73295138889</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28747,7 +28747,7 @@
         <v>45720.70986111111</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28804,7 +28804,7 @@
         <v>45216.47443287037</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28861,7 +28861,7 @@
         <v>45460.42804398148</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28918,7 +28918,7 @@
         <v>45588</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28975,7 +28975,7 @@
         <v>45009</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29032,7 +29032,7 @@
         <v>45784.84850694444</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29089,7 +29089,7 @@
         <v>44605.45792824074</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29146,7 +29146,7 @@
         <v>45175.44625</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29203,7 +29203,7 @@
         <v>45401.34349537037</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29260,7 +29260,7 @@
         <v>44172</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29317,7 +29317,7 @@
         <v>45750.40476851852</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29374,7 +29374,7 @@
         <v>45586</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29431,7 +29431,7 @@
         <v>45789.54226851852</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29488,7 +29488,7 @@
         <v>45764.42304398148</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29545,7 +29545,7 @@
         <v>45566</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29602,7 +29602,7 @@
         <v>45105.34402777778</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29659,7 +29659,7 @@
         <v>45405</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29716,7 +29716,7 @@
         <v>45405</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29773,7 +29773,7 @@
         <v>45184</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29830,7 +29830,7 @@
         <v>45547.83950231481</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29892,7 +29892,7 @@
         <v>44578.52657407407</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29949,7 +29949,7 @@
         <v>45788.88399305556</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30006,7 +30006,7 @@
         <v>44592.28611111111</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30063,7 +30063,7 @@
         <v>45541</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30120,7 +30120,7 @@
         <v>45545.65415509259</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30182,7 +30182,7 @@
         <v>45412</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30244,7 +30244,7 @@
         <v>45194</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30301,7 +30301,7 @@
         <v>45552.48335648148</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30358,7 +30358,7 @@
         <v>45462.38087962963</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30415,7 +30415,7 @@
         <v>44585</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30472,7 +30472,7 @@
         <v>45788.3231712963</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30529,7 +30529,7 @@
         <v>45763.49402777778</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30586,7 +30586,7 @@
         <v>45177</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30643,7 +30643,7 @@
         <v>45788.32225694445</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30700,7 +30700,7 @@
         <v>45197</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30757,7 +30757,7 @@
         <v>45670.66061342593</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30814,7 +30814,7 @@
         <v>45021</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30871,7 +30871,7 @@
         <v>45646.5796412037</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30928,7 +30928,7 @@
         <v>45519.49606481481</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30985,7 +30985,7 @@
         <v>44950</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31042,7 +31042,7 @@
         <v>45600.47958333333</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31099,7 +31099,7 @@
         <v>45560.35614583334</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31156,7 +31156,7 @@
         <v>45043</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31213,7 +31213,7 @@
         <v>45790.82361111111</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31270,7 +31270,7 @@
         <v>45205</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31327,7 +31327,7 @@
         <v>44938</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31389,7 +31389,7 @@
         <v>45645.57626157408</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31446,7 +31446,7 @@
         <v>44187</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31508,7 +31508,7 @@
         <v>45551.36004629629</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31565,7 +31565,7 @@
         <v>44977.26300925926</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31622,7 +31622,7 @@
         <v>45541.38644675926</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31679,7 +31679,7 @@
         <v>45587</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31736,7 +31736,7 @@
         <v>45790.81799768518</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31793,7 +31793,7 @@
         <v>45791.85732638889</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31850,7 +31850,7 @@
         <v>45184</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31907,7 +31907,7 @@
         <v>45350.56959490741</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31964,7 +31964,7 @@
         <v>44252</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32021,7 +32021,7 @@
         <v>45701.31962962963</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32078,7 +32078,7 @@
         <v>44943.4652199074</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32135,7 +32135,7 @@
         <v>44943.46980324074</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32192,7 +32192,7 @@
         <v>45681.48793981481</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32249,7 +32249,7 @@
         <v>45681.53460648148</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32306,7 +32306,7 @@
         <v>45622.35340277778</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32363,7 +32363,7 @@
         <v>45558.63807870371</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32425,7 +32425,7 @@
         <v>44591</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32482,7 +32482,7 @@
         <v>44608</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32539,7 +32539,7 @@
         <v>45169</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32596,7 +32596,7 @@
         <v>45637.51090277778</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32653,7 +32653,7 @@
         <v>45112.3174074074</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32710,7 +32710,7 @@
         <v>45112</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32767,7 +32767,7 @@
         <v>44930</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32824,7 +32824,7 @@
         <v>45759.74934027778</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32881,7 +32881,7 @@
         <v>45587.47273148148</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32938,7 +32938,7 @@
         <v>45701.37818287037</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32995,7 +32995,7 @@
         <v>44626</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33052,7 +33052,7 @@
         <v>45646.39016203704</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33109,7 +33109,7 @@
         <v>45628</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33171,7 +33171,7 @@
         <v>45628</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33233,7 +33233,7 @@
         <v>45570.58934027778</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33290,7 +33290,7 @@
         <v>44575.80709490741</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33347,7 +33347,7 @@
         <v>44950</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33404,7 +33404,7 @@
         <v>44249</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33461,7 +33461,7 @@
         <v>44225</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33518,7 +33518,7 @@
         <v>45793</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33575,7 +33575,7 @@
         <v>44249.66673611111</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33632,7 +33632,7 @@
         <v>45581.52885416667</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33689,7 +33689,7 @@
         <v>45363.91521990741</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33746,7 +33746,7 @@
         <v>45364.40862268519</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33803,7 +33803,7 @@
         <v>45435</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33865,7 +33865,7 @@
         <v>44966.52741898148</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33927,7 +33927,7 @@
         <v>45030</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33984,7 +33984,7 @@
         <v>45371.60959490741</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34041,7 +34041,7 @@
         <v>45630.70101851852</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34103,7 +34103,7 @@
         <v>45182.36129629629</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34160,7 +34160,7 @@
         <v>44988</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34217,7 +34217,7 @@
         <v>45617.92190972222</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34274,7 +34274,7 @@
         <v>45056</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34331,7 +34331,7 @@
         <v>45600.48127314815</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34388,7 +34388,7 @@
         <v>45600.48347222222</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34445,7 +34445,7 @@
         <v>45736</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34502,7 +34502,7 @@
         <v>45740.59474537037</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34559,7 +34559,7 @@
         <v>44564.8419212963</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34616,7 +34616,7 @@
         <v>45839.71761574074</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34673,7 +34673,7 @@
         <v>45174</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34730,7 +34730,7 @@
         <v>45727.55315972222</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34787,7 +34787,7 @@
         <v>45736.67693287037</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34844,7 +34844,7 @@
         <v>45727.3134375</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34901,7 +34901,7 @@
         <v>45727.36650462963</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34958,7 +34958,7 @@
         <v>45735</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35015,7 +35015,7 @@
         <v>45734.35039351852</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35072,7 +35072,7 @@
         <v>45740.91412037037</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35129,7 +35129,7 @@
         <v>45741.65699074074</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35186,7 +35186,7 @@
         <v>45741.69303240741</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35243,7 +35243,7 @@
         <v>45726.44835648148</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35300,7 +35300,7 @@
         <v>45735.65969907407</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35357,7 +35357,7 @@
         <v>45797.56770833334</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35414,7 +35414,7 @@
         <v>44571</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35471,7 +35471,7 @@
         <v>45764.40184027778</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35528,7 +35528,7 @@
         <v>45755</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35585,7 +35585,7 @@
         <v>45728</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35642,7 +35642,7 @@
         <v>45727.35745370371</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35699,7 +35699,7 @@
         <v>45727.36243055556</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35756,7 +35756,7 @@
         <v>45734.3584837963</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35813,7 +35813,7 @@
         <v>44711</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35870,7 +35870,7 @@
         <v>45730.44528935185</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35932,7 +35932,7 @@
         <v>45201</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35989,7 +35989,7 @@
         <v>45372.34530092592</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36046,7 +36046,7 @@
         <v>45179.9259375</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36103,7 +36103,7 @@
         <v>45736</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36160,7 +36160,7 @@
         <v>44261</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36217,7 +36217,7 @@
         <v>45743.59641203703</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36274,7 +36274,7 @@
         <v>45797.67148148148</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36331,7 +36331,7 @@
         <v>45734.35122685185</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36388,7 +36388,7 @@
         <v>45726.52925925926</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36445,7 +36445,7 @@
         <v>45624.41041666667</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36502,7 +36502,7 @@
         <v>44998.8734837963</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36559,7 +36559,7 @@
         <v>45730.65831018519</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36616,7 +36616,7 @@
         <v>45547.84315972222</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36678,7 +36678,7 @@
         <v>45737.67416666666</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36735,7 +36735,7 @@
         <v>45730.3782175926</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36797,7 +36797,7 @@
         <v>45799.50931712963</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36854,7 +36854,7 @@
         <v>45799.52318287037</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36911,7 +36911,7 @@
         <v>45799.58894675926</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36968,7 +36968,7 @@
         <v>45799.5803125</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37025,7 +37025,7 @@
         <v>45182.71081018518</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37082,7 +37082,7 @@
         <v>44894</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37139,7 +37139,7 @@
         <v>45763.49306712963</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37196,7 +37196,7 @@
         <v>45751.51961805556</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37258,7 +37258,7 @@
         <v>45841.4390625</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37315,7 +37315,7 @@
         <v>45295.4037962963</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37377,7 +37377,7 @@
         <v>45799.50469907407</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37434,7 +37434,7 @@
         <v>45547.42313657407</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37496,7 +37496,7 @@
         <v>45547.53320601852</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37553,7 +37553,7 @@
         <v>45842.49056712963</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37610,7 +37610,7 @@
         <v>45671.44894675926</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37667,7 +37667,7 @@
         <v>45842.49457175926</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37724,7 +37724,7 @@
         <v>45842.5059375</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37781,7 +37781,7 @@
         <v>45440.3712037037</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37838,7 +37838,7 @@
         <v>45617.4922337963</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37895,7 +37895,7 @@
         <v>45799.51578703704</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37952,7 +37952,7 @@
         <v>45113.31806712963</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38009,7 +38009,7 @@
         <v>44614.68596064814</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38066,7 +38066,7 @@
         <v>45435.51875</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38123,7 +38123,7 @@
         <v>45841.71503472222</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38180,7 +38180,7 @@
         <v>45621.52203703704</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38237,7 +38237,7 @@
         <v>45691.5603125</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38294,7 +38294,7 @@
         <v>45316</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38351,7 +38351,7 @@
         <v>45761.40570601852</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38408,7 +38408,7 @@
         <v>44839</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38470,7 +38470,7 @@
         <v>45693.67859953704</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38527,7 +38527,7 @@
         <v>45803.70234953704</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38584,7 +38584,7 @@
         <v>45603.60537037037</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38641,7 +38641,7 @@
         <v>45700.60138888889</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38698,7 +38698,7 @@
         <v>44659</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38760,7 +38760,7 @@
         <v>45804.31922453704</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38817,7 +38817,7 @@
         <v>45623.4970949074</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38874,7 +38874,7 @@
         <v>45705</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38931,7 +38931,7 @@
         <v>45845.60700231481</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38988,7 +38988,7 @@
         <v>45804</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39045,7 +39045,7 @@
         <v>45803.48614583333</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39102,7 +39102,7 @@
         <v>44272</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39159,7 +39159,7 @@
         <v>45434.58377314815</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39216,7 +39216,7 @@
         <v>44992.66236111111</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39273,7 +39273,7 @@
         <v>45846.48190972222</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39330,7 +39330,7 @@
         <v>45846.73861111111</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39387,7 +39387,7 @@
         <v>45687</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39444,7 +39444,7 @@
         <v>45687</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39501,7 +39501,7 @@
         <v>45630.3944675926</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39563,7 +39563,7 @@
         <v>45805</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39620,7 +39620,7 @@
         <v>44360.54226851852</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39677,7 +39677,7 @@
         <v>45806.26452546296</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39734,7 +39734,7 @@
         <v>45806.28703703704</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39791,7 +39791,7 @@
         <v>44965</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39848,7 +39848,7 @@
         <v>45701</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39905,7 +39905,7 @@
         <v>45706.66618055556</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39967,7 +39967,7 @@
         <v>44734</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40029,7 +40029,7 @@
         <v>45671.44716435186</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40086,7 +40086,7 @@
         <v>45733</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40143,7 +40143,7 @@
         <v>45805.58325231481</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40200,7 +40200,7 @@
         <v>45805.60481481482</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40257,7 +40257,7 @@
         <v>45643</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40314,7 +40314,7 @@
         <v>45015</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40371,7 +40371,7 @@
         <v>45617.91424768518</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40428,7 +40428,7 @@
         <v>45456.66137731481</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40485,7 +40485,7 @@
         <v>45215.72212962963</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40542,7 +40542,7 @@
         <v>45404.58408564814</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40599,7 +40599,7 @@
         <v>45806.2833912037</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40656,7 +40656,7 @@
         <v>45523.5090625</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40718,7 +40718,7 @@
         <v>45523.58461805555</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40780,7 +40780,7 @@
         <v>45392.63664351852</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40837,7 +40837,7 @@
         <v>45846</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40899,7 +40899,7 @@
         <v>45846</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40961,7 +40961,7 @@
         <v>44064</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41018,7 +41018,7 @@
         <v>45805.58372685185</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41075,7 +41075,7 @@
         <v>44704.65815972222</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41132,7 +41132,7 @@
         <v>45198.59607638889</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41189,7 +41189,7 @@
         <v>45706.67424768519</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41251,7 +41251,7 @@
         <v>45630.39777777778</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41313,7 +41313,7 @@
         <v>45630.4022337963</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41375,7 +41375,7 @@
         <v>45198.60034722222</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41432,7 +41432,7 @@
         <v>45764.42006944444</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41489,7 +41489,7 @@
         <v>45764.42517361111</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41546,7 +41546,7 @@
         <v>44655.48328703704</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41603,7 +41603,7 @@
         <v>45211</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41660,7 +41660,7 @@
         <v>45679.36950231482</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41717,7 +41717,7 @@
         <v>44321</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41779,7 +41779,7 @@
         <v>45644.62803240741</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41836,7 +41836,7 @@
         <v>45751</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41898,7 +41898,7 @@
         <v>44734</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41960,7 +41960,7 @@
         <v>44734</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42022,7 +42022,7 @@
         <v>45194</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42079,7 +42079,7 @@
         <v>45194</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42136,7 +42136,7 @@
         <v>45210.34773148148</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42193,7 +42193,7 @@
         <v>45681.57949074074</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42250,7 +42250,7 @@
         <v>45810</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42307,7 +42307,7 @@
         <v>44750</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42364,7 +42364,7 @@
         <v>45708.52121527777</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42421,7 +42421,7 @@
         <v>45597.43615740741</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42478,7 +42478,7 @@
         <v>45642.60125</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42535,7 +42535,7 @@
         <v>45617.45760416667</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42592,7 +42592,7 @@
         <v>45642.8053125</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42654,7 +42654,7 @@
         <v>45736</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42711,7 +42711,7 @@
         <v>44614</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42768,7 +42768,7 @@
         <v>45756</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42825,7 +42825,7 @@
         <v>45169</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42882,7 +42882,7 @@
         <v>45197.38018518518</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42939,7 +42939,7 @@
         <v>45769.43446759259</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42996,7 +42996,7 @@
         <v>45693</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43053,7 +43053,7 @@
         <v>44729</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43110,7 +43110,7 @@
         <v>44423.87825231482</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43167,7 +43167,7 @@
         <v>45469.43982638889</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43224,7 +43224,7 @@
         <v>45811</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43281,7 +43281,7 @@
         <v>45759.5549537037</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43338,7 +43338,7 @@
         <v>45751</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43400,7 +43400,7 @@
         <v>45314</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43457,7 +43457,7 @@
         <v>45706.66388888889</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43519,7 +43519,7 @@
         <v>45706.67943287037</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43581,7 +43581,7 @@
         <v>45303.63494212963</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43643,7 +43643,7 @@
         <v>45245.46393518519</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43700,7 +43700,7 @@
         <v>45189</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43757,7 +43757,7 @@
         <v>45294</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43819,7 +43819,7 @@
         <v>44904.59393518518</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43881,7 +43881,7 @@
         <v>44897</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43938,7 +43938,7 @@
         <v>44904.61212962963</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44000,7 +44000,7 @@
         <v>45246.50074074074</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44062,7 +44062,7 @@
         <v>45149</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44119,7 +44119,7 @@
         <v>45268</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44176,7 +44176,7 @@
         <v>45201</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44233,7 +44233,7 @@
         <v>45761.49107638889</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44290,7 +44290,7 @@
         <v>45679.98971064815</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44347,7 +44347,7 @@
         <v>45679.99299768519</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44404,7 +44404,7 @@
         <v>45272</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44461,7 +44461,7 @@
         <v>45643.89232638889</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44518,7 +44518,7 @@
         <v>45561.87885416667</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44575,7 +44575,7 @@
         <v>45226.3731712963</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44632,7 +44632,7 @@
         <v>45726.42344907407</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44694,7 +44694,7 @@
         <v>45769.60498842593</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44751,7 +44751,7 @@
         <v>44719.43577546296</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44808,7 +44808,7 @@
         <v>45860.54674768518</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44865,7 +44865,7 @@
         <v>45035</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44922,7 +44922,7 @@
         <v>45861.46241898148</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44979,7 +44979,7 @@
         <v>45861.68065972222</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45036,7 +45036,7 @@
         <v>45240</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45093,7 +45093,7 @@
         <v>44076</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45150,7 +45150,7 @@
         <v>44090</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45207,7 +45207,7 @@
         <v>45764.53740740741</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45264,7 +45264,7 @@
         <v>45188.3012037037</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45321,7 +45321,7 @@
         <v>45819.53688657407</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45378,7 +45378,7 @@
         <v>45819.53980324074</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45435,7 +45435,7 @@
         <v>45819.5429050926</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45492,7 +45492,7 @@
         <v>44103</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45549,7 +45549,7 @@
         <v>45862.63645833333</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45606,7 +45606,7 @@
         <v>44803.44065972222</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45663,7 +45663,7 @@
         <v>44882</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45720,7 +45720,7 @@
         <v>45621</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45777,7 +45777,7 @@
         <v>45182</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45834,7 +45834,7 @@
         <v>45271</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45891,7 +45891,7 @@
         <v>44137</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45948,7 +45948,7 @@
         <v>44063.68225694444</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46005,7 +46005,7 @@
         <v>45708.50255787037</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46062,7 +46062,7 @@
         <v>45715.65605324074</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46119,7 +46119,7 @@
         <v>45867.66349537037</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46176,7 +46176,7 @@
         <v>44077</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46233,7 +46233,7 @@
         <v>44627.41212962963</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46290,7 +46290,7 @@
         <v>44054</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46347,7 +46347,7 @@
         <v>44985.35407407407</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46404,7 +46404,7 @@
         <v>45852</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46461,7 +46461,7 @@
         <v>45826</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46518,7 +46518,7 @@
         <v>45870.62511574074</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46580,7 +46580,7 @@
         <v>45870.62930555556</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46642,7 +46642,7 @@
         <v>45681.57619212963</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46699,7 +46699,7 @@
         <v>45682.47550925926</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46756,7 +46756,7 @@
         <v>44889</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46813,7 +46813,7 @@
         <v>45198.41381944445</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46870,7 +46870,7 @@
         <v>45198.41887731481</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46927,7 +46927,7 @@
         <v>45735.82282407407</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46984,7 +46984,7 @@
         <v>45201.45827546297</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47041,7 +47041,7 @@
         <v>45534.36645833333</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47098,7 +47098,7 @@
         <v>45831.51019675926</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47155,7 +47155,7 @@
         <v>45831.50266203703</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47212,7 +47212,7 @@
         <v>45253.73424768518</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47269,7 +47269,7 @@
         <v>45300</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47326,7 +47326,7 @@
         <v>45215.71418981482</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47383,7 +47383,7 @@
         <v>45392.58569444445</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47440,7 +47440,7 @@
         <v>44540.57753472222</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47497,7 +47497,7 @@
         <v>45846</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47559,7 +47559,7 @@
         <v>45674.47359953704</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47616,7 +47616,7 @@
         <v>44867</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47673,7 +47673,7 @@
         <v>45477.38554398148</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47730,7 +47730,7 @@
         <v>45477.38663194444</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47787,7 +47787,7 @@
         <v>44904</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47844,7 +47844,7 @@
         <v>45875.57328703703</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47906,7 +47906,7 @@
         <v>45875.60922453704</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47963,7 +47963,7 @@
         <v>45777.50238425926</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48020,7 +48020,7 @@
         <v>45534.43841435185</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48077,7 +48077,7 @@
         <v>45876.6799537037</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48134,7 +48134,7 @@
         <v>45833.65434027778</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48191,7 +48191,7 @@
         <v>45833.63770833334</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48248,7 +48248,7 @@
         <v>44308.520625</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48305,7 +48305,7 @@
         <v>45684</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48362,7 +48362,7 @@
         <v>45834.48820601852</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48419,7 +48419,7 @@
         <v>44130</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48476,7 +48476,7 @@
         <v>44113</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48533,7 +48533,7 @@
         <v>45302</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48590,7 +48590,7 @@
         <v>44175</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48647,7 +48647,7 @@
         <v>44893</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48704,7 +48704,7 @@
         <v>44082</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48761,7 +48761,7 @@
         <v>45547.43438657407</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48823,7 +48823,7 @@
         <v>45406.89568287037</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48880,7 +48880,7 @@
         <v>45406.89640046296</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48937,7 +48937,7 @@
         <v>44853</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48994,7 +48994,7 @@
         <v>44484</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49051,7 +49051,7 @@
         <v>44949</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49108,7 +49108,7 @@
         <v>44648</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49165,7 +49165,7 @@
         <v>44861.62300925926</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49222,7 +49222,7 @@
         <v>44938.53719907408</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49284,7 +49284,7 @@
         <v>44084.61673611111</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49341,7 +49341,7 @@
         <v>44056</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49398,7 +49398,7 @@
         <v>45375</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49455,7 +49455,7 @@
         <v>45180</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49512,7 +49512,7 @@
         <v>44943.44811342593</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49569,7 +49569,7 @@
         <v>44614.56209490741</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49626,7 +49626,7 @@
         <v>44074</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49688,7 +49688,7 @@
         <v>44711</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49745,7 +49745,7 @@
         <v>44622</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49802,7 +49802,7 @@
         <v>45058</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49859,7 +49859,7 @@
         <v>44173</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49916,7 +49916,7 @@
         <v>44662</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49973,7 +49973,7 @@
         <v>45184</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50030,7 +50030,7 @@
         <v>45751.58130787037</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50087,7 +50087,7 @@
         <v>45706.69384259259</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50149,7 +50149,7 @@
         <v>45271</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50206,7 +50206,7 @@
         <v>44861.6108912037</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50263,7 +50263,7 @@
         <v>44861</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50320,7 +50320,7 @@
         <v>44211</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50377,7 +50377,7 @@
         <v>45461.65380787037</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50434,7 +50434,7 @@
         <v>45541.36828703704</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50491,7 +50491,7 @@
         <v>45043.43777777778</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50548,7 +50548,7 @@
         <v>44897.3564699074</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50610,7 +50610,7 @@
         <v>45455.40401620371</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50672,7 +50672,7 @@
         <v>44507.43497685185</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50729,7 +50729,7 @@
         <v>44943.44532407408</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50786,7 +50786,7 @@
         <v>44943.48144675926</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50843,7 +50843,7 @@
         <v>45580.46572916667</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50900,7 +50900,7 @@
         <v>44963</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50957,7 +50957,7 @@
         <v>45770.51686342592</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51014,7 +51014,7 @@
         <v>45477.48915509259</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51071,7 +51071,7 @@
         <v>45408.67427083333</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51133,7 +51133,7 @@
         <v>45547.83519675926</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51195,7 +51195,7 @@
         <v>44158</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51252,7 +51252,7 @@
         <v>45034</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51309,7 +51309,7 @@
         <v>44677</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51366,7 +51366,7 @@
         <v>44231</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51423,7 +51423,7 @@
         <v>45758</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51485,7 +51485,7 @@
         <v>44295.31922453704</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51542,7 +51542,7 @@
         <v>45470.6672337963</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51599,7 +51599,7 @@
         <v>44992.67101851852</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51676,7 +51676,7 @@
         <v>44658</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51733,7 +51733,7 @@
         <v>45048</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51790,7 +51790,7 @@
         <v>44959.36028935185</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -51852,7 +51852,7 @@
         <v>45051.37461805555</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -51909,7 +51909,7 @@
         <v>45764.4140162037</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -51966,7 +51966,7 @@
         <v>44846.68375</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52023,7 +52023,7 @@
         <v>45130</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -52080,7 +52080,7 @@
         <v>45764.31284722222</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -52137,7 +52137,7 @@
         <v>45471.4034837963</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -52194,7 +52194,7 @@
         <v>44977.26482638889</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45879</v>
+        <v>45880</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>

--- a/Översikt JÖNKÖPING.xlsx
+++ b/Översikt JÖNKÖPING.xlsx
@@ -567,7 +567,7 @@
         <v>45856.56684027778</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -665,7 +665,7 @@
         <v>45856.57200231482</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
         <v>45777</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>45609</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         <v>45348</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         <v>45275</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>44111</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>45698.48634259259</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>44083</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>45788.88578703703</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>45846.47335648148</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>45751.53178240741</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>44992</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>44530</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>44512.62668981482</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
         <v>44602</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>45604.53402777778</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>44974</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>45373.44148148148</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>45790.83706018519</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2403,7 +2403,7 @@
         <v>45679.98452546296</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>45358.52763888889</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2575,7 +2575,7 @@
         <v>45302</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>44991</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>45751.60517361111</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>45539</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>44278</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>44419</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         <v>44463</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
         <v>44095</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>44347.63069444444</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         <v>44467</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         <v>44083</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>44469</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>45783</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3702,7 +3702,7 @@
         <v>45740.58743055556</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>45587</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         <v>45846</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         <v>44404.71972222222</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4042,7 +4042,7 @@
         <v>45758</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4132,7 +4132,7 @@
         <v>44840</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
         <v>45856.55965277777</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4306,7 +4306,7 @@
         <v>45819.60131944445</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>45302</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4476,7 +4476,7 @@
         <v>45846</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
         <v>45876.69954861111</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         <v>45538.45523148148</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4740,7 +4740,7 @@
         <v>44879</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         <v>45841.4303125</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4914,7 +4914,7 @@
         <v>45580.46207175926</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4999,7 +4999,7 @@
         <v>45295.3942824074</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5089,7 +5089,7 @@
         <v>45343</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>45616</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
         <v>45569.41550925926</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5348,7 +5348,7 @@
         <v>44943</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5433,7 +5433,7 @@
         <v>45205</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5518,7 +5518,7 @@
         <v>45751</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5612,7 +5612,7 @@
         <v>44260</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5669,7 +5669,7 @@
         <v>44188</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5726,7 +5726,7 @@
         <v>44137</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5783,7 +5783,7 @@
         <v>44147</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>44306</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5897,7 +5897,7 @@
         <v>44308</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5959,7 +5959,7 @@
         <v>44066</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6016,7 +6016,7 @@
         <v>44144</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6073,7 +6073,7 @@
         <v>44328.35063657408</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6130,7 +6130,7 @@
         <v>44239.33525462963</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         <v>44496</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6244,7 +6244,7 @@
         <v>44278.3859375</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6301,7 +6301,7 @@
         <v>44404.84280092592</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6358,7 +6358,7 @@
         <v>44404.84659722223</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         <v>44575.80925925926</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>44662</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>44487</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6586,7 +6586,7 @@
         <v>44749.55936342593</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         <v>44749.55703703704</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6700,7 +6700,7 @@
         <v>44273.62572916667</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6757,7 +6757,7 @@
         <v>44454.35472222222</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6814,7 +6814,7 @@
         <v>44308</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6876,7 +6876,7 @@
         <v>44225</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6933,7 +6933,7 @@
         <v>44308</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6995,7 +6995,7 @@
         <v>44349</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7052,7 +7052,7 @@
         <v>44411</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7109,7 +7109,7 @@
         <v>44792.53711805555</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7166,7 +7166,7 @@
         <v>44194</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         <v>44809</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7280,7 +7280,7 @@
         <v>44225</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7337,7 +7337,7 @@
         <v>44442</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7394,7 +7394,7 @@
         <v>44487</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7451,7 +7451,7 @@
         <v>44487.49392361111</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7508,7 +7508,7 @@
         <v>44749.32716435185</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7565,7 +7565,7 @@
         <v>44420.68987268519</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7622,7 +7622,7 @@
         <v>44404.84138888889</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7679,7 +7679,7 @@
         <v>44266</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7736,7 +7736,7 @@
         <v>44881.81052083334</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7793,7 +7793,7 @@
         <v>44665.60081018518</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7850,7 +7850,7 @@
         <v>44869.49265046296</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>44734</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7974,7 +7974,7 @@
         <v>44792</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
         <v>44259</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8088,7 +8088,7 @@
         <v>44365</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8145,7 +8145,7 @@
         <v>44538</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8202,7 +8202,7 @@
         <v>44263</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8264,7 +8264,7 @@
         <v>44113</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8321,7 +8321,7 @@
         <v>44272</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8378,7 +8378,7 @@
         <v>44487</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8435,7 +8435,7 @@
         <v>44487</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8492,7 +8492,7 @@
         <v>44875.59231481481</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8549,7 +8549,7 @@
         <v>44852.74376157407</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         <v>44200</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8668,7 +8668,7 @@
         <v>44292</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8725,7 +8725,7 @@
         <v>44498.56373842592</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8782,7 +8782,7 @@
         <v>44111</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         <v>44881.79847222222</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8896,7 +8896,7 @@
         <v>44286.34827546297</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8953,7 +8953,7 @@
         <v>44273</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
         <v>44673</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9067,7 +9067,7 @@
         <v>44298.46462962963</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9129,7 +9129,7 @@
         <v>44298.46582175926</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         <v>44278.38752314815</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9248,7 +9248,7 @@
         <v>44279.37552083333</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9305,7 +9305,7 @@
         <v>44347.61920138889</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9362,7 +9362,7 @@
         <v>44754.47359953704</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>44855.3080787037</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9481,7 +9481,7 @@
         <v>44476</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         <v>44373.75251157407</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9595,7 +9595,7 @@
         <v>44347.6287962963</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9652,7 +9652,7 @@
         <v>44511</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9709,7 +9709,7 @@
         <v>44466.4425</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
         <v>44377</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9823,7 +9823,7 @@
         <v>44440.71997685185</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9880,7 +9880,7 @@
         <v>44840</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9937,7 +9937,7 @@
         <v>44104</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9994,7 +9994,7 @@
         <v>44280</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10051,7 +10051,7 @@
         <v>44613</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10108,7 +10108,7 @@
         <v>44537</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10165,7 +10165,7 @@
         <v>44456.46952546296</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10222,7 +10222,7 @@
         <v>44356</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10279,7 +10279,7 @@
         <v>44360</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10336,7 +10336,7 @@
         <v>44476</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10393,7 +10393,7 @@
         <v>44575</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10450,7 +10450,7 @@
         <v>44298.44060185185</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10512,7 +10512,7 @@
         <v>44711</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10569,7 +10569,7 @@
         <v>44659.57226851852</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10631,7 +10631,7 @@
         <v>44659</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10693,7 +10693,7 @@
         <v>44454.4800925926</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10750,7 +10750,7 @@
         <v>44578</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10807,7 +10807,7 @@
         <v>44474.25150462963</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10864,7 +10864,7 @@
         <v>44628</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10921,7 +10921,7 @@
         <v>44711</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10978,7 +10978,7 @@
         <v>44711</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11035,7 +11035,7 @@
         <v>44082.79793981482</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11092,7 +11092,7 @@
         <v>44082</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11149,7 +11149,7 @@
         <v>44841.31997685185</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11206,7 +11206,7 @@
         <v>44579.41064814815</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11263,7 +11263,7 @@
         <v>44467.68283564815</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11320,7 +11320,7 @@
         <v>44532.30398148148</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11377,7 +11377,7 @@
         <v>44557.71989583333</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11434,7 +11434,7 @@
         <v>44792.53936342592</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11491,7 +11491,7 @@
         <v>44616.39256944445</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11548,7 +11548,7 @@
         <v>44593</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11605,7 +11605,7 @@
         <v>44373</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11662,7 +11662,7 @@
         <v>44428.34821759259</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11724,7 +11724,7 @@
         <v>44259</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11781,7 +11781,7 @@
         <v>44272</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11838,7 +11838,7 @@
         <v>44239</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11895,7 +11895,7 @@
         <v>44239</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11952,7 +11952,7 @@
         <v>44464.40523148148</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12009,7 +12009,7 @@
         <v>44088</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12066,7 +12066,7 @@
         <v>44412</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12123,7 +12123,7 @@
         <v>44830.90146990741</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12180,7 +12180,7 @@
         <v>44787.80010416666</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12237,7 +12237,7 @@
         <v>44294</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12294,7 +12294,7 @@
         <v>44575</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12351,7 +12351,7 @@
         <v>44428.58511574074</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12413,7 +12413,7 @@
         <v>44729</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12470,7 +12470,7 @@
         <v>44308</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12532,7 +12532,7 @@
         <v>44825.40940972222</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12594,7 +12594,7 @@
         <v>44279.61517361111</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12651,7 +12651,7 @@
         <v>44614</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12713,7 +12713,7 @@
         <v>44272</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12770,7 +12770,7 @@
         <v>44161.31023148148</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12827,7 +12827,7 @@
         <v>44585.30171296297</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12884,7 +12884,7 @@
         <v>44536</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12946,7 +12946,7 @@
         <v>44075</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13003,7 +13003,7 @@
         <v>44428</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13065,7 +13065,7 @@
         <v>44805</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13127,7 +13127,7 @@
         <v>44811</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13184,7 +13184,7 @@
         <v>44464.42415509259</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13241,7 +13241,7 @@
         <v>44488</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13298,7 +13298,7 @@
         <v>44579</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13355,7 +13355,7 @@
         <v>44711</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13412,7 +13412,7 @@
         <v>44252</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13469,7 +13469,7 @@
         <v>44151</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13526,7 +13526,7 @@
         <v>44074</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13583,7 +13583,7 @@
         <v>44326</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13640,7 +13640,7 @@
         <v>44575.8194212963</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13697,7 +13697,7 @@
         <v>44428.596875</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13759,7 +13759,7 @@
         <v>44819</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13816,7 +13816,7 @@
         <v>44819.28449074074</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13873,7 +13873,7 @@
         <v>44292</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13930,7 +13930,7 @@
         <v>44846.66688657407</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13987,7 +13987,7 @@
         <v>44605.44909722222</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14044,7 +14044,7 @@
         <v>44523.65311342593</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14101,7 +14101,7 @@
         <v>45621.52488425926</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14158,7 +14158,7 @@
         <v>45621.5278125</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14215,7 +14215,7 @@
         <v>44596</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14272,7 +14272,7 @@
         <v>45008</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14329,7 +14329,7 @@
         <v>45338.69246527777</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14391,7 +14391,7 @@
         <v>44498.57181712963</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14448,7 +14448,7 @@
         <v>45531</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14505,7 +14505,7 @@
         <v>45716.7125</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14562,7 +14562,7 @@
         <v>45111</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14619,7 +14619,7 @@
         <v>45341</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14676,7 +14676,7 @@
         <v>44325.76335648148</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14733,7 +14733,7 @@
         <v>45112</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14790,7 +14790,7 @@
         <v>44950</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14847,7 +14847,7 @@
         <v>44950</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14904,7 +14904,7 @@
         <v>45406</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14961,7 +14961,7 @@
         <v>44344</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15018,7 +15018,7 @@
         <v>45772.45813657407</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15075,7 +15075,7 @@
         <v>45349</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15132,7 +15132,7 @@
         <v>45119.54038194445</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15189,7 +15189,7 @@
         <v>45775.4219212963</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15246,7 +15246,7 @@
         <v>45324.64579861111</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15308,7 +15308,7 @@
         <v>45324.64745370371</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15370,7 +15370,7 @@
         <v>44893</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15432,7 +15432,7 @@
         <v>45197.61039351852</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15494,7 +15494,7 @@
         <v>45615.89965277778</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15551,7 +15551,7 @@
         <v>45331</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15608,7 +15608,7 @@
         <v>45747.45038194444</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15665,7 +15665,7 @@
         <v>45701.38606481482</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15722,7 +15722,7 @@
         <v>45092.39466435185</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15779,7 +15779,7 @@
         <v>45697.26537037037</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15836,7 +15836,7 @@
         <v>45758</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15898,7 +15898,7 @@
         <v>45758.64109953704</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15955,7 +15955,7 @@
         <v>44804</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16012,7 +16012,7 @@
         <v>45770</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16069,7 +16069,7 @@
         <v>45764.53915509259</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16126,7 +16126,7 @@
         <v>44449</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16183,7 +16183,7 @@
         <v>45116.44680555556</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16240,7 +16240,7 @@
         <v>44944.40825231482</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16297,7 +16297,7 @@
         <v>45587.49814814814</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>45630.39188657407</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16416,7 +16416,7 @@
         <v>44957.36059027778</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16473,7 +16473,7 @@
         <v>44273</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16530,7 +16530,7 @@
         <v>45118</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16587,7 +16587,7 @@
         <v>44063</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16649,7 +16649,7 @@
         <v>45764.3996412037</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16706,7 +16706,7 @@
         <v>45643.47644675926</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16763,7 +16763,7 @@
         <v>45338</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16825,7 +16825,7 @@
         <v>45307.72520833334</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16882,7 +16882,7 @@
         <v>45562.38306712963</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16939,7 +16939,7 @@
         <v>45099.74195601852</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16996,7 +16996,7 @@
         <v>44882</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17053,7 +17053,7 @@
         <v>45321</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17110,7 +17110,7 @@
         <v>45750.50650462963</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17167,7 +17167,7 @@
         <v>45107</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17224,7 +17224,7 @@
         <v>45299</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17281,7 +17281,7 @@
         <v>45704</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17338,7 +17338,7 @@
         <v>45270.42966435185</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17395,7 +17395,7 @@
         <v>45474.70864583334</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17452,7 +17452,7 @@
         <v>45358</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17509,7 +17509,7 @@
         <v>45358.61696759259</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17566,7 +17566,7 @@
         <v>44484.49586805556</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17623,7 +17623,7 @@
         <v>45281.57759259259</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17685,7 +17685,7 @@
         <v>45275</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17742,7 +17742,7 @@
         <v>44414</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17799,7 +17799,7 @@
         <v>45455.4374537037</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17861,7 +17861,7 @@
         <v>45667.63950231481</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17918,7 +17918,7 @@
         <v>44628</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17975,7 +17975,7 @@
         <v>45777.60824074074</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18032,7 +18032,7 @@
         <v>45777.50512731481</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18089,7 +18089,7 @@
         <v>45335.76891203703</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18151,7 +18151,7 @@
         <v>45541.37402777778</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18208,7 +18208,7 @@
         <v>44507.82581018518</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18265,7 +18265,7 @@
         <v>45558.51949074074</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18327,7 +18327,7 @@
         <v>45586.62837962963</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18384,7 +18384,7 @@
         <v>45560.35501157407</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18441,7 +18441,7 @@
         <v>45519.48550925926</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18498,7 +18498,7 @@
         <v>45785.65899305556</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18555,7 +18555,7 @@
         <v>45124.59594907407</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18612,7 +18612,7 @@
         <v>45267.62943287037</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18669,7 +18669,7 @@
         <v>45747.73295138889</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18726,7 +18726,7 @@
         <v>45460.42804398148</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18783,7 +18783,7 @@
         <v>45588</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18840,7 +18840,7 @@
         <v>44605.45792824074</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18897,7 +18897,7 @@
         <v>44893</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18959,7 +18959,7 @@
         <v>45789.54226851852</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19016,7 +19016,7 @@
         <v>45175.44625</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19073,7 +19073,7 @@
         <v>45586</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19130,7 +19130,7 @@
         <v>45788.88399305556</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19187,7 +19187,7 @@
         <v>45788.3231712963</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19244,7 +19244,7 @@
         <v>45788.32225694445</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19301,7 +19301,7 @@
         <v>45646.5796412037</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19358,7 +19358,7 @@
         <v>45764.42304398148</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19415,7 +19415,7 @@
         <v>45790.82361111111</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19472,7 +19472,7 @@
         <v>45405</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19529,7 +19529,7 @@
         <v>45405</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19586,7 +19586,7 @@
         <v>45184</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19643,7 +19643,7 @@
         <v>45547.83950231481</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19705,7 +19705,7 @@
         <v>44578.52657407407</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19762,7 +19762,7 @@
         <v>44592.28611111111</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19819,7 +19819,7 @@
         <v>44187</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19881,7 +19881,7 @@
         <v>45541</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19938,7 +19938,7 @@
         <v>45551.36004629629</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19995,7 +19995,7 @@
         <v>45541.38644675926</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20052,7 +20052,7 @@
         <v>45545.65415509259</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20114,7 +20114,7 @@
         <v>45412</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20176,7 +20176,7 @@
         <v>45552.48335648148</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20233,7 +20233,7 @@
         <v>45462.38087962963</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20290,7 +20290,7 @@
         <v>44585</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20347,7 +20347,7 @@
         <v>45763.49402777778</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20404,7 +20404,7 @@
         <v>45790.81799768518</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20461,7 +20461,7 @@
         <v>45177</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20518,7 +20518,7 @@
         <v>45791.85732638889</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20575,7 +20575,7 @@
         <v>45350.56959490741</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20632,7 +20632,7 @@
         <v>44368.64017361111</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20689,7 +20689,7 @@
         <v>45600.47958333333</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20746,7 +20746,7 @@
         <v>45243</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20808,7 +20808,7 @@
         <v>45560.35614583334</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20865,7 +20865,7 @@
         <v>45205</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20922,7 +20922,7 @@
         <v>45645.57626157408</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20979,7 +20979,7 @@
         <v>45763.38354166667</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21056,7 +21056,7 @@
         <v>45114.55280092593</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21113,7 +21113,7 @@
         <v>45570.58934027778</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21170,7 +21170,7 @@
         <v>45793</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21227,7 +21227,7 @@
         <v>45184</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21284,7 +21284,7 @@
         <v>45701.31962962963</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21341,7 +21341,7 @@
         <v>45736</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21398,7 +21398,7 @@
         <v>45740.59474537037</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21455,7 +21455,7 @@
         <v>45736.67693287037</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21512,7 +21512,7 @@
         <v>45727.3134375</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21569,7 +21569,7 @@
         <v>45727.36650462963</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21626,7 +21626,7 @@
         <v>45735</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21683,7 +21683,7 @@
         <v>45734.35039351852</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21740,7 +21740,7 @@
         <v>45740.91412037037</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21797,7 +21797,7 @@
         <v>45741.65699074074</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21854,7 +21854,7 @@
         <v>45741.69303240741</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21911,7 +21911,7 @@
         <v>45735.65969907407</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21968,7 +21968,7 @@
         <v>45681.48793981481</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22025,7 +22025,7 @@
         <v>45681.53460648148</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22082,7 +22082,7 @@
         <v>45797.56770833334</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22139,7 +22139,7 @@
         <v>45755</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22196,7 +22196,7 @@
         <v>45728</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22253,7 +22253,7 @@
         <v>45727.35745370371</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22310,7 +22310,7 @@
         <v>45727.36243055556</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22367,7 +22367,7 @@
         <v>45734.3584837963</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22424,7 +22424,7 @@
         <v>45736</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22481,7 +22481,7 @@
         <v>45558.63807870371</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22543,7 +22543,7 @@
         <v>44591</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22600,7 +22600,7 @@
         <v>45743.59641203703</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22657,7 +22657,7 @@
         <v>45797.67148148148</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22714,7 +22714,7 @@
         <v>45734.35122685185</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22771,7 +22771,7 @@
         <v>45726.52925925926</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22828,7 +22828,7 @@
         <v>44608</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22885,7 +22885,7 @@
         <v>45730.65831018519</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22942,7 +22942,7 @@
         <v>45169</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22999,7 +22999,7 @@
         <v>45737.67416666666</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23056,7 +23056,7 @@
         <v>45730.3782175926</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23118,7 +23118,7 @@
         <v>45799.50931712963</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23175,7 +23175,7 @@
         <v>45799.52318287037</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23232,7 +23232,7 @@
         <v>45799.58894675926</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23289,7 +23289,7 @@
         <v>45799.5803125</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23346,7 +23346,7 @@
         <v>45587.47273148148</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23403,7 +23403,7 @@
         <v>44626</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23460,7 +23460,7 @@
         <v>45799.50469907407</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23517,7 +23517,7 @@
         <v>45646.39016203704</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23574,7 +23574,7 @@
         <v>45628</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23636,7 +23636,7 @@
         <v>45628</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23698,7 +23698,7 @@
         <v>45799.51578703704</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23755,7 +23755,7 @@
         <v>45761.40570601852</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23812,7 +23812,7 @@
         <v>45435</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23874,7 +23874,7 @@
         <v>45030</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23931,7 +23931,7 @@
         <v>45803.70234953704</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23988,7 +23988,7 @@
         <v>44837</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24045,7 +24045,7 @@
         <v>45371.60959490741</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24102,7 +24102,7 @@
         <v>45804.31922453704</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24159,7 +24159,7 @@
         <v>45617.92190972222</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24216,7 +24216,7 @@
         <v>45056</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24273,7 +24273,7 @@
         <v>44564.8419212963</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24330,7 +24330,7 @@
         <v>45845.60700231481</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24387,7 +24387,7 @@
         <v>45804</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24444,7 +24444,7 @@
         <v>45803.48614583333</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24501,7 +24501,7 @@
         <v>45174</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24558,7 +24558,7 @@
         <v>44992.66236111111</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24615,7 +24615,7 @@
         <v>45846.48190972222</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24672,7 +24672,7 @@
         <v>45846.73861111111</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24729,7 +24729,7 @@
         <v>45477.48771990741</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24786,7 +24786,7 @@
         <v>45726.44835648148</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24843,7 +24843,7 @@
         <v>44571</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24900,7 +24900,7 @@
         <v>45805</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24957,7 +24957,7 @@
         <v>45730.44528935185</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25019,7 +25019,7 @@
         <v>45436.68626157408</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25076,7 +25076,7 @@
         <v>45806.26452546296</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25133,7 +25133,7 @@
         <v>45806.28703703704</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25190,7 +25190,7 @@
         <v>45314</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25247,7 +25247,7 @@
         <v>45372.34530092592</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25304,7 +25304,7 @@
         <v>45179.9259375</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25361,7 +25361,7 @@
         <v>45455.42533564815</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25423,7 +25423,7 @@
         <v>45455.42981481482</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25485,7 +25485,7 @@
         <v>45733</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25542,7 +25542,7 @@
         <v>45805.58325231481</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25599,7 +25599,7 @@
         <v>45805.60481481482</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25656,7 +25656,7 @@
         <v>44963.66563657407</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25713,7 +25713,7 @@
         <v>44261</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25770,7 +25770,7 @@
         <v>45806.2833912037</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25827,7 +25827,7 @@
         <v>45624.41041666667</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25884,7 +25884,7 @@
         <v>44449</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25941,7 +25941,7 @@
         <v>45359.54100694445</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25998,7 +25998,7 @@
         <v>45846</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26060,7 +26060,7 @@
         <v>45846</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26122,7 +26122,7 @@
         <v>45477.38181712963</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26179,7 +26179,7 @@
         <v>45533.46368055556</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26236,7 +26236,7 @@
         <v>45805.58372685185</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26293,7 +26293,7 @@
         <v>45182.71081018518</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26350,7 +26350,7 @@
         <v>45539.34539351852</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26407,7 +26407,7 @@
         <v>45751.51961805556</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26469,7 +26469,7 @@
         <v>45462.37888888889</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26526,7 +26526,7 @@
         <v>45547.42313657407</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26588,7 +26588,7 @@
         <v>45547.53320601852</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26645,7 +26645,7 @@
         <v>45502.32021990741</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26702,7 +26702,7 @@
         <v>45502.33179398148</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26759,7 +26759,7 @@
         <v>44853</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26821,7 +26821,7 @@
         <v>45440.3712037037</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26878,7 +26878,7 @@
         <v>44614.68596064814</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26935,7 +26935,7 @@
         <v>45810</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26992,7 +26992,7 @@
         <v>45621.52203703704</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27049,7 +27049,7 @@
         <v>45691.5603125</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27106,7 +27106,7 @@
         <v>44355.60153935185</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27163,7 +27163,7 @@
         <v>44839</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27225,7 +27225,7 @@
         <v>45693.67859953704</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27282,7 +27282,7 @@
         <v>45145.47684027778</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27339,7 +27339,7 @@
         <v>44488</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27396,7 +27396,7 @@
         <v>44966.57471064815</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27458,7 +27458,7 @@
         <v>44936</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27515,7 +27515,7 @@
         <v>45700.60138888889</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27572,7 +27572,7 @@
         <v>44659</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27634,7 +27634,7 @@
         <v>45705</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27691,7 +27691,7 @@
         <v>44411</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27748,7 +27748,7 @@
         <v>45597.43615740741</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27805,7 +27805,7 @@
         <v>44853</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27862,7 +27862,7 @@
         <v>45434.58377314815</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27919,7 +27919,7 @@
         <v>44083</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27976,7 +27976,7 @@
         <v>45497</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28033,7 +28033,7 @@
         <v>45687</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28090,7 +28090,7 @@
         <v>45687</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28147,7 +28147,7 @@
         <v>45630.3944675926</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28209,7 +28209,7 @@
         <v>44360.54226851852</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28266,7 +28266,7 @@
         <v>45169.38410879629</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28323,7 +28323,7 @@
         <v>44935.37284722222</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28380,7 +28380,7 @@
         <v>45701</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28437,7 +28437,7 @@
         <v>45012.47533564815</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28494,7 +28494,7 @@
         <v>44482</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28551,7 +28551,7 @@
         <v>45456.66137731481</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28608,7 +28608,7 @@
         <v>45215.72212962963</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28665,7 +28665,7 @@
         <v>45404.58408564814</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28722,7 +28722,7 @@
         <v>45523.5090625</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28784,7 +28784,7 @@
         <v>45523.58461805555</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28846,7 +28846,7 @@
         <v>45392.63664351852</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28903,7 +28903,7 @@
         <v>45557.35435185185</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28960,7 +28960,7 @@
         <v>44064</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29017,7 +29017,7 @@
         <v>45635.28104166667</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29074,7 +29074,7 @@
         <v>44704.65815972222</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29131,7 +29131,7 @@
         <v>45295.40646990741</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29193,7 +29193,7 @@
         <v>45198.59607638889</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29250,7 +29250,7 @@
         <v>45706.67424768519</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29312,7 +29312,7 @@
         <v>45811</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29369,7 +29369,7 @@
         <v>45198.60034722222</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29426,7 +29426,7 @@
         <v>44090</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29483,7 +29483,7 @@
         <v>45764.42006944444</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29540,7 +29540,7 @@
         <v>45764.42517361111</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29597,7 +29597,7 @@
         <v>44655.48328703704</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29654,7 +29654,7 @@
         <v>45211</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29711,7 +29711,7 @@
         <v>45618</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29768,7 +29768,7 @@
         <v>45414</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29825,7 +29825,7 @@
         <v>44589.74348379629</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29882,7 +29882,7 @@
         <v>45751</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29944,7 +29944,7 @@
         <v>44734</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30006,7 +30006,7 @@
         <v>44734</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30068,7 +30068,7 @@
         <v>45194</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30125,7 +30125,7 @@
         <v>45194</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30182,7 +30182,7 @@
         <v>44893.50922453704</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30244,7 +30244,7 @@
         <v>45545.59315972222</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30306,7 +30306,7 @@
         <v>45681.57949074074</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30363,7 +30363,7 @@
         <v>45538</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30420,7 +30420,7 @@
         <v>45643.89232638889</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30477,7 +30477,7 @@
         <v>45561.87885416667</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30534,7 +30534,7 @@
         <v>45646.67994212963</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30591,7 +30591,7 @@
         <v>44648.61840277778</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30648,7 +30648,7 @@
         <v>45860.54674768518</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30705,7 +30705,7 @@
         <v>45642.8053125</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30767,7 +30767,7 @@
         <v>44109</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30824,7 +30824,7 @@
         <v>44097</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30881,7 +30881,7 @@
         <v>44550.30402777778</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30938,7 +30938,7 @@
         <v>45756</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30995,7 +30995,7 @@
         <v>45169</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31052,7 +31052,7 @@
         <v>44118</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31114,7 +31114,7 @@
         <v>44589.73825231481</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31171,7 +31171,7 @@
         <v>45861.46241898148</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31228,7 +31228,7 @@
         <v>45197.38018518518</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31285,7 +31285,7 @@
         <v>45861.68065972222</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31342,7 +31342,7 @@
         <v>45769.43446759259</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31399,7 +31399,7 @@
         <v>45819.53688657407</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31456,7 +31456,7 @@
         <v>45819.53980324074</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31513,7 +31513,7 @@
         <v>45819.5429050926</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31570,7 +31570,7 @@
         <v>44557</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31627,7 +31627,7 @@
         <v>45862.63645833333</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31684,7 +31684,7 @@
         <v>44423.87825231482</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31741,7 +31741,7 @@
         <v>44904</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31798,7 +31798,7 @@
         <v>45759.5549537037</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31855,7 +31855,7 @@
         <v>45751</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31917,7 +31917,7 @@
         <v>45314</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31974,7 +31974,7 @@
         <v>45303.63494212963</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32036,7 +32036,7 @@
         <v>45245.46393518519</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32093,7 +32093,7 @@
         <v>44943</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32150,7 +32150,7 @@
         <v>45189</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32207,7 +32207,7 @@
         <v>45294</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32269,7 +32269,7 @@
         <v>44904.59393518518</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32331,7 +32331,7 @@
         <v>44897</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32388,7 +32388,7 @@
         <v>44904.61212962963</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32450,7 +32450,7 @@
         <v>45246.50074074074</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32512,7 +32512,7 @@
         <v>45867.66349537037</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32569,7 +32569,7 @@
         <v>45720.70986111111</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32626,7 +32626,7 @@
         <v>45216.47443287037</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32683,7 +32683,7 @@
         <v>45268</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32740,7 +32740,7 @@
         <v>45761.49107638889</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32797,7 +32797,7 @@
         <v>45009</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32854,7 +32854,7 @@
         <v>45679.98971064815</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32911,7 +32911,7 @@
         <v>45679.99299768519</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32968,7 +32968,7 @@
         <v>45272</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33025,7 +33025,7 @@
         <v>45826</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33082,7 +33082,7 @@
         <v>45870.62511574074</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33144,7 +33144,7 @@
         <v>45401.34349537037</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33201,7 +33201,7 @@
         <v>45870.62930555556</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33263,7 +33263,7 @@
         <v>44172</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33320,7 +33320,7 @@
         <v>45750.40476851852</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33377,7 +33377,7 @@
         <v>45226.3731712963</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33434,7 +33434,7 @@
         <v>45769.60498842593</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33491,7 +33491,7 @@
         <v>45566</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33548,7 +33548,7 @@
         <v>45105.34402777778</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33605,7 +33605,7 @@
         <v>45831.51019675926</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33662,7 +33662,7 @@
         <v>45240</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33719,7 +33719,7 @@
         <v>44076</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33776,7 +33776,7 @@
         <v>44090</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33833,7 +33833,7 @@
         <v>45764.53740740741</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33890,7 +33890,7 @@
         <v>45831.50266203703</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33947,7 +33947,7 @@
         <v>45194</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34004,7 +34004,7 @@
         <v>45846</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34066,7 +34066,7 @@
         <v>45197</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34123,7 +34123,7 @@
         <v>45021</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34180,7 +34180,7 @@
         <v>45519.49606481481</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34237,7 +34237,7 @@
         <v>45875.57328703703</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34299,7 +34299,7 @@
         <v>45875.60922453704</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34356,7 +34356,7 @@
         <v>45271</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34413,7 +34413,7 @@
         <v>44950</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34470,7 +34470,7 @@
         <v>45777.50238425926</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34527,7 +34527,7 @@
         <v>45876.6799537037</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34584,7 +34584,7 @@
         <v>45833.65434027778</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34641,7 +34641,7 @@
         <v>45833.63770833334</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34698,7 +34698,7 @@
         <v>45684</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34755,7 +34755,7 @@
         <v>45834.48820601852</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34812,7 +34812,7 @@
         <v>45043</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34869,7 +34869,7 @@
         <v>44889</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34926,7 +34926,7 @@
         <v>45880.43709490741</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34983,7 +34983,7 @@
         <v>45198.41381944445</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35040,7 +35040,7 @@
         <v>45198.41887731481</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35097,7 +35097,7 @@
         <v>45735.82282407407</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35154,7 +35154,7 @@
         <v>44938</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35216,7 +35216,7 @@
         <v>45201.45827546297</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35273,7 +35273,7 @@
         <v>45877.87582175926</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35330,7 +35330,7 @@
         <v>45534.36645833333</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35387,7 +35387,7 @@
         <v>45880.49957175926</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35444,7 +35444,7 @@
         <v>45880.46642361111</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35501,7 +35501,7 @@
         <v>45253.73424768518</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35558,7 +35558,7 @@
         <v>45300</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35615,7 +35615,7 @@
         <v>45215.71418981482</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35672,7 +35672,7 @@
         <v>45392.58569444445</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35729,7 +35729,7 @@
         <v>44977.26300925926</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35786,7 +35786,7 @@
         <v>44540.57753472222</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35843,7 +35843,7 @@
         <v>45587</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35900,7 +35900,7 @@
         <v>44252</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35957,7 +35957,7 @@
         <v>44943.4652199074</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36014,7 +36014,7 @@
         <v>44943.46980324074</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36071,7 +36071,7 @@
         <v>45674.47359953704</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36128,7 +36128,7 @@
         <v>44867</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36185,7 +36185,7 @@
         <v>45477.38554398148</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36242,7 +36242,7 @@
         <v>45477.38663194444</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36299,7 +36299,7 @@
         <v>44904</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36356,7 +36356,7 @@
         <v>45882.43462962963</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36413,7 +36413,7 @@
         <v>45534.43841435185</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36470,7 +36470,7 @@
         <v>45839.71761574074</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36527,7 +36527,7 @@
         <v>45883.60416666666</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36584,7 +36584,7 @@
         <v>45622.35340277778</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36641,7 +36641,7 @@
         <v>45637.51090277778</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36698,7 +36698,7 @@
         <v>45112.3174074074</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36755,7 +36755,7 @@
         <v>45112</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36812,7 +36812,7 @@
         <v>44308.520625</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36869,7 +36869,7 @@
         <v>44930</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36926,7 +36926,7 @@
         <v>45701.37818287037</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36983,7 +36983,7 @@
         <v>45883.58956018519</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37040,7 +37040,7 @@
         <v>45842.49457175926</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37097,7 +37097,7 @@
         <v>45842.5059375</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37154,7 +37154,7 @@
         <v>44575.80709490741</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37211,7 +37211,7 @@
         <v>45883.59239583334</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37268,7 +37268,7 @@
         <v>45883.60604166667</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37325,7 +37325,7 @@
         <v>44950</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37382,7 +37382,7 @@
         <v>44249</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37439,7 +37439,7 @@
         <v>44130</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37496,7 +37496,7 @@
         <v>44225</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37553,7 +37553,7 @@
         <v>44249.66673611111</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37610,7 +37610,7 @@
         <v>45842.49056712963</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37667,7 +37667,7 @@
         <v>45581.52885416667</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37724,7 +37724,7 @@
         <v>44113</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37781,7 +37781,7 @@
         <v>45363.91521990741</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37838,7 +37838,7 @@
         <v>45364.40862268519</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37895,7 +37895,7 @@
         <v>45302</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37952,7 +37952,7 @@
         <v>45841.71503472222</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38009,7 +38009,7 @@
         <v>44966.52741898148</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38071,7 +38071,7 @@
         <v>45841.4390625</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38128,7 +38128,7 @@
         <v>44175</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38185,7 +38185,7 @@
         <v>45630.70101851852</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38247,7 +38247,7 @@
         <v>45182.36129629629</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38304,7 +38304,7 @@
         <v>44988</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38361,7 +38361,7 @@
         <v>44893</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38418,7 +38418,7 @@
         <v>44082</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38475,7 +38475,7 @@
         <v>45600.48127314815</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38532,7 +38532,7 @@
         <v>45600.48347222222</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38589,7 +38589,7 @@
         <v>45547.43438657407</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38651,7 +38651,7 @@
         <v>45406.89568287037</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38708,7 +38708,7 @@
         <v>45406.89640046296</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38765,7 +38765,7 @@
         <v>44853</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38822,7 +38822,7 @@
         <v>44484</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38879,7 +38879,7 @@
         <v>45764.40184027778</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38936,7 +38936,7 @@
         <v>44949</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38993,7 +38993,7 @@
         <v>44648</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39050,7 +39050,7 @@
         <v>44711</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39107,7 +39107,7 @@
         <v>44861.62300925926</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39164,7 +39164,7 @@
         <v>45201</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39221,7 +39221,7 @@
         <v>44938.53719907408</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39283,7 +39283,7 @@
         <v>44084.61673611111</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39340,7 +39340,7 @@
         <v>45375</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39397,7 +39397,7 @@
         <v>45180</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39454,7 +39454,7 @@
         <v>44998.8734837963</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39511,7 +39511,7 @@
         <v>44943.44811342593</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39568,7 +39568,7 @@
         <v>45547.84315972222</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39630,7 +39630,7 @@
         <v>44894</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39687,7 +39687,7 @@
         <v>44614.56209490741</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39744,7 +39744,7 @@
         <v>45763.49306712963</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39801,7 +39801,7 @@
         <v>44074</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39863,7 +39863,7 @@
         <v>44711</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39920,7 +39920,7 @@
         <v>45295.4037962963</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39982,7 +39982,7 @@
         <v>45671.44894675926</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40039,7 +40039,7 @@
         <v>44622</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40096,7 +40096,7 @@
         <v>45617.4922337963</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40153,7 +40153,7 @@
         <v>45113.31806712963</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40210,7 +40210,7 @@
         <v>45435.51875</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40267,7 +40267,7 @@
         <v>45316</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40324,7 +40324,7 @@
         <v>45058</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40381,7 +40381,7 @@
         <v>45603.60537037037</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40438,7 +40438,7 @@
         <v>44173</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40495,7 +40495,7 @@
         <v>44662</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40552,7 +40552,7 @@
         <v>45184</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40609,7 +40609,7 @@
         <v>45623.4970949074</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40666,7 +40666,7 @@
         <v>44272</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40723,7 +40723,7 @@
         <v>44965</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40780,7 +40780,7 @@
         <v>45751.58130787037</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40837,7 +40837,7 @@
         <v>45706.69384259259</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40899,7 +40899,7 @@
         <v>45706.66618055556</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40961,7 +40961,7 @@
         <v>44734</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41023,7 +41023,7 @@
         <v>45271</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41080,7 +41080,7 @@
         <v>45671.44716435186</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41137,7 +41137,7 @@
         <v>44861.6108912037</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41194,7 +41194,7 @@
         <v>44861</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41251,7 +41251,7 @@
         <v>45643</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41308,7 +41308,7 @@
         <v>44211</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41365,7 +41365,7 @@
         <v>45015</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41422,7 +41422,7 @@
         <v>45617.91424768518</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41479,7 +41479,7 @@
         <v>45461.65380787037</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41536,7 +41536,7 @@
         <v>45630.39777777778</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41598,7 +41598,7 @@
         <v>45630.4022337963</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41660,7 +41660,7 @@
         <v>45541.36828703704</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41717,7 +41717,7 @@
         <v>45679.36950231482</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41774,7 +41774,7 @@
         <v>45043.43777777778</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41831,7 +41831,7 @@
         <v>44321</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41893,7 +41893,7 @@
         <v>45644.62803240741</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41950,7 +41950,7 @@
         <v>44897.3564699074</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42012,7 +42012,7 @@
         <v>45210.34773148148</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42069,7 +42069,7 @@
         <v>45455.40401620371</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42131,7 +42131,7 @@
         <v>44750</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42188,7 +42188,7 @@
         <v>45708.52121527777</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42245,7 +42245,7 @@
         <v>44507.43497685185</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42302,7 +42302,7 @@
         <v>44943.44532407408</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42359,7 +42359,7 @@
         <v>44943.48144675926</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42416,7 +42416,7 @@
         <v>45580.46572916667</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42473,7 +42473,7 @@
         <v>45642.60125</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42530,7 +42530,7 @@
         <v>45617.45760416667</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42587,7 +42587,7 @@
         <v>44963</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42644,7 +42644,7 @@
         <v>45770.51686342592</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42701,7 +42701,7 @@
         <v>45736</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42758,7 +42758,7 @@
         <v>44614</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42815,7 +42815,7 @@
         <v>45477.48915509259</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42872,7 +42872,7 @@
         <v>45408.67427083333</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42934,7 +42934,7 @@
         <v>45547.83519675926</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42996,7 +42996,7 @@
         <v>44158</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43053,7 +43053,7 @@
         <v>45034</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43110,7 +43110,7 @@
         <v>44677</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43167,7 +43167,7 @@
         <v>44231</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43224,7 +43224,7 @@
         <v>45758</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43286,7 +43286,7 @@
         <v>45693</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43343,7 +43343,7 @@
         <v>44295.31922453704</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43400,7 +43400,7 @@
         <v>44729</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43457,7 +43457,7 @@
         <v>45470.6672337963</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43514,7 +43514,7 @@
         <v>44992.67101851852</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43591,7 +43591,7 @@
         <v>45469.43982638889</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43648,7 +43648,7 @@
         <v>44658</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43705,7 +43705,7 @@
         <v>45048</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43762,7 +43762,7 @@
         <v>45706.66388888889</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43824,7 +43824,7 @@
         <v>45706.67943287037</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43886,7 +43886,7 @@
         <v>44959.36028935185</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43948,7 +43948,7 @@
         <v>45149</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44005,7 +44005,7 @@
         <v>45201</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44062,7 +44062,7 @@
         <v>45726.42344907407</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44124,7 +44124,7 @@
         <v>45051.37461805555</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44181,7 +44181,7 @@
         <v>44719.43577546296</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44238,7 +44238,7 @@
         <v>45035</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44295,7 +44295,7 @@
         <v>45764.4140162037</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44352,7 +44352,7 @@
         <v>44846.68375</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44409,7 +44409,7 @@
         <v>45130</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44466,7 +44466,7 @@
         <v>45188.3012037037</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44523,7 +44523,7 @@
         <v>44103</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44580,7 +44580,7 @@
         <v>45764.31284722222</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44637,7 +44637,7 @@
         <v>44803.44065972222</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44694,7 +44694,7 @@
         <v>44882</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44751,7 +44751,7 @@
         <v>45471.4034837963</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44808,7 +44808,7 @@
         <v>45621</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44865,7 +44865,7 @@
         <v>45182</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44922,7 +44922,7 @@
         <v>44137</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44979,7 +44979,7 @@
         <v>44063.68225694444</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45036,7 +45036,7 @@
         <v>44977.26482638889</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45093,7 +45093,7 @@
         <v>45708.50255787037</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45150,7 +45150,7 @@
         <v>45715.65605324074</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45207,7 +45207,7 @@
         <v>44998</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45264,7 +45264,7 @@
         <v>44077</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45321,7 +45321,7 @@
         <v>44627.41212962963</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45378,7 +45378,7 @@
         <v>45673.71842592592</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45435,7 +45435,7 @@
         <v>44985.35407407407</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45492,7 +45492,7 @@
         <v>45152</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45549,7 +45549,7 @@
         <v>45401</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45611,7 +45611,7 @@
         <v>45373.60802083334</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45668,7 +45668,7 @@
         <v>45127</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45725,7 +45725,7 @@
         <v>44967.6228125</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45782,7 +45782,7 @@
         <v>45605.84435185185</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45839,7 +45839,7 @@
         <v>45681.57619212963</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45896,7 +45896,7 @@
         <v>45682.47550925926</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45953,7 +45953,7 @@
         <v>45152</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46010,7 +46010,7 @@
         <v>45092</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46067,7 +46067,7 @@
         <v>45756</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46124,7 +46124,7 @@
         <v>45757.29700231482</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46181,7 +46181,7 @@
         <v>45615.90662037037</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46238,7 +46238,7 @@
         <v>44412.7071875</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46295,7 +46295,7 @@
         <v>44361</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46352,7 +46352,7 @@
         <v>44631</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46409,7 +46409,7 @@
         <v>45758</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46471,7 +46471,7 @@
         <v>45747.30204861111</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46528,7 +46528,7 @@
         <v>45567</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46585,7 +46585,7 @@
         <v>45628</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46642,7 +46642,7 @@
         <v>45630.6993287037</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46699,7 +46699,7 @@
         <v>45240</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46756,7 +46756,7 @@
         <v>45642.92393518519</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46813,7 +46813,7 @@
         <v>45272.42149305555</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46870,7 +46870,7 @@
         <v>44229</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46927,7 +46927,7 @@
         <v>45260.85619212963</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46984,7 +46984,7 @@
         <v>44735</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47041,7 +47041,7 @@
         <v>44886.3340625</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47098,7 +47098,7 @@
         <v>45043.67869212963</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47155,7 +47155,7 @@
         <v>45751.5153125</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47217,7 +47217,7 @@
         <v>45012</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47274,7 +47274,7 @@
         <v>45300</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47331,7 +47331,7 @@
         <v>45751.62381944444</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47393,7 +47393,7 @@
         <v>45588</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47450,7 +47450,7 @@
         <v>45588</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47507,7 +47507,7 @@
         <v>44985</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47564,7 +47564,7 @@
         <v>44741.69432870371</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47621,7 +47621,7 @@
         <v>45099</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47678,7 +47678,7 @@
         <v>45363.45982638889</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47735,7 +47735,7 @@
         <v>44082</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47792,7 +47792,7 @@
         <v>45177.5462962963</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47849,7 +47849,7 @@
         <v>45223.65527777778</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47906,7 +47906,7 @@
         <v>45181</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47963,7 +47963,7 @@
         <v>45735.81920138889</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48020,7 +48020,7 @@
         <v>45112</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48077,7 +48077,7 @@
         <v>45775.4233912037</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48134,7 +48134,7 @@
         <v>45749.67842592593</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48191,7 +48191,7 @@
         <v>44840</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48248,7 +48248,7 @@
         <v>45252.58925925926</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48305,7 +48305,7 @@
         <v>44487</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48362,7 +48362,7 @@
         <v>45356.65395833334</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48424,7 +48424,7 @@
         <v>45587</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48481,7 +48481,7 @@
         <v>45107</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48538,7 +48538,7 @@
         <v>44588.50104166667</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48595,7 +48595,7 @@
         <v>44468</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48652,7 +48652,7 @@
         <v>44148</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48709,7 +48709,7 @@
         <v>45706.69090277778</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48771,7 +48771,7 @@
         <v>45747.44508101852</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48828,7 +48828,7 @@
         <v>45747.45177083334</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48885,7 +48885,7 @@
         <v>45757</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48942,7 +48942,7 @@
         <v>44979</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48999,7 +48999,7 @@
         <v>45201</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49061,7 +49061,7 @@
         <v>45545.53883101852</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49118,7 +49118,7 @@
         <v>45169</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49175,7 +49175,7 @@
         <v>45468.44574074074</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49232,7 +49232,7 @@
         <v>45775.32407407407</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49289,7 +49289,7 @@
         <v>44904</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49351,7 +49351,7 @@
         <v>45597.53744212963</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49408,7 +49408,7 @@
         <v>45769.60440972223</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49465,7 +49465,7 @@
         <v>44433</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49522,7 +49522,7 @@
         <v>45037.67510416666</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49579,7 +49579,7 @@
         <v>45447.55340277778</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49636,7 +49636,7 @@
         <v>45644.62243055556</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49693,7 +49693,7 @@
         <v>44904.49826388889</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49750,7 +49750,7 @@
         <v>45079</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49807,7 +49807,7 @@
         <v>44904</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49864,7 +49864,7 @@
         <v>44151</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49921,7 +49921,7 @@
         <v>44923.55936342593</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49978,7 +49978,7 @@
         <v>45414</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50035,7 +50035,7 @@
         <v>45377.42784722222</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50092,7 +50092,7 @@
         <v>45351.65180555556</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50154,7 +50154,7 @@
         <v>45764.30016203703</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50211,7 +50211,7 @@
         <v>44882</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50268,7 +50268,7 @@
         <v>45764.30391203704</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50325,7 +50325,7 @@
         <v>45617.48947916667</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50382,7 +50382,7 @@
         <v>45355.56604166667</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50439,7 +50439,7 @@
         <v>45324.64302083333</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50501,7 +50501,7 @@
         <v>45219</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50558,7 +50558,7 @@
         <v>45740.59871527777</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50615,7 +50615,7 @@
         <v>45477.33712962963</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50672,7 +50672,7 @@
         <v>45775.32163194445</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50729,7 +50729,7 @@
         <v>45406.89703703704</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50786,7 +50786,7 @@
         <v>45547.43793981482</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50848,7 +50848,7 @@
         <v>45183</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50905,7 +50905,7 @@
         <v>45056.6438425926</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50962,7 +50962,7 @@
         <v>45757.30554398148</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51019,7 +51019,7 @@
         <v>45755.70262731481</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51076,7 +51076,7 @@
         <v>45201.59743055556</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51133,7 +51133,7 @@
         <v>45761.41857638889</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51190,7 +51190,7 @@
         <v>45492.70833333334</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51247,7 +51247,7 @@
         <v>44483.58045138889</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51304,7 +51304,7 @@
         <v>45566</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51361,7 +51361,7 @@
         <v>45751.52445601852</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51423,7 +51423,7 @@
         <v>45751.59875</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51485,7 +51485,7 @@
         <v>45751.61236111111</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51547,7 +51547,7 @@
         <v>45751.61556712963</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51609,7 +51609,7 @@
         <v>45748</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51671,7 +51671,7 @@
         <v>45092.42630787037</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51728,7 +51728,7 @@
         <v>45446.56622685185</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51785,7 +51785,7 @@
         <v>45049</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -51842,7 +51842,7 @@
         <v>45706.68554398148</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -51904,7 +51904,7 @@
         <v>45051</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -51961,7 +51961,7 @@
         <v>45645.88440972222</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52018,7 +52018,7 @@
         <v>45734.59972222222</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45885</v>
+        <v>45886</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>

--- a/Översikt JÖNKÖPING.xlsx
+++ b/Översikt JÖNKÖPING.xlsx
@@ -567,7 +567,7 @@
         <v>45856.56684027778</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -665,7 +665,7 @@
         <v>45856.57200231482</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
         <v>45777</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>45609</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         <v>45348</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         <v>45275</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>44111</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>45698.48634259259</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>44083</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>45788.88578703703</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1505,7 +1505,7 @@
         <v>45846.47335648148</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>45751.53178240741</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1694,7 +1694,7 @@
         <v>44992</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1786,7 +1786,7 @@
         <v>44530</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1873,7 +1873,7 @@
         <v>44512.62668981482</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1965,7 +1965,7 @@
         <v>44602</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>45604.53402777778</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2144,7 +2144,7 @@
         <v>44974</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>45373.44148148148</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2317,7 +2317,7 @@
         <v>45790.83706018519</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2403,7 +2403,7 @@
         <v>45679.98452546296</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2489,7 +2489,7 @@
         <v>45358.52763888889</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2575,7 +2575,7 @@
         <v>45302</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2661,7 +2661,7 @@
         <v>44991</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2747,7 +2747,7 @@
         <v>45751.60517361111</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>45539</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2928,7 +2928,7 @@
         <v>44278</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3013,7 +3013,7 @@
         <v>44419</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3098,7 +3098,7 @@
         <v>44463</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3183,7 +3183,7 @@
         <v>44095</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3268,7 +3268,7 @@
         <v>44347.63069444444</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         <v>44467</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3438,7 +3438,7 @@
         <v>44083</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3528,7 +3528,7 @@
         <v>44469</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>45783</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3702,7 +3702,7 @@
         <v>45740.58743055556</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3787,7 +3787,7 @@
         <v>45587</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3872,7 +3872,7 @@
         <v>45846</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3957,7 +3957,7 @@
         <v>44404.71972222222</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4042,7 +4042,7 @@
         <v>45758</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4132,7 +4132,7 @@
         <v>44840</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4217,7 +4217,7 @@
         <v>45856.55965277777</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4306,7 +4306,7 @@
         <v>45819.60131944445</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>45302</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4476,7 +4476,7 @@
         <v>45846</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4570,7 +4570,7 @@
         <v>45876.69954861111</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4655,7 +4655,7 @@
         <v>45538.45523148148</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4740,7 +4740,7 @@
         <v>44879</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4829,7 +4829,7 @@
         <v>45841.4303125</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4914,7 +4914,7 @@
         <v>45580.46207175926</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4999,7 +4999,7 @@
         <v>45295.3942824074</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5089,7 +5089,7 @@
         <v>45343</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5174,7 +5174,7 @@
         <v>45616</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5263,7 +5263,7 @@
         <v>45569.41550925926</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5348,7 +5348,7 @@
         <v>44943</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5433,7 +5433,7 @@
         <v>45205</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5518,7 +5518,7 @@
         <v>45751</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5612,7 +5612,7 @@
         <v>44260</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5669,7 +5669,7 @@
         <v>44188</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5726,7 +5726,7 @@
         <v>44137</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5783,7 +5783,7 @@
         <v>44147</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5840,7 +5840,7 @@
         <v>44306</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5897,7 +5897,7 @@
         <v>44308</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5959,7 +5959,7 @@
         <v>44066</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6016,7 +6016,7 @@
         <v>44144</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6073,7 +6073,7 @@
         <v>44328.35063657408</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6130,7 +6130,7 @@
         <v>44239.33525462963</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6187,7 +6187,7 @@
         <v>44496</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6244,7 +6244,7 @@
         <v>44278.3859375</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6301,7 +6301,7 @@
         <v>44404.84280092592</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6358,7 +6358,7 @@
         <v>44404.84659722223</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6415,7 +6415,7 @@
         <v>44575.80925925926</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6472,7 +6472,7 @@
         <v>44662</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6529,7 +6529,7 @@
         <v>44487</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6586,7 +6586,7 @@
         <v>44749.55936342593</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         <v>44749.55703703704</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6700,7 +6700,7 @@
         <v>44273.62572916667</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6757,7 +6757,7 @@
         <v>44454.35472222222</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6814,7 +6814,7 @@
         <v>44308</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6876,7 +6876,7 @@
         <v>44225</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6933,7 +6933,7 @@
         <v>44308</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6995,7 +6995,7 @@
         <v>44349</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -7052,7 +7052,7 @@
         <v>44411</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7109,7 +7109,7 @@
         <v>44792.53711805555</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7166,7 +7166,7 @@
         <v>44194</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         <v>44809</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7280,7 +7280,7 @@
         <v>44225</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7337,7 +7337,7 @@
         <v>44442</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7394,7 +7394,7 @@
         <v>44487</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7451,7 +7451,7 @@
         <v>44487.49392361111</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7508,7 +7508,7 @@
         <v>44749.32716435185</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7565,7 +7565,7 @@
         <v>44420.68987268519</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7622,7 +7622,7 @@
         <v>44404.84138888889</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7679,7 +7679,7 @@
         <v>44266</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7736,7 +7736,7 @@
         <v>44881.81052083334</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7793,7 +7793,7 @@
         <v>44665.60081018518</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7850,7 +7850,7 @@
         <v>44869.49265046296</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7912,7 +7912,7 @@
         <v>44734</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7974,7 +7974,7 @@
         <v>44792</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -8031,7 +8031,7 @@
         <v>44259</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8088,7 +8088,7 @@
         <v>44365</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8145,7 +8145,7 @@
         <v>44538</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8202,7 +8202,7 @@
         <v>44263</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8264,7 +8264,7 @@
         <v>44113</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8321,7 +8321,7 @@
         <v>44272</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8378,7 +8378,7 @@
         <v>44487</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8435,7 +8435,7 @@
         <v>44487</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8492,7 +8492,7 @@
         <v>44875.59231481481</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8549,7 +8549,7 @@
         <v>44852.74376157407</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8611,7 +8611,7 @@
         <v>44200</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8668,7 +8668,7 @@
         <v>44292</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8725,7 +8725,7 @@
         <v>44498.56373842592</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8782,7 +8782,7 @@
         <v>44111</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8839,7 +8839,7 @@
         <v>44881.79847222222</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8896,7 +8896,7 @@
         <v>44286.34827546297</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8953,7 +8953,7 @@
         <v>44273</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
         <v>44673</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9067,7 +9067,7 @@
         <v>44298.46462962963</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9129,7 +9129,7 @@
         <v>44298.46582175926</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         <v>44278.38752314815</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9248,7 +9248,7 @@
         <v>44279.37552083333</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9305,7 +9305,7 @@
         <v>44347.61920138889</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9362,7 +9362,7 @@
         <v>44754.47359953704</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9424,7 +9424,7 @@
         <v>44855.3080787037</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9481,7 +9481,7 @@
         <v>44476</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9538,7 +9538,7 @@
         <v>44373.75251157407</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9595,7 +9595,7 @@
         <v>44347.6287962963</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9652,7 +9652,7 @@
         <v>44511</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9709,7 +9709,7 @@
         <v>44466.4425</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
         <v>44377</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9823,7 +9823,7 @@
         <v>44440.71997685185</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9880,7 +9880,7 @@
         <v>44840</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9937,7 +9937,7 @@
         <v>44104</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9994,7 +9994,7 @@
         <v>44280</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -10051,7 +10051,7 @@
         <v>44613</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10108,7 +10108,7 @@
         <v>44537</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10165,7 +10165,7 @@
         <v>44456.46952546296</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10222,7 +10222,7 @@
         <v>44356</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10279,7 +10279,7 @@
         <v>44360</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10336,7 +10336,7 @@
         <v>44476</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10393,7 +10393,7 @@
         <v>44575</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10450,7 +10450,7 @@
         <v>44298.44060185185</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10512,7 +10512,7 @@
         <v>44711</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10569,7 +10569,7 @@
         <v>44659.57226851852</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10631,7 +10631,7 @@
         <v>44659</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10693,7 +10693,7 @@
         <v>44454.4800925926</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10750,7 +10750,7 @@
         <v>44578</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10807,7 +10807,7 @@
         <v>44474.25150462963</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10864,7 +10864,7 @@
         <v>44628</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10921,7 +10921,7 @@
         <v>44711</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10978,7 +10978,7 @@
         <v>44711</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -11035,7 +11035,7 @@
         <v>44082.79793981482</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11092,7 +11092,7 @@
         <v>44082</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11149,7 +11149,7 @@
         <v>44841.31997685185</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11206,7 +11206,7 @@
         <v>44579.41064814815</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11263,7 +11263,7 @@
         <v>44467.68283564815</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11320,7 +11320,7 @@
         <v>44532.30398148148</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11377,7 +11377,7 @@
         <v>44557.71989583333</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11434,7 +11434,7 @@
         <v>44792.53936342592</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11491,7 +11491,7 @@
         <v>44616.39256944445</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11548,7 +11548,7 @@
         <v>44593</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11605,7 +11605,7 @@
         <v>44373</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11662,7 +11662,7 @@
         <v>44428.34821759259</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11724,7 +11724,7 @@
         <v>44259</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11781,7 +11781,7 @@
         <v>44272</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11838,7 +11838,7 @@
         <v>44239</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11895,7 +11895,7 @@
         <v>44239</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11952,7 +11952,7 @@
         <v>44464.40523148148</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -12009,7 +12009,7 @@
         <v>44088</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -12066,7 +12066,7 @@
         <v>44412</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12123,7 +12123,7 @@
         <v>44830.90146990741</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12180,7 +12180,7 @@
         <v>44787.80010416666</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12237,7 +12237,7 @@
         <v>44294</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12294,7 +12294,7 @@
         <v>44575</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12351,7 +12351,7 @@
         <v>44428.58511574074</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12413,7 +12413,7 @@
         <v>44729</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12470,7 +12470,7 @@
         <v>44308</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12532,7 +12532,7 @@
         <v>44825.40940972222</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12594,7 +12594,7 @@
         <v>44279.61517361111</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12651,7 +12651,7 @@
         <v>44614</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12713,7 +12713,7 @@
         <v>44272</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12770,7 +12770,7 @@
         <v>44161.31023148148</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12827,7 +12827,7 @@
         <v>44585.30171296297</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12884,7 +12884,7 @@
         <v>44536</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12946,7 +12946,7 @@
         <v>44075</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -13003,7 +13003,7 @@
         <v>44428</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -13065,7 +13065,7 @@
         <v>44805</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13127,7 +13127,7 @@
         <v>44811</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13184,7 +13184,7 @@
         <v>44464.42415509259</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13241,7 +13241,7 @@
         <v>44488</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13298,7 +13298,7 @@
         <v>44579</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13355,7 +13355,7 @@
         <v>44711</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13412,7 +13412,7 @@
         <v>44252</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13469,7 +13469,7 @@
         <v>44151</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13526,7 +13526,7 @@
         <v>44074</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13583,7 +13583,7 @@
         <v>44326</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13640,7 +13640,7 @@
         <v>44575.8194212963</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13697,7 +13697,7 @@
         <v>44428.596875</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13759,7 +13759,7 @@
         <v>44819</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13816,7 +13816,7 @@
         <v>44819.28449074074</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13873,7 +13873,7 @@
         <v>44292</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13930,7 +13930,7 @@
         <v>44846.66688657407</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13987,7 +13987,7 @@
         <v>44605.44909722222</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -14044,7 +14044,7 @@
         <v>44523.65311342593</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14101,7 +14101,7 @@
         <v>45621.52488425926</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14158,7 +14158,7 @@
         <v>45621.5278125</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14215,7 +14215,7 @@
         <v>44596</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14272,7 +14272,7 @@
         <v>45008</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14329,7 +14329,7 @@
         <v>45338.69246527777</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14391,7 +14391,7 @@
         <v>44498.57181712963</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14448,7 +14448,7 @@
         <v>45531</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14505,7 +14505,7 @@
         <v>45716.7125</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14562,7 +14562,7 @@
         <v>45111</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14619,7 +14619,7 @@
         <v>45341</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14676,7 +14676,7 @@
         <v>44325.76335648148</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14733,7 +14733,7 @@
         <v>45112</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14790,7 +14790,7 @@
         <v>44950</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14847,7 +14847,7 @@
         <v>44950</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14904,7 +14904,7 @@
         <v>45406</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14961,7 +14961,7 @@
         <v>44344</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -15018,7 +15018,7 @@
         <v>45772.45813657407</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15075,7 +15075,7 @@
         <v>45349</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15132,7 +15132,7 @@
         <v>45119.54038194445</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15189,7 +15189,7 @@
         <v>45775.4219212963</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15246,7 +15246,7 @@
         <v>45324.64579861111</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15308,7 +15308,7 @@
         <v>45324.64745370371</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15370,7 +15370,7 @@
         <v>44893</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15432,7 +15432,7 @@
         <v>45197.61039351852</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15494,7 +15494,7 @@
         <v>45615.89965277778</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15551,7 +15551,7 @@
         <v>45331</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15608,7 +15608,7 @@
         <v>45747.45038194444</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15665,7 +15665,7 @@
         <v>45701.38606481482</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15722,7 +15722,7 @@
         <v>45092.39466435185</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15779,7 +15779,7 @@
         <v>45697.26537037037</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15836,7 +15836,7 @@
         <v>45758</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15898,7 +15898,7 @@
         <v>45758.64109953704</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15955,7 +15955,7 @@
         <v>44804</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -16012,7 +16012,7 @@
         <v>45770</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -16069,7 +16069,7 @@
         <v>45764.53915509259</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16126,7 +16126,7 @@
         <v>44449</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16183,7 +16183,7 @@
         <v>45116.44680555556</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16240,7 +16240,7 @@
         <v>44944.40825231482</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16297,7 +16297,7 @@
         <v>45587.49814814814</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16354,7 +16354,7 @@
         <v>45630.39188657407</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16416,7 +16416,7 @@
         <v>44957.36059027778</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16473,7 +16473,7 @@
         <v>44273</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16530,7 +16530,7 @@
         <v>45118</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16587,7 +16587,7 @@
         <v>44063</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16649,7 +16649,7 @@
         <v>45764.3996412037</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16706,7 +16706,7 @@
         <v>45643.47644675926</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16763,7 +16763,7 @@
         <v>45338</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16825,7 +16825,7 @@
         <v>45307.72520833334</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16882,7 +16882,7 @@
         <v>45562.38306712963</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16939,7 +16939,7 @@
         <v>45099.74195601852</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16996,7 +16996,7 @@
         <v>44882</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -17053,7 +17053,7 @@
         <v>45321</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17110,7 +17110,7 @@
         <v>45750.50650462963</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17167,7 +17167,7 @@
         <v>45107</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17224,7 +17224,7 @@
         <v>45299</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17281,7 +17281,7 @@
         <v>45704</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17338,7 +17338,7 @@
         <v>45270.42966435185</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17395,7 +17395,7 @@
         <v>45474.70864583334</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17452,7 +17452,7 @@
         <v>45358</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17509,7 +17509,7 @@
         <v>45358.61696759259</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17566,7 +17566,7 @@
         <v>44484.49586805556</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17623,7 +17623,7 @@
         <v>45281.57759259259</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17685,7 +17685,7 @@
         <v>45275</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17742,7 +17742,7 @@
         <v>44414</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17799,7 +17799,7 @@
         <v>45455.4374537037</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17861,7 +17861,7 @@
         <v>45667.63950231481</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17918,7 +17918,7 @@
         <v>44628</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17975,7 +17975,7 @@
         <v>45777.60824074074</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -18032,7 +18032,7 @@
         <v>45777.50512731481</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18089,7 +18089,7 @@
         <v>45335.76891203703</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18151,7 +18151,7 @@
         <v>45541.37402777778</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18208,7 +18208,7 @@
         <v>44507.82581018518</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18265,7 +18265,7 @@
         <v>45558.51949074074</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18327,7 +18327,7 @@
         <v>45586.62837962963</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18384,7 +18384,7 @@
         <v>45560.35501157407</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18441,7 +18441,7 @@
         <v>45519.48550925926</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18498,7 +18498,7 @@
         <v>45785.65899305556</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18555,7 +18555,7 @@
         <v>45124.59594907407</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18612,7 +18612,7 @@
         <v>45267.62943287037</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18669,7 +18669,7 @@
         <v>45747.73295138889</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18726,7 +18726,7 @@
         <v>45460.42804398148</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18783,7 +18783,7 @@
         <v>45588</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18840,7 +18840,7 @@
         <v>44605.45792824074</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18897,7 +18897,7 @@
         <v>44893</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18959,7 +18959,7 @@
         <v>45789.54226851852</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -19016,7 +19016,7 @@
         <v>45175.44625</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19073,7 +19073,7 @@
         <v>45586</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19130,7 +19130,7 @@
         <v>45788.88399305556</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19187,7 +19187,7 @@
         <v>45788.3231712963</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19244,7 +19244,7 @@
         <v>45788.32225694445</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19301,7 +19301,7 @@
         <v>45646.5796412037</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19358,7 +19358,7 @@
         <v>45764.42304398148</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19415,7 +19415,7 @@
         <v>45790.82361111111</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19472,7 +19472,7 @@
         <v>45405</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19529,7 +19529,7 @@
         <v>45405</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19586,7 +19586,7 @@
         <v>45184</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19643,7 +19643,7 @@
         <v>45547.83950231481</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19705,7 +19705,7 @@
         <v>44578.52657407407</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19762,7 +19762,7 @@
         <v>44592.28611111111</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19819,7 +19819,7 @@
         <v>44187</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19881,7 +19881,7 @@
         <v>45541</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19938,7 +19938,7 @@
         <v>45551.36004629629</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19995,7 +19995,7 @@
         <v>45541.38644675926</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -20052,7 +20052,7 @@
         <v>45545.65415509259</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20114,7 +20114,7 @@
         <v>45412</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20176,7 +20176,7 @@
         <v>45552.48335648148</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20233,7 +20233,7 @@
         <v>45462.38087962963</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20290,7 +20290,7 @@
         <v>44585</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20347,7 +20347,7 @@
         <v>45763.49402777778</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20404,7 +20404,7 @@
         <v>45790.81799768518</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20461,7 +20461,7 @@
         <v>45177</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20518,7 +20518,7 @@
         <v>45791.85732638889</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20575,7 +20575,7 @@
         <v>45350.56959490741</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20632,7 +20632,7 @@
         <v>44368.64017361111</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20689,7 +20689,7 @@
         <v>45600.47958333333</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20746,7 +20746,7 @@
         <v>45243</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20808,7 +20808,7 @@
         <v>45560.35614583334</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20865,7 +20865,7 @@
         <v>45205</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20922,7 +20922,7 @@
         <v>45645.57626157408</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20979,7 +20979,7 @@
         <v>45763.38354166667</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -21056,7 +21056,7 @@
         <v>45114.55280092593</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21113,7 +21113,7 @@
         <v>45570.58934027778</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21170,7 +21170,7 @@
         <v>45793</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21227,7 +21227,7 @@
         <v>45184</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21284,7 +21284,7 @@
         <v>45701.31962962963</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21341,7 +21341,7 @@
         <v>45736</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21398,7 +21398,7 @@
         <v>45740.59474537037</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21455,7 +21455,7 @@
         <v>45736.67693287037</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21512,7 +21512,7 @@
         <v>45727.3134375</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21569,7 +21569,7 @@
         <v>45727.36650462963</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21626,7 +21626,7 @@
         <v>45735</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21683,7 +21683,7 @@
         <v>45734.35039351852</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21740,7 +21740,7 @@
         <v>45740.91412037037</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21797,7 +21797,7 @@
         <v>45741.65699074074</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21854,7 +21854,7 @@
         <v>45741.69303240741</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21911,7 +21911,7 @@
         <v>45735.65969907407</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21968,7 +21968,7 @@
         <v>45681.48793981481</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -22025,7 +22025,7 @@
         <v>45681.53460648148</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22082,7 +22082,7 @@
         <v>45797.56770833334</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22139,7 +22139,7 @@
         <v>45755</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22196,7 +22196,7 @@
         <v>45728</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22253,7 +22253,7 @@
         <v>45727.35745370371</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22310,7 +22310,7 @@
         <v>45727.36243055556</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22367,7 +22367,7 @@
         <v>45734.3584837963</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22424,7 +22424,7 @@
         <v>45736</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22481,7 +22481,7 @@
         <v>45558.63807870371</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22543,7 +22543,7 @@
         <v>44591</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22600,7 +22600,7 @@
         <v>45743.59641203703</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22657,7 +22657,7 @@
         <v>45797.67148148148</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22714,7 +22714,7 @@
         <v>45734.35122685185</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22771,7 +22771,7 @@
         <v>45726.52925925926</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22828,7 +22828,7 @@
         <v>44608</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22885,7 +22885,7 @@
         <v>45730.65831018519</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22942,7 +22942,7 @@
         <v>45169</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22999,7 +22999,7 @@
         <v>45737.67416666666</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23056,7 +23056,7 @@
         <v>45730.3782175926</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23118,7 +23118,7 @@
         <v>45799.50931712963</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23175,7 +23175,7 @@
         <v>45799.52318287037</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23232,7 +23232,7 @@
         <v>45799.58894675926</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23289,7 +23289,7 @@
         <v>45799.5803125</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23346,7 +23346,7 @@
         <v>45587.47273148148</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23403,7 +23403,7 @@
         <v>44626</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23460,7 +23460,7 @@
         <v>45799.50469907407</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23517,7 +23517,7 @@
         <v>45646.39016203704</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23574,7 +23574,7 @@
         <v>45628</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23636,7 +23636,7 @@
         <v>45628</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23698,7 +23698,7 @@
         <v>45799.51578703704</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23755,7 +23755,7 @@
         <v>45761.40570601852</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23812,7 +23812,7 @@
         <v>45435</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23874,7 +23874,7 @@
         <v>45030</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23931,7 +23931,7 @@
         <v>45803.70234953704</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23988,7 +23988,7 @@
         <v>44837</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -24045,7 +24045,7 @@
         <v>45371.60959490741</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24102,7 +24102,7 @@
         <v>45804.31922453704</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24159,7 +24159,7 @@
         <v>45617.92190972222</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24216,7 +24216,7 @@
         <v>45056</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24273,7 +24273,7 @@
         <v>44564.8419212963</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24330,7 +24330,7 @@
         <v>45845.60700231481</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24387,7 +24387,7 @@
         <v>45804</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24444,7 +24444,7 @@
         <v>45803.48614583333</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24501,7 +24501,7 @@
         <v>45174</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24558,7 +24558,7 @@
         <v>44992.66236111111</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24615,7 +24615,7 @@
         <v>45846.48190972222</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24672,7 +24672,7 @@
         <v>45846.73861111111</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24729,7 +24729,7 @@
         <v>45477.48771990741</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24786,7 +24786,7 @@
         <v>45726.44835648148</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24843,7 +24843,7 @@
         <v>44571</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24900,7 +24900,7 @@
         <v>45805</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24957,7 +24957,7 @@
         <v>45730.44528935185</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -25019,7 +25019,7 @@
         <v>45436.68626157408</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25076,7 +25076,7 @@
         <v>45806.26452546296</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25133,7 +25133,7 @@
         <v>45806.28703703704</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25190,7 +25190,7 @@
         <v>45314</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25247,7 +25247,7 @@
         <v>45372.34530092592</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25304,7 +25304,7 @@
         <v>45179.9259375</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25361,7 +25361,7 @@
         <v>45455.42533564815</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25423,7 +25423,7 @@
         <v>45455.42981481482</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25485,7 +25485,7 @@
         <v>45733</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25542,7 +25542,7 @@
         <v>45805.58325231481</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25599,7 +25599,7 @@
         <v>45805.60481481482</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25656,7 +25656,7 @@
         <v>44963.66563657407</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25713,7 +25713,7 @@
         <v>44261</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25770,7 +25770,7 @@
         <v>45806.2833912037</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25827,7 +25827,7 @@
         <v>45624.41041666667</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25884,7 +25884,7 @@
         <v>44449</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25941,7 +25941,7 @@
         <v>45359.54100694445</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25998,7 +25998,7 @@
         <v>45846</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -26060,7 +26060,7 @@
         <v>45846</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26122,7 +26122,7 @@
         <v>45477.38181712963</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26179,7 +26179,7 @@
         <v>45533.46368055556</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26236,7 +26236,7 @@
         <v>45805.58372685185</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26293,7 +26293,7 @@
         <v>45182.71081018518</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26350,7 +26350,7 @@
         <v>45539.34539351852</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26407,7 +26407,7 @@
         <v>45751.51961805556</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26469,7 +26469,7 @@
         <v>45462.37888888889</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26526,7 +26526,7 @@
         <v>45547.42313657407</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26588,7 +26588,7 @@
         <v>45547.53320601852</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26645,7 +26645,7 @@
         <v>45502.32021990741</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26702,7 +26702,7 @@
         <v>45502.33179398148</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26759,7 +26759,7 @@
         <v>44853</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26821,7 +26821,7 @@
         <v>45440.3712037037</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26878,7 +26878,7 @@
         <v>44614.68596064814</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26935,7 +26935,7 @@
         <v>45810</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26992,7 +26992,7 @@
         <v>45621.52203703704</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -27049,7 +27049,7 @@
         <v>45691.5603125</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27106,7 +27106,7 @@
         <v>44355.60153935185</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27163,7 +27163,7 @@
         <v>44839</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27225,7 +27225,7 @@
         <v>45693.67859953704</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27282,7 +27282,7 @@
         <v>45145.47684027778</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27339,7 +27339,7 @@
         <v>44488</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27396,7 +27396,7 @@
         <v>44966.57471064815</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27458,7 +27458,7 @@
         <v>44936</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27515,7 +27515,7 @@
         <v>45700.60138888889</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27572,7 +27572,7 @@
         <v>44659</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27634,7 +27634,7 @@
         <v>45705</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27691,7 +27691,7 @@
         <v>44411</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27748,7 +27748,7 @@
         <v>45597.43615740741</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27805,7 +27805,7 @@
         <v>44853</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27862,7 +27862,7 @@
         <v>45434.58377314815</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27919,7 +27919,7 @@
         <v>44083</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27976,7 +27976,7 @@
         <v>45497</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -28033,7 +28033,7 @@
         <v>45687</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28090,7 +28090,7 @@
         <v>45687</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28147,7 +28147,7 @@
         <v>45630.3944675926</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28209,7 +28209,7 @@
         <v>44360.54226851852</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28266,7 +28266,7 @@
         <v>45169.38410879629</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28323,7 +28323,7 @@
         <v>44935.37284722222</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28380,7 +28380,7 @@
         <v>45701</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28437,7 +28437,7 @@
         <v>45012.47533564815</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28494,7 +28494,7 @@
         <v>44482</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28551,7 +28551,7 @@
         <v>45456.66137731481</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28608,7 +28608,7 @@
         <v>45215.72212962963</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28665,7 +28665,7 @@
         <v>45404.58408564814</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28722,7 +28722,7 @@
         <v>45523.5090625</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28784,7 +28784,7 @@
         <v>45523.58461805555</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28846,7 +28846,7 @@
         <v>45392.63664351852</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28903,7 +28903,7 @@
         <v>45557.35435185185</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28960,7 +28960,7 @@
         <v>44064</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -29017,7 +29017,7 @@
         <v>45635.28104166667</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -29074,7 +29074,7 @@
         <v>44704.65815972222</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29131,7 +29131,7 @@
         <v>45295.40646990741</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29193,7 +29193,7 @@
         <v>45198.59607638889</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29250,7 +29250,7 @@
         <v>45706.67424768519</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29312,7 +29312,7 @@
         <v>45811</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29369,7 +29369,7 @@
         <v>45198.60034722222</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29426,7 +29426,7 @@
         <v>44090</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29483,7 +29483,7 @@
         <v>45764.42006944444</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29540,7 +29540,7 @@
         <v>45764.42517361111</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29597,7 +29597,7 @@
         <v>44655.48328703704</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29654,7 +29654,7 @@
         <v>45211</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29711,7 +29711,7 @@
         <v>45618</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29768,7 +29768,7 @@
         <v>45414</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29825,7 +29825,7 @@
         <v>44589.74348379629</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29882,7 +29882,7 @@
         <v>45751</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29944,7 +29944,7 @@
         <v>44734</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -30006,7 +30006,7 @@
         <v>44734</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -30068,7 +30068,7 @@
         <v>45194</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30125,7 +30125,7 @@
         <v>45194</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30182,7 +30182,7 @@
         <v>44893.50922453704</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30244,7 +30244,7 @@
         <v>45545.59315972222</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30306,7 +30306,7 @@
         <v>45681.57949074074</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30363,7 +30363,7 @@
         <v>45538</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30420,7 +30420,7 @@
         <v>45643.89232638889</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30477,7 +30477,7 @@
         <v>45561.87885416667</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30534,7 +30534,7 @@
         <v>45646.67994212963</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30591,7 +30591,7 @@
         <v>44648.61840277778</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30648,7 +30648,7 @@
         <v>45860.54674768518</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30705,7 +30705,7 @@
         <v>45642.8053125</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30767,7 +30767,7 @@
         <v>44109</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30824,7 +30824,7 @@
         <v>44097</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30881,7 +30881,7 @@
         <v>44550.30402777778</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30938,7 +30938,7 @@
         <v>45756</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30995,7 +30995,7 @@
         <v>45169</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -31052,7 +31052,7 @@
         <v>44118</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31114,7 +31114,7 @@
         <v>44589.73825231481</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31171,7 +31171,7 @@
         <v>45861.46241898148</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31228,7 +31228,7 @@
         <v>45197.38018518518</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31285,7 +31285,7 @@
         <v>45861.68065972222</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31342,7 +31342,7 @@
         <v>45769.43446759259</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31399,7 +31399,7 @@
         <v>45819.53688657407</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31456,7 +31456,7 @@
         <v>45819.53980324074</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31513,7 +31513,7 @@
         <v>45819.5429050926</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31570,7 +31570,7 @@
         <v>44557</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31627,7 +31627,7 @@
         <v>45862.63645833333</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31684,7 +31684,7 @@
         <v>44423.87825231482</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31741,7 +31741,7 @@
         <v>44904</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31798,7 +31798,7 @@
         <v>45759.5549537037</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31855,7 +31855,7 @@
         <v>45751</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31917,7 +31917,7 @@
         <v>45314</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31974,7 +31974,7 @@
         <v>45303.63494212963</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -32036,7 +32036,7 @@
         <v>45245.46393518519</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32093,7 +32093,7 @@
         <v>44943</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32150,7 +32150,7 @@
         <v>45189</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32207,7 +32207,7 @@
         <v>45294</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32269,7 +32269,7 @@
         <v>44904.59393518518</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32331,7 +32331,7 @@
         <v>44897</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32388,7 +32388,7 @@
         <v>44904.61212962963</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32450,7 +32450,7 @@
         <v>45246.50074074074</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32512,7 +32512,7 @@
         <v>45867.66349537037</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32569,7 +32569,7 @@
         <v>45720.70986111111</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32626,7 +32626,7 @@
         <v>45216.47443287037</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32683,7 +32683,7 @@
         <v>45268</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32740,7 +32740,7 @@
         <v>45761.49107638889</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32797,7 +32797,7 @@
         <v>45009</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32854,7 +32854,7 @@
         <v>45679.98971064815</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32911,7 +32911,7 @@
         <v>45679.99299768519</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32968,7 +32968,7 @@
         <v>45272</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -33025,7 +33025,7 @@
         <v>45826</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -33082,7 +33082,7 @@
         <v>45870.62511574074</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33144,7 +33144,7 @@
         <v>45401.34349537037</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33201,7 +33201,7 @@
         <v>45870.62930555556</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33263,7 +33263,7 @@
         <v>44172</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33320,7 +33320,7 @@
         <v>45750.40476851852</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33377,7 +33377,7 @@
         <v>45226.3731712963</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33434,7 +33434,7 @@
         <v>45769.60498842593</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33491,7 +33491,7 @@
         <v>45566</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33548,7 +33548,7 @@
         <v>45105.34402777778</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33605,7 +33605,7 @@
         <v>45831.51019675926</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33662,7 +33662,7 @@
         <v>45240</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33719,7 +33719,7 @@
         <v>44076</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33776,7 +33776,7 @@
         <v>44090</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33833,7 +33833,7 @@
         <v>45764.53740740741</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33890,7 +33890,7 @@
         <v>45831.50266203703</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33947,7 +33947,7 @@
         <v>45194</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -34004,7 +34004,7 @@
         <v>45846</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -34066,7 +34066,7 @@
         <v>45197</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34123,7 +34123,7 @@
         <v>45021</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34180,7 +34180,7 @@
         <v>45519.49606481481</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34237,7 +34237,7 @@
         <v>45875.57328703703</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34299,7 +34299,7 @@
         <v>45875.60922453704</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34356,7 +34356,7 @@
         <v>45271</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34413,7 +34413,7 @@
         <v>44950</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34470,7 +34470,7 @@
         <v>45777.50238425926</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34527,7 +34527,7 @@
         <v>45876.6799537037</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34584,7 +34584,7 @@
         <v>45833.65434027778</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34641,7 +34641,7 @@
         <v>45833.63770833334</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34698,7 +34698,7 @@
         <v>45684</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34755,7 +34755,7 @@
         <v>45834.48820601852</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34812,7 +34812,7 @@
         <v>45043</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34869,7 +34869,7 @@
         <v>44889</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34926,7 +34926,7 @@
         <v>45880.43709490741</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34983,7 +34983,7 @@
         <v>45198.41381944445</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -35040,7 +35040,7 @@
         <v>45198.41887731481</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35097,7 +35097,7 @@
         <v>45735.82282407407</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35154,7 +35154,7 @@
         <v>44938</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35216,7 +35216,7 @@
         <v>45201.45827546297</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35273,7 +35273,7 @@
         <v>45877.87582175926</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35330,7 +35330,7 @@
         <v>45534.36645833333</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35387,7 +35387,7 @@
         <v>45880.49957175926</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35444,7 +35444,7 @@
         <v>45880.46642361111</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35501,7 +35501,7 @@
         <v>45253.73424768518</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35558,7 +35558,7 @@
         <v>45300</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35615,7 +35615,7 @@
         <v>45215.71418981482</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35672,7 +35672,7 @@
         <v>45392.58569444445</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35729,7 +35729,7 @@
         <v>44977.26300925926</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35786,7 +35786,7 @@
         <v>44540.57753472222</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35843,7 +35843,7 @@
         <v>45587</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35900,7 +35900,7 @@
         <v>44252</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35957,7 +35957,7 @@
         <v>44943.4652199074</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -36014,7 +36014,7 @@
         <v>44943.46980324074</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -36071,7 +36071,7 @@
         <v>45674.47359953704</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36128,7 +36128,7 @@
         <v>44867</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36185,7 +36185,7 @@
         <v>45477.38554398148</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36242,7 +36242,7 @@
         <v>45477.38663194444</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36299,7 +36299,7 @@
         <v>44904</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36356,7 +36356,7 @@
         <v>45882.43462962963</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36413,7 +36413,7 @@
         <v>45534.43841435185</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36470,7 +36470,7 @@
         <v>45839.71761574074</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36527,7 +36527,7 @@
         <v>45883.60416666666</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36584,7 +36584,7 @@
         <v>45622.35340277778</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36641,7 +36641,7 @@
         <v>45637.51090277778</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36698,7 +36698,7 @@
         <v>45112.3174074074</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36755,7 +36755,7 @@
         <v>45112</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36812,7 +36812,7 @@
         <v>44308.520625</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36869,7 +36869,7 @@
         <v>44930</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36926,7 +36926,7 @@
         <v>45701.37818287037</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36983,7 +36983,7 @@
         <v>45883.58956018519</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -37040,7 +37040,7 @@
         <v>45842.49457175926</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37097,7 +37097,7 @@
         <v>45842.5059375</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37154,7 +37154,7 @@
         <v>44575.80709490741</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37211,7 +37211,7 @@
         <v>45883.59239583334</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37268,7 +37268,7 @@
         <v>45883.60604166667</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37325,7 +37325,7 @@
         <v>44950</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37382,7 +37382,7 @@
         <v>44249</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37439,7 +37439,7 @@
         <v>44130</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37496,7 +37496,7 @@
         <v>44225</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37553,7 +37553,7 @@
         <v>44249.66673611111</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37610,7 +37610,7 @@
         <v>45842.49056712963</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37667,7 +37667,7 @@
         <v>45581.52885416667</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37724,7 +37724,7 @@
         <v>44113</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37781,7 +37781,7 @@
         <v>45363.91521990741</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37838,7 +37838,7 @@
         <v>45364.40862268519</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37895,7 +37895,7 @@
         <v>45302</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37952,7 +37952,7 @@
         <v>45841.71503472222</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -38009,7 +38009,7 @@
         <v>44966.52741898148</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -38071,7 +38071,7 @@
         <v>45841.4390625</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38128,7 +38128,7 @@
         <v>44175</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38185,7 +38185,7 @@
         <v>45630.70101851852</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38247,7 +38247,7 @@
         <v>45182.36129629629</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38304,7 +38304,7 @@
         <v>44988</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38361,7 +38361,7 @@
         <v>44893</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38418,7 +38418,7 @@
         <v>44082</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38475,7 +38475,7 @@
         <v>45600.48127314815</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38532,7 +38532,7 @@
         <v>45600.48347222222</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38589,7 +38589,7 @@
         <v>45547.43438657407</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38651,7 +38651,7 @@
         <v>45406.89568287037</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38708,7 +38708,7 @@
         <v>45406.89640046296</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38765,7 +38765,7 @@
         <v>44853</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38822,7 +38822,7 @@
         <v>44484</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38879,7 +38879,7 @@
         <v>45764.40184027778</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38936,7 +38936,7 @@
         <v>44949</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38993,7 +38993,7 @@
         <v>44648</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -39050,7 +39050,7 @@
         <v>44711</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39107,7 +39107,7 @@
         <v>44861.62300925926</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39164,7 +39164,7 @@
         <v>45201</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39221,7 +39221,7 @@
         <v>44938.53719907408</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39283,7 +39283,7 @@
         <v>44084.61673611111</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39340,7 +39340,7 @@
         <v>45375</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39397,7 +39397,7 @@
         <v>45180</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39454,7 +39454,7 @@
         <v>44998.8734837963</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39511,7 +39511,7 @@
         <v>44943.44811342593</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39568,7 +39568,7 @@
         <v>45547.84315972222</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39630,7 +39630,7 @@
         <v>44894</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39687,7 +39687,7 @@
         <v>44614.56209490741</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39744,7 +39744,7 @@
         <v>45763.49306712963</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39801,7 +39801,7 @@
         <v>44074</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39863,7 +39863,7 @@
         <v>44711</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39920,7 +39920,7 @@
         <v>45295.4037962963</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39982,7 +39982,7 @@
         <v>45671.44894675926</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -40039,7 +40039,7 @@
         <v>44622</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40096,7 +40096,7 @@
         <v>45617.4922337963</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40153,7 +40153,7 @@
         <v>45113.31806712963</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40210,7 +40210,7 @@
         <v>45435.51875</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40267,7 +40267,7 @@
         <v>45316</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40324,7 +40324,7 @@
         <v>45058</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40381,7 +40381,7 @@
         <v>45603.60537037037</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40438,7 +40438,7 @@
         <v>44173</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40495,7 +40495,7 @@
         <v>44662</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40552,7 +40552,7 @@
         <v>45184</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40609,7 +40609,7 @@
         <v>45623.4970949074</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40666,7 +40666,7 @@
         <v>44272</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40723,7 +40723,7 @@
         <v>44965</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40780,7 +40780,7 @@
         <v>45751.58130787037</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40837,7 +40837,7 @@
         <v>45706.69384259259</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40899,7 +40899,7 @@
         <v>45706.66618055556</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40961,7 +40961,7 @@
         <v>44734</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -41023,7 +41023,7 @@
         <v>45271</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -41080,7 +41080,7 @@
         <v>45671.44716435186</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41137,7 +41137,7 @@
         <v>44861.6108912037</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41194,7 +41194,7 @@
         <v>44861</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41251,7 +41251,7 @@
         <v>45643</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41308,7 +41308,7 @@
         <v>44211</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41365,7 +41365,7 @@
         <v>45015</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41422,7 +41422,7 @@
         <v>45617.91424768518</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41479,7 +41479,7 @@
         <v>45461.65380787037</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41536,7 +41536,7 @@
         <v>45630.39777777778</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41598,7 +41598,7 @@
         <v>45630.4022337963</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41660,7 +41660,7 @@
         <v>45541.36828703704</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41717,7 +41717,7 @@
         <v>45679.36950231482</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41774,7 +41774,7 @@
         <v>45043.43777777778</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41831,7 +41831,7 @@
         <v>44321</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41893,7 +41893,7 @@
         <v>45644.62803240741</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41950,7 +41950,7 @@
         <v>44897.3564699074</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -42012,7 +42012,7 @@
         <v>45210.34773148148</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -42069,7 +42069,7 @@
         <v>45455.40401620371</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42131,7 +42131,7 @@
         <v>44750</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42188,7 +42188,7 @@
         <v>45708.52121527777</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42245,7 +42245,7 @@
         <v>44507.43497685185</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42302,7 +42302,7 @@
         <v>44943.44532407408</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42359,7 +42359,7 @@
         <v>44943.48144675926</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42416,7 +42416,7 @@
         <v>45580.46572916667</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42473,7 +42473,7 @@
         <v>45642.60125</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42530,7 +42530,7 @@
         <v>45617.45760416667</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42587,7 +42587,7 @@
         <v>44963</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42644,7 +42644,7 @@
         <v>45770.51686342592</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42701,7 +42701,7 @@
         <v>45736</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42758,7 +42758,7 @@
         <v>44614</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42815,7 +42815,7 @@
         <v>45477.48915509259</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42872,7 +42872,7 @@
         <v>45408.67427083333</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42934,7 +42934,7 @@
         <v>45547.83519675926</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42996,7 +42996,7 @@
         <v>44158</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -43053,7 +43053,7 @@
         <v>45034</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43110,7 +43110,7 @@
         <v>44677</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43167,7 +43167,7 @@
         <v>44231</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43224,7 +43224,7 @@
         <v>45758</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43286,7 +43286,7 @@
         <v>45693</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43343,7 +43343,7 @@
         <v>44295.31922453704</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43400,7 +43400,7 @@
         <v>44729</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43457,7 +43457,7 @@
         <v>45470.6672337963</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43514,7 +43514,7 @@
         <v>44992.67101851852</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43591,7 +43591,7 @@
         <v>45469.43982638889</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43648,7 +43648,7 @@
         <v>44658</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43705,7 +43705,7 @@
         <v>45048</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43762,7 +43762,7 @@
         <v>45706.66388888889</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43824,7 +43824,7 @@
         <v>45706.67943287037</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43886,7 +43886,7 @@
         <v>44959.36028935185</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43948,7 +43948,7 @@
         <v>45149</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -44005,7 +44005,7 @@
         <v>45201</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -44062,7 +44062,7 @@
         <v>45726.42344907407</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -44124,7 +44124,7 @@
         <v>45051.37461805555</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44181,7 +44181,7 @@
         <v>44719.43577546296</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44238,7 +44238,7 @@
         <v>45035</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44295,7 +44295,7 @@
         <v>45764.4140162037</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44352,7 +44352,7 @@
         <v>44846.68375</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44409,7 +44409,7 @@
         <v>45130</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44466,7 +44466,7 @@
         <v>45188.3012037037</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44523,7 +44523,7 @@
         <v>44103</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44580,7 +44580,7 @@
         <v>45764.31284722222</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44637,7 +44637,7 @@
         <v>44803.44065972222</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44694,7 +44694,7 @@
         <v>44882</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44751,7 +44751,7 @@
         <v>45471.4034837963</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44808,7 +44808,7 @@
         <v>45621</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44865,7 +44865,7 @@
         <v>45182</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44922,7 +44922,7 @@
         <v>44137</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44979,7 +44979,7 @@
         <v>44063.68225694444</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -45036,7 +45036,7 @@
         <v>44977.26482638889</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -45093,7 +45093,7 @@
         <v>45708.50255787037</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45150,7 +45150,7 @@
         <v>45715.65605324074</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45207,7 +45207,7 @@
         <v>44998</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45264,7 +45264,7 @@
         <v>44077</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45321,7 +45321,7 @@
         <v>44627.41212962963</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45378,7 +45378,7 @@
         <v>45673.71842592592</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45435,7 +45435,7 @@
         <v>44985.35407407407</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45492,7 +45492,7 @@
         <v>45152</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45549,7 +45549,7 @@
         <v>45401</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45611,7 +45611,7 @@
         <v>45373.60802083334</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45668,7 +45668,7 @@
         <v>45127</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45725,7 +45725,7 @@
         <v>44967.6228125</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45782,7 +45782,7 @@
         <v>45605.84435185185</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45839,7 +45839,7 @@
         <v>45681.57619212963</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45896,7 +45896,7 @@
         <v>45682.47550925926</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45953,7 +45953,7 @@
         <v>45152</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -46010,7 +46010,7 @@
         <v>45092</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -46067,7 +46067,7 @@
         <v>45756</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46124,7 +46124,7 @@
         <v>45757.29700231482</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46181,7 +46181,7 @@
         <v>45615.90662037037</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46238,7 +46238,7 @@
         <v>44412.7071875</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46295,7 +46295,7 @@
         <v>44361</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46352,7 +46352,7 @@
         <v>44631</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46409,7 +46409,7 @@
         <v>45758</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46471,7 +46471,7 @@
         <v>45747.30204861111</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46528,7 +46528,7 @@
         <v>45567</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46585,7 +46585,7 @@
         <v>45628</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46642,7 +46642,7 @@
         <v>45630.6993287037</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46699,7 +46699,7 @@
         <v>45240</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46756,7 +46756,7 @@
         <v>45642.92393518519</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46813,7 +46813,7 @@
         <v>45272.42149305555</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46870,7 +46870,7 @@
         <v>44229</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46927,7 +46927,7 @@
         <v>45260.85619212963</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46984,7 +46984,7 @@
         <v>44735</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -47041,7 +47041,7 @@
         <v>44886.3340625</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47098,7 +47098,7 @@
         <v>45043.67869212963</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47155,7 +47155,7 @@
         <v>45751.5153125</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47217,7 +47217,7 @@
         <v>45012</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47274,7 +47274,7 @@
         <v>45300</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47331,7 +47331,7 @@
         <v>45751.62381944444</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47393,7 +47393,7 @@
         <v>45588</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47450,7 +47450,7 @@
         <v>45588</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47507,7 +47507,7 @@
         <v>44985</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47564,7 +47564,7 @@
         <v>44741.69432870371</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47621,7 +47621,7 @@
         <v>45099</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47678,7 +47678,7 @@
         <v>45363.45982638889</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47735,7 +47735,7 @@
         <v>44082</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47792,7 +47792,7 @@
         <v>45177.5462962963</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47849,7 +47849,7 @@
         <v>45223.65527777778</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47906,7 +47906,7 @@
         <v>45181</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47963,7 +47963,7 @@
         <v>45735.81920138889</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -48020,7 +48020,7 @@
         <v>45112</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -48077,7 +48077,7 @@
         <v>45775.4233912037</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48134,7 +48134,7 @@
         <v>45749.67842592593</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48191,7 +48191,7 @@
         <v>44840</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48248,7 +48248,7 @@
         <v>45252.58925925926</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48305,7 +48305,7 @@
         <v>44487</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48362,7 +48362,7 @@
         <v>45356.65395833334</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48424,7 +48424,7 @@
         <v>45587</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48481,7 +48481,7 @@
         <v>45107</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48538,7 +48538,7 @@
         <v>44588.50104166667</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48595,7 +48595,7 @@
         <v>44468</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48652,7 +48652,7 @@
         <v>44148</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48709,7 +48709,7 @@
         <v>45706.69090277778</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48771,7 +48771,7 @@
         <v>45747.44508101852</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48828,7 +48828,7 @@
         <v>45747.45177083334</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48885,7 +48885,7 @@
         <v>45757</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48942,7 +48942,7 @@
         <v>44979</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48999,7 +48999,7 @@
         <v>45201</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -49061,7 +49061,7 @@
         <v>45545.53883101852</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49118,7 +49118,7 @@
         <v>45169</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49175,7 +49175,7 @@
         <v>45468.44574074074</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49232,7 +49232,7 @@
         <v>45775.32407407407</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49289,7 +49289,7 @@
         <v>44904</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49351,7 +49351,7 @@
         <v>45597.53744212963</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49408,7 +49408,7 @@
         <v>45769.60440972223</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49465,7 +49465,7 @@
         <v>44433</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49522,7 +49522,7 @@
         <v>45037.67510416666</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49579,7 +49579,7 @@
         <v>45447.55340277778</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49636,7 +49636,7 @@
         <v>45644.62243055556</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49693,7 +49693,7 @@
         <v>44904.49826388889</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49750,7 +49750,7 @@
         <v>45079</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49807,7 +49807,7 @@
         <v>44904</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49864,7 +49864,7 @@
         <v>44151</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49921,7 +49921,7 @@
         <v>44923.55936342593</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49978,7 +49978,7 @@
         <v>45414</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -50035,7 +50035,7 @@
         <v>45377.42784722222</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50092,7 +50092,7 @@
         <v>45351.65180555556</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50154,7 +50154,7 @@
         <v>45764.30016203703</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50211,7 +50211,7 @@
         <v>44882</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50268,7 +50268,7 @@
         <v>45764.30391203704</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50325,7 +50325,7 @@
         <v>45617.48947916667</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50382,7 +50382,7 @@
         <v>45355.56604166667</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50439,7 +50439,7 @@
         <v>45324.64302083333</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50501,7 +50501,7 @@
         <v>45219</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50558,7 +50558,7 @@
         <v>45740.59871527777</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50615,7 +50615,7 @@
         <v>45477.33712962963</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50672,7 +50672,7 @@
         <v>45775.32163194445</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50729,7 +50729,7 @@
         <v>45406.89703703704</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50786,7 +50786,7 @@
         <v>45547.43793981482</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50848,7 +50848,7 @@
         <v>45183</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50905,7 +50905,7 @@
         <v>45056.6438425926</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -50962,7 +50962,7 @@
         <v>45757.30554398148</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -51019,7 +51019,7 @@
         <v>45755.70262731481</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -51076,7 +51076,7 @@
         <v>45201.59743055556</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -51133,7 +51133,7 @@
         <v>45761.41857638889</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -51190,7 +51190,7 @@
         <v>45492.70833333334</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -51247,7 +51247,7 @@
         <v>44483.58045138889</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -51304,7 +51304,7 @@
         <v>45566</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -51361,7 +51361,7 @@
         <v>45751.52445601852</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -51423,7 +51423,7 @@
         <v>45751.59875</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -51485,7 +51485,7 @@
         <v>45751.61236111111</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -51547,7 +51547,7 @@
         <v>45751.61556712963</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -51609,7 +51609,7 @@
         <v>45748</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -51671,7 +51671,7 @@
         <v>45092.42630787037</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -51728,7 +51728,7 @@
         <v>45446.56622685185</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -51785,7 +51785,7 @@
         <v>45049</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -51842,7 +51842,7 @@
         <v>45706.68554398148</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -51904,7 +51904,7 @@
         <v>45051</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -51961,7 +51961,7 @@
         <v>45645.88440972222</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -52018,7 +52018,7 @@
         <v>45734.59972222222</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45886</v>
+        <v>45887</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>

--- a/Översikt JÖNKÖPING.xlsx
+++ b/Översikt JÖNKÖPING.xlsx
@@ -567,7 +567,7 @@
         <v>45856.56684027778</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -665,7 +665,7 @@
         <v>45856.57200231482</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
         <v>45777</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>45609</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         <v>45348</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         <v>45275</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>45698.48634259259</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>44111</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>44083</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>44992</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>45846.47335648148</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>45788.88578703703</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>44530</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>44512.62668981482</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>44602</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>44974</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>45604.53402777778</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>45358.52763888889</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         <v>45539</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>45302</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         <v>45790.83706018519</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>45751.60517361111</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         <v>45679.98452546296</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2659,7 +2659,7 @@
         <v>45373.44148148148</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2745,7 +2745,7 @@
         <v>44991</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>44278</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>44419</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>44463</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>44095</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
         <v>44083</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3261,7 +3261,7 @@
         <v>44469</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3350,7 +3350,7 @@
         <v>44347.63069444444</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
         <v>44467</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3520,7 +3520,7 @@
         <v>45580.46207175926</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         <v>45569.41550925926</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
         <v>45295.3942824074</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         <v>44840</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
         <v>44404.71972222222</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>45302</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
         <v>45783</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4120,7 +4120,7 @@
         <v>45740.58743055556</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4205,7 +4205,7 @@
         <v>45587</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4290,7 +4290,7 @@
         <v>45856.55965277777</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         <v>45819.60131944445</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         <v>44879</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4553,7 +4553,7 @@
         <v>45876.69954861111</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4638,7 +4638,7 @@
         <v>45846</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>44943</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         <v>45758</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4907,7 +4907,7 @@
         <v>45343</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4992,7 +4992,7 @@
         <v>45841.4303125</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5077,7 +5077,7 @@
         <v>45538.45523148148</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5162,7 +5162,7 @@
         <v>45846</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>45616</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5336,7 +5336,7 @@
         <v>45205</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5421,7 +5421,7 @@
         <v>44260</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5478,7 +5478,7 @@
         <v>44188</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5535,7 +5535,7 @@
         <v>44147</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5592,7 +5592,7 @@
         <v>44137</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5649,7 +5649,7 @@
         <v>44306</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5706,7 +5706,7 @@
         <v>44308</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5768,7 +5768,7 @@
         <v>44066</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5825,7 +5825,7 @@
         <v>44144</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5882,7 +5882,7 @@
         <v>44239.33525462963</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5939,7 +5939,7 @@
         <v>44328.35063657408</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5996,7 +5996,7 @@
         <v>44496</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6053,7 +6053,7 @@
         <v>44278.3859375</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6110,7 +6110,7 @@
         <v>44575.80925925926</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6167,7 +6167,7 @@
         <v>44662</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6224,7 +6224,7 @@
         <v>44404.84280092592</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6281,7 +6281,7 @@
         <v>44404.84659722223</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6338,7 +6338,7 @@
         <v>44487</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6395,7 +6395,7 @@
         <v>44749.55936342593</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6452,7 +6452,7 @@
         <v>44749.55703703704</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6509,7 +6509,7 @@
         <v>44273.62572916667</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6566,7 +6566,7 @@
         <v>44454.35472222222</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6623,7 +6623,7 @@
         <v>44308</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6685,7 +6685,7 @@
         <v>44225</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6742,7 +6742,7 @@
         <v>44308</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6804,7 +6804,7 @@
         <v>44349</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6861,7 +6861,7 @@
         <v>44792.53711805555</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6918,7 +6918,7 @@
         <v>44411</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6975,7 +6975,7 @@
         <v>44194</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7032,7 +7032,7 @@
         <v>44225</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7089,7 +7089,7 @@
         <v>44809</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7146,7 +7146,7 @@
         <v>44442</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7203,7 +7203,7 @@
         <v>44487</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         <v>44487.49392361111</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         <v>44749.32716435185</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7374,7 +7374,7 @@
         <v>44420.68987268519</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7431,7 +7431,7 @@
         <v>44881.81052083334</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7488,7 +7488,7 @@
         <v>44404.84138888889</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         <v>44665.60081018518</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7602,7 +7602,7 @@
         <v>44266</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7659,7 +7659,7 @@
         <v>44869.49265046296</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         <v>44734</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         <v>44792</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7840,7 +7840,7 @@
         <v>44259</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7897,7 +7897,7 @@
         <v>44365</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7954,7 +7954,7 @@
         <v>44538</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
         <v>44263</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8073,7 +8073,7 @@
         <v>44487</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8130,7 +8130,7 @@
         <v>44487</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8187,7 +8187,7 @@
         <v>44113</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8244,7 +8244,7 @@
         <v>44272</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         <v>44875.59231481481</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8358,7 +8358,7 @@
         <v>44852.74376157407</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8420,7 +8420,7 @@
         <v>44292</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8477,7 +8477,7 @@
         <v>44200</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8534,7 +8534,7 @@
         <v>44498.56373842592</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8591,7 +8591,7 @@
         <v>44111</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8648,7 +8648,7 @@
         <v>44881.79847222222</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         <v>44286.34827546297</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8762,7 +8762,7 @@
         <v>44273</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8819,7 +8819,7 @@
         <v>44673</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8876,7 +8876,7 @@
         <v>44298.46462962963</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8938,7 +8938,7 @@
         <v>44298.46582175926</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9000,7 +9000,7 @@
         <v>44278.38752314815</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9057,7 +9057,7 @@
         <v>44279.37552083333</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         <v>44347.61920138889</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9171,7 +9171,7 @@
         <v>44754.47359953704</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9233,7 +9233,7 @@
         <v>44855.3080787037</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9290,7 +9290,7 @@
         <v>44476</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9347,7 +9347,7 @@
         <v>44373.75251157407</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9404,7 +9404,7 @@
         <v>44347.6287962963</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9461,7 +9461,7 @@
         <v>44511</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9518,7 +9518,7 @@
         <v>44466.4425</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9575,7 +9575,7 @@
         <v>44377</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9632,7 +9632,7 @@
         <v>44440.71997685185</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9689,7 +9689,7 @@
         <v>44840</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9746,7 +9746,7 @@
         <v>44104</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9803,7 +9803,7 @@
         <v>44280</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9860,7 +9860,7 @@
         <v>44613</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9917,7 +9917,7 @@
         <v>44456.46952546296</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9974,7 +9974,7 @@
         <v>44537</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10031,7 +10031,7 @@
         <v>44356</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10088,7 +10088,7 @@
         <v>44360</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10145,7 +10145,7 @@
         <v>44476</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10202,7 +10202,7 @@
         <v>44575</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10259,7 +10259,7 @@
         <v>44298.44060185185</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10321,7 +10321,7 @@
         <v>44711</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10378,7 +10378,7 @@
         <v>44659.57226851852</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10440,7 +10440,7 @@
         <v>44659</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10502,7 +10502,7 @@
         <v>44711</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10559,7 +10559,7 @@
         <v>44428.596875</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10621,7 +10621,7 @@
         <v>44819</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10678,7 +10678,7 @@
         <v>44819.28449074074</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10735,7 +10735,7 @@
         <v>44292</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10792,7 +10792,7 @@
         <v>44846.66688657407</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10849,7 +10849,7 @@
         <v>44605.44909722222</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10906,7 +10906,7 @@
         <v>44523.65311342593</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10963,7 +10963,7 @@
         <v>44454.4800925926</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11020,7 +11020,7 @@
         <v>44151</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11077,7 +11077,7 @@
         <v>44578</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11134,7 +11134,7 @@
         <v>44474.25150462963</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11191,7 +11191,7 @@
         <v>44596</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11248,7 +11248,7 @@
         <v>44344</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11305,7 +11305,7 @@
         <v>44498.57181712963</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11362,7 +11362,7 @@
         <v>44628</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11419,7 +11419,7 @@
         <v>44082.79793981482</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11476,7 +11476,7 @@
         <v>44082</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11533,7 +11533,7 @@
         <v>44711</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11590,7 +11590,7 @@
         <v>44711</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11647,7 +11647,7 @@
         <v>44841.31997685185</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11704,7 +11704,7 @@
         <v>44579.41064814815</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11761,7 +11761,7 @@
         <v>44467.68283564815</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11818,7 +11818,7 @@
         <v>44532.30398148148</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11875,7 +11875,7 @@
         <v>44428.34821759259</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11937,7 +11937,7 @@
         <v>44792.53936342592</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11994,7 +11994,7 @@
         <v>44557.71989583333</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12051,7 +12051,7 @@
         <v>44593</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12108,7 +12108,7 @@
         <v>44272</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12165,7 +12165,7 @@
         <v>44259</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12222,7 +12222,7 @@
         <v>44088</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12279,7 +12279,7 @@
         <v>44412</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12336,7 +12336,7 @@
         <v>44830.90146990741</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12393,7 +12393,7 @@
         <v>44787.80010416666</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12450,7 +12450,7 @@
         <v>44616.39256944445</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12507,7 +12507,7 @@
         <v>44373</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12564,7 +12564,7 @@
         <v>44239</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12621,7 +12621,7 @@
         <v>44239</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12678,7 +12678,7 @@
         <v>44464.40523148148</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12735,7 +12735,7 @@
         <v>44294</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12792,7 +12792,7 @@
         <v>44575</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12849,7 +12849,7 @@
         <v>44729</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12906,7 +12906,7 @@
         <v>44308</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12968,7 +12968,7 @@
         <v>44428.58511574074</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13030,7 +13030,7 @@
         <v>44825.40940972222</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13092,7 +13092,7 @@
         <v>44614</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13154,7 +13154,7 @@
         <v>44272</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13211,7 +13211,7 @@
         <v>44161.31023148148</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13268,7 +13268,7 @@
         <v>44585.30171296297</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13325,7 +13325,7 @@
         <v>44805</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13387,7 +13387,7 @@
         <v>44811</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13444,7 +13444,7 @@
         <v>44428</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13506,7 +13506,7 @@
         <v>44579</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13563,7 +13563,7 @@
         <v>44279.61517361111</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13620,7 +13620,7 @@
         <v>44074</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13677,7 +13677,7 @@
         <v>45586</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13734,7 +13734,7 @@
         <v>45630.39777777778</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13796,7 +13796,7 @@
         <v>45630.4022337963</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13858,7 +13858,7 @@
         <v>45735.81920138889</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13915,7 +13915,7 @@
         <v>44464.42415509259</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13972,7 +13972,7 @@
         <v>44488</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
         <v>44536</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14091,7 +14091,7 @@
         <v>44075</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14148,7 +14148,7 @@
         <v>45477.38181712963</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14205,7 +14205,7 @@
         <v>45600.47958333333</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14262,7 +14262,7 @@
         <v>45435</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14324,7 +14324,7 @@
         <v>44853</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14386,7 +14386,7 @@
         <v>45194</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14443,7 +14443,7 @@
         <v>44252</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14500,7 +14500,7 @@
         <v>45763.49306712963</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14557,7 +14557,7 @@
         <v>45643.47644675926</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14614,7 +14614,7 @@
         <v>44943.4652199074</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14671,7 +14671,7 @@
         <v>44943.46980324074</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14728,7 +14728,7 @@
         <v>45587.49814814814</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14785,7 +14785,7 @@
         <v>45435.51875</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14842,7 +14842,7 @@
         <v>44967.6228125</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14899,7 +14899,7 @@
         <v>44326</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14956,7 +14956,7 @@
         <v>44575.8194212963</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15013,7 +15013,7 @@
         <v>45252.58925925926</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15070,7 +15070,7 @@
         <v>44734</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15132,7 +15132,7 @@
         <v>45642.8053125</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15194,7 +15194,7 @@
         <v>45642.92393518519</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15251,7 +15251,7 @@
         <v>45272.42149305555</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15308,7 +15308,7 @@
         <v>45617.48947916667</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15365,7 +15365,7 @@
         <v>45720.70986111111</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15422,7 +15422,7 @@
         <v>44750</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15479,7 +15479,7 @@
         <v>45734.59972222222</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15536,7 +15536,7 @@
         <v>45747.30204861111</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15593,7 +15593,7 @@
         <v>45043.43777777778</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15650,7 +15650,7 @@
         <v>44411</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15707,7 +15707,7 @@
         <v>45533.46368055556</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15764,7 +15764,7 @@
         <v>45114.55280092593</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15821,7 +15821,7 @@
         <v>45628</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15883,7 +15883,7 @@
         <v>45764.30391203704</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15940,7 +15940,7 @@
         <v>44711</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15997,7 +15997,7 @@
         <v>45617.4922337963</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16054,7 +16054,7 @@
         <v>45469.43982638889</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16111,7 +16111,7 @@
         <v>45392.63664351852</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16168,7 +16168,7 @@
         <v>44979</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16225,7 +16225,7 @@
         <v>45706.66388888889</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16287,7 +16287,7 @@
         <v>45706.67943287037</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16349,7 +16349,7 @@
         <v>45701</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16406,7 +16406,7 @@
         <v>45643</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16463,7 +16463,7 @@
         <v>44249.66673611111</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16520,7 +16520,7 @@
         <v>44249</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16577,7 +16577,7 @@
         <v>45012</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16634,7 +16634,7 @@
         <v>45271</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16691,7 +16691,7 @@
         <v>44173</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16748,7 +16748,7 @@
         <v>45747.73295138889</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16805,7 +16805,7 @@
         <v>45404.58408564814</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16862,7 +16862,7 @@
         <v>45635.28104166667</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16919,7 +16919,7 @@
         <v>45764.42304398148</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16976,7 +16976,7 @@
         <v>45541</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17033,7 +17033,7 @@
         <v>45201</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17090,7 +17090,7 @@
         <v>45201.59743055556</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17147,7 +17147,7 @@
         <v>45341</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17204,7 +17204,7 @@
         <v>44950</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17261,7 +17261,7 @@
         <v>45099</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17318,7 +17318,7 @@
         <v>45697.26537037037</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17375,7 +17375,7 @@
         <v>45169</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17432,7 +17432,7 @@
         <v>45681.57949074074</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17489,7 +17489,7 @@
         <v>45048</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17546,7 +17546,7 @@
         <v>45605.84435185185</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17603,7 +17603,7 @@
         <v>45152</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17660,7 +17660,7 @@
         <v>45215.72212962963</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17717,7 +17717,7 @@
         <v>44803.44065972222</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17774,7 +17774,7 @@
         <v>45715.65605324074</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17831,7 +17831,7 @@
         <v>45673.71842592592</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17888,7 +17888,7 @@
         <v>44957.36059027778</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17945,7 +17945,7 @@
         <v>44589.73825231481</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18002,7 +18002,7 @@
         <v>45460.42804398148</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18059,7 +18059,7 @@
         <v>45145.47684027778</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18116,7 +18116,7 @@
         <v>45111</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18173,7 +18173,7 @@
         <v>44628</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18230,7 +18230,7 @@
         <v>45030</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18287,7 +18287,7 @@
         <v>44977.26482638889</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18344,7 +18344,7 @@
         <v>45706.69384259259</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18406,7 +18406,7 @@
         <v>45642.60125</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18463,7 +18463,7 @@
         <v>45034</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18520,7 +18520,7 @@
         <v>44468</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18577,7 +18577,7 @@
         <v>45750.40476851852</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18634,7 +18634,7 @@
         <v>45349</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18691,7 +18691,7 @@
         <v>44627.41212962963</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18748,7 +18748,7 @@
         <v>45056</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18805,7 +18805,7 @@
         <v>45770</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18862,7 +18862,7 @@
         <v>45182</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18919,7 +18919,7 @@
         <v>45764.53915509259</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18976,7 +18976,7 @@
         <v>45763.38354166667</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19053,7 +19053,7 @@
         <v>45763.49402777778</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19110,7 +19110,7 @@
         <v>45748</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19172,7 +19172,7 @@
         <v>45177</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19229,7 +19229,7 @@
         <v>45355.56604166667</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19286,7 +19286,7 @@
         <v>44084.61673611111</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19343,7 +19343,7 @@
         <v>45758</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19405,7 +19405,7 @@
         <v>44966.52741898148</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19467,7 +19467,7 @@
         <v>45307.72520833334</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19524,7 +19524,7 @@
         <v>45646.67994212963</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19581,7 +19581,7 @@
         <v>45184</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19638,7 +19638,7 @@
         <v>45169</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19695,7 +19695,7 @@
         <v>45012.47533564815</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19752,7 +19752,7 @@
         <v>44588.50104166667</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19809,7 +19809,7 @@
         <v>44488</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19866,7 +19866,7 @@
         <v>45169.38410879629</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19923,7 +19923,7 @@
         <v>45092.42630787037</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19980,7 +19980,7 @@
         <v>44704.65815972222</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20037,7 +20037,7 @@
         <v>44361</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20094,7 +20094,7 @@
         <v>45401</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20156,7 +20156,7 @@
         <v>45414</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20213,7 +20213,7 @@
         <v>45197</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20270,7 +20270,7 @@
         <v>45547.84315972222</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20332,7 +20332,7 @@
         <v>45693.67859953704</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20389,7 +20389,7 @@
         <v>45726.42344907407</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20451,7 +20451,7 @@
         <v>45405</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20508,7 +20508,7 @@
         <v>45405</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20565,7 +20565,7 @@
         <v>45621</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20622,7 +20622,7 @@
         <v>45758</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20684,7 +20684,7 @@
         <v>44943.44811342593</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20741,7 +20741,7 @@
         <v>45747.45038194444</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20798,7 +20798,7 @@
         <v>44998</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20855,7 +20855,7 @@
         <v>45547.43438657407</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20917,7 +20917,7 @@
         <v>45621.52488425926</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20974,7 +20974,7 @@
         <v>45621.5278125</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21031,7 +21031,7 @@
         <v>45436.68626157408</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21088,7 +21088,7 @@
         <v>45295.4037962963</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21150,7 +21150,7 @@
         <v>45392.58569444445</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21207,7 +21207,7 @@
         <v>45691.5603125</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21264,7 +21264,7 @@
         <v>45772.45813657407</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21321,7 +21321,7 @@
         <v>44897.3564699074</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21383,7 +21383,7 @@
         <v>44118</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21445,7 +21445,7 @@
         <v>45764.3996412037</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21502,7 +21502,7 @@
         <v>45764.42006944444</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21559,7 +21559,7 @@
         <v>45764.42517361111</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21616,7 +21616,7 @@
         <v>45545.65415509259</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21678,7 +21678,7 @@
         <v>44540.57753472222</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21735,7 +21735,7 @@
         <v>45198.41381944445</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21792,7 +21792,7 @@
         <v>45198.41887731481</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21849,7 +21849,7 @@
         <v>45198.60034722222</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21906,7 +21906,7 @@
         <v>45456.66137731481</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21963,7 +21963,7 @@
         <v>44557</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22020,7 +22020,7 @@
         <v>45056.6438425926</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22077,7 +22077,7 @@
         <v>44886.3340625</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22134,7 +22134,7 @@
         <v>44658</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22191,7 +22191,7 @@
         <v>45303.63494212963</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22253,7 +22253,7 @@
         <v>45645.57626157408</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22310,7 +22310,7 @@
         <v>45580.46572916667</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22367,7 +22367,7 @@
         <v>44550.30402777778</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22424,7 +22424,7 @@
         <v>45455.42533564815</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22486,7 +22486,7 @@
         <v>45130</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22543,7 +22543,7 @@
         <v>45477.33712962963</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22600,7 +22600,7 @@
         <v>45547.83519675926</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22662,7 +22662,7 @@
         <v>45112.3174074074</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22719,7 +22719,7 @@
         <v>45112</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22776,7 +22776,7 @@
         <v>44151</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22833,7 +22833,7 @@
         <v>45174</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22890,7 +22890,7 @@
         <v>45751.59875</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22952,7 +22952,7 @@
         <v>45557.35435185185</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23009,7 +23009,7 @@
         <v>45268</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23066,7 +23066,7 @@
         <v>45757.29700231482</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23123,7 +23123,7 @@
         <v>44614</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23180,7 +23180,7 @@
         <v>45406.89568287037</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23237,7 +23237,7 @@
         <v>45406.89640046296</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23294,7 +23294,7 @@
         <v>45462.38087962963</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23351,7 +23351,7 @@
         <v>44861.62300925926</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23408,7 +23408,7 @@
         <v>45747.45177083334</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23465,7 +23465,7 @@
         <v>45440.3712037037</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23522,7 +23522,7 @@
         <v>44252</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23579,7 +23579,7 @@
         <v>44172</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23636,7 +23636,7 @@
         <v>45216.47443287037</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23693,7 +23693,7 @@
         <v>44103</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23750,7 +23750,7 @@
         <v>45324.64302083333</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23812,7 +23812,7 @@
         <v>44938.53719907408</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23874,7 +23874,7 @@
         <v>45270.42966435185</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23931,7 +23931,7 @@
         <v>45777.50512731481</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23988,7 +23988,7 @@
         <v>45588</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24045,7 +24045,7 @@
         <v>45667.63950231481</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24102,7 +24102,7 @@
         <v>44943</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24159,7 +24159,7 @@
         <v>45179.9259375</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24216,7 +24216,7 @@
         <v>44273</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24273,7 +24273,7 @@
         <v>45777.60824074074</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24330,7 +24330,7 @@
         <v>44507.43497685185</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24387,7 +24387,7 @@
         <v>45775.4233912037</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24444,7 +24444,7 @@
         <v>45253.73424768518</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24501,7 +24501,7 @@
         <v>45331</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24558,7 +24558,7 @@
         <v>45184</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24615,7 +24615,7 @@
         <v>45751</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24677,7 +24677,7 @@
         <v>45755.70262731481</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24734,7 +24734,7 @@
         <v>44076</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24791,7 +24791,7 @@
         <v>45519.48550925926</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24848,7 +24848,7 @@
         <v>45618</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24905,7 +24905,7 @@
         <v>45534.43841435185</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24962,7 +24962,7 @@
         <v>44130</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25019,7 +25019,7 @@
         <v>45275</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25076,7 +25076,7 @@
         <v>45785.65899305556</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25133,7 +25133,7 @@
         <v>45586.62837962963</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25190,7 +25190,7 @@
         <v>44936</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25247,7 +25247,7 @@
         <v>45116.44680555556</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25304,7 +25304,7 @@
         <v>45538</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25361,7 +25361,7 @@
         <v>45788.3231712963</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25418,7 +25418,7 @@
         <v>45545.53883101852</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25475,7 +25475,7 @@
         <v>45630.70101851852</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25537,7 +25537,7 @@
         <v>44949</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25594,7 +25594,7 @@
         <v>45519.49606481481</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25651,7 +25651,7 @@
         <v>45302</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25708,7 +25708,7 @@
         <v>45300</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25765,7 +25765,7 @@
         <v>44482</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25822,7 +25822,7 @@
         <v>45412</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25884,7 +25884,7 @@
         <v>44662</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25941,7 +25941,7 @@
         <v>44904.49826388889</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25998,7 +25998,7 @@
         <v>45764.4140162037</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26055,7 +26055,7 @@
         <v>44904.59393518518</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26117,7 +26117,7 @@
         <v>44897</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26174,7 +26174,7 @@
         <v>44904.61212962963</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26236,7 +26236,7 @@
         <v>45788.32225694445</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26293,7 +26293,7 @@
         <v>45182.36129629629</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26350,7 +26350,7 @@
         <v>44861.6108912037</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26407,7 +26407,7 @@
         <v>44861</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26464,7 +26464,7 @@
         <v>45523.5090625</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26526,7 +26526,7 @@
         <v>45789.54226851852</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26583,7 +26583,7 @@
         <v>45267.62943287037</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26640,7 +26640,7 @@
         <v>45790.81799768518</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26697,7 +26697,7 @@
         <v>45149</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26754,7 +26754,7 @@
         <v>44943.44532407408</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26811,7 +26811,7 @@
         <v>45272</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26868,7 +26868,7 @@
         <v>44082</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26925,7 +26925,7 @@
         <v>45615.89965277778</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26982,7 +26982,7 @@
         <v>45615.90662037037</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27039,7 +27039,7 @@
         <v>45406</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27096,7 +27096,7 @@
         <v>45622.35340277778</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27153,7 +27153,7 @@
         <v>45523.58461805555</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27215,7 +27215,7 @@
         <v>45541.38644675926</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27272,7 +27272,7 @@
         <v>45646.39016203704</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27329,7 +27329,7 @@
         <v>45551.36004629629</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27386,7 +27386,7 @@
         <v>44231</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27443,7 +27443,7 @@
         <v>45350.56959490741</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27500,7 +27500,7 @@
         <v>45587</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27557,7 +27557,7 @@
         <v>45646.5796412037</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27614,7 +27614,7 @@
         <v>44187</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27676,7 +27676,7 @@
         <v>45205</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27733,7 +27733,7 @@
         <v>45790.82361111111</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27790,7 +27790,7 @@
         <v>45706.67424768519</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27852,7 +27852,7 @@
         <v>45791.85732638889</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27909,7 +27909,7 @@
         <v>44449</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27966,7 +27966,7 @@
         <v>44423.87825231482</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28023,7 +28023,7 @@
         <v>45281.57759259259</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28085,7 +28085,7 @@
         <v>44882</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28142,7 +28142,7 @@
         <v>45793</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28199,7 +28199,7 @@
         <v>44944.40825231482</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28256,7 +28256,7 @@
         <v>44225</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28313,7 +28313,7 @@
         <v>44614.68596064814</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28370,7 +28370,7 @@
         <v>44090</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28427,7 +28427,7 @@
         <v>44729</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28484,7 +28484,7 @@
         <v>45751.58130787037</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28541,7 +28541,7 @@
         <v>44137</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28598,7 +28598,7 @@
         <v>45570.58934027778</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28655,7 +28655,7 @@
         <v>45797.67148148148</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28712,7 +28712,7 @@
         <v>45183</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28769,7 +28769,7 @@
         <v>44648.61840277778</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28826,7 +28826,7 @@
         <v>45470.6672337963</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28883,7 +28883,7 @@
         <v>45177.5462962963</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28940,7 +28940,7 @@
         <v>44295.31922453704</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28997,7 +28997,7 @@
         <v>45769.60498842593</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29054,7 +29054,7 @@
         <v>44963</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29111,7 +29111,7 @@
         <v>45630.3944675926</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29173,7 +29173,7 @@
         <v>45373.60802083334</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29230,7 +29230,7 @@
         <v>44211</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29287,7 +29287,7 @@
         <v>44938</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29349,7 +29349,7 @@
         <v>45455.4374537037</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29411,7 +29411,7 @@
         <v>44571</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29468,7 +29468,7 @@
         <v>45588</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29525,7 +29525,7 @@
         <v>45539.34539351852</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29582,7 +29582,7 @@
         <v>44655.48328703704</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29639,7 +29639,7 @@
         <v>45687</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29696,7 +29696,7 @@
         <v>45687</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29753,7 +29753,7 @@
         <v>44592.28611111111</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29810,7 +29810,7 @@
         <v>45547.83950231481</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29872,7 +29872,7 @@
         <v>45769.43446759259</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29929,7 +29929,7 @@
         <v>44368.64017361111</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29986,7 +29986,7 @@
         <v>45741.65699074074</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30043,7 +30043,7 @@
         <v>45741.69303240741</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30100,7 +30100,7 @@
         <v>45755</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30157,7 +30157,7 @@
         <v>45727.35745370371</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30214,7 +30214,7 @@
         <v>45727.36243055556</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30271,7 +30271,7 @@
         <v>45734.3584837963</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30328,7 +30328,7 @@
         <v>45736</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30385,7 +30385,7 @@
         <v>45740.91412037037</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30442,7 +30442,7 @@
         <v>45730.44528935185</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30504,7 +30504,7 @@
         <v>45799.52318287037</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30561,7 +30561,7 @@
         <v>45730.3782175926</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30623,7 +30623,7 @@
         <v>45736</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30680,7 +30680,7 @@
         <v>45799.5803125</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30737,7 +30737,7 @@
         <v>45455.42981481482</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30799,7 +30799,7 @@
         <v>44839</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30861,7 +30861,7 @@
         <v>45092.39466435185</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30918,7 +30918,7 @@
         <v>44893</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30975,7 +30975,7 @@
         <v>45182.71081018518</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31032,7 +31032,7 @@
         <v>45461.65380787037</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31089,7 +31089,7 @@
         <v>44622</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31146,7 +31146,7 @@
         <v>44893</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31208,7 +31208,7 @@
         <v>45037.67510416666</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31265,7 +31265,7 @@
         <v>45600.48127314815</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31322,7 +31322,7 @@
         <v>45600.48347222222</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31379,7 +31379,7 @@
         <v>45701.37818287037</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31436,7 +31436,7 @@
         <v>45726.44835648148</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31493,7 +31493,7 @@
         <v>45363.91521990741</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31550,7 +31550,7 @@
         <v>45743.59641203703</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31607,7 +31607,7 @@
         <v>45736.67693287037</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31664,7 +31664,7 @@
         <v>45740.59474537037</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31721,7 +31721,7 @@
         <v>45215.71418981482</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31778,7 +31778,7 @@
         <v>45727.3134375</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31835,7 +31835,7 @@
         <v>45727.36650462963</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31892,7 +31892,7 @@
         <v>45314</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31949,7 +31949,7 @@
         <v>45799.58894675926</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32006,7 +32006,7 @@
         <v>45728</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32063,7 +32063,7 @@
         <v>45799.50469907407</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32120,7 +32120,7 @@
         <v>45735.65969907407</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32177,7 +32177,7 @@
         <v>45799.51578703704</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32234,7 +32234,7 @@
         <v>44484.49586805556</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32291,7 +32291,7 @@
         <v>45799.50931712963</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32348,7 +32348,7 @@
         <v>45735</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32405,7 +32405,7 @@
         <v>45737.67416666666</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32462,7 +32462,7 @@
         <v>45730.65831018519</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32519,7 +32519,7 @@
         <v>45734.35039351852</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32576,7 +32576,7 @@
         <v>45734.35122685185</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32633,7 +32633,7 @@
         <v>45726.52925925926</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32690,7 +32690,7 @@
         <v>45468.44574074074</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32747,7 +32747,7 @@
         <v>45371.60959490741</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32804,7 +32804,7 @@
         <v>45226.3731712963</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32861,7 +32861,7 @@
         <v>45624.41041666667</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32918,7 +32918,7 @@
         <v>44589.74348379629</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32975,7 +32975,7 @@
         <v>44578.52657407407</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33032,7 +33032,7 @@
         <v>45597.53744212963</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33089,7 +33089,7 @@
         <v>45803.48614583333</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33146,7 +33146,7 @@
         <v>44992.66236111111</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33203,7 +33203,7 @@
         <v>45587</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33260,7 +33260,7 @@
         <v>44804</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33317,7 +33317,7 @@
         <v>45043.67869212963</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33374,7 +33374,7 @@
         <v>45682.47550925926</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33431,7 +33431,7 @@
         <v>45733</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33488,7 +33488,7 @@
         <v>44977.26300925926</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33545,7 +33545,7 @@
         <v>45805</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33602,7 +33602,7 @@
         <v>45446.56622685185</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33659,7 +33659,7 @@
         <v>45804.31922453704</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33716,7 +33716,7 @@
         <v>45113.31806712963</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33773,7 +33773,7 @@
         <v>45805.60481481482</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33830,7 +33830,7 @@
         <v>45805.58372685185</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33887,7 +33887,7 @@
         <v>45804</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33944,7 +33944,7 @@
         <v>45805.58325231481</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34001,7 +34001,7 @@
         <v>45806.2833912037</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34058,7 +34058,7 @@
         <v>45806.28703703704</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34115,7 +34115,7 @@
         <v>45617.92190972222</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34172,7 +34172,7 @@
         <v>45806.26452546296</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34229,7 +34229,7 @@
         <v>45751.52445601852</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34291,7 +34291,7 @@
         <v>44585</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34348,7 +34348,7 @@
         <v>45152</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34405,7 +34405,7 @@
         <v>45597.43615740741</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34462,7 +34462,7 @@
         <v>45811</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34519,7 +34519,7 @@
         <v>45623.4970949074</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34576,7 +34576,7 @@
         <v>45701.38606481482</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34633,7 +34633,7 @@
         <v>45558.63807870371</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34695,7 +34695,7 @@
         <v>44992.67101851852</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34772,7 +34772,7 @@
         <v>45750.50650462963</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34829,7 +34829,7 @@
         <v>45701.31962962963</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34886,7 +34886,7 @@
         <v>45637.51090277778</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34943,7 +34943,7 @@
         <v>45351.65180555556</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35005,7 +35005,7 @@
         <v>45644.62803240741</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35062,7 +35062,7 @@
         <v>44433</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35119,7 +35119,7 @@
         <v>44846.68375</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35176,7 +35176,7 @@
         <v>45810</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35233,7 +35233,7 @@
         <v>44608</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35290,7 +35290,7 @@
         <v>45775.32407407407</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35347,7 +35347,7 @@
         <v>45502.32021990741</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35404,7 +35404,7 @@
         <v>44734</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35466,7 +35466,7 @@
         <v>44734</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35528,7 +35528,7 @@
         <v>44904</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35585,7 +35585,7 @@
         <v>44904</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35647,7 +35647,7 @@
         <v>44158</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35704,7 +35704,7 @@
         <v>45189</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35761,7 +35761,7 @@
         <v>45197.38018518518</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35818,7 +35818,7 @@
         <v>45321</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35875,7 +35875,7 @@
         <v>45043</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35932,7 +35932,7 @@
         <v>44507.82581018518</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35989,7 +35989,7 @@
         <v>45358</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36046,7 +36046,7 @@
         <v>45358.61696759259</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36103,7 +36103,7 @@
         <v>44308.520625</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36160,7 +36160,7 @@
         <v>44449</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36217,7 +36217,7 @@
         <v>45434.58377314815</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36274,7 +36274,7 @@
         <v>45294</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36336,7 +36336,7 @@
         <v>45372.34530092592</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36393,7 +36393,7 @@
         <v>45643.89232638889</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36450,7 +36450,7 @@
         <v>45079</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36507,7 +36507,7 @@
         <v>45545.59315972222</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36569,7 +36569,7 @@
         <v>44711</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36626,7 +36626,7 @@
         <v>45477.48771990741</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36683,7 +36683,7 @@
         <v>45477.48915509259</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36740,7 +36740,7 @@
         <v>45561.87885416667</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36797,7 +36797,7 @@
         <v>45299</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36854,7 +36854,7 @@
         <v>44998.8734837963</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36911,7 +36911,7 @@
         <v>45175.44625</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36968,7 +36968,7 @@
         <v>45035</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37025,7 +37025,7 @@
         <v>45118</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37082,7 +37082,7 @@
         <v>44950</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37139,7 +37139,7 @@
         <v>45861.46241898148</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37196,7 +37196,7 @@
         <v>45240</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37253,7 +37253,7 @@
         <v>44591</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37310,7 +37310,7 @@
         <v>44626</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37367,7 +37367,7 @@
         <v>45708.50255787037</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37424,7 +37424,7 @@
         <v>45211</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37481,7 +37481,7 @@
         <v>45112</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37538,7 +37538,7 @@
         <v>44082</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37595,7 +37595,7 @@
         <v>45246.50074074074</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37657,7 +37657,7 @@
         <v>45058</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37714,7 +37714,7 @@
         <v>45819.53688657407</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37771,7 +37771,7 @@
         <v>45819.53980324074</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37828,7 +37828,7 @@
         <v>45819.5429050926</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37885,7 +37885,7 @@
         <v>45860.54674768518</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37942,7 +37942,7 @@
         <v>45861.68065972222</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37999,7 +37999,7 @@
         <v>45679.36950231482</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38056,7 +38056,7 @@
         <v>45547.42313657407</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38118,7 +38118,7 @@
         <v>45119.54038194445</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38175,7 +38175,7 @@
         <v>45862.63645833333</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38232,7 +38232,7 @@
         <v>45375</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38289,7 +38289,7 @@
         <v>45566</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38346,7 +38346,7 @@
         <v>45566</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38403,7 +38403,7 @@
         <v>44109</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38460,7 +38460,7 @@
         <v>45541.36828703704</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38517,7 +38517,7 @@
         <v>44853</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38574,7 +38574,7 @@
         <v>45492.70833333334</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38631,7 +38631,7 @@
         <v>45867.66349537037</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38688,7 +38688,7 @@
         <v>45502.33179398148</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38745,7 +38745,7 @@
         <v>45674.47359953704</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38802,7 +38802,7 @@
         <v>44837</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38859,7 +38859,7 @@
         <v>45681.57619212963</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38916,7 +38916,7 @@
         <v>45562.38306712963</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38973,7 +38973,7 @@
         <v>45581.52885416667</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39030,7 +39030,7 @@
         <v>45477.38554398148</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39087,7 +39087,7 @@
         <v>45477.38663194444</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39144,7 +39144,7 @@
         <v>45210.34773148148</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39201,7 +39201,7 @@
         <v>44097</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39258,7 +39258,7 @@
         <v>45359.54100694445</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39315,7 +39315,7 @@
         <v>44614.56209490741</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39372,7 +39372,7 @@
         <v>45243</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39434,7 +39434,7 @@
         <v>45184</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39491,7 +39491,7 @@
         <v>45021</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39548,7 +39548,7 @@
         <v>45826</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39605,7 +39605,7 @@
         <v>45757</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39662,7 +39662,7 @@
         <v>44963.66563657407</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39719,7 +39719,7 @@
         <v>44083</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39776,7 +39776,7 @@
         <v>44935.37284722222</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39833,7 +39833,7 @@
         <v>44867</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39890,7 +39890,7 @@
         <v>45870.62930555556</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39952,7 +39952,7 @@
         <v>44355.60153935185</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40009,7 +40009,7 @@
         <v>45180</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40066,7 +40066,7 @@
         <v>44904</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40123,7 +40123,7 @@
         <v>44575.80709490741</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40180,7 +40180,7 @@
         <v>44950</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40237,7 +40237,7 @@
         <v>44950</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40294,7 +40294,7 @@
         <v>45831.51019675926</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40351,7 +40351,7 @@
         <v>45497</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40408,7 +40408,7 @@
         <v>45684</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40465,7 +40465,7 @@
         <v>44360.54226851852</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40522,7 +40522,7 @@
         <v>45833.65434027778</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40579,7 +40579,7 @@
         <v>45875.57328703703</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40641,7 +40641,7 @@
         <v>45875.60922453704</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40698,7 +40698,7 @@
         <v>45735.82282407407</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40755,7 +40755,7 @@
         <v>44930</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40812,7 +40812,7 @@
         <v>45531</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40869,7 +40869,7 @@
         <v>45833.63770833334</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40926,7 +40926,7 @@
         <v>45757.30554398148</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40983,7 +40983,7 @@
         <v>45462.37888888889</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41040,7 +41040,7 @@
         <v>45201</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41097,7 +41097,7 @@
         <v>45747.44508101852</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41154,7 +41154,7 @@
         <v>45547.53320601852</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41211,7 +41211,7 @@
         <v>45260.85619212963</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41268,7 +41268,7 @@
         <v>44325.76335648148</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41325,7 +41325,7 @@
         <v>45201.45827546297</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41382,7 +41382,7 @@
         <v>44719.43577546296</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41439,7 +41439,7 @@
         <v>45008</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41496,7 +41496,7 @@
         <v>45777.50238425926</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41553,7 +41553,7 @@
         <v>45335.76891203703</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41615,7 +41615,7 @@
         <v>45105.34402777778</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41672,7 +41672,7 @@
         <v>45092</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41729,7 +41729,7 @@
         <v>45474.70864583334</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41786,7 +41786,7 @@
         <v>44077</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41843,7 +41843,7 @@
         <v>45099.74195601852</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41900,7 +41900,7 @@
         <v>44321</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41962,7 +41962,7 @@
         <v>45271</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42019,7 +42019,7 @@
         <v>45124.59594907407</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42076,7 +42076,7 @@
         <v>44943.48144675926</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42133,7 +42133,7 @@
         <v>45759.5549537037</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42190,7 +42190,7 @@
         <v>45051</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42247,7 +42247,7 @@
         <v>45201</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42309,7 +42309,7 @@
         <v>44985</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42366,7 +42366,7 @@
         <v>44959.36028935185</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42428,7 +42428,7 @@
         <v>44487</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42485,7 +42485,7 @@
         <v>44229</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42542,7 +42542,7 @@
         <v>45877.87582175926</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42599,7 +42599,7 @@
         <v>45876.6799537037</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42656,7 +42656,7 @@
         <v>45245.46393518519</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42713,7 +42713,7 @@
         <v>45834.48820601852</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42770,7 +42770,7 @@
         <v>45107</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42827,7 +42827,7 @@
         <v>45408.67427083333</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42889,7 +42889,7 @@
         <v>45316</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42946,7 +42946,7 @@
         <v>45880.49957175926</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43003,7 +43003,7 @@
         <v>45764.40184027778</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43060,7 +43060,7 @@
         <v>45314</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43117,7 +43117,7 @@
         <v>45295.40646990741</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43179,7 +43179,7 @@
         <v>44631</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43236,7 +43236,7 @@
         <v>45880.43709490741</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43293,7 +43293,7 @@
         <v>45880.46642361111</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43350,7 +43350,7 @@
         <v>45552.48335648148</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43407,7 +43407,7 @@
         <v>45617.91424768518</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43464,7 +43464,7 @@
         <v>45839.71761574074</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43521,7 +43521,7 @@
         <v>45775.4219212963</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43578,7 +43578,7 @@
         <v>44113</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43635,7 +43635,7 @@
         <v>45534.36645833333</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43692,7 +43692,7 @@
         <v>45617.45760416667</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43749,7 +43749,7 @@
         <v>45700.60138888889</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43806,7 +43806,7 @@
         <v>44074</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43868,7 +43868,7 @@
         <v>45841.71503472222</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43925,7 +43925,7 @@
         <v>44564.8419212963</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43982,7 +43982,7 @@
         <v>45338.69246527777</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44044,7 +44044,7 @@
         <v>44483.58045138889</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44101,7 +44101,7 @@
         <v>45169</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44158,7 +44158,7 @@
         <v>45377.42784722222</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44215,7 +44215,7 @@
         <v>45219</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44272,7 +44272,7 @@
         <v>45679.98971064815</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44329,7 +44329,7 @@
         <v>45679.99299768519</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44386,7 +44386,7 @@
         <v>44261</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44443,7 +44443,7 @@
         <v>45882.43462962963</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44500,7 +44500,7 @@
         <v>45363.45982638889</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44557,7 +44557,7 @@
         <v>45841.4390625</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44614,7 +44614,7 @@
         <v>45240</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44671,7 +44671,7 @@
         <v>45883.58956018519</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44728,7 +44728,7 @@
         <v>45883.59239583334</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44785,7 +44785,7 @@
         <v>45883.60604166667</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44842,7 +44842,7 @@
         <v>45630.39188657407</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44904,7 +44904,7 @@
         <v>45769.60440972223</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44961,7 +44961,7 @@
         <v>44966.57471064815</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45023,7 +45023,7 @@
         <v>45645.88440972222</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45080,7 +45080,7 @@
         <v>45883.60416666666</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45137,7 +45137,7 @@
         <v>45194</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45194,7 +45194,7 @@
         <v>45194</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45251,7 +45251,7 @@
         <v>45112</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45308,7 +45308,7 @@
         <v>44148</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45365,7 +45365,7 @@
         <v>45107</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45422,7 +45422,7 @@
         <v>45756</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45479,7 +45479,7 @@
         <v>45681.48793981481</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45536,7 +45536,7 @@
         <v>44412.7071875</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45593,7 +45593,7 @@
         <v>45015</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45650,7 +45650,7 @@
         <v>44923.55936342593</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45707,7 +45707,7 @@
         <v>44904</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45764,7 +45764,7 @@
         <v>45049</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45821,7 +45821,7 @@
         <v>45338</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45883,7 +45883,7 @@
         <v>45764.31284722222</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45940,7 +45940,7 @@
         <v>45887.62158564815</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45997,7 +45997,7 @@
         <v>45887.62953703704</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46054,7 +46054,7 @@
         <v>44893</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46116,7 +46116,7 @@
         <v>45300</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46173,7 +46173,7 @@
         <v>45842.49056712963</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46230,7 +46230,7 @@
         <v>45887.68474537037</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46287,7 +46287,7 @@
         <v>45716.7125</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46344,7 +46344,7 @@
         <v>44894</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46401,7 +46401,7 @@
         <v>45797.56770833334</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46458,7 +46458,7 @@
         <v>45845.60700231481</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46515,7 +46515,7 @@
         <v>44090</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46572,7 +46572,7 @@
         <v>45842.49457175926</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46629,7 +46629,7 @@
         <v>45842.5059375</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46686,7 +46686,7 @@
         <v>45587.47273148148</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46743,7 +46743,7 @@
         <v>45630.6993287037</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46800,7 +46800,7 @@
         <v>44840</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46857,7 +46857,7 @@
         <v>44735</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46914,7 +46914,7 @@
         <v>44893.50922453704</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46976,7 +46976,7 @@
         <v>45846.73861111111</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47033,7 +47033,7 @@
         <v>44605.45792824074</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47090,7 +47090,7 @@
         <v>45887</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47147,7 +47147,7 @@
         <v>45764.53740740741</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47204,7 +47204,7 @@
         <v>45603.60537037037</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47261,7 +47261,7 @@
         <v>45197.61039351852</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47323,7 +47323,7 @@
         <v>45681.53460648148</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47380,7 +47380,7 @@
         <v>45406.89703703704</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47437,7 +47437,7 @@
         <v>45846.48190972222</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47494,7 +47494,7 @@
         <v>45884</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47551,7 +47551,7 @@
         <v>44985.35407407407</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47608,7 +47608,7 @@
         <v>45736</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47665,7 +47665,7 @@
         <v>45846</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47727,7 +47727,7 @@
         <v>45051.37461805555</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47784,7 +47784,7 @@
         <v>44659</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47846,7 +47846,7 @@
         <v>44484</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47903,7 +47903,7 @@
         <v>45846</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47965,7 +47965,7 @@
         <v>45628</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48022,7 +48022,7 @@
         <v>45770.51686342592</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48079,7 +48079,7 @@
         <v>45846</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48141,7 +48141,7 @@
         <v>45558.51949074074</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48203,7 +48203,7 @@
         <v>45758</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48265,7 +48265,7 @@
         <v>45706.66618055556</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48327,7 +48327,7 @@
         <v>45671.44716435186</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48384,7 +48384,7 @@
         <v>45705</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48441,7 +48441,7 @@
         <v>45870.62511574074</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48503,7 +48503,7 @@
         <v>45740.59871527777</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48560,7 +48560,7 @@
         <v>45455.40401620371</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48622,7 +48622,7 @@
         <v>45693</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48679,7 +48679,7 @@
         <v>45009</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48736,7 +48736,7 @@
         <v>44272</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48793,7 +48793,7 @@
         <v>44889</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48850,7 +48850,7 @@
         <v>45644.62243055556</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48907,7 +48907,7 @@
         <v>45127</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48964,7 +48964,7 @@
         <v>44853</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49021,7 +49021,7 @@
         <v>45401.34349537037</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49078,7 +49078,7 @@
         <v>44988</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49135,7 +49135,7 @@
         <v>45471.4034837963</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49192,7 +49192,7 @@
         <v>45198.59607638889</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49249,7 +49249,7 @@
         <v>44677</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49306,7 +49306,7 @@
         <v>45706.69090277778</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49368,7 +49368,7 @@
         <v>45756</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49425,7 +49425,7 @@
         <v>45764.30016203703</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49482,7 +49482,7 @@
         <v>44414</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49539,7 +49539,7 @@
         <v>45324.64579861111</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49601,7 +49601,7 @@
         <v>45324.64745370371</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49663,7 +49663,7 @@
         <v>45671.44894675926</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49720,7 +49720,7 @@
         <v>45414</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49777,7 +49777,7 @@
         <v>45761.49107638889</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49834,7 +49834,7 @@
         <v>45704</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49891,7 +49891,7 @@
         <v>45364.40862268519</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49948,7 +49948,7 @@
         <v>45567</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50005,7 +50005,7 @@
         <v>44741.69432870371</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50062,7 +50062,7 @@
         <v>45188.3012037037</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50119,7 +50119,7 @@
         <v>45356.65395833334</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50181,7 +50181,7 @@
         <v>45181</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50238,7 +50238,7 @@
         <v>44882</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50295,7 +50295,7 @@
         <v>45223.65527777778</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50352,7 +50352,7 @@
         <v>45547.43793981482</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50414,7 +50414,7 @@
         <v>44965</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50471,7 +50471,7 @@
         <v>45541.37402777778</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50528,7 +50528,7 @@
         <v>45708.52121527777</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50585,7 +50585,7 @@
         <v>45749.67842592593</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50642,7 +50642,7 @@
         <v>44648</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50699,7 +50699,7 @@
         <v>44175</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50756,7 +50756,7 @@
         <v>45447.55340277778</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50813,7 +50813,7 @@
         <v>45706.68554398148</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45892</v>
+        <v>45893</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>

--- a/Översikt JÖNKÖPING.xlsx
+++ b/Översikt JÖNKÖPING.xlsx
@@ -567,7 +567,7 @@
         <v>45856.56684027778</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -665,7 +665,7 @@
         <v>45856.57200231482</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
         <v>45777</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>45609</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         <v>45348</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         <v>45275</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1143,7 +1143,7 @@
         <v>45698.48634259259</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>44111</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>44083</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>44992</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>45846.47335648148</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1601,7 +1601,7 @@
         <v>45788.88578703703</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>44530</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>44512.62668981482</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>44602</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>44974</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>45604.53402777778</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>45358.52763888889</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         <v>45539</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>45302</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         <v>45790.83706018519</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>45751.60517361111</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2573,7 +2573,7 @@
         <v>45679.98452546296</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2659,7 +2659,7 @@
         <v>45373.44148148148</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2745,7 +2745,7 @@
         <v>44991</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2831,7 +2831,7 @@
         <v>44278</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2916,7 +2916,7 @@
         <v>44419</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3001,7 +3001,7 @@
         <v>44463</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3086,7 +3086,7 @@
         <v>44095</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
         <v>44083</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3261,7 +3261,7 @@
         <v>44469</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3350,7 +3350,7 @@
         <v>44347.63069444444</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3435,7 +3435,7 @@
         <v>44467</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3520,7 +3520,7 @@
         <v>45580.46207175926</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         <v>45569.41550925926</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
         <v>45295.3942824074</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3780,7 +3780,7 @@
         <v>44840</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3865,7 +3865,7 @@
         <v>44404.71972222222</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3950,7 +3950,7 @@
         <v>45302</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4035,7 +4035,7 @@
         <v>45783</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4120,7 +4120,7 @@
         <v>45740.58743055556</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4205,7 +4205,7 @@
         <v>45587</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4290,7 +4290,7 @@
         <v>45856.55965277777</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         <v>45819.60131944445</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         <v>44879</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4553,7 +4553,7 @@
         <v>45876.69954861111</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4638,7 +4638,7 @@
         <v>45846</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4732,7 +4732,7 @@
         <v>44943</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4817,7 +4817,7 @@
         <v>45758</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4907,7 +4907,7 @@
         <v>45343</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4992,7 +4992,7 @@
         <v>45841.4303125</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5077,7 +5077,7 @@
         <v>45538.45523148148</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5162,7 +5162,7 @@
         <v>45846</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5247,7 +5247,7 @@
         <v>45616</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5336,7 +5336,7 @@
         <v>45205</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5421,7 +5421,7 @@
         <v>44260</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5478,7 +5478,7 @@
         <v>44188</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5535,7 +5535,7 @@
         <v>44147</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5592,7 +5592,7 @@
         <v>44137</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5649,7 +5649,7 @@
         <v>44306</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5706,7 +5706,7 @@
         <v>44308</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5768,7 +5768,7 @@
         <v>44066</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5825,7 +5825,7 @@
         <v>44144</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5882,7 +5882,7 @@
         <v>44239.33525462963</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5939,7 +5939,7 @@
         <v>44328.35063657408</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5996,7 +5996,7 @@
         <v>44496</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6053,7 +6053,7 @@
         <v>44278.3859375</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6110,7 +6110,7 @@
         <v>44575.80925925926</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6167,7 +6167,7 @@
         <v>44662</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6224,7 +6224,7 @@
         <v>44404.84280092592</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6281,7 +6281,7 @@
         <v>44404.84659722223</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6338,7 +6338,7 @@
         <v>44487</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6395,7 +6395,7 @@
         <v>44749.55936342593</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6452,7 +6452,7 @@
         <v>44749.55703703704</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6509,7 +6509,7 @@
         <v>44273.62572916667</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6566,7 +6566,7 @@
         <v>44454.35472222222</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6623,7 +6623,7 @@
         <v>44308</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6685,7 +6685,7 @@
         <v>44225</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6742,7 +6742,7 @@
         <v>44308</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6804,7 +6804,7 @@
         <v>44349</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6861,7 +6861,7 @@
         <v>44792.53711805555</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6918,7 +6918,7 @@
         <v>44411</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6975,7 +6975,7 @@
         <v>44194</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7032,7 +7032,7 @@
         <v>44225</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7089,7 +7089,7 @@
         <v>44809</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7146,7 +7146,7 @@
         <v>44442</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7203,7 +7203,7 @@
         <v>44487</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7260,7 +7260,7 @@
         <v>44487.49392361111</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7317,7 +7317,7 @@
         <v>44749.32716435185</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7374,7 +7374,7 @@
         <v>44420.68987268519</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7431,7 +7431,7 @@
         <v>44881.81052083334</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7488,7 +7488,7 @@
         <v>44404.84138888889</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7545,7 +7545,7 @@
         <v>44665.60081018518</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7602,7 +7602,7 @@
         <v>44266</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7659,7 +7659,7 @@
         <v>44869.49265046296</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         <v>44734</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7783,7 +7783,7 @@
         <v>44792</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7840,7 +7840,7 @@
         <v>44259</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7897,7 +7897,7 @@
         <v>44365</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7954,7 +7954,7 @@
         <v>44538</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
         <v>44263</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8073,7 +8073,7 @@
         <v>44487</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8130,7 +8130,7 @@
         <v>44487</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8187,7 +8187,7 @@
         <v>44113</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8244,7 +8244,7 @@
         <v>44272</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8301,7 +8301,7 @@
         <v>44875.59231481481</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8358,7 +8358,7 @@
         <v>44852.74376157407</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8420,7 +8420,7 @@
         <v>44292</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8477,7 +8477,7 @@
         <v>44200</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8534,7 +8534,7 @@
         <v>44498.56373842592</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8591,7 +8591,7 @@
         <v>44111</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8648,7 +8648,7 @@
         <v>44881.79847222222</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8705,7 +8705,7 @@
         <v>44286.34827546297</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8762,7 +8762,7 @@
         <v>44273</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8819,7 +8819,7 @@
         <v>44673</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8876,7 +8876,7 @@
         <v>44298.46462962963</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8938,7 +8938,7 @@
         <v>44298.46582175926</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -9000,7 +9000,7 @@
         <v>44278.38752314815</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9057,7 +9057,7 @@
         <v>44279.37552083333</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         <v>44347.61920138889</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9171,7 +9171,7 @@
         <v>44754.47359953704</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9233,7 +9233,7 @@
         <v>44855.3080787037</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9290,7 +9290,7 @@
         <v>44476</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9347,7 +9347,7 @@
         <v>44373.75251157407</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9404,7 +9404,7 @@
         <v>44347.6287962963</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9461,7 +9461,7 @@
         <v>44511</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9518,7 +9518,7 @@
         <v>44466.4425</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9575,7 +9575,7 @@
         <v>44377</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9632,7 +9632,7 @@
         <v>44440.71997685185</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9689,7 +9689,7 @@
         <v>44840</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9746,7 +9746,7 @@
         <v>44104</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9803,7 +9803,7 @@
         <v>44280</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9860,7 +9860,7 @@
         <v>44613</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9917,7 +9917,7 @@
         <v>44456.46952546296</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9974,7 +9974,7 @@
         <v>44537</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10031,7 +10031,7 @@
         <v>44356</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10088,7 +10088,7 @@
         <v>44360</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10145,7 +10145,7 @@
         <v>44476</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10202,7 +10202,7 @@
         <v>44575</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10259,7 +10259,7 @@
         <v>44298.44060185185</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10321,7 +10321,7 @@
         <v>44711</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10378,7 +10378,7 @@
         <v>44659.57226851852</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10440,7 +10440,7 @@
         <v>44659</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10502,7 +10502,7 @@
         <v>44711</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10559,7 +10559,7 @@
         <v>44428.596875</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10621,7 +10621,7 @@
         <v>44819</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10678,7 +10678,7 @@
         <v>44819.28449074074</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10735,7 +10735,7 @@
         <v>44292</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10792,7 +10792,7 @@
         <v>44846.66688657407</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10849,7 +10849,7 @@
         <v>44605.44909722222</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10906,7 +10906,7 @@
         <v>44523.65311342593</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10963,7 +10963,7 @@
         <v>44454.4800925926</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11020,7 +11020,7 @@
         <v>44151</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11077,7 +11077,7 @@
         <v>44578</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11134,7 +11134,7 @@
         <v>44474.25150462963</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11191,7 +11191,7 @@
         <v>44596</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11248,7 +11248,7 @@
         <v>44344</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11305,7 +11305,7 @@
         <v>44498.57181712963</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11362,7 +11362,7 @@
         <v>44628</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11419,7 +11419,7 @@
         <v>44082.79793981482</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11476,7 +11476,7 @@
         <v>44082</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11533,7 +11533,7 @@
         <v>44711</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11590,7 +11590,7 @@
         <v>44711</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11647,7 +11647,7 @@
         <v>44841.31997685185</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11704,7 +11704,7 @@
         <v>44579.41064814815</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11761,7 +11761,7 @@
         <v>44467.68283564815</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11818,7 +11818,7 @@
         <v>44532.30398148148</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11875,7 +11875,7 @@
         <v>44428.34821759259</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11937,7 +11937,7 @@
         <v>44792.53936342592</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11994,7 +11994,7 @@
         <v>44557.71989583333</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12051,7 +12051,7 @@
         <v>44593</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12108,7 +12108,7 @@
         <v>44272</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12165,7 +12165,7 @@
         <v>44259</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12222,7 +12222,7 @@
         <v>44088</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12279,7 +12279,7 @@
         <v>44412</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12336,7 +12336,7 @@
         <v>44830.90146990741</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12393,7 +12393,7 @@
         <v>44787.80010416666</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12450,7 +12450,7 @@
         <v>44616.39256944445</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12507,7 +12507,7 @@
         <v>44373</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12564,7 +12564,7 @@
         <v>44239</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12621,7 +12621,7 @@
         <v>44239</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12678,7 +12678,7 @@
         <v>44464.40523148148</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12735,7 +12735,7 @@
         <v>44294</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12792,7 +12792,7 @@
         <v>44575</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12849,7 +12849,7 @@
         <v>44729</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12906,7 +12906,7 @@
         <v>44308</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12968,7 +12968,7 @@
         <v>44428.58511574074</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13030,7 +13030,7 @@
         <v>44825.40940972222</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13092,7 +13092,7 @@
         <v>44614</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13154,7 +13154,7 @@
         <v>44272</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13211,7 +13211,7 @@
         <v>44161.31023148148</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13268,7 +13268,7 @@
         <v>44585.30171296297</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13325,7 +13325,7 @@
         <v>44805</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13387,7 +13387,7 @@
         <v>44811</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13444,7 +13444,7 @@
         <v>44428</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13506,7 +13506,7 @@
         <v>44579</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13563,7 +13563,7 @@
         <v>44279.61517361111</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13620,7 +13620,7 @@
         <v>44074</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13677,7 +13677,7 @@
         <v>45586</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13734,7 +13734,7 @@
         <v>45630.39777777778</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13796,7 +13796,7 @@
         <v>45630.4022337963</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13858,7 +13858,7 @@
         <v>45735.81920138889</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13915,7 +13915,7 @@
         <v>44464.42415509259</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13972,7 +13972,7 @@
         <v>44488</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14029,7 +14029,7 @@
         <v>44536</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14091,7 +14091,7 @@
         <v>44075</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14148,7 +14148,7 @@
         <v>45477.38181712963</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14205,7 +14205,7 @@
         <v>45600.47958333333</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14262,7 +14262,7 @@
         <v>45435</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14324,7 +14324,7 @@
         <v>44853</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14386,7 +14386,7 @@
         <v>45194</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14443,7 +14443,7 @@
         <v>44252</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14500,7 +14500,7 @@
         <v>45763.49306712963</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14557,7 +14557,7 @@
         <v>45643.47644675926</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14614,7 +14614,7 @@
         <v>44943.4652199074</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14671,7 +14671,7 @@
         <v>44943.46980324074</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14728,7 +14728,7 @@
         <v>45587.49814814814</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14785,7 +14785,7 @@
         <v>45435.51875</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14842,7 +14842,7 @@
         <v>44967.6228125</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14899,7 +14899,7 @@
         <v>44326</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14956,7 +14956,7 @@
         <v>44575.8194212963</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -15013,7 +15013,7 @@
         <v>45252.58925925926</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15070,7 +15070,7 @@
         <v>44734</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15132,7 +15132,7 @@
         <v>45642.8053125</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15194,7 +15194,7 @@
         <v>45642.92393518519</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15251,7 +15251,7 @@
         <v>45272.42149305555</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15308,7 +15308,7 @@
         <v>45617.48947916667</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15365,7 +15365,7 @@
         <v>45720.70986111111</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15422,7 +15422,7 @@
         <v>44750</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15479,7 +15479,7 @@
         <v>45734.59972222222</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15536,7 +15536,7 @@
         <v>45747.30204861111</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15593,7 +15593,7 @@
         <v>45043.43777777778</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15650,7 +15650,7 @@
         <v>44411</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15707,7 +15707,7 @@
         <v>45533.46368055556</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15764,7 +15764,7 @@
         <v>45114.55280092593</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15821,7 +15821,7 @@
         <v>45628</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15883,7 +15883,7 @@
         <v>45764.30391203704</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15940,7 +15940,7 @@
         <v>44711</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15997,7 +15997,7 @@
         <v>45617.4922337963</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16054,7 +16054,7 @@
         <v>45469.43982638889</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16111,7 +16111,7 @@
         <v>45392.63664351852</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16168,7 +16168,7 @@
         <v>44979</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16225,7 +16225,7 @@
         <v>45706.66388888889</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16287,7 +16287,7 @@
         <v>45706.67943287037</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16349,7 +16349,7 @@
         <v>45701</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16406,7 +16406,7 @@
         <v>45643</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16463,7 +16463,7 @@
         <v>44249.66673611111</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16520,7 +16520,7 @@
         <v>44249</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16577,7 +16577,7 @@
         <v>45012</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16634,7 +16634,7 @@
         <v>45271</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16691,7 +16691,7 @@
         <v>44173</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16748,7 +16748,7 @@
         <v>45747.73295138889</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16805,7 +16805,7 @@
         <v>45404.58408564814</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16862,7 +16862,7 @@
         <v>45635.28104166667</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16919,7 +16919,7 @@
         <v>45764.42304398148</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16976,7 +16976,7 @@
         <v>45541</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17033,7 +17033,7 @@
         <v>45201</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17090,7 +17090,7 @@
         <v>45201.59743055556</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17147,7 +17147,7 @@
         <v>45341</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17204,7 +17204,7 @@
         <v>44950</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17261,7 +17261,7 @@
         <v>45099</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17318,7 +17318,7 @@
         <v>45697.26537037037</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17375,7 +17375,7 @@
         <v>45169</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17432,7 +17432,7 @@
         <v>45681.57949074074</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17489,7 +17489,7 @@
         <v>45048</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17546,7 +17546,7 @@
         <v>45605.84435185185</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17603,7 +17603,7 @@
         <v>45152</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17660,7 +17660,7 @@
         <v>45215.72212962963</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17717,7 +17717,7 @@
         <v>44803.44065972222</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17774,7 +17774,7 @@
         <v>45715.65605324074</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17831,7 +17831,7 @@
         <v>45673.71842592592</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17888,7 +17888,7 @@
         <v>44957.36059027778</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17945,7 +17945,7 @@
         <v>44589.73825231481</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18002,7 +18002,7 @@
         <v>45460.42804398148</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18059,7 +18059,7 @@
         <v>45145.47684027778</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18116,7 +18116,7 @@
         <v>45111</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18173,7 +18173,7 @@
         <v>44628</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18230,7 +18230,7 @@
         <v>45030</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18287,7 +18287,7 @@
         <v>44977.26482638889</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18344,7 +18344,7 @@
         <v>45706.69384259259</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18406,7 +18406,7 @@
         <v>45642.60125</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18463,7 +18463,7 @@
         <v>45034</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18520,7 +18520,7 @@
         <v>44468</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18577,7 +18577,7 @@
         <v>45750.40476851852</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18634,7 +18634,7 @@
         <v>45349</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18691,7 +18691,7 @@
         <v>44627.41212962963</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18748,7 +18748,7 @@
         <v>45056</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18805,7 +18805,7 @@
         <v>45770</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18862,7 +18862,7 @@
         <v>45182</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18919,7 +18919,7 @@
         <v>45764.53915509259</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18976,7 +18976,7 @@
         <v>45763.38354166667</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19053,7 +19053,7 @@
         <v>45763.49402777778</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19110,7 +19110,7 @@
         <v>45748</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19172,7 +19172,7 @@
         <v>45177</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19229,7 +19229,7 @@
         <v>45355.56604166667</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19286,7 +19286,7 @@
         <v>44084.61673611111</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19343,7 +19343,7 @@
         <v>45758</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19405,7 +19405,7 @@
         <v>44966.52741898148</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19467,7 +19467,7 @@
         <v>45307.72520833334</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19524,7 +19524,7 @@
         <v>45646.67994212963</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19581,7 +19581,7 @@
         <v>45184</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19638,7 +19638,7 @@
         <v>45169</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19695,7 +19695,7 @@
         <v>45012.47533564815</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19752,7 +19752,7 @@
         <v>44588.50104166667</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19809,7 +19809,7 @@
         <v>44488</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19866,7 +19866,7 @@
         <v>45169.38410879629</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19923,7 +19923,7 @@
         <v>45092.42630787037</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19980,7 +19980,7 @@
         <v>44704.65815972222</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20037,7 +20037,7 @@
         <v>44361</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20094,7 +20094,7 @@
         <v>45401</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20156,7 +20156,7 @@
         <v>45414</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20213,7 +20213,7 @@
         <v>45197</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20270,7 +20270,7 @@
         <v>45547.84315972222</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20332,7 +20332,7 @@
         <v>45693.67859953704</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20389,7 +20389,7 @@
         <v>45726.42344907407</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20451,7 +20451,7 @@
         <v>45405</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20508,7 +20508,7 @@
         <v>45405</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20565,7 +20565,7 @@
         <v>45621</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20622,7 +20622,7 @@
         <v>45758</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20684,7 +20684,7 @@
         <v>44943.44811342593</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20741,7 +20741,7 @@
         <v>45747.45038194444</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20798,7 +20798,7 @@
         <v>44998</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20855,7 +20855,7 @@
         <v>45547.43438657407</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20917,7 +20917,7 @@
         <v>45621.52488425926</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20974,7 +20974,7 @@
         <v>45621.5278125</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21031,7 +21031,7 @@
         <v>45436.68626157408</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21088,7 +21088,7 @@
         <v>45295.4037962963</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21150,7 +21150,7 @@
         <v>45392.58569444445</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21207,7 +21207,7 @@
         <v>45691.5603125</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21264,7 +21264,7 @@
         <v>45772.45813657407</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21321,7 +21321,7 @@
         <v>44897.3564699074</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21383,7 +21383,7 @@
         <v>44118</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21445,7 +21445,7 @@
         <v>45764.3996412037</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21502,7 +21502,7 @@
         <v>45764.42006944444</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21559,7 +21559,7 @@
         <v>45764.42517361111</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21616,7 +21616,7 @@
         <v>45545.65415509259</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21678,7 +21678,7 @@
         <v>44540.57753472222</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21735,7 +21735,7 @@
         <v>45198.41381944445</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21792,7 +21792,7 @@
         <v>45198.41887731481</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21849,7 +21849,7 @@
         <v>45198.60034722222</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21906,7 +21906,7 @@
         <v>45456.66137731481</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21963,7 +21963,7 @@
         <v>44557</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22020,7 +22020,7 @@
         <v>45056.6438425926</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22077,7 +22077,7 @@
         <v>44886.3340625</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22134,7 +22134,7 @@
         <v>44658</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22191,7 +22191,7 @@
         <v>45303.63494212963</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22253,7 +22253,7 @@
         <v>45645.57626157408</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22310,7 +22310,7 @@
         <v>45580.46572916667</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22367,7 +22367,7 @@
         <v>44550.30402777778</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22424,7 +22424,7 @@
         <v>45455.42533564815</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22486,7 +22486,7 @@
         <v>45130</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22543,7 +22543,7 @@
         <v>45477.33712962963</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22600,7 +22600,7 @@
         <v>45547.83519675926</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22662,7 +22662,7 @@
         <v>45112.3174074074</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22719,7 +22719,7 @@
         <v>45112</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22776,7 +22776,7 @@
         <v>44151</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22833,7 +22833,7 @@
         <v>45174</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22890,7 +22890,7 @@
         <v>45751.59875</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22952,7 +22952,7 @@
         <v>45557.35435185185</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -23009,7 +23009,7 @@
         <v>45268</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23066,7 +23066,7 @@
         <v>45757.29700231482</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23123,7 +23123,7 @@
         <v>44614</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23180,7 +23180,7 @@
         <v>45406.89568287037</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23237,7 +23237,7 @@
         <v>45406.89640046296</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23294,7 +23294,7 @@
         <v>45462.38087962963</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23351,7 +23351,7 @@
         <v>44861.62300925926</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23408,7 +23408,7 @@
         <v>45747.45177083334</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23465,7 +23465,7 @@
         <v>45440.3712037037</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23522,7 +23522,7 @@
         <v>44252</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23579,7 +23579,7 @@
         <v>44172</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23636,7 +23636,7 @@
         <v>45216.47443287037</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23693,7 +23693,7 @@
         <v>44103</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23750,7 +23750,7 @@
         <v>45324.64302083333</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23812,7 +23812,7 @@
         <v>44938.53719907408</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23874,7 +23874,7 @@
         <v>45270.42966435185</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23931,7 +23931,7 @@
         <v>45777.50512731481</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23988,7 +23988,7 @@
         <v>45588</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24045,7 +24045,7 @@
         <v>45667.63950231481</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24102,7 +24102,7 @@
         <v>44943</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24159,7 +24159,7 @@
         <v>45179.9259375</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24216,7 +24216,7 @@
         <v>44273</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24273,7 +24273,7 @@
         <v>45777.60824074074</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24330,7 +24330,7 @@
         <v>44507.43497685185</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24387,7 +24387,7 @@
         <v>45775.4233912037</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24444,7 +24444,7 @@
         <v>45253.73424768518</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24501,7 +24501,7 @@
         <v>45331</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24558,7 +24558,7 @@
         <v>45184</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24615,7 +24615,7 @@
         <v>45751</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24677,7 +24677,7 @@
         <v>45755.70262731481</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24734,7 +24734,7 @@
         <v>44076</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24791,7 +24791,7 @@
         <v>45519.48550925926</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24848,7 +24848,7 @@
         <v>45618</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24905,7 +24905,7 @@
         <v>45534.43841435185</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24962,7 +24962,7 @@
         <v>44130</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -25019,7 +25019,7 @@
         <v>45275</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25076,7 +25076,7 @@
         <v>45785.65899305556</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25133,7 +25133,7 @@
         <v>45586.62837962963</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25190,7 +25190,7 @@
         <v>44936</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25247,7 +25247,7 @@
         <v>45116.44680555556</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25304,7 +25304,7 @@
         <v>45538</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25361,7 +25361,7 @@
         <v>45788.3231712963</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25418,7 +25418,7 @@
         <v>45545.53883101852</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25475,7 +25475,7 @@
         <v>45630.70101851852</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25537,7 +25537,7 @@
         <v>44949</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25594,7 +25594,7 @@
         <v>45519.49606481481</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25651,7 +25651,7 @@
         <v>45302</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25708,7 +25708,7 @@
         <v>45300</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25765,7 +25765,7 @@
         <v>44482</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25822,7 +25822,7 @@
         <v>45412</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25884,7 +25884,7 @@
         <v>44662</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25941,7 +25941,7 @@
         <v>44904.49826388889</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25998,7 +25998,7 @@
         <v>45764.4140162037</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26055,7 +26055,7 @@
         <v>44904.59393518518</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26117,7 +26117,7 @@
         <v>44897</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26174,7 +26174,7 @@
         <v>44904.61212962963</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26236,7 +26236,7 @@
         <v>45788.32225694445</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26293,7 +26293,7 @@
         <v>45182.36129629629</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26350,7 +26350,7 @@
         <v>44861.6108912037</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26407,7 +26407,7 @@
         <v>44861</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26464,7 +26464,7 @@
         <v>45523.5090625</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26526,7 +26526,7 @@
         <v>45789.54226851852</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26583,7 +26583,7 @@
         <v>45267.62943287037</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26640,7 +26640,7 @@
         <v>45790.81799768518</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26697,7 +26697,7 @@
         <v>45149</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26754,7 +26754,7 @@
         <v>44943.44532407408</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26811,7 +26811,7 @@
         <v>45272</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26868,7 +26868,7 @@
         <v>44082</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26925,7 +26925,7 @@
         <v>45615.89965277778</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26982,7 +26982,7 @@
         <v>45615.90662037037</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27039,7 +27039,7 @@
         <v>45406</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27096,7 +27096,7 @@
         <v>45622.35340277778</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27153,7 +27153,7 @@
         <v>45523.58461805555</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27215,7 +27215,7 @@
         <v>45541.38644675926</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27272,7 +27272,7 @@
         <v>45646.39016203704</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27329,7 +27329,7 @@
         <v>45551.36004629629</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27386,7 +27386,7 @@
         <v>44231</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27443,7 +27443,7 @@
         <v>45350.56959490741</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27500,7 +27500,7 @@
         <v>45587</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27557,7 +27557,7 @@
         <v>45646.5796412037</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27614,7 +27614,7 @@
         <v>44187</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27676,7 +27676,7 @@
         <v>45205</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27733,7 +27733,7 @@
         <v>45790.82361111111</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27790,7 +27790,7 @@
         <v>45706.67424768519</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27852,7 +27852,7 @@
         <v>45791.85732638889</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27909,7 +27909,7 @@
         <v>44449</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27966,7 +27966,7 @@
         <v>44423.87825231482</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -28023,7 +28023,7 @@
         <v>45281.57759259259</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28085,7 +28085,7 @@
         <v>44882</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28142,7 +28142,7 @@
         <v>45793</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28199,7 +28199,7 @@
         <v>44944.40825231482</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28256,7 +28256,7 @@
         <v>44225</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28313,7 +28313,7 @@
         <v>44614.68596064814</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28370,7 +28370,7 @@
         <v>44090</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28427,7 +28427,7 @@
         <v>44729</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28484,7 +28484,7 @@
         <v>45751.58130787037</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28541,7 +28541,7 @@
         <v>44137</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28598,7 +28598,7 @@
         <v>45570.58934027778</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28655,7 +28655,7 @@
         <v>45797.67148148148</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28712,7 +28712,7 @@
         <v>45183</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28769,7 +28769,7 @@
         <v>44648.61840277778</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28826,7 +28826,7 @@
         <v>45470.6672337963</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28883,7 +28883,7 @@
         <v>45177.5462962963</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28940,7 +28940,7 @@
         <v>44295.31922453704</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28997,7 +28997,7 @@
         <v>45769.60498842593</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29054,7 +29054,7 @@
         <v>44963</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29111,7 +29111,7 @@
         <v>45630.3944675926</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29173,7 +29173,7 @@
         <v>45373.60802083334</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29230,7 +29230,7 @@
         <v>44211</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29287,7 +29287,7 @@
         <v>44938</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29349,7 +29349,7 @@
         <v>45455.4374537037</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29411,7 +29411,7 @@
         <v>44571</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29468,7 +29468,7 @@
         <v>45588</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29525,7 +29525,7 @@
         <v>45539.34539351852</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29582,7 +29582,7 @@
         <v>44655.48328703704</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29639,7 +29639,7 @@
         <v>45687</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29696,7 +29696,7 @@
         <v>45687</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29753,7 +29753,7 @@
         <v>44592.28611111111</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29810,7 +29810,7 @@
         <v>45547.83950231481</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29872,7 +29872,7 @@
         <v>45769.43446759259</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29929,7 +29929,7 @@
         <v>44368.64017361111</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29986,7 +29986,7 @@
         <v>45741.65699074074</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -30043,7 +30043,7 @@
         <v>45741.69303240741</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30100,7 +30100,7 @@
         <v>45755</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30157,7 +30157,7 @@
         <v>45727.35745370371</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30214,7 +30214,7 @@
         <v>45727.36243055556</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30271,7 +30271,7 @@
         <v>45734.3584837963</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30328,7 +30328,7 @@
         <v>45736</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30385,7 +30385,7 @@
         <v>45740.91412037037</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30442,7 +30442,7 @@
         <v>45730.44528935185</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30504,7 +30504,7 @@
         <v>45799.52318287037</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30561,7 +30561,7 @@
         <v>45730.3782175926</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30623,7 +30623,7 @@
         <v>45736</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30680,7 +30680,7 @@
         <v>45799.5803125</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30737,7 +30737,7 @@
         <v>45455.42981481482</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30799,7 +30799,7 @@
         <v>44839</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30861,7 +30861,7 @@
         <v>45092.39466435185</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30918,7 +30918,7 @@
         <v>44893</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30975,7 +30975,7 @@
         <v>45182.71081018518</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -31032,7 +31032,7 @@
         <v>45461.65380787037</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31089,7 +31089,7 @@
         <v>44622</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31146,7 +31146,7 @@
         <v>44893</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31208,7 +31208,7 @@
         <v>45037.67510416666</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31265,7 +31265,7 @@
         <v>45600.48127314815</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31322,7 +31322,7 @@
         <v>45600.48347222222</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31379,7 +31379,7 @@
         <v>45701.37818287037</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31436,7 +31436,7 @@
         <v>45726.44835648148</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31493,7 +31493,7 @@
         <v>45363.91521990741</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31550,7 +31550,7 @@
         <v>45743.59641203703</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31607,7 +31607,7 @@
         <v>45736.67693287037</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31664,7 +31664,7 @@
         <v>45740.59474537037</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31721,7 +31721,7 @@
         <v>45215.71418981482</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31778,7 +31778,7 @@
         <v>45727.3134375</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31835,7 +31835,7 @@
         <v>45727.36650462963</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31892,7 +31892,7 @@
         <v>45314</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31949,7 +31949,7 @@
         <v>45799.58894675926</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -32006,7 +32006,7 @@
         <v>45728</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32063,7 +32063,7 @@
         <v>45799.50469907407</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32120,7 +32120,7 @@
         <v>45735.65969907407</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32177,7 +32177,7 @@
         <v>45799.51578703704</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32234,7 +32234,7 @@
         <v>44484.49586805556</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32291,7 +32291,7 @@
         <v>45799.50931712963</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32348,7 +32348,7 @@
         <v>45735</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32405,7 +32405,7 @@
         <v>45737.67416666666</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32462,7 +32462,7 @@
         <v>45730.65831018519</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32519,7 +32519,7 @@
         <v>45734.35039351852</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32576,7 +32576,7 @@
         <v>45734.35122685185</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32633,7 +32633,7 @@
         <v>45726.52925925926</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32690,7 +32690,7 @@
         <v>45468.44574074074</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32747,7 +32747,7 @@
         <v>45371.60959490741</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32804,7 +32804,7 @@
         <v>45226.3731712963</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32861,7 +32861,7 @@
         <v>45624.41041666667</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32918,7 +32918,7 @@
         <v>44589.74348379629</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32975,7 +32975,7 @@
         <v>44578.52657407407</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33032,7 +33032,7 @@
         <v>45597.53744212963</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33089,7 +33089,7 @@
         <v>45803.48614583333</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33146,7 +33146,7 @@
         <v>44992.66236111111</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33203,7 +33203,7 @@
         <v>45587</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33260,7 +33260,7 @@
         <v>44804</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33317,7 +33317,7 @@
         <v>45043.67869212963</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33374,7 +33374,7 @@
         <v>45682.47550925926</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33431,7 +33431,7 @@
         <v>45733</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33488,7 +33488,7 @@
         <v>44977.26300925926</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33545,7 +33545,7 @@
         <v>45805</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33602,7 +33602,7 @@
         <v>45446.56622685185</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33659,7 +33659,7 @@
         <v>45804.31922453704</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33716,7 +33716,7 @@
         <v>45113.31806712963</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33773,7 +33773,7 @@
         <v>45805.60481481482</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33830,7 +33830,7 @@
         <v>45805.58372685185</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33887,7 +33887,7 @@
         <v>45804</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33944,7 +33944,7 @@
         <v>45805.58325231481</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -34001,7 +34001,7 @@
         <v>45806.2833912037</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34058,7 +34058,7 @@
         <v>45806.28703703704</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34115,7 +34115,7 @@
         <v>45617.92190972222</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34172,7 +34172,7 @@
         <v>45806.26452546296</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34229,7 +34229,7 @@
         <v>45751.52445601852</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34291,7 +34291,7 @@
         <v>44585</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34348,7 +34348,7 @@
         <v>45152</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34405,7 +34405,7 @@
         <v>45597.43615740741</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34462,7 +34462,7 @@
         <v>45811</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34519,7 +34519,7 @@
         <v>45623.4970949074</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34576,7 +34576,7 @@
         <v>45701.38606481482</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34633,7 +34633,7 @@
         <v>45558.63807870371</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34695,7 +34695,7 @@
         <v>44992.67101851852</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34772,7 +34772,7 @@
         <v>45750.50650462963</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34829,7 +34829,7 @@
         <v>45701.31962962963</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34886,7 +34886,7 @@
         <v>45637.51090277778</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34943,7 +34943,7 @@
         <v>45351.65180555556</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -35005,7 +35005,7 @@
         <v>45644.62803240741</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35062,7 +35062,7 @@
         <v>44433</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35119,7 +35119,7 @@
         <v>44846.68375</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35176,7 +35176,7 @@
         <v>45810</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35233,7 +35233,7 @@
         <v>44608</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35290,7 +35290,7 @@
         <v>45775.32407407407</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35347,7 +35347,7 @@
         <v>45502.32021990741</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35404,7 +35404,7 @@
         <v>44734</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35466,7 +35466,7 @@
         <v>44734</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35528,7 +35528,7 @@
         <v>44904</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35585,7 +35585,7 @@
         <v>44904</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35647,7 +35647,7 @@
         <v>44158</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35704,7 +35704,7 @@
         <v>45189</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35761,7 +35761,7 @@
         <v>45197.38018518518</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35818,7 +35818,7 @@
         <v>45321</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35875,7 +35875,7 @@
         <v>45043</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35932,7 +35932,7 @@
         <v>44507.82581018518</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35989,7 +35989,7 @@
         <v>45358</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36046,7 +36046,7 @@
         <v>45358.61696759259</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36103,7 +36103,7 @@
         <v>44308.520625</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36160,7 +36160,7 @@
         <v>44449</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36217,7 +36217,7 @@
         <v>45434.58377314815</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36274,7 +36274,7 @@
         <v>45294</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36336,7 +36336,7 @@
         <v>45372.34530092592</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36393,7 +36393,7 @@
         <v>45643.89232638889</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36450,7 +36450,7 @@
         <v>45079</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36507,7 +36507,7 @@
         <v>45545.59315972222</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36569,7 +36569,7 @@
         <v>44711</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36626,7 +36626,7 @@
         <v>45477.48771990741</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36683,7 +36683,7 @@
         <v>45477.48915509259</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36740,7 +36740,7 @@
         <v>45561.87885416667</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36797,7 +36797,7 @@
         <v>45299</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36854,7 +36854,7 @@
         <v>44998.8734837963</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36911,7 +36911,7 @@
         <v>45175.44625</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36968,7 +36968,7 @@
         <v>45035</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37025,7 +37025,7 @@
         <v>45118</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37082,7 +37082,7 @@
         <v>44950</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37139,7 +37139,7 @@
         <v>45861.46241898148</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37196,7 +37196,7 @@
         <v>45240</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37253,7 +37253,7 @@
         <v>44591</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37310,7 +37310,7 @@
         <v>44626</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37367,7 +37367,7 @@
         <v>45708.50255787037</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37424,7 +37424,7 @@
         <v>45211</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37481,7 +37481,7 @@
         <v>45112</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37538,7 +37538,7 @@
         <v>44082</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37595,7 +37595,7 @@
         <v>45246.50074074074</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37657,7 +37657,7 @@
         <v>45058</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37714,7 +37714,7 @@
         <v>45819.53688657407</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37771,7 +37771,7 @@
         <v>45819.53980324074</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37828,7 +37828,7 @@
         <v>45819.5429050926</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37885,7 +37885,7 @@
         <v>45860.54674768518</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37942,7 +37942,7 @@
         <v>45861.68065972222</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37999,7 +37999,7 @@
         <v>45679.36950231482</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38056,7 +38056,7 @@
         <v>45547.42313657407</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38118,7 +38118,7 @@
         <v>45119.54038194445</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38175,7 +38175,7 @@
         <v>45862.63645833333</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38232,7 +38232,7 @@
         <v>45375</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38289,7 +38289,7 @@
         <v>45566</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38346,7 +38346,7 @@
         <v>45566</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38403,7 +38403,7 @@
         <v>44109</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38460,7 +38460,7 @@
         <v>45541.36828703704</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38517,7 +38517,7 @@
         <v>44853</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38574,7 +38574,7 @@
         <v>45492.70833333334</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38631,7 +38631,7 @@
         <v>45867.66349537037</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38688,7 +38688,7 @@
         <v>45502.33179398148</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38745,7 +38745,7 @@
         <v>45674.47359953704</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38802,7 +38802,7 @@
         <v>44837</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38859,7 +38859,7 @@
         <v>45681.57619212963</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38916,7 +38916,7 @@
         <v>45562.38306712963</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38973,7 +38973,7 @@
         <v>45581.52885416667</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39030,7 +39030,7 @@
         <v>45477.38554398148</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39087,7 +39087,7 @@
         <v>45477.38663194444</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39144,7 +39144,7 @@
         <v>45210.34773148148</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39201,7 +39201,7 @@
         <v>44097</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39258,7 +39258,7 @@
         <v>45359.54100694445</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39315,7 +39315,7 @@
         <v>44614.56209490741</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39372,7 +39372,7 @@
         <v>45243</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39434,7 +39434,7 @@
         <v>45184</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39491,7 +39491,7 @@
         <v>45021</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39548,7 +39548,7 @@
         <v>45826</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39605,7 +39605,7 @@
         <v>45757</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39662,7 +39662,7 @@
         <v>44963.66563657407</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39719,7 +39719,7 @@
         <v>44083</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39776,7 +39776,7 @@
         <v>44935.37284722222</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39833,7 +39833,7 @@
         <v>44867</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39890,7 +39890,7 @@
         <v>45870.62930555556</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39952,7 +39952,7 @@
         <v>44355.60153935185</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40009,7 +40009,7 @@
         <v>45180</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40066,7 +40066,7 @@
         <v>44904</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40123,7 +40123,7 @@
         <v>44575.80709490741</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40180,7 +40180,7 @@
         <v>44950</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40237,7 +40237,7 @@
         <v>44950</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40294,7 +40294,7 @@
         <v>45831.51019675926</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40351,7 +40351,7 @@
         <v>45497</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40408,7 +40408,7 @@
         <v>45684</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40465,7 +40465,7 @@
         <v>44360.54226851852</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40522,7 +40522,7 @@
         <v>45833.65434027778</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40579,7 +40579,7 @@
         <v>45875.57328703703</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40641,7 +40641,7 @@
         <v>45875.60922453704</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40698,7 +40698,7 @@
         <v>45735.82282407407</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40755,7 +40755,7 @@
         <v>44930</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40812,7 +40812,7 @@
         <v>45531</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40869,7 +40869,7 @@
         <v>45833.63770833334</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40926,7 +40926,7 @@
         <v>45757.30554398148</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40983,7 +40983,7 @@
         <v>45462.37888888889</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41040,7 +41040,7 @@
         <v>45201</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41097,7 +41097,7 @@
         <v>45747.44508101852</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41154,7 +41154,7 @@
         <v>45547.53320601852</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41211,7 +41211,7 @@
         <v>45260.85619212963</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41268,7 +41268,7 @@
         <v>44325.76335648148</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41325,7 +41325,7 @@
         <v>45201.45827546297</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41382,7 +41382,7 @@
         <v>44719.43577546296</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41439,7 +41439,7 @@
         <v>45008</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41496,7 +41496,7 @@
         <v>45777.50238425926</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41553,7 +41553,7 @@
         <v>45335.76891203703</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41615,7 +41615,7 @@
         <v>45105.34402777778</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41672,7 +41672,7 @@
         <v>45092</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41729,7 +41729,7 @@
         <v>45474.70864583334</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41786,7 +41786,7 @@
         <v>44077</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41843,7 +41843,7 @@
         <v>45099.74195601852</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41900,7 +41900,7 @@
         <v>44321</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41962,7 +41962,7 @@
         <v>45271</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42019,7 +42019,7 @@
         <v>45124.59594907407</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42076,7 +42076,7 @@
         <v>44943.48144675926</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42133,7 +42133,7 @@
         <v>45759.5549537037</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42190,7 +42190,7 @@
         <v>45051</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42247,7 +42247,7 @@
         <v>45201</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42309,7 +42309,7 @@
         <v>44985</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42366,7 +42366,7 @@
         <v>44959.36028935185</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42428,7 +42428,7 @@
         <v>44487</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42485,7 +42485,7 @@
         <v>44229</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42542,7 +42542,7 @@
         <v>45877.87582175926</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42599,7 +42599,7 @@
         <v>45876.6799537037</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42656,7 +42656,7 @@
         <v>45245.46393518519</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42713,7 +42713,7 @@
         <v>45834.48820601852</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42770,7 +42770,7 @@
         <v>45107</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42827,7 +42827,7 @@
         <v>45408.67427083333</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42889,7 +42889,7 @@
         <v>45316</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42946,7 +42946,7 @@
         <v>45880.49957175926</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -43003,7 +43003,7 @@
         <v>45764.40184027778</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43060,7 +43060,7 @@
         <v>45314</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43117,7 +43117,7 @@
         <v>45295.40646990741</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43179,7 +43179,7 @@
         <v>44631</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43236,7 +43236,7 @@
         <v>45880.43709490741</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43293,7 +43293,7 @@
         <v>45880.46642361111</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43350,7 +43350,7 @@
         <v>45552.48335648148</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43407,7 +43407,7 @@
         <v>45617.91424768518</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43464,7 +43464,7 @@
         <v>45839.71761574074</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43521,7 +43521,7 @@
         <v>45775.4219212963</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43578,7 +43578,7 @@
         <v>44113</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43635,7 +43635,7 @@
         <v>45534.36645833333</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43692,7 +43692,7 @@
         <v>45617.45760416667</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43749,7 +43749,7 @@
         <v>45700.60138888889</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43806,7 +43806,7 @@
         <v>44074</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43868,7 +43868,7 @@
         <v>45841.71503472222</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43925,7 +43925,7 @@
         <v>44564.8419212963</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43982,7 +43982,7 @@
         <v>45338.69246527777</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44044,7 +44044,7 @@
         <v>44483.58045138889</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44101,7 +44101,7 @@
         <v>45169</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44158,7 +44158,7 @@
         <v>45377.42784722222</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44215,7 +44215,7 @@
         <v>45219</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44272,7 +44272,7 @@
         <v>45679.98971064815</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44329,7 +44329,7 @@
         <v>45679.99299768519</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44386,7 +44386,7 @@
         <v>44261</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44443,7 +44443,7 @@
         <v>45882.43462962963</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44500,7 +44500,7 @@
         <v>45363.45982638889</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44557,7 +44557,7 @@
         <v>45841.4390625</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44614,7 +44614,7 @@
         <v>45240</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44671,7 +44671,7 @@
         <v>45883.58956018519</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44728,7 +44728,7 @@
         <v>45883.59239583334</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44785,7 +44785,7 @@
         <v>45883.60604166667</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44842,7 +44842,7 @@
         <v>45630.39188657407</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44904,7 +44904,7 @@
         <v>45769.60440972223</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44961,7 +44961,7 @@
         <v>44966.57471064815</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45023,7 +45023,7 @@
         <v>45645.88440972222</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45080,7 +45080,7 @@
         <v>45883.60416666666</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45137,7 +45137,7 @@
         <v>45194</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45194,7 +45194,7 @@
         <v>45194</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45251,7 +45251,7 @@
         <v>45112</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45308,7 +45308,7 @@
         <v>44148</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45365,7 +45365,7 @@
         <v>45107</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45422,7 +45422,7 @@
         <v>45756</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45479,7 +45479,7 @@
         <v>45681.48793981481</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45536,7 +45536,7 @@
         <v>44412.7071875</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45593,7 +45593,7 @@
         <v>45015</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45650,7 +45650,7 @@
         <v>44923.55936342593</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45707,7 +45707,7 @@
         <v>44904</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45764,7 +45764,7 @@
         <v>45049</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45821,7 +45821,7 @@
         <v>45338</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45883,7 +45883,7 @@
         <v>45764.31284722222</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45940,7 +45940,7 @@
         <v>45887.62158564815</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45997,7 +45997,7 @@
         <v>45887.62953703704</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46054,7 +46054,7 @@
         <v>44893</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46116,7 +46116,7 @@
         <v>45300</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46173,7 +46173,7 @@
         <v>45842.49056712963</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46230,7 +46230,7 @@
         <v>45887.68474537037</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46287,7 +46287,7 @@
         <v>45716.7125</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46344,7 +46344,7 @@
         <v>44894</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46401,7 +46401,7 @@
         <v>45797.56770833334</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46458,7 +46458,7 @@
         <v>45845.60700231481</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46515,7 +46515,7 @@
         <v>44090</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46572,7 +46572,7 @@
         <v>45842.49457175926</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46629,7 +46629,7 @@
         <v>45842.5059375</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46686,7 +46686,7 @@
         <v>45587.47273148148</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46743,7 +46743,7 @@
         <v>45630.6993287037</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46800,7 +46800,7 @@
         <v>44840</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46857,7 +46857,7 @@
         <v>44735</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46914,7 +46914,7 @@
         <v>44893.50922453704</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46976,7 +46976,7 @@
         <v>45846.73861111111</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47033,7 +47033,7 @@
         <v>44605.45792824074</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47090,7 +47090,7 @@
         <v>45887</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47147,7 +47147,7 @@
         <v>45764.53740740741</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47204,7 +47204,7 @@
         <v>45603.60537037037</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47261,7 +47261,7 @@
         <v>45197.61039351852</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47323,7 +47323,7 @@
         <v>45681.53460648148</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47380,7 +47380,7 @@
         <v>45406.89703703704</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47437,7 +47437,7 @@
         <v>45846.48190972222</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47494,7 +47494,7 @@
         <v>45884</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47551,7 +47551,7 @@
         <v>44985.35407407407</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47608,7 +47608,7 @@
         <v>45736</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47665,7 +47665,7 @@
         <v>45846</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47727,7 +47727,7 @@
         <v>45051.37461805555</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47784,7 +47784,7 @@
         <v>44659</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47846,7 +47846,7 @@
         <v>44484</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47903,7 +47903,7 @@
         <v>45846</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47965,7 +47965,7 @@
         <v>45628</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48022,7 +48022,7 @@
         <v>45770.51686342592</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48079,7 +48079,7 @@
         <v>45846</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48141,7 +48141,7 @@
         <v>45558.51949074074</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48203,7 +48203,7 @@
         <v>45758</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48265,7 +48265,7 @@
         <v>45706.66618055556</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48327,7 +48327,7 @@
         <v>45671.44716435186</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48384,7 +48384,7 @@
         <v>45705</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48441,7 +48441,7 @@
         <v>45870.62511574074</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48503,7 +48503,7 @@
         <v>45740.59871527777</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48560,7 +48560,7 @@
         <v>45455.40401620371</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48622,7 +48622,7 @@
         <v>45693</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48679,7 +48679,7 @@
         <v>45009</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48736,7 +48736,7 @@
         <v>44272</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48793,7 +48793,7 @@
         <v>44889</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48850,7 +48850,7 @@
         <v>45644.62243055556</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48907,7 +48907,7 @@
         <v>45127</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48964,7 +48964,7 @@
         <v>44853</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49021,7 +49021,7 @@
         <v>45401.34349537037</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49078,7 +49078,7 @@
         <v>44988</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49135,7 +49135,7 @@
         <v>45471.4034837963</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49192,7 +49192,7 @@
         <v>45198.59607638889</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49249,7 +49249,7 @@
         <v>44677</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49306,7 +49306,7 @@
         <v>45706.69090277778</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49368,7 +49368,7 @@
         <v>45756</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49425,7 +49425,7 @@
         <v>45764.30016203703</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49482,7 +49482,7 @@
         <v>44414</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49539,7 +49539,7 @@
         <v>45324.64579861111</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49601,7 +49601,7 @@
         <v>45324.64745370371</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49663,7 +49663,7 @@
         <v>45671.44894675926</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49720,7 +49720,7 @@
         <v>45414</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49777,7 +49777,7 @@
         <v>45761.49107638889</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49834,7 +49834,7 @@
         <v>45704</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49891,7 +49891,7 @@
         <v>45364.40862268519</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49948,7 +49948,7 @@
         <v>45567</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -50005,7 +50005,7 @@
         <v>44741.69432870371</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50062,7 +50062,7 @@
         <v>45188.3012037037</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50119,7 +50119,7 @@
         <v>45356.65395833334</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50181,7 +50181,7 @@
         <v>45181</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50238,7 +50238,7 @@
         <v>44882</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50295,7 +50295,7 @@
         <v>45223.65527777778</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50352,7 +50352,7 @@
         <v>45547.43793981482</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50414,7 +50414,7 @@
         <v>44965</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50471,7 +50471,7 @@
         <v>45541.37402777778</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50528,7 +50528,7 @@
         <v>45708.52121527777</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -50585,7 +50585,7 @@
         <v>45749.67842592593</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -50642,7 +50642,7 @@
         <v>44648</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -50699,7 +50699,7 @@
         <v>44175</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -50756,7 +50756,7 @@
         <v>45447.55340277778</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -50813,7 +50813,7 @@
         <v>45706.68554398148</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45893</v>
+        <v>45894</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>

--- a/Översikt JÖNKÖPING.xlsx
+++ b/Översikt JÖNKÖPING.xlsx
@@ -567,7 +567,7 @@
         <v>45856.56684027778</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -665,7 +665,7 @@
         <v>45856.57200231482</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
         <v>45777</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>45609</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         <v>45348</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         <v>44111</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>45275</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>45698.48634259259</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>44083</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>45846.47335648148</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>45788.88578703703</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>44992</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>44530</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>44512.62668981482</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>44602</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>45604.53402777778</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>44974</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>45373.44148148148</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         <v>45790.83706018519</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>45679.98452546296</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         <v>45358.52763888889</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>45898.45456018519</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         <v>45302</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>44991</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>45539</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>44278</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>44419</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2996,7 +2996,7 @@
         <v>44463</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
         <v>44095</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3166,7 +3166,7 @@
         <v>44083</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
         <v>44347.63069444444</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         <v>44467</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         <v>44469</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3515,7 +3515,7 @@
         <v>44404.71972222222</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>45783</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
         <v>44840</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3770,7 +3770,7 @@
         <v>45740.58743055556</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         <v>45587</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3940,7 +3940,7 @@
         <v>45819.60131944445</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         <v>45758</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         <v>45580.46207175926</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         <v>45846</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>45876.69954861111</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         <v>45295.3942824074</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4469,7 +4469,7 @@
         <v>45343</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
         <v>45302</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         <v>45841.4303125</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>45846</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         <v>45616</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4898,7 +4898,7 @@
         <v>45538.45523148148</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4983,7 +4983,7 @@
         <v>44879</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5072,7 +5072,7 @@
         <v>45856.55965277777</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
         <v>45205</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5246,7 +5246,7 @@
         <v>45569.41550925926</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         <v>44943</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5416,7 +5416,7 @@
         <v>44260</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5473,7 +5473,7 @@
         <v>44188</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5530,7 +5530,7 @@
         <v>44137</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5587,7 +5587,7 @@
         <v>44147</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5644,7 +5644,7 @@
         <v>44306</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5701,7 +5701,7 @@
         <v>44308</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5763,7 +5763,7 @@
         <v>44144</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5820,7 +5820,7 @@
         <v>44328.35063657408</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5877,7 +5877,7 @@
         <v>44239.33525462963</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         <v>44496</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5991,7 +5991,7 @@
         <v>44404.84280092592</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6048,7 +6048,7 @@
         <v>44404.84659722223</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6105,7 +6105,7 @@
         <v>44278.3859375</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6162,7 +6162,7 @@
         <v>44575.80925925926</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6219,7 +6219,7 @@
         <v>44662</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         <v>44487</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         <v>44749.55936342593</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6390,7 +6390,7 @@
         <v>44749.55703703704</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6447,7 +6447,7 @@
         <v>44273.62572916667</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6504,7 +6504,7 @@
         <v>44454.35472222222</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         <v>44308</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6623,7 +6623,7 @@
         <v>44225</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6680,7 +6680,7 @@
         <v>44308</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6742,7 +6742,7 @@
         <v>44349</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6799,7 +6799,7 @@
         <v>44792.53711805555</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6856,7 +6856,7 @@
         <v>44411</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6913,7 +6913,7 @@
         <v>44194</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6970,7 +6970,7 @@
         <v>44225</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7027,7 +7027,7 @@
         <v>44809</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7084,7 +7084,7 @@
         <v>44442</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         <v>44487.49392361111</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7198,7 +7198,7 @@
         <v>44487</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7255,7 +7255,7 @@
         <v>44749.32716435185</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7312,7 +7312,7 @@
         <v>44420.68987268519</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7369,7 +7369,7 @@
         <v>44404.84138888889</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7426,7 +7426,7 @@
         <v>44266</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7483,7 +7483,7 @@
         <v>44881.81052083334</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7540,7 +7540,7 @@
         <v>44665.60081018518</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
         <v>44869.49265046296</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7659,7 +7659,7 @@
         <v>44734</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         <v>44792</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7778,7 +7778,7 @@
         <v>44259</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
         <v>44365</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7892,7 +7892,7 @@
         <v>44538</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
         <v>44263</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
         <v>44113</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8068,7 +8068,7 @@
         <v>44487</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         <v>44487</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8182,7 +8182,7 @@
         <v>44272</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8239,7 +8239,7 @@
         <v>44875.59231481481</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8296,7 +8296,7 @@
         <v>44852.74376157407</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8358,7 +8358,7 @@
         <v>44292</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8415,7 +8415,7 @@
         <v>44200</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8472,7 +8472,7 @@
         <v>44498.56373842592</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         <v>44111</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8586,7 +8586,7 @@
         <v>44881.79847222222</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8643,7 +8643,7 @@
         <v>44286.34827546297</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8700,7 +8700,7 @@
         <v>44673</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8757,7 +8757,7 @@
         <v>44273</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8814,7 +8814,7 @@
         <v>44298.46462962963</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8876,7 +8876,7 @@
         <v>44298.46582175926</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8938,7 +8938,7 @@
         <v>44278.38752314815</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8995,7 +8995,7 @@
         <v>44279.37552083333</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9052,7 +9052,7 @@
         <v>44347.61920138889</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         <v>44754.47359953704</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9171,7 +9171,7 @@
         <v>44855.3080787037</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9228,7 +9228,7 @@
         <v>44476</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         <v>44373.75251157407</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9342,7 +9342,7 @@
         <v>44347.6287962963</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9399,7 +9399,7 @@
         <v>44511</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9456,7 +9456,7 @@
         <v>44466.4425</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9513,7 +9513,7 @@
         <v>44377</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9570,7 +9570,7 @@
         <v>44440.71997685185</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9627,7 +9627,7 @@
         <v>44840</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9684,7 +9684,7 @@
         <v>44104</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9741,7 +9741,7 @@
         <v>44280</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9798,7 +9798,7 @@
         <v>44613</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9855,7 +9855,7 @@
         <v>44456.46952546296</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9912,7 +9912,7 @@
         <v>44537</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9969,7 +9969,7 @@
         <v>44356</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         <v>44360</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10083,7 +10083,7 @@
         <v>44476</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10140,7 +10140,7 @@
         <v>44575</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10197,7 +10197,7 @@
         <v>44298.44060185185</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10259,7 +10259,7 @@
         <v>44711</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10316,7 +10316,7 @@
         <v>44659.57226851852</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10378,7 +10378,7 @@
         <v>44659</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10440,7 +10440,7 @@
         <v>44454.4800925926</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10497,7 +10497,7 @@
         <v>44578</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10554,7 +10554,7 @@
         <v>44344</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10611,7 +10611,7 @@
         <v>44474.25150462963</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10668,7 +10668,7 @@
         <v>44628</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10725,7 +10725,7 @@
         <v>44596</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10782,7 +10782,7 @@
         <v>44711</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10839,7 +10839,7 @@
         <v>44711</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10896,7 +10896,7 @@
         <v>44498.57181712963</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10953,7 +10953,7 @@
         <v>44082.79793981482</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11010,7 +11010,7 @@
         <v>44082</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11067,7 +11067,7 @@
         <v>44841.31997685185</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11124,7 +11124,7 @@
         <v>44579.41064814815</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11181,7 +11181,7 @@
         <v>44467.68283564815</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11238,7 +11238,7 @@
         <v>44557.71989583333</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11295,7 +11295,7 @@
         <v>44792.53936342592</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11352,7 +11352,7 @@
         <v>44616.39256944445</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11409,7 +11409,7 @@
         <v>44259</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11466,7 +11466,7 @@
         <v>44373</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11523,7 +11523,7 @@
         <v>44532.30398148148</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
         <v>44428.34821759259</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11642,7 +11642,7 @@
         <v>44239</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11699,7 +11699,7 @@
         <v>44239</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11756,7 +11756,7 @@
         <v>44272</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11813,7 +11813,7 @@
         <v>44464.40523148148</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11870,7 +11870,7 @@
         <v>44412</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11927,7 +11927,7 @@
         <v>44830.90146990741</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11984,7 +11984,7 @@
         <v>44787.80010416666</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12041,7 +12041,7 @@
         <v>44593</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12098,7 +12098,7 @@
         <v>44088</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12155,7 +12155,7 @@
         <v>44294</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12212,7 +12212,7 @@
         <v>44575</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12269,7 +12269,7 @@
         <v>44428.58511574074</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12331,7 +12331,7 @@
         <v>44825.40940972222</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12393,7 +12393,7 @@
         <v>44308</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12455,7 +12455,7 @@
         <v>44729</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12512,7 +12512,7 @@
         <v>44614</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12574,7 +12574,7 @@
         <v>44279.61517361111</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12631,7 +12631,7 @@
         <v>44585.30171296297</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12688,7 +12688,7 @@
         <v>44272</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12745,7 +12745,7 @@
         <v>44161.31023148148</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12802,7 +12802,7 @@
         <v>44536</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12864,7 +12864,7 @@
         <v>44075</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12921,7 +12921,7 @@
         <v>44428</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12983,7 +12983,7 @@
         <v>44579</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13040,7 +13040,7 @@
         <v>44805</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13102,7 +13102,7 @@
         <v>44811</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13159,7 +13159,7 @@
         <v>44464.42415509259</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13216,7 +13216,7 @@
         <v>44711</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13273,7 +13273,7 @@
         <v>44488</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13330,7 +13330,7 @@
         <v>44151</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13387,7 +13387,7 @@
         <v>44252</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13444,7 +13444,7 @@
         <v>44273</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13501,7 +13501,7 @@
         <v>44326</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13558,7 +13558,7 @@
         <v>44575.8194212963</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13615,7 +13615,7 @@
         <v>44074</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13672,7 +13672,7 @@
         <v>44428.596875</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13734,7 +13734,7 @@
         <v>44819</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13791,7 +13791,7 @@
         <v>44819.28449074074</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13848,7 +13848,7 @@
         <v>45750.50650462963</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13905,7 +13905,7 @@
         <v>44292</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13962,7 +13962,7 @@
         <v>44846.66688657407</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14019,7 +14019,7 @@
         <v>45716.7125</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14076,7 +14076,7 @@
         <v>44605.44909722222</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14133,7 +14133,7 @@
         <v>45111</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14190,7 +14190,7 @@
         <v>44523.65311342593</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14247,7 +14247,7 @@
         <v>45621.52488425926</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14304,7 +14304,7 @@
         <v>45621.5278125</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14361,7 +14361,7 @@
         <v>45008</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14418,7 +14418,7 @@
         <v>45112</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14475,7 +14475,7 @@
         <v>45338.69246527777</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14537,7 +14537,7 @@
         <v>44950</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14594,7 +14594,7 @@
         <v>44950</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14651,7 +14651,7 @@
         <v>45341</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14708,7 +14708,7 @@
         <v>45615.89965277778</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14765,7 +14765,7 @@
         <v>45349</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14822,7 +14822,7 @@
         <v>45119.54038194445</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14879,7 +14879,7 @@
         <v>45747.45038194444</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14936,7 +14936,7 @@
         <v>45701.38606481482</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14993,7 +14993,7 @@
         <v>44893</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15055,7 +15055,7 @@
         <v>45772.45813657407</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15112,7 +15112,7 @@
         <v>45775.4219212963</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15169,7 +15169,7 @@
         <v>45531</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15226,7 +15226,7 @@
         <v>45331</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15283,7 +15283,7 @@
         <v>45197.61039351852</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15345,7 +15345,7 @@
         <v>44325.76335648148</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15402,7 +15402,7 @@
         <v>45406</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15459,7 +15459,7 @@
         <v>45758</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15521,7 +15521,7 @@
         <v>45697.26537037037</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15578,7 +15578,7 @@
         <v>45324.64579861111</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15640,7 +15640,7 @@
         <v>45324.64745370371</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15702,7 +15702,7 @@
         <v>45770</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15759,7 +15759,7 @@
         <v>45092.39466435185</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15816,7 +15816,7 @@
         <v>44944.40825231482</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15873,7 +15873,7 @@
         <v>44804</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15930,7 +15930,7 @@
         <v>45764.3996412037</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15987,7 +15987,7 @@
         <v>45643.47644675926</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16044,7 +16044,7 @@
         <v>45307.72520833334</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16101,7 +16101,7 @@
         <v>45099.74195601852</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16158,7 +16158,7 @@
         <v>45116.44680555556</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16215,7 +16215,7 @@
         <v>45764.53915509259</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16272,7 +16272,7 @@
         <v>44449</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16329,7 +16329,7 @@
         <v>45587.49814814814</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16386,7 +16386,7 @@
         <v>44957.36059027778</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16443,7 +16443,7 @@
         <v>45118</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16500,7 +16500,7 @@
         <v>45338</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16562,7 +16562,7 @@
         <v>45562.38306712963</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16619,7 +16619,7 @@
         <v>45667.63950231481</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16676,7 +16676,7 @@
         <v>45704</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16733,7 +16733,7 @@
         <v>45777.60824074074</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16790,7 +16790,7 @@
         <v>45777.50512731481</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16847,7 +16847,7 @@
         <v>45358</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16904,7 +16904,7 @@
         <v>45358.61696759259</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16961,7 +16961,7 @@
         <v>44484.49586805556</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17018,7 +17018,7 @@
         <v>45321</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17075,7 +17075,7 @@
         <v>45107</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17132,7 +17132,7 @@
         <v>45299</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17189,7 +17189,7 @@
         <v>45281.57759259259</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17251,7 +17251,7 @@
         <v>45275</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17308,7 +17308,7 @@
         <v>45270.42966435185</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17365,7 +17365,7 @@
         <v>45455.4374537037</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17427,7 +17427,7 @@
         <v>45474.70864583334</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17484,7 +17484,7 @@
         <v>44628</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17541,7 +17541,7 @@
         <v>44414</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17598,7 +17598,7 @@
         <v>45558.51949074074</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17660,7 +17660,7 @@
         <v>45335.76891203703</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17722,7 +17722,7 @@
         <v>44893</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17784,7 +17784,7 @@
         <v>45586.62837962963</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17841,7 +17841,7 @@
         <v>45541.37402777778</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17898,7 +17898,7 @@
         <v>45519.48550925926</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17955,7 +17955,7 @@
         <v>45785.65899305556</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18012,7 +18012,7 @@
         <v>44368.64017361111</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18069,7 +18069,7 @@
         <v>45243</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18131,7 +18131,7 @@
         <v>44507.82581018518</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18188,7 +18188,7 @@
         <v>45763.38354166667</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18265,7 +18265,7 @@
         <v>45114.55280092593</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18322,7 +18322,7 @@
         <v>44837</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18379,7 +18379,7 @@
         <v>45477.48771990741</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18436,7 +18436,7 @@
         <v>45436.68626157408</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18493,7 +18493,7 @@
         <v>45314</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18550,7 +18550,7 @@
         <v>45455.42533564815</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18612,7 +18612,7 @@
         <v>45455.42981481482</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18674,7 +18674,7 @@
         <v>44963.66563657407</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18731,7 +18731,7 @@
         <v>44449</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18788,7 +18788,7 @@
         <v>45359.54100694445</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18845,7 +18845,7 @@
         <v>45477.38181712963</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18902,7 +18902,7 @@
         <v>45533.46368055556</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18959,7 +18959,7 @@
         <v>45539.34539351852</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19016,7 +19016,7 @@
         <v>45462.37888888889</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19073,7 +19073,7 @@
         <v>45502.32021990741</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19130,7 +19130,7 @@
         <v>45502.33179398148</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19187,7 +19187,7 @@
         <v>45789.54226851852</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19244,7 +19244,7 @@
         <v>45124.59594907407</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19301,7 +19301,7 @@
         <v>44853</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19363,7 +19363,7 @@
         <v>45267.62943287037</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19420,7 +19420,7 @@
         <v>45747.73295138889</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19477,7 +19477,7 @@
         <v>44355.60153935185</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19534,7 +19534,7 @@
         <v>45460.42804398148</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19591,7 +19591,7 @@
         <v>45788.3231712963</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19648,7 +19648,7 @@
         <v>45588</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19705,7 +19705,7 @@
         <v>45788.32225694445</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19762,7 +19762,7 @@
         <v>45646.5796412037</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19819,7 +19819,7 @@
         <v>45145.47684027778</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19876,7 +19876,7 @@
         <v>44488</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19933,7 +19933,7 @@
         <v>45790.82361111111</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19990,7 +19990,7 @@
         <v>44605.45792824074</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20047,7 +20047,7 @@
         <v>44966.57471064815</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20109,7 +20109,7 @@
         <v>44936</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20166,7 +20166,7 @@
         <v>44411</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20223,7 +20223,7 @@
         <v>45175.44625</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20280,7 +20280,7 @@
         <v>44187</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20342,7 +20342,7 @@
         <v>45551.36004629629</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20399,7 +20399,7 @@
         <v>45541.38644675926</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20456,7 +20456,7 @@
         <v>45586</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20513,7 +20513,7 @@
         <v>45764.42304398148</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20570,7 +20570,7 @@
         <v>45790.81799768518</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20627,7 +20627,7 @@
         <v>45791.85732638889</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20684,7 +20684,7 @@
         <v>45405</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20741,7 +20741,7 @@
         <v>45405</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20798,7 +20798,7 @@
         <v>45184</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20855,7 +20855,7 @@
         <v>45547.83950231481</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20917,7 +20917,7 @@
         <v>44578.52657407407</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20974,7 +20974,7 @@
         <v>45350.56959490741</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21031,7 +21031,7 @@
         <v>44592.28611111111</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21088,7 +21088,7 @@
         <v>45541</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21145,7 +21145,7 @@
         <v>44853</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21202,7 +21202,7 @@
         <v>45545.65415509259</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21264,7 +21264,7 @@
         <v>45412</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21326,7 +21326,7 @@
         <v>44083</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21383,7 +21383,7 @@
         <v>45497</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21440,7 +21440,7 @@
         <v>45552.48335648148</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21497,7 +21497,7 @@
         <v>45462.38087962963</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21554,7 +21554,7 @@
         <v>44585</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21611,7 +21611,7 @@
         <v>45169.38410879629</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21668,7 +21668,7 @@
         <v>44935.37284722222</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21725,7 +21725,7 @@
         <v>45763.49402777778</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21782,7 +21782,7 @@
         <v>45177</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21839,7 +21839,7 @@
         <v>45570.58934027778</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21896,7 +21896,7 @@
         <v>45600.47958333333</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21953,7 +21953,7 @@
         <v>45793</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22010,7 +22010,7 @@
         <v>45012.47533564815</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22067,7 +22067,7 @@
         <v>44482</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22124,7 +22124,7 @@
         <v>45205</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22181,7 +22181,7 @@
         <v>45557.35435185185</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22238,7 +22238,7 @@
         <v>45736</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22295,7 +22295,7 @@
         <v>45740.59474537037</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22352,7 +22352,7 @@
         <v>45736.67693287037</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22409,7 +22409,7 @@
         <v>45635.28104166667</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22466,7 +22466,7 @@
         <v>45727.3134375</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22523,7 +22523,7 @@
         <v>45727.36650462963</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22580,7 +22580,7 @@
         <v>45295.40646990741</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22642,7 +22642,7 @@
         <v>45735</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22699,7 +22699,7 @@
         <v>45645.57626157408</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22756,7 +22756,7 @@
         <v>45734.35039351852</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22813,7 +22813,7 @@
         <v>45740.91412037037</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22870,7 +22870,7 @@
         <v>45741.65699074074</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22927,7 +22927,7 @@
         <v>45741.69303240741</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22984,7 +22984,7 @@
         <v>45735.65969907407</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23041,7 +23041,7 @@
         <v>45755</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23098,7 +23098,7 @@
         <v>45728</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23155,7 +23155,7 @@
         <v>45727.35745370371</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23212,7 +23212,7 @@
         <v>45727.36243055556</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23269,7 +23269,7 @@
         <v>45734.3584837963</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23326,7 +23326,7 @@
         <v>45736</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23383,7 +23383,7 @@
         <v>44090</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23440,7 +23440,7 @@
         <v>45743.59641203703</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23497,7 +23497,7 @@
         <v>45797.67148148148</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23554,7 +23554,7 @@
         <v>45734.35122685185</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23611,7 +23611,7 @@
         <v>45726.52925925926</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23668,7 +23668,7 @@
         <v>45730.65831018519</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23725,7 +23725,7 @@
         <v>45737.67416666666</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23782,7 +23782,7 @@
         <v>45730.3782175926</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23844,7 +23844,7 @@
         <v>45799.52318287037</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23901,7 +23901,7 @@
         <v>45799.58894675926</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23958,7 +23958,7 @@
         <v>45184</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24015,7 +24015,7 @@
         <v>45799.5803125</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24072,7 +24072,7 @@
         <v>45701.31962962963</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24129,7 +24129,7 @@
         <v>45618</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24186,7 +24186,7 @@
         <v>45414</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24243,7 +24243,7 @@
         <v>45799.50469907407</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24300,7 +24300,7 @@
         <v>44589.74348379629</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24357,7 +24357,7 @@
         <v>44893.50922453704</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24419,7 +24419,7 @@
         <v>45681.48793981481</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24476,7 +24476,7 @@
         <v>45681.53460648148</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24533,7 +24533,7 @@
         <v>45545.59315972222</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24595,7 +24595,7 @@
         <v>45799.51578703704</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24652,7 +24652,7 @@
         <v>45538</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24709,7 +24709,7 @@
         <v>45558.63807870371</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24771,7 +24771,7 @@
         <v>44591</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24828,7 +24828,7 @@
         <v>44608</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24885,7 +24885,7 @@
         <v>45169</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24942,7 +24942,7 @@
         <v>45646.67994212963</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24999,7 +24999,7 @@
         <v>44648.61840277778</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25056,7 +25056,7 @@
         <v>45804.31922453704</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25113,7 +25113,7 @@
         <v>45804</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25170,7 +25170,7 @@
         <v>44992.66236111111</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25227,7 +25227,7 @@
         <v>45805</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25284,7 +25284,7 @@
         <v>44626</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25341,7 +25341,7 @@
         <v>44109</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25398,7 +25398,7 @@
         <v>45646.39016203704</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25455,7 +25455,7 @@
         <v>44097</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25512,7 +25512,7 @@
         <v>45806.26452546296</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25569,7 +25569,7 @@
         <v>45806.28703703704</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25626,7 +25626,7 @@
         <v>44550.30402777778</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25683,7 +25683,7 @@
         <v>45733</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25740,7 +25740,7 @@
         <v>45805.58325231481</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25797,7 +25797,7 @@
         <v>45805.60481481482</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25854,7 +25854,7 @@
         <v>45806.2833912037</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25911,7 +25911,7 @@
         <v>44118</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25973,7 +25973,7 @@
         <v>44589.73825231481</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26030,7 +26030,7 @@
         <v>44557</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26087,7 +26087,7 @@
         <v>45805.58372685185</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26144,7 +26144,7 @@
         <v>44904</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26201,7 +26201,7 @@
         <v>44943</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26258,7 +26258,7 @@
         <v>45435</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26320,7 +26320,7 @@
         <v>45030</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26377,7 +26377,7 @@
         <v>45371.60959490741</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26434,7 +26434,7 @@
         <v>45617.92190972222</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26491,7 +26491,7 @@
         <v>45056</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26548,7 +26548,7 @@
         <v>44564.8419212963</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26605,7 +26605,7 @@
         <v>45810</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26662,7 +26662,7 @@
         <v>45174</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26719,7 +26719,7 @@
         <v>45597.43615740741</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26776,7 +26776,7 @@
         <v>45726.44835648148</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26833,7 +26833,7 @@
         <v>44571</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26890,7 +26890,7 @@
         <v>45730.44528935185</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26952,7 +26952,7 @@
         <v>45720.70986111111</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27009,7 +27009,7 @@
         <v>45216.47443287037</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27066,7 +27066,7 @@
         <v>45372.34530092592</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27123,7 +27123,7 @@
         <v>45179.9259375</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27180,7 +27180,7 @@
         <v>45009</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27237,7 +27237,7 @@
         <v>44261</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27294,7 +27294,7 @@
         <v>45624.41041666667</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27351,7 +27351,7 @@
         <v>45811</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27408,7 +27408,7 @@
         <v>45401.34349537037</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27465,7 +27465,7 @@
         <v>45182.71081018518</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27522,7 +27522,7 @@
         <v>44172</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27579,7 +27579,7 @@
         <v>45750.40476851852</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27636,7 +27636,7 @@
         <v>45643.89232638889</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27693,7 +27693,7 @@
         <v>45561.87885416667</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27750,7 +27750,7 @@
         <v>45566</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27807,7 +27807,7 @@
         <v>45547.42313657407</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27869,7 +27869,7 @@
         <v>45547.53320601852</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27926,7 +27926,7 @@
         <v>45105.34402777778</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27983,7 +27983,7 @@
         <v>45440.3712037037</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28040,7 +28040,7 @@
         <v>45194</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28097,7 +28097,7 @@
         <v>45860.54674768518</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28154,7 +28154,7 @@
         <v>44614.68596064814</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28211,7 +28211,7 @@
         <v>45691.5603125</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28268,7 +28268,7 @@
         <v>45861.46241898148</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28325,7 +28325,7 @@
         <v>45861.68065972222</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28382,7 +28382,7 @@
         <v>45197</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28439,7 +28439,7 @@
         <v>45021</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28496,7 +28496,7 @@
         <v>45519.49606481481</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28553,7 +28553,7 @@
         <v>44950</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28610,7 +28610,7 @@
         <v>45819.53688657407</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28667,7 +28667,7 @@
         <v>45819.53980324074</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28724,7 +28724,7 @@
         <v>45819.5429050926</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28781,7 +28781,7 @@
         <v>44839</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28843,7 +28843,7 @@
         <v>45043</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28900,7 +28900,7 @@
         <v>45862.63645833333</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28957,7 +28957,7 @@
         <v>44938</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29019,7 +29019,7 @@
         <v>45693.67859953704</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29076,7 +29076,7 @@
         <v>44977.26300925926</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29133,7 +29133,7 @@
         <v>45700.60138888889</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29190,7 +29190,7 @@
         <v>44659</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29252,7 +29252,7 @@
         <v>45587</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29309,7 +29309,7 @@
         <v>45705</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29366,7 +29366,7 @@
         <v>44252</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29423,7 +29423,7 @@
         <v>45434.58377314815</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29480,7 +29480,7 @@
         <v>44943.4652199074</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29537,7 +29537,7 @@
         <v>44943.46980324074</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29594,7 +29594,7 @@
         <v>45867.66349537037</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29651,7 +29651,7 @@
         <v>45622.35340277778</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29708,7 +29708,7 @@
         <v>45687</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29765,7 +29765,7 @@
         <v>45687</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29822,7 +29822,7 @@
         <v>45637.51090277778</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29879,7 +29879,7 @@
         <v>45112.3174074074</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29936,7 +29936,7 @@
         <v>45112</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29993,7 +29993,7 @@
         <v>44930</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30050,7 +30050,7 @@
         <v>45826</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30107,7 +30107,7 @@
         <v>44360.54226851852</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30164,7 +30164,7 @@
         <v>45701.37818287037</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30221,7 +30221,7 @@
         <v>44575.80709490741</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30278,7 +30278,7 @@
         <v>45701</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30335,7 +30335,7 @@
         <v>44950</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30392,7 +30392,7 @@
         <v>45870.62930555556</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30454,7 +30454,7 @@
         <v>44249</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30511,7 +30511,7 @@
         <v>44225</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30568,7 +30568,7 @@
         <v>44249.66673611111</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30625,7 +30625,7 @@
         <v>45363.91521990741</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30682,7 +30682,7 @@
         <v>45364.40862268519</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30739,7 +30739,7 @@
         <v>44966.52741898148</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30801,7 +30801,7 @@
         <v>45456.66137731481</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30858,7 +30858,7 @@
         <v>45630.70101851852</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30920,7 +30920,7 @@
         <v>45215.72212962963</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30977,7 +30977,7 @@
         <v>45182.36129629629</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31034,7 +31034,7 @@
         <v>45404.58408564814</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31091,7 +31091,7 @@
         <v>45523.5090625</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31153,7 +31153,7 @@
         <v>45523.58461805555</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31215,7 +31215,7 @@
         <v>44988</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31272,7 +31272,7 @@
         <v>45392.63664351852</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31329,7 +31329,7 @@
         <v>45600.48127314815</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31386,7 +31386,7 @@
         <v>45600.48347222222</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31443,7 +31443,7 @@
         <v>45831.51019675926</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31500,7 +31500,7 @@
         <v>44704.65815972222</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31557,7 +31557,7 @@
         <v>45198.59607638889</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31614,7 +31614,7 @@
         <v>45706.67424768519</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31676,7 +31676,7 @@
         <v>45198.60034722222</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31733,7 +31733,7 @@
         <v>45764.40184027778</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31790,7 +31790,7 @@
         <v>45764.42006944444</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31847,7 +31847,7 @@
         <v>45764.42517361111</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31904,7 +31904,7 @@
         <v>44711</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31961,7 +31961,7 @@
         <v>44655.48328703704</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32018,7 +32018,7 @@
         <v>45211</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32075,7 +32075,7 @@
         <v>45875.57328703703</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32137,7 +32137,7 @@
         <v>45875.60922453704</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32194,7 +32194,7 @@
         <v>45201</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32251,7 +32251,7 @@
         <v>45876.6799537037</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32308,7 +32308,7 @@
         <v>44734</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32370,7 +32370,7 @@
         <v>44734</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32432,7 +32432,7 @@
         <v>45194</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32489,7 +32489,7 @@
         <v>45194</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32546,7 +32546,7 @@
         <v>44998.8734837963</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32603,7 +32603,7 @@
         <v>45681.57949074074</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32660,7 +32660,7 @@
         <v>45547.84315972222</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32722,7 +32722,7 @@
         <v>45642.8053125</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32784,7 +32784,7 @@
         <v>44894</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32841,7 +32841,7 @@
         <v>45763.49306712963</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32898,7 +32898,7 @@
         <v>45833.65434027778</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32955,7 +32955,7 @@
         <v>45295.4037962963</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33017,7 +33017,7 @@
         <v>45756</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33074,7 +33074,7 @@
         <v>45833.63770833334</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33131,7 +33131,7 @@
         <v>45169</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33188,7 +33188,7 @@
         <v>45197.38018518518</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33245,7 +33245,7 @@
         <v>45834.48820601852</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33302,7 +33302,7 @@
         <v>45671.44894675926</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33359,7 +33359,7 @@
         <v>45769.43446759259</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33416,7 +33416,7 @@
         <v>45617.4922337963</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33473,7 +33473,7 @@
         <v>45880.43709490741</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33530,7 +33530,7 @@
         <v>45113.31806712963</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33587,7 +33587,7 @@
         <v>45435.51875</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33644,7 +33644,7 @@
         <v>44423.87825231482</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33701,7 +33701,7 @@
         <v>45316</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33758,7 +33758,7 @@
         <v>45877.87582175926</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33815,7 +33815,7 @@
         <v>45880.49957175926</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33872,7 +33872,7 @@
         <v>45880.46642361111</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33929,7 +33929,7 @@
         <v>45759.5549537037</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33986,7 +33986,7 @@
         <v>45314</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34043,7 +34043,7 @@
         <v>45303.63494212963</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34105,7 +34105,7 @@
         <v>45245.46393518519</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34162,7 +34162,7 @@
         <v>45189</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34219,7 +34219,7 @@
         <v>45294</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34281,7 +34281,7 @@
         <v>44272</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34338,7 +34338,7 @@
         <v>44904.59393518518</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34400,7 +34400,7 @@
         <v>44897</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34457,7 +34457,7 @@
         <v>44904.61212962963</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34519,7 +34519,7 @@
         <v>45246.50074074074</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34581,7 +34581,7 @@
         <v>45268</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34638,7 +34638,7 @@
         <v>45882.43462962963</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34695,7 +34695,7 @@
         <v>45839.71761574074</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34752,7 +34752,7 @@
         <v>45761.49107638889</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34809,7 +34809,7 @@
         <v>45883.60416666666</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34866,7 +34866,7 @@
         <v>45679.98971064815</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34923,7 +34923,7 @@
         <v>45679.99299768519</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34980,7 +34980,7 @@
         <v>45272</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35037,7 +35037,7 @@
         <v>45226.3731712963</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35094,7 +35094,7 @@
         <v>45769.60498842593</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35151,7 +35151,7 @@
         <v>44965</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35208,7 +35208,7 @@
         <v>45883.58956018519</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35265,7 +35265,7 @@
         <v>45706.66618055556</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35327,7 +35327,7 @@
         <v>44734</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35389,7 +35389,7 @@
         <v>45842.49457175926</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35446,7 +35446,7 @@
         <v>45842.5059375</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35503,7 +35503,7 @@
         <v>45671.44716435186</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35560,7 +35560,7 @@
         <v>45643</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35617,7 +35617,7 @@
         <v>45883.59239583334</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35674,7 +35674,7 @@
         <v>45883.60604166667</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35731,7 +35731,7 @@
         <v>45842.49056712963</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35788,7 +35788,7 @@
         <v>45015</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35845,7 +35845,7 @@
         <v>45617.91424768518</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35902,7 +35902,7 @@
         <v>45841.71503472222</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35959,7 +35959,7 @@
         <v>45240</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36016,7 +36016,7 @@
         <v>44076</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36073,7 +36073,7 @@
         <v>45841.4390625</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36130,7 +36130,7 @@
         <v>44090</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36187,7 +36187,7 @@
         <v>45846</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36249,7 +36249,7 @@
         <v>45846</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36311,7 +36311,7 @@
         <v>45756</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36368,7 +36368,7 @@
         <v>45797.56770833334</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36425,7 +36425,7 @@
         <v>45587.47273148148</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36482,7 +36482,7 @@
         <v>45630.39777777778</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36544,7 +36544,7 @@
         <v>45630.4022337963</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36606,7 +36606,7 @@
         <v>45846</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36668,7 +36668,7 @@
         <v>45887.68474537037</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36725,7 +36725,7 @@
         <v>45887.62953703704</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36782,7 +36782,7 @@
         <v>45679.36950231482</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36839,7 +36839,7 @@
         <v>45846.48190972222</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36896,7 +36896,7 @@
         <v>44321</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36958,7 +36958,7 @@
         <v>45644.62803240741</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37015,7 +37015,7 @@
         <v>45887.62158564815</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37072,7 +37072,7 @@
         <v>45845.60700231481</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37129,7 +37129,7 @@
         <v>45846.73861111111</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37186,7 +37186,7 @@
         <v>45210.34773148148</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37243,7 +37243,7 @@
         <v>45271</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37300,7 +37300,7 @@
         <v>44750</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37357,7 +37357,7 @@
         <v>45708.52121527777</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37414,7 +37414,7 @@
         <v>45603.60537037037</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37471,7 +37471,7 @@
         <v>45642.60125</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37528,7 +37528,7 @@
         <v>45617.45760416667</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37585,7 +37585,7 @@
         <v>45887</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37642,7 +37642,7 @@
         <v>45736</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37699,7 +37699,7 @@
         <v>44614</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37756,7 +37756,7 @@
         <v>45884</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37813,7 +37813,7 @@
         <v>45892.38811342593</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37870,7 +37870,7 @@
         <v>45892.46936342592</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37927,7 +37927,7 @@
         <v>44889</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37984,7 +37984,7 @@
         <v>45198.41381944445</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38041,7 +38041,7 @@
         <v>45198.41887731481</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38098,7 +38098,7 @@
         <v>45892.43763888889</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38155,7 +38155,7 @@
         <v>45735.82282407407</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38212,7 +38212,7 @@
         <v>45892.42259259259</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38269,7 +38269,7 @@
         <v>45201.45827546297</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38326,7 +38326,7 @@
         <v>45870.62511574074</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38388,7 +38388,7 @@
         <v>45534.36645833333</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38445,7 +38445,7 @@
         <v>45693</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38502,7 +38502,7 @@
         <v>44729</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38559,7 +38559,7 @@
         <v>45469.43982638889</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38616,7 +38616,7 @@
         <v>45895.29351851852</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38673,7 +38673,7 @@
         <v>45253.73424768518</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38730,7 +38730,7 @@
         <v>45300</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38787,7 +38787,7 @@
         <v>45706.66388888889</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38849,7 +38849,7 @@
         <v>45706.67943287037</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38911,7 +38911,7 @@
         <v>45764.53740740741</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38968,7 +38968,7 @@
         <v>45215.71418981482</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39025,7 +39025,7 @@
         <v>45392.58569444445</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39082,7 +39082,7 @@
         <v>44540.57753472222</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39139,7 +39139,7 @@
         <v>45149</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39196,7 +39196,7 @@
         <v>45751</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39258,7 +39258,7 @@
         <v>45630.3944675926</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39320,7 +39320,7 @@
         <v>45201</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39377,7 +39377,7 @@
         <v>45674.47359953704</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39434,7 +39434,7 @@
         <v>45898.46327546296</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39491,7 +39491,7 @@
         <v>44867</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39548,7 +39548,7 @@
         <v>45477.38554398148</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39605,7 +39605,7 @@
         <v>45477.38663194444</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39662,7 +39662,7 @@
         <v>44904</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39719,7 +39719,7 @@
         <v>45726.42344907407</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39781,7 +39781,7 @@
         <v>44719.43577546296</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39838,7 +39838,7 @@
         <v>45897</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39895,7 +39895,7 @@
         <v>45035</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39952,7 +39952,7 @@
         <v>44308.520625</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40009,7 +40009,7 @@
         <v>45188.3012037037</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40066,7 +40066,7 @@
         <v>44103</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40123,7 +40123,7 @@
         <v>44130</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40180,7 +40180,7 @@
         <v>44803.44065972222</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40237,7 +40237,7 @@
         <v>44882</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40294,7 +40294,7 @@
         <v>44113</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40351,7 +40351,7 @@
         <v>45302</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40408,7 +40408,7 @@
         <v>45621</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40465,7 +40465,7 @@
         <v>45182</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40522,7 +40522,7 @@
         <v>44137</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40579,7 +40579,7 @@
         <v>44175</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40636,7 +40636,7 @@
         <v>45708.50255787037</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40693,7 +40693,7 @@
         <v>45715.65605324074</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40750,7 +40750,7 @@
         <v>44077</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40807,7 +40807,7 @@
         <v>44627.41212962963</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40864,7 +40864,7 @@
         <v>44985.35407407407</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40921,7 +40921,7 @@
         <v>44893</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40978,7 +40978,7 @@
         <v>44082</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41035,7 +41035,7 @@
         <v>45547.43438657407</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41097,7 +41097,7 @@
         <v>45406.89568287037</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41154,7 +41154,7 @@
         <v>45406.89640046296</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41211,7 +41211,7 @@
         <v>44853</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41268,7 +41268,7 @@
         <v>44484</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41325,7 +41325,7 @@
         <v>45681.57619212963</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41382,7 +41382,7 @@
         <v>45682.47550925926</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41439,7 +41439,7 @@
         <v>44949</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41496,7 +41496,7 @@
         <v>44648</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41553,7 +41553,7 @@
         <v>44861.62300925926</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41610,7 +41610,7 @@
         <v>44412.7071875</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41667,7 +41667,7 @@
         <v>44938.53719907408</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41729,7 +41729,7 @@
         <v>44084.61673611111</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41786,7 +41786,7 @@
         <v>44361</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41843,7 +41843,7 @@
         <v>45375</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41900,7 +41900,7 @@
         <v>45758</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41962,7 +41962,7 @@
         <v>45180</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42019,7 +42019,7 @@
         <v>45747.30204861111</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42076,7 +42076,7 @@
         <v>44943.44811342593</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42133,7 +42133,7 @@
         <v>45272.42149305555</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42190,7 +42190,7 @@
         <v>45260.85619212963</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42247,7 +42247,7 @@
         <v>44614.56209490741</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42304,7 +42304,7 @@
         <v>44074</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42366,7 +42366,7 @@
         <v>44711</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42423,7 +42423,7 @@
         <v>44886.3340625</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42480,7 +42480,7 @@
         <v>45043.67869212963</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42537,7 +42537,7 @@
         <v>44622</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42594,7 +42594,7 @@
         <v>44741.69432870371</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42651,7 +42651,7 @@
         <v>45058</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42708,7 +42708,7 @@
         <v>44173</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42765,7 +42765,7 @@
         <v>44662</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42822,7 +42822,7 @@
         <v>45184</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42879,7 +42879,7 @@
         <v>44082</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42936,7 +42936,7 @@
         <v>45735.81920138889</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42993,7 +42993,7 @@
         <v>45112</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43050,7 +43050,7 @@
         <v>45775.4233912037</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43107,7 +43107,7 @@
         <v>45749.67842592593</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43164,7 +43164,7 @@
         <v>45751.58130787037</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43221,7 +43221,7 @@
         <v>45706.69384259259</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43283,7 +43283,7 @@
         <v>45271</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43340,7 +43340,7 @@
         <v>44861.6108912037</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43397,7 +43397,7 @@
         <v>44861</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43454,7 +43454,7 @@
         <v>45587</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43511,7 +43511,7 @@
         <v>44211</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43568,7 +43568,7 @@
         <v>44468</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43625,7 +43625,7 @@
         <v>44148</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43682,7 +43682,7 @@
         <v>45706.69090277778</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43744,7 +43744,7 @@
         <v>45757</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43801,7 +43801,7 @@
         <v>45461.65380787037</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43858,7 +43858,7 @@
         <v>44904</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43920,7 +43920,7 @@
         <v>45541.36828703704</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43977,7 +43977,7 @@
         <v>45769.60440972223</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44034,7 +44034,7 @@
         <v>44433</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44091,7 +44091,7 @@
         <v>45043.43777777778</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44148,7 +44148,7 @@
         <v>45037.67510416666</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44205,7 +44205,7 @@
         <v>45079</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44262,7 +44262,7 @@
         <v>44151</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44319,7 +44319,7 @@
         <v>44897.3564699074</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44381,7 +44381,7 @@
         <v>45455.40401620371</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44443,7 +44443,7 @@
         <v>44507.43497685185</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44500,7 +44500,7 @@
         <v>45764.30016203703</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44557,7 +44557,7 @@
         <v>44882</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44614,7 +44614,7 @@
         <v>45764.30391203704</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44671,7 +44671,7 @@
         <v>44943.44532407408</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44728,7 +44728,7 @@
         <v>44943.48144675926</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44785,7 +44785,7 @@
         <v>45580.46572916667</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44842,7 +44842,7 @@
         <v>45355.56604166667</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44899,7 +44899,7 @@
         <v>45324.64302083333</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44961,7 +44961,7 @@
         <v>45740.59871527777</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45018,7 +45018,7 @@
         <v>44963</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45075,7 +45075,7 @@
         <v>45770.51686342592</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45132,7 +45132,7 @@
         <v>45477.48915509259</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45189,7 +45189,7 @@
         <v>45408.67427083333</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45251,7 +45251,7 @@
         <v>45547.83519675926</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45313,7 +45313,7 @@
         <v>44158</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45370,7 +45370,7 @@
         <v>45034</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45427,7 +45427,7 @@
         <v>45183</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45484,7 +45484,7 @@
         <v>45056.6438425926</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45541,7 +45541,7 @@
         <v>44677</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45598,7 +45598,7 @@
         <v>44231</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45655,7 +45655,7 @@
         <v>45758</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45717,7 +45717,7 @@
         <v>45757.30554398148</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45774,7 +45774,7 @@
         <v>45755.70262731481</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45831,7 +45831,7 @@
         <v>45201.59743055556</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45888,7 +45888,7 @@
         <v>44295.31922453704</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45945,7 +45945,7 @@
         <v>44483.58045138889</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46002,7 +46002,7 @@
         <v>45470.6672337963</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46059,7 +46059,7 @@
         <v>44992.67101851852</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46136,7 +46136,7 @@
         <v>45751.52445601852</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46198,7 +46198,7 @@
         <v>45748</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46260,7 +46260,7 @@
         <v>44658</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46317,7 +46317,7 @@
         <v>45092.42630787037</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46374,7 +46374,7 @@
         <v>45446.56622685185</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46431,7 +46431,7 @@
         <v>45049</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46488,7 +46488,7 @@
         <v>45051</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46545,7 +46545,7 @@
         <v>45048</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46602,7 +46602,7 @@
         <v>44959.36028935185</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46664,7 +46664,7 @@
         <v>45051.37461805555</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46721,7 +46721,7 @@
         <v>45764.4140162037</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46778,7 +46778,7 @@
         <v>44846.68375</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46835,7 +46835,7 @@
         <v>45130</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46892,7 +46892,7 @@
         <v>45764.31284722222</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46949,7 +46949,7 @@
         <v>45471.4034837963</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47006,7 +47006,7 @@
         <v>44977.26482638889</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47063,7 +47063,7 @@
         <v>44998</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47120,7 +47120,7 @@
         <v>45673.71842592592</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47177,7 +47177,7 @@
         <v>45152</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47234,7 +47234,7 @@
         <v>45401</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47296,7 +47296,7 @@
         <v>45373.60802083334</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47353,7 +47353,7 @@
         <v>45127</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47410,7 +47410,7 @@
         <v>44967.6228125</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47467,7 +47467,7 @@
         <v>45605.84435185185</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47524,7 +47524,7 @@
         <v>45152</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47581,7 +47581,7 @@
         <v>45092</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47638,7 +47638,7 @@
         <v>45757.29700231482</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47695,7 +47695,7 @@
         <v>45615.90662037037</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47752,7 +47752,7 @@
         <v>44631</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47809,7 +47809,7 @@
         <v>45567</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47866,7 +47866,7 @@
         <v>45630.6993287037</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47923,7 +47923,7 @@
         <v>45240</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47980,7 +47980,7 @@
         <v>45642.92393518519</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48037,7 +48037,7 @@
         <v>44229</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48094,7 +48094,7 @@
         <v>44735</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48151,7 +48151,7 @@
         <v>45012</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48208,7 +48208,7 @@
         <v>45300</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48265,7 +48265,7 @@
         <v>45588</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48322,7 +48322,7 @@
         <v>44985</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48379,7 +48379,7 @@
         <v>45099</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48436,7 +48436,7 @@
         <v>45363.45982638889</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48493,7 +48493,7 @@
         <v>45177.5462962963</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48550,7 +48550,7 @@
         <v>45223.65527777778</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48607,7 +48607,7 @@
         <v>45181</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48664,7 +48664,7 @@
         <v>44840</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48721,7 +48721,7 @@
         <v>45252.58925925926</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48778,7 +48778,7 @@
         <v>44487</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48835,7 +48835,7 @@
         <v>45356.65395833334</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48897,7 +48897,7 @@
         <v>45107</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48954,7 +48954,7 @@
         <v>44588.50104166667</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49011,7 +49011,7 @@
         <v>45747.44508101852</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49068,7 +49068,7 @@
         <v>45747.45177083334</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49125,7 +49125,7 @@
         <v>44979</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49182,7 +49182,7 @@
         <v>45201</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49244,7 +49244,7 @@
         <v>45545.53883101852</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49301,7 +49301,7 @@
         <v>45169</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49358,7 +49358,7 @@
         <v>45468.44574074074</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49415,7 +49415,7 @@
         <v>45775.32407407407</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49472,7 +49472,7 @@
         <v>45597.53744212963</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49529,7 +49529,7 @@
         <v>45447.55340277778</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49586,7 +49586,7 @@
         <v>45644.62243055556</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49643,7 +49643,7 @@
         <v>44904.49826388889</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49700,7 +49700,7 @@
         <v>44904</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49757,7 +49757,7 @@
         <v>44923.55936342593</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49814,7 +49814,7 @@
         <v>45414</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49871,7 +49871,7 @@
         <v>45377.42784722222</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49928,7 +49928,7 @@
         <v>45351.65180555556</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49990,7 +49990,7 @@
         <v>45617.48947916667</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50047,7 +50047,7 @@
         <v>45219</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50104,7 +50104,7 @@
         <v>45477.33712962963</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50161,7 +50161,7 @@
         <v>45406.89703703704</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50218,7 +50218,7 @@
         <v>45547.43793981482</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50280,7 +50280,7 @@
         <v>45492.70833333334</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50337,7 +50337,7 @@
         <v>45566</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50394,7 +50394,7 @@
         <v>45706.68554398148</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50456,7 +50456,7 @@
         <v>45645.88440972222</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50513,7 +50513,7 @@
         <v>45734.59972222222</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45899</v>
+        <v>45900</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>

--- a/Översikt JÖNKÖPING.xlsx
+++ b/Översikt JÖNKÖPING.xlsx
@@ -567,7 +567,7 @@
         <v>45856.56684027778</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -665,7 +665,7 @@
         <v>45856.57200231482</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
         <v>45777</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>45609</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         <v>45348</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         <v>44111</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>45275</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>45698.48634259259</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>44083</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>45846.47335648148</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>45788.88578703703</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>44992</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>44530</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>44512.62668981482</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>44602</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>45604.53402777778</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>44974</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>45373.44148148148</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         <v>45790.83706018519</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>45679.98452546296</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         <v>45358.52763888889</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>45898.45456018519</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2568,7 +2568,7 @@
         <v>45302</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>44991</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>45539</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>44278</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>44419</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2996,7 +2996,7 @@
         <v>44463</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
         <v>44095</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3166,7 +3166,7 @@
         <v>44083</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3256,7 +3256,7 @@
         <v>44347.63069444444</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3341,7 +3341,7 @@
         <v>44467</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         <v>44469</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3515,7 +3515,7 @@
         <v>44404.71972222222</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3600,7 +3600,7 @@
         <v>45783</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3685,7 +3685,7 @@
         <v>44840</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3770,7 +3770,7 @@
         <v>45740.58743055556</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3855,7 +3855,7 @@
         <v>45587</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3940,7 +3940,7 @@
         <v>45819.60131944445</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4025,7 +4025,7 @@
         <v>45758</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         <v>45580.46207175926</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         <v>45846</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4294,7 +4294,7 @@
         <v>45876.69954861111</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4379,7 +4379,7 @@
         <v>45295.3942824074</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4469,7 +4469,7 @@
         <v>45343</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
         <v>45302</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4639,7 +4639,7 @@
         <v>45841.4303125</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4724,7 +4724,7 @@
         <v>45846</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4809,7 +4809,7 @@
         <v>45616</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4898,7 +4898,7 @@
         <v>45538.45523148148</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4983,7 +4983,7 @@
         <v>44879</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5072,7 +5072,7 @@
         <v>45856.55965277777</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
         <v>45205</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5246,7 +5246,7 @@
         <v>45569.41550925926</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         <v>44943</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5416,7 +5416,7 @@
         <v>44260</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5473,7 +5473,7 @@
         <v>44188</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5530,7 +5530,7 @@
         <v>44137</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5587,7 +5587,7 @@
         <v>44147</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5644,7 +5644,7 @@
         <v>44306</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5701,7 +5701,7 @@
         <v>44308</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5763,7 +5763,7 @@
         <v>44144</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5820,7 +5820,7 @@
         <v>44328.35063657408</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5877,7 +5877,7 @@
         <v>44239.33525462963</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         <v>44496</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5991,7 +5991,7 @@
         <v>44404.84280092592</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6048,7 +6048,7 @@
         <v>44404.84659722223</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6105,7 +6105,7 @@
         <v>44278.3859375</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6162,7 +6162,7 @@
         <v>44575.80925925926</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6219,7 +6219,7 @@
         <v>44662</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         <v>44487</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         <v>44749.55936342593</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6390,7 +6390,7 @@
         <v>44749.55703703704</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6447,7 +6447,7 @@
         <v>44273.62572916667</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6504,7 +6504,7 @@
         <v>44454.35472222222</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         <v>44308</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6623,7 +6623,7 @@
         <v>44225</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6680,7 +6680,7 @@
         <v>44308</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6742,7 +6742,7 @@
         <v>44349</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6799,7 +6799,7 @@
         <v>44792.53711805555</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6856,7 +6856,7 @@
         <v>44411</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6913,7 +6913,7 @@
         <v>44194</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6970,7 +6970,7 @@
         <v>44225</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7027,7 +7027,7 @@
         <v>44809</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7084,7 +7084,7 @@
         <v>44442</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         <v>44487.49392361111</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7198,7 +7198,7 @@
         <v>44487</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7255,7 +7255,7 @@
         <v>44749.32716435185</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7312,7 +7312,7 @@
         <v>44420.68987268519</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7369,7 +7369,7 @@
         <v>44404.84138888889</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7426,7 +7426,7 @@
         <v>44266</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7483,7 +7483,7 @@
         <v>44881.81052083334</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7540,7 +7540,7 @@
         <v>44665.60081018518</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
         <v>44869.49265046296</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7659,7 +7659,7 @@
         <v>44734</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         <v>44792</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7778,7 +7778,7 @@
         <v>44259</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
         <v>44365</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7892,7 +7892,7 @@
         <v>44538</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
         <v>44263</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
         <v>44113</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8068,7 +8068,7 @@
         <v>44487</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         <v>44487</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8182,7 +8182,7 @@
         <v>44272</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8239,7 +8239,7 @@
         <v>44875.59231481481</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8296,7 +8296,7 @@
         <v>44852.74376157407</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8358,7 +8358,7 @@
         <v>44292</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8415,7 +8415,7 @@
         <v>44200</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8472,7 +8472,7 @@
         <v>44498.56373842592</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         <v>44111</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8586,7 +8586,7 @@
         <v>44881.79847222222</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8643,7 +8643,7 @@
         <v>44286.34827546297</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8700,7 +8700,7 @@
         <v>44673</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8757,7 +8757,7 @@
         <v>44273</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8814,7 +8814,7 @@
         <v>44298.46462962963</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8876,7 +8876,7 @@
         <v>44298.46582175926</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8938,7 +8938,7 @@
         <v>44278.38752314815</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8995,7 +8995,7 @@
         <v>44279.37552083333</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9052,7 +9052,7 @@
         <v>44347.61920138889</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         <v>44754.47359953704</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9171,7 +9171,7 @@
         <v>44855.3080787037</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9228,7 +9228,7 @@
         <v>44476</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         <v>44373.75251157407</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9342,7 +9342,7 @@
         <v>44347.6287962963</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9399,7 +9399,7 @@
         <v>44511</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9456,7 +9456,7 @@
         <v>44466.4425</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9513,7 +9513,7 @@
         <v>44377</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9570,7 +9570,7 @@
         <v>44440.71997685185</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9627,7 +9627,7 @@
         <v>44840</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9684,7 +9684,7 @@
         <v>44104</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9741,7 +9741,7 @@
         <v>44280</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9798,7 +9798,7 @@
         <v>44613</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9855,7 +9855,7 @@
         <v>44456.46952546296</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9912,7 +9912,7 @@
         <v>44537</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9969,7 +9969,7 @@
         <v>44356</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         <v>44360</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10083,7 +10083,7 @@
         <v>44476</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10140,7 +10140,7 @@
         <v>44575</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10197,7 +10197,7 @@
         <v>44298.44060185185</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10259,7 +10259,7 @@
         <v>44711</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10316,7 +10316,7 @@
         <v>44659.57226851852</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10378,7 +10378,7 @@
         <v>44659</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10440,7 +10440,7 @@
         <v>44454.4800925926</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10497,7 +10497,7 @@
         <v>44578</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10554,7 +10554,7 @@
         <v>44344</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10611,7 +10611,7 @@
         <v>44474.25150462963</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10668,7 +10668,7 @@
         <v>44628</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10725,7 +10725,7 @@
         <v>44596</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10782,7 +10782,7 @@
         <v>44711</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10839,7 +10839,7 @@
         <v>44711</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10896,7 +10896,7 @@
         <v>44498.57181712963</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10953,7 +10953,7 @@
         <v>44082.79793981482</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11010,7 +11010,7 @@
         <v>44082</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11067,7 +11067,7 @@
         <v>44841.31997685185</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11124,7 +11124,7 @@
         <v>44579.41064814815</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11181,7 +11181,7 @@
         <v>44467.68283564815</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11238,7 +11238,7 @@
         <v>44557.71989583333</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11295,7 +11295,7 @@
         <v>44792.53936342592</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11352,7 +11352,7 @@
         <v>44616.39256944445</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11409,7 +11409,7 @@
         <v>44259</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11466,7 +11466,7 @@
         <v>44373</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11523,7 +11523,7 @@
         <v>44532.30398148148</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
         <v>44428.34821759259</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11642,7 +11642,7 @@
         <v>44239</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11699,7 +11699,7 @@
         <v>44239</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11756,7 +11756,7 @@
         <v>44272</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11813,7 +11813,7 @@
         <v>44464.40523148148</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11870,7 +11870,7 @@
         <v>44412</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11927,7 +11927,7 @@
         <v>44830.90146990741</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11984,7 +11984,7 @@
         <v>44787.80010416666</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12041,7 +12041,7 @@
         <v>44593</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12098,7 +12098,7 @@
         <v>44088</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12155,7 +12155,7 @@
         <v>44294</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12212,7 +12212,7 @@
         <v>44575</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12269,7 +12269,7 @@
         <v>44428.58511574074</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12331,7 +12331,7 @@
         <v>44825.40940972222</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12393,7 +12393,7 @@
         <v>44308</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12455,7 +12455,7 @@
         <v>44729</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12512,7 +12512,7 @@
         <v>44614</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12574,7 +12574,7 @@
         <v>44279.61517361111</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12631,7 +12631,7 @@
         <v>44585.30171296297</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12688,7 +12688,7 @@
         <v>44272</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12745,7 +12745,7 @@
         <v>44161.31023148148</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12802,7 +12802,7 @@
         <v>44536</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12864,7 +12864,7 @@
         <v>44075</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12921,7 +12921,7 @@
         <v>44428</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12983,7 +12983,7 @@
         <v>44579</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13040,7 +13040,7 @@
         <v>44805</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13102,7 +13102,7 @@
         <v>44811</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13159,7 +13159,7 @@
         <v>44464.42415509259</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13216,7 +13216,7 @@
         <v>44711</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13273,7 +13273,7 @@
         <v>44488</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13330,7 +13330,7 @@
         <v>44151</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13387,7 +13387,7 @@
         <v>44252</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13444,7 +13444,7 @@
         <v>44273</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13501,7 +13501,7 @@
         <v>44326</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13558,7 +13558,7 @@
         <v>44575.8194212963</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13615,7 +13615,7 @@
         <v>44074</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13672,7 +13672,7 @@
         <v>44428.596875</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13734,7 +13734,7 @@
         <v>44819</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13791,7 +13791,7 @@
         <v>44819.28449074074</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13848,7 +13848,7 @@
         <v>45750.50650462963</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13905,7 +13905,7 @@
         <v>44292</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13962,7 +13962,7 @@
         <v>44846.66688657407</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14019,7 +14019,7 @@
         <v>45716.7125</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14076,7 +14076,7 @@
         <v>44605.44909722222</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14133,7 +14133,7 @@
         <v>45111</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14190,7 +14190,7 @@
         <v>44523.65311342593</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14247,7 +14247,7 @@
         <v>45621.52488425926</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14304,7 +14304,7 @@
         <v>45621.5278125</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14361,7 +14361,7 @@
         <v>45008</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14418,7 +14418,7 @@
         <v>45112</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14475,7 +14475,7 @@
         <v>45338.69246527777</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14537,7 +14537,7 @@
         <v>44950</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14594,7 +14594,7 @@
         <v>44950</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14651,7 +14651,7 @@
         <v>45341</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14708,7 +14708,7 @@
         <v>45615.89965277778</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14765,7 +14765,7 @@
         <v>45349</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14822,7 +14822,7 @@
         <v>45119.54038194445</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14879,7 +14879,7 @@
         <v>45747.45038194444</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14936,7 +14936,7 @@
         <v>45701.38606481482</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14993,7 +14993,7 @@
         <v>44893</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15055,7 +15055,7 @@
         <v>45772.45813657407</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15112,7 +15112,7 @@
         <v>45775.4219212963</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15169,7 +15169,7 @@
         <v>45531</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15226,7 +15226,7 @@
         <v>45331</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15283,7 +15283,7 @@
         <v>45197.61039351852</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15345,7 +15345,7 @@
         <v>44325.76335648148</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15402,7 +15402,7 @@
         <v>45406</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15459,7 +15459,7 @@
         <v>45758</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15521,7 +15521,7 @@
         <v>45697.26537037037</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15578,7 +15578,7 @@
         <v>45324.64579861111</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15640,7 +15640,7 @@
         <v>45324.64745370371</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15702,7 +15702,7 @@
         <v>45770</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15759,7 +15759,7 @@
         <v>45092.39466435185</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15816,7 +15816,7 @@
         <v>44944.40825231482</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15873,7 +15873,7 @@
         <v>44804</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15930,7 +15930,7 @@
         <v>45764.3996412037</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15987,7 +15987,7 @@
         <v>45643.47644675926</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16044,7 +16044,7 @@
         <v>45307.72520833334</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16101,7 +16101,7 @@
         <v>45099.74195601852</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16158,7 +16158,7 @@
         <v>45116.44680555556</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16215,7 +16215,7 @@
         <v>45764.53915509259</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16272,7 +16272,7 @@
         <v>44449</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16329,7 +16329,7 @@
         <v>45587.49814814814</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16386,7 +16386,7 @@
         <v>44957.36059027778</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16443,7 +16443,7 @@
         <v>45118</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16500,7 +16500,7 @@
         <v>45338</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16562,7 +16562,7 @@
         <v>45562.38306712963</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16619,7 +16619,7 @@
         <v>45667.63950231481</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16676,7 +16676,7 @@
         <v>45704</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16733,7 +16733,7 @@
         <v>45777.60824074074</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16790,7 +16790,7 @@
         <v>45777.50512731481</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16847,7 +16847,7 @@
         <v>45358</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16904,7 +16904,7 @@
         <v>45358.61696759259</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16961,7 +16961,7 @@
         <v>44484.49586805556</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17018,7 +17018,7 @@
         <v>45321</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17075,7 +17075,7 @@
         <v>45107</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17132,7 +17132,7 @@
         <v>45299</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17189,7 +17189,7 @@
         <v>45281.57759259259</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17251,7 +17251,7 @@
         <v>45275</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17308,7 +17308,7 @@
         <v>45270.42966435185</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17365,7 +17365,7 @@
         <v>45455.4374537037</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17427,7 +17427,7 @@
         <v>45474.70864583334</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17484,7 +17484,7 @@
         <v>44628</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17541,7 +17541,7 @@
         <v>44414</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17598,7 +17598,7 @@
         <v>45558.51949074074</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17660,7 +17660,7 @@
         <v>45335.76891203703</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17722,7 +17722,7 @@
         <v>44893</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17784,7 +17784,7 @@
         <v>45586.62837962963</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17841,7 +17841,7 @@
         <v>45541.37402777778</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17898,7 +17898,7 @@
         <v>45519.48550925926</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17955,7 +17955,7 @@
         <v>45785.65899305556</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -18012,7 +18012,7 @@
         <v>44368.64017361111</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18069,7 +18069,7 @@
         <v>45243</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18131,7 +18131,7 @@
         <v>44507.82581018518</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18188,7 +18188,7 @@
         <v>45763.38354166667</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18265,7 +18265,7 @@
         <v>45114.55280092593</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18322,7 +18322,7 @@
         <v>44837</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18379,7 +18379,7 @@
         <v>45477.48771990741</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18436,7 +18436,7 @@
         <v>45436.68626157408</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18493,7 +18493,7 @@
         <v>45314</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18550,7 +18550,7 @@
         <v>45455.42533564815</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18612,7 +18612,7 @@
         <v>45455.42981481482</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18674,7 +18674,7 @@
         <v>44963.66563657407</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18731,7 +18731,7 @@
         <v>44449</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18788,7 +18788,7 @@
         <v>45359.54100694445</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18845,7 +18845,7 @@
         <v>45477.38181712963</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18902,7 +18902,7 @@
         <v>45533.46368055556</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18959,7 +18959,7 @@
         <v>45539.34539351852</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -19016,7 +19016,7 @@
         <v>45462.37888888889</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19073,7 +19073,7 @@
         <v>45502.32021990741</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19130,7 +19130,7 @@
         <v>45502.33179398148</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19187,7 +19187,7 @@
         <v>45789.54226851852</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19244,7 +19244,7 @@
         <v>45124.59594907407</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19301,7 +19301,7 @@
         <v>44853</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19363,7 +19363,7 @@
         <v>45267.62943287037</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19420,7 +19420,7 @@
         <v>45747.73295138889</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19477,7 +19477,7 @@
         <v>44355.60153935185</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19534,7 +19534,7 @@
         <v>45460.42804398148</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19591,7 +19591,7 @@
         <v>45788.3231712963</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19648,7 +19648,7 @@
         <v>45588</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19705,7 +19705,7 @@
         <v>45788.32225694445</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19762,7 +19762,7 @@
         <v>45646.5796412037</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19819,7 +19819,7 @@
         <v>45145.47684027778</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19876,7 +19876,7 @@
         <v>44488</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19933,7 +19933,7 @@
         <v>45790.82361111111</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19990,7 +19990,7 @@
         <v>44605.45792824074</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20047,7 +20047,7 @@
         <v>44966.57471064815</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20109,7 +20109,7 @@
         <v>44936</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20166,7 +20166,7 @@
         <v>44411</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20223,7 +20223,7 @@
         <v>45175.44625</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20280,7 +20280,7 @@
         <v>44187</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20342,7 +20342,7 @@
         <v>45551.36004629629</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20399,7 +20399,7 @@
         <v>45541.38644675926</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20456,7 +20456,7 @@
         <v>45586</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20513,7 +20513,7 @@
         <v>45764.42304398148</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20570,7 +20570,7 @@
         <v>45790.81799768518</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20627,7 +20627,7 @@
         <v>45791.85732638889</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20684,7 +20684,7 @@
         <v>45405</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20741,7 +20741,7 @@
         <v>45405</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20798,7 +20798,7 @@
         <v>45184</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20855,7 +20855,7 @@
         <v>45547.83950231481</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20917,7 +20917,7 @@
         <v>44578.52657407407</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20974,7 +20974,7 @@
         <v>45350.56959490741</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -21031,7 +21031,7 @@
         <v>44592.28611111111</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21088,7 +21088,7 @@
         <v>45541</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21145,7 +21145,7 @@
         <v>44853</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21202,7 +21202,7 @@
         <v>45545.65415509259</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21264,7 +21264,7 @@
         <v>45412</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21326,7 +21326,7 @@
         <v>44083</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21383,7 +21383,7 @@
         <v>45497</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21440,7 +21440,7 @@
         <v>45552.48335648148</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21497,7 +21497,7 @@
         <v>45462.38087962963</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21554,7 +21554,7 @@
         <v>44585</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21611,7 +21611,7 @@
         <v>45169.38410879629</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21668,7 +21668,7 @@
         <v>44935.37284722222</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21725,7 +21725,7 @@
         <v>45763.49402777778</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21782,7 +21782,7 @@
         <v>45177</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21839,7 +21839,7 @@
         <v>45570.58934027778</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21896,7 +21896,7 @@
         <v>45600.47958333333</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21953,7 +21953,7 @@
         <v>45793</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -22010,7 +22010,7 @@
         <v>45012.47533564815</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22067,7 +22067,7 @@
         <v>44482</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22124,7 +22124,7 @@
         <v>45205</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22181,7 +22181,7 @@
         <v>45557.35435185185</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22238,7 +22238,7 @@
         <v>45736</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22295,7 +22295,7 @@
         <v>45740.59474537037</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22352,7 +22352,7 @@
         <v>45736.67693287037</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22409,7 +22409,7 @@
         <v>45635.28104166667</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22466,7 +22466,7 @@
         <v>45727.3134375</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22523,7 +22523,7 @@
         <v>45727.36650462963</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22580,7 +22580,7 @@
         <v>45295.40646990741</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22642,7 +22642,7 @@
         <v>45735</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22699,7 +22699,7 @@
         <v>45645.57626157408</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22756,7 +22756,7 @@
         <v>45734.35039351852</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22813,7 +22813,7 @@
         <v>45740.91412037037</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22870,7 +22870,7 @@
         <v>45741.65699074074</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22927,7 +22927,7 @@
         <v>45741.69303240741</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22984,7 +22984,7 @@
         <v>45735.65969907407</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23041,7 +23041,7 @@
         <v>45755</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23098,7 +23098,7 @@
         <v>45728</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23155,7 +23155,7 @@
         <v>45727.35745370371</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23212,7 +23212,7 @@
         <v>45727.36243055556</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23269,7 +23269,7 @@
         <v>45734.3584837963</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23326,7 +23326,7 @@
         <v>45736</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23383,7 +23383,7 @@
         <v>44090</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23440,7 +23440,7 @@
         <v>45743.59641203703</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23497,7 +23497,7 @@
         <v>45797.67148148148</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23554,7 +23554,7 @@
         <v>45734.35122685185</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23611,7 +23611,7 @@
         <v>45726.52925925926</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23668,7 +23668,7 @@
         <v>45730.65831018519</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23725,7 +23725,7 @@
         <v>45737.67416666666</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23782,7 +23782,7 @@
         <v>45730.3782175926</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23844,7 +23844,7 @@
         <v>45799.52318287037</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23901,7 +23901,7 @@
         <v>45799.58894675926</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23958,7 +23958,7 @@
         <v>45184</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -24015,7 +24015,7 @@
         <v>45799.5803125</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24072,7 +24072,7 @@
         <v>45701.31962962963</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24129,7 +24129,7 @@
         <v>45618</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24186,7 +24186,7 @@
         <v>45414</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24243,7 +24243,7 @@
         <v>45799.50469907407</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24300,7 +24300,7 @@
         <v>44589.74348379629</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24357,7 +24357,7 @@
         <v>44893.50922453704</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24419,7 +24419,7 @@
         <v>45681.48793981481</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24476,7 +24476,7 @@
         <v>45681.53460648148</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24533,7 +24533,7 @@
         <v>45545.59315972222</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24595,7 +24595,7 @@
         <v>45799.51578703704</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24652,7 +24652,7 @@
         <v>45538</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24709,7 +24709,7 @@
         <v>45558.63807870371</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24771,7 +24771,7 @@
         <v>44591</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24828,7 +24828,7 @@
         <v>44608</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24885,7 +24885,7 @@
         <v>45169</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24942,7 +24942,7 @@
         <v>45646.67994212963</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24999,7 +24999,7 @@
         <v>44648.61840277778</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25056,7 +25056,7 @@
         <v>45804.31922453704</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25113,7 +25113,7 @@
         <v>45804</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25170,7 +25170,7 @@
         <v>44992.66236111111</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25227,7 +25227,7 @@
         <v>45805</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25284,7 +25284,7 @@
         <v>44626</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25341,7 +25341,7 @@
         <v>44109</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25398,7 +25398,7 @@
         <v>45646.39016203704</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25455,7 +25455,7 @@
         <v>44097</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25512,7 +25512,7 @@
         <v>45806.26452546296</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25569,7 +25569,7 @@
         <v>45806.28703703704</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25626,7 +25626,7 @@
         <v>44550.30402777778</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25683,7 +25683,7 @@
         <v>45733</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25740,7 +25740,7 @@
         <v>45805.58325231481</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25797,7 +25797,7 @@
         <v>45805.60481481482</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25854,7 +25854,7 @@
         <v>45806.2833912037</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25911,7 +25911,7 @@
         <v>44118</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25973,7 +25973,7 @@
         <v>44589.73825231481</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -26030,7 +26030,7 @@
         <v>44557</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26087,7 +26087,7 @@
         <v>45805.58372685185</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26144,7 +26144,7 @@
         <v>44904</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26201,7 +26201,7 @@
         <v>44943</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26258,7 +26258,7 @@
         <v>45435</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26320,7 +26320,7 @@
         <v>45030</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26377,7 +26377,7 @@
         <v>45371.60959490741</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26434,7 +26434,7 @@
         <v>45617.92190972222</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26491,7 +26491,7 @@
         <v>45056</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26548,7 +26548,7 @@
         <v>44564.8419212963</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26605,7 +26605,7 @@
         <v>45810</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26662,7 +26662,7 @@
         <v>45174</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26719,7 +26719,7 @@
         <v>45597.43615740741</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26776,7 +26776,7 @@
         <v>45726.44835648148</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26833,7 +26833,7 @@
         <v>44571</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26890,7 +26890,7 @@
         <v>45730.44528935185</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26952,7 +26952,7 @@
         <v>45720.70986111111</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -27009,7 +27009,7 @@
         <v>45216.47443287037</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27066,7 +27066,7 @@
         <v>45372.34530092592</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27123,7 +27123,7 @@
         <v>45179.9259375</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27180,7 +27180,7 @@
         <v>45009</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27237,7 +27237,7 @@
         <v>44261</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27294,7 +27294,7 @@
         <v>45624.41041666667</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27351,7 +27351,7 @@
         <v>45811</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27408,7 +27408,7 @@
         <v>45401.34349537037</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27465,7 +27465,7 @@
         <v>45182.71081018518</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27522,7 +27522,7 @@
         <v>44172</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27579,7 +27579,7 @@
         <v>45750.40476851852</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27636,7 +27636,7 @@
         <v>45643.89232638889</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27693,7 +27693,7 @@
         <v>45561.87885416667</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27750,7 +27750,7 @@
         <v>45566</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27807,7 +27807,7 @@
         <v>45547.42313657407</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27869,7 +27869,7 @@
         <v>45547.53320601852</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27926,7 +27926,7 @@
         <v>45105.34402777778</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27983,7 +27983,7 @@
         <v>45440.3712037037</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28040,7 +28040,7 @@
         <v>45194</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28097,7 +28097,7 @@
         <v>45860.54674768518</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28154,7 +28154,7 @@
         <v>44614.68596064814</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28211,7 +28211,7 @@
         <v>45691.5603125</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28268,7 +28268,7 @@
         <v>45861.46241898148</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28325,7 +28325,7 @@
         <v>45861.68065972222</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28382,7 +28382,7 @@
         <v>45197</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28439,7 +28439,7 @@
         <v>45021</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28496,7 +28496,7 @@
         <v>45519.49606481481</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28553,7 +28553,7 @@
         <v>44950</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28610,7 +28610,7 @@
         <v>45819.53688657407</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28667,7 +28667,7 @@
         <v>45819.53980324074</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28724,7 +28724,7 @@
         <v>45819.5429050926</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28781,7 +28781,7 @@
         <v>44839</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28843,7 +28843,7 @@
         <v>45043</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28900,7 +28900,7 @@
         <v>45862.63645833333</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28957,7 +28957,7 @@
         <v>44938</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29019,7 +29019,7 @@
         <v>45693.67859953704</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29076,7 +29076,7 @@
         <v>44977.26300925926</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29133,7 +29133,7 @@
         <v>45700.60138888889</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29190,7 +29190,7 @@
         <v>44659</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29252,7 +29252,7 @@
         <v>45587</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29309,7 +29309,7 @@
         <v>45705</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29366,7 +29366,7 @@
         <v>44252</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29423,7 +29423,7 @@
         <v>45434.58377314815</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29480,7 +29480,7 @@
         <v>44943.4652199074</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29537,7 +29537,7 @@
         <v>44943.46980324074</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29594,7 +29594,7 @@
         <v>45867.66349537037</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29651,7 +29651,7 @@
         <v>45622.35340277778</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29708,7 +29708,7 @@
         <v>45687</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29765,7 +29765,7 @@
         <v>45687</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29822,7 +29822,7 @@
         <v>45637.51090277778</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29879,7 +29879,7 @@
         <v>45112.3174074074</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29936,7 +29936,7 @@
         <v>45112</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29993,7 +29993,7 @@
         <v>44930</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30050,7 +30050,7 @@
         <v>45826</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30107,7 +30107,7 @@
         <v>44360.54226851852</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30164,7 +30164,7 @@
         <v>45701.37818287037</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30221,7 +30221,7 @@
         <v>44575.80709490741</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30278,7 +30278,7 @@
         <v>45701</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30335,7 +30335,7 @@
         <v>44950</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30392,7 +30392,7 @@
         <v>45870.62930555556</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30454,7 +30454,7 @@
         <v>44249</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30511,7 +30511,7 @@
         <v>44225</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30568,7 +30568,7 @@
         <v>44249.66673611111</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30625,7 +30625,7 @@
         <v>45363.91521990741</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30682,7 +30682,7 @@
         <v>45364.40862268519</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30739,7 +30739,7 @@
         <v>44966.52741898148</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30801,7 +30801,7 @@
         <v>45456.66137731481</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30858,7 +30858,7 @@
         <v>45630.70101851852</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30920,7 +30920,7 @@
         <v>45215.72212962963</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30977,7 +30977,7 @@
         <v>45182.36129629629</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31034,7 +31034,7 @@
         <v>45404.58408564814</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31091,7 +31091,7 @@
         <v>45523.5090625</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31153,7 +31153,7 @@
         <v>45523.58461805555</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31215,7 +31215,7 @@
         <v>44988</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31272,7 +31272,7 @@
         <v>45392.63664351852</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31329,7 +31329,7 @@
         <v>45600.48127314815</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31386,7 +31386,7 @@
         <v>45600.48347222222</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31443,7 +31443,7 @@
         <v>45831.51019675926</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31500,7 +31500,7 @@
         <v>44704.65815972222</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31557,7 +31557,7 @@
         <v>45198.59607638889</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31614,7 +31614,7 @@
         <v>45706.67424768519</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31676,7 +31676,7 @@
         <v>45198.60034722222</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31733,7 +31733,7 @@
         <v>45764.40184027778</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31790,7 +31790,7 @@
         <v>45764.42006944444</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31847,7 +31847,7 @@
         <v>45764.42517361111</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31904,7 +31904,7 @@
         <v>44711</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31961,7 +31961,7 @@
         <v>44655.48328703704</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -32018,7 +32018,7 @@
         <v>45211</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32075,7 +32075,7 @@
         <v>45875.57328703703</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32137,7 +32137,7 @@
         <v>45875.60922453704</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32194,7 +32194,7 @@
         <v>45201</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32251,7 +32251,7 @@
         <v>45876.6799537037</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32308,7 +32308,7 @@
         <v>44734</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32370,7 +32370,7 @@
         <v>44734</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32432,7 +32432,7 @@
         <v>45194</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32489,7 +32489,7 @@
         <v>45194</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32546,7 +32546,7 @@
         <v>44998.8734837963</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32603,7 +32603,7 @@
         <v>45681.57949074074</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32660,7 +32660,7 @@
         <v>45547.84315972222</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32722,7 +32722,7 @@
         <v>45642.8053125</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32784,7 +32784,7 @@
         <v>44894</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32841,7 +32841,7 @@
         <v>45763.49306712963</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32898,7 +32898,7 @@
         <v>45833.65434027778</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32955,7 +32955,7 @@
         <v>45295.4037962963</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -33017,7 +33017,7 @@
         <v>45756</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33074,7 +33074,7 @@
         <v>45833.63770833334</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33131,7 +33131,7 @@
         <v>45169</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33188,7 +33188,7 @@
         <v>45197.38018518518</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33245,7 +33245,7 @@
         <v>45834.48820601852</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33302,7 +33302,7 @@
         <v>45671.44894675926</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33359,7 +33359,7 @@
         <v>45769.43446759259</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33416,7 +33416,7 @@
         <v>45617.4922337963</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33473,7 +33473,7 @@
         <v>45880.43709490741</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33530,7 +33530,7 @@
         <v>45113.31806712963</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33587,7 +33587,7 @@
         <v>45435.51875</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33644,7 +33644,7 @@
         <v>44423.87825231482</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33701,7 +33701,7 @@
         <v>45316</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33758,7 +33758,7 @@
         <v>45877.87582175926</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33815,7 +33815,7 @@
         <v>45880.49957175926</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33872,7 +33872,7 @@
         <v>45880.46642361111</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33929,7 +33929,7 @@
         <v>45759.5549537037</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33986,7 +33986,7 @@
         <v>45314</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34043,7 +34043,7 @@
         <v>45303.63494212963</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34105,7 +34105,7 @@
         <v>45245.46393518519</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34162,7 +34162,7 @@
         <v>45189</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34219,7 +34219,7 @@
         <v>45294</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34281,7 +34281,7 @@
         <v>44272</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34338,7 +34338,7 @@
         <v>44904.59393518518</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34400,7 +34400,7 @@
         <v>44897</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34457,7 +34457,7 @@
         <v>44904.61212962963</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34519,7 +34519,7 @@
         <v>45246.50074074074</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34581,7 +34581,7 @@
         <v>45268</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34638,7 +34638,7 @@
         <v>45882.43462962963</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34695,7 +34695,7 @@
         <v>45839.71761574074</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34752,7 +34752,7 @@
         <v>45761.49107638889</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34809,7 +34809,7 @@
         <v>45883.60416666666</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34866,7 +34866,7 @@
         <v>45679.98971064815</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34923,7 +34923,7 @@
         <v>45679.99299768519</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34980,7 +34980,7 @@
         <v>45272</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -35037,7 +35037,7 @@
         <v>45226.3731712963</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35094,7 +35094,7 @@
         <v>45769.60498842593</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35151,7 +35151,7 @@
         <v>44965</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35208,7 +35208,7 @@
         <v>45883.58956018519</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35265,7 +35265,7 @@
         <v>45706.66618055556</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35327,7 +35327,7 @@
         <v>44734</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35389,7 +35389,7 @@
         <v>45842.49457175926</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35446,7 +35446,7 @@
         <v>45842.5059375</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35503,7 +35503,7 @@
         <v>45671.44716435186</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35560,7 +35560,7 @@
         <v>45643</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35617,7 +35617,7 @@
         <v>45883.59239583334</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35674,7 +35674,7 @@
         <v>45883.60604166667</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35731,7 +35731,7 @@
         <v>45842.49056712963</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35788,7 +35788,7 @@
         <v>45015</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35845,7 +35845,7 @@
         <v>45617.91424768518</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35902,7 +35902,7 @@
         <v>45841.71503472222</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35959,7 +35959,7 @@
         <v>45240</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -36016,7 +36016,7 @@
         <v>44076</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36073,7 +36073,7 @@
         <v>45841.4390625</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36130,7 +36130,7 @@
         <v>44090</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36187,7 +36187,7 @@
         <v>45846</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36249,7 +36249,7 @@
         <v>45846</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36311,7 +36311,7 @@
         <v>45756</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36368,7 +36368,7 @@
         <v>45797.56770833334</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36425,7 +36425,7 @@
         <v>45587.47273148148</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36482,7 +36482,7 @@
         <v>45630.39777777778</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36544,7 +36544,7 @@
         <v>45630.4022337963</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36606,7 +36606,7 @@
         <v>45846</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36668,7 +36668,7 @@
         <v>45887.68474537037</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36725,7 +36725,7 @@
         <v>45887.62953703704</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36782,7 +36782,7 @@
         <v>45679.36950231482</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36839,7 +36839,7 @@
         <v>45846.48190972222</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36896,7 +36896,7 @@
         <v>44321</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36958,7 +36958,7 @@
         <v>45644.62803240741</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -37015,7 +37015,7 @@
         <v>45887.62158564815</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37072,7 +37072,7 @@
         <v>45845.60700231481</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37129,7 +37129,7 @@
         <v>45846.73861111111</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37186,7 +37186,7 @@
         <v>45210.34773148148</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37243,7 +37243,7 @@
         <v>45271</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37300,7 +37300,7 @@
         <v>44750</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37357,7 +37357,7 @@
         <v>45708.52121527777</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37414,7 +37414,7 @@
         <v>45603.60537037037</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37471,7 +37471,7 @@
         <v>45642.60125</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37528,7 +37528,7 @@
         <v>45617.45760416667</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37585,7 +37585,7 @@
         <v>45887</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37642,7 +37642,7 @@
         <v>45736</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37699,7 +37699,7 @@
         <v>44614</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37756,7 +37756,7 @@
         <v>45884</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37813,7 +37813,7 @@
         <v>45892.38811342593</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37870,7 +37870,7 @@
         <v>45892.46936342592</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37927,7 +37927,7 @@
         <v>44889</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37984,7 +37984,7 @@
         <v>45198.41381944445</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -38041,7 +38041,7 @@
         <v>45198.41887731481</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38098,7 +38098,7 @@
         <v>45892.43763888889</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38155,7 +38155,7 @@
         <v>45735.82282407407</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38212,7 +38212,7 @@
         <v>45892.42259259259</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38269,7 +38269,7 @@
         <v>45201.45827546297</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38326,7 +38326,7 @@
         <v>45870.62511574074</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38388,7 +38388,7 @@
         <v>45534.36645833333</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38445,7 +38445,7 @@
         <v>45693</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38502,7 +38502,7 @@
         <v>44729</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38559,7 +38559,7 @@
         <v>45469.43982638889</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38616,7 +38616,7 @@
         <v>45895.29351851852</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38673,7 +38673,7 @@
         <v>45253.73424768518</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38730,7 +38730,7 @@
         <v>45300</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38787,7 +38787,7 @@
         <v>45706.66388888889</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38849,7 +38849,7 @@
         <v>45706.67943287037</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38911,7 +38911,7 @@
         <v>45764.53740740741</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38968,7 +38968,7 @@
         <v>45215.71418981482</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -39025,7 +39025,7 @@
         <v>45392.58569444445</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39082,7 +39082,7 @@
         <v>44540.57753472222</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39139,7 +39139,7 @@
         <v>45149</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39196,7 +39196,7 @@
         <v>45751</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39258,7 +39258,7 @@
         <v>45630.3944675926</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39320,7 +39320,7 @@
         <v>45201</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39377,7 +39377,7 @@
         <v>45674.47359953704</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39434,7 +39434,7 @@
         <v>45898.46327546296</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39491,7 +39491,7 @@
         <v>44867</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39548,7 +39548,7 @@
         <v>45477.38554398148</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39605,7 +39605,7 @@
         <v>45477.38663194444</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39662,7 +39662,7 @@
         <v>44904</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39719,7 +39719,7 @@
         <v>45726.42344907407</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39781,7 +39781,7 @@
         <v>44719.43577546296</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39838,7 +39838,7 @@
         <v>45897</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39895,7 +39895,7 @@
         <v>45035</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39952,7 +39952,7 @@
         <v>44308.520625</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -40009,7 +40009,7 @@
         <v>45188.3012037037</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40066,7 +40066,7 @@
         <v>44103</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40123,7 +40123,7 @@
         <v>44130</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40180,7 +40180,7 @@
         <v>44803.44065972222</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40237,7 +40237,7 @@
         <v>44882</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40294,7 +40294,7 @@
         <v>44113</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40351,7 +40351,7 @@
         <v>45302</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40408,7 +40408,7 @@
         <v>45621</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40465,7 +40465,7 @@
         <v>45182</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40522,7 +40522,7 @@
         <v>44137</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40579,7 +40579,7 @@
         <v>44175</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40636,7 +40636,7 @@
         <v>45708.50255787037</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40693,7 +40693,7 @@
         <v>45715.65605324074</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40750,7 +40750,7 @@
         <v>44077</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40807,7 +40807,7 @@
         <v>44627.41212962963</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40864,7 +40864,7 @@
         <v>44985.35407407407</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40921,7 +40921,7 @@
         <v>44893</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40978,7 +40978,7 @@
         <v>44082</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -41035,7 +41035,7 @@
         <v>45547.43438657407</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41097,7 +41097,7 @@
         <v>45406.89568287037</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41154,7 +41154,7 @@
         <v>45406.89640046296</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41211,7 +41211,7 @@
         <v>44853</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41268,7 +41268,7 @@
         <v>44484</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41325,7 +41325,7 @@
         <v>45681.57619212963</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41382,7 +41382,7 @@
         <v>45682.47550925926</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41439,7 +41439,7 @@
         <v>44949</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41496,7 +41496,7 @@
         <v>44648</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41553,7 +41553,7 @@
         <v>44861.62300925926</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41610,7 +41610,7 @@
         <v>44412.7071875</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41667,7 +41667,7 @@
         <v>44938.53719907408</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41729,7 +41729,7 @@
         <v>44084.61673611111</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41786,7 +41786,7 @@
         <v>44361</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41843,7 +41843,7 @@
         <v>45375</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41900,7 +41900,7 @@
         <v>45758</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41962,7 +41962,7 @@
         <v>45180</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -42019,7 +42019,7 @@
         <v>45747.30204861111</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42076,7 +42076,7 @@
         <v>44943.44811342593</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42133,7 +42133,7 @@
         <v>45272.42149305555</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42190,7 +42190,7 @@
         <v>45260.85619212963</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42247,7 +42247,7 @@
         <v>44614.56209490741</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42304,7 +42304,7 @@
         <v>44074</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42366,7 +42366,7 @@
         <v>44711</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42423,7 +42423,7 @@
         <v>44886.3340625</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42480,7 +42480,7 @@
         <v>45043.67869212963</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42537,7 +42537,7 @@
         <v>44622</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42594,7 +42594,7 @@
         <v>44741.69432870371</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42651,7 +42651,7 @@
         <v>45058</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42708,7 +42708,7 @@
         <v>44173</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42765,7 +42765,7 @@
         <v>44662</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42822,7 +42822,7 @@
         <v>45184</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42879,7 +42879,7 @@
         <v>44082</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42936,7 +42936,7 @@
         <v>45735.81920138889</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42993,7 +42993,7 @@
         <v>45112</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43050,7 +43050,7 @@
         <v>45775.4233912037</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43107,7 +43107,7 @@
         <v>45749.67842592593</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43164,7 +43164,7 @@
         <v>45751.58130787037</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43221,7 +43221,7 @@
         <v>45706.69384259259</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43283,7 +43283,7 @@
         <v>45271</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43340,7 +43340,7 @@
         <v>44861.6108912037</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43397,7 +43397,7 @@
         <v>44861</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43454,7 +43454,7 @@
         <v>45587</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43511,7 +43511,7 @@
         <v>44211</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43568,7 +43568,7 @@
         <v>44468</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43625,7 +43625,7 @@
         <v>44148</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43682,7 +43682,7 @@
         <v>45706.69090277778</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43744,7 +43744,7 @@
         <v>45757</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43801,7 +43801,7 @@
         <v>45461.65380787037</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43858,7 +43858,7 @@
         <v>44904</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43920,7 +43920,7 @@
         <v>45541.36828703704</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43977,7 +43977,7 @@
         <v>45769.60440972223</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44034,7 +44034,7 @@
         <v>44433</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44091,7 +44091,7 @@
         <v>45043.43777777778</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44148,7 +44148,7 @@
         <v>45037.67510416666</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44205,7 +44205,7 @@
         <v>45079</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44262,7 +44262,7 @@
         <v>44151</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44319,7 +44319,7 @@
         <v>44897.3564699074</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44381,7 +44381,7 @@
         <v>45455.40401620371</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44443,7 +44443,7 @@
         <v>44507.43497685185</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44500,7 +44500,7 @@
         <v>45764.30016203703</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44557,7 +44557,7 @@
         <v>44882</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44614,7 +44614,7 @@
         <v>45764.30391203704</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44671,7 +44671,7 @@
         <v>44943.44532407408</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44728,7 +44728,7 @@
         <v>44943.48144675926</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44785,7 +44785,7 @@
         <v>45580.46572916667</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44842,7 +44842,7 @@
         <v>45355.56604166667</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44899,7 +44899,7 @@
         <v>45324.64302083333</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44961,7 +44961,7 @@
         <v>45740.59871527777</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -45018,7 +45018,7 @@
         <v>44963</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45075,7 +45075,7 @@
         <v>45770.51686342592</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45132,7 +45132,7 @@
         <v>45477.48915509259</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45189,7 +45189,7 @@
         <v>45408.67427083333</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45251,7 +45251,7 @@
         <v>45547.83519675926</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45313,7 +45313,7 @@
         <v>44158</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45370,7 +45370,7 @@
         <v>45034</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45427,7 +45427,7 @@
         <v>45183</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45484,7 +45484,7 @@
         <v>45056.6438425926</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45541,7 +45541,7 @@
         <v>44677</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45598,7 +45598,7 @@
         <v>44231</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45655,7 +45655,7 @@
         <v>45758</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45717,7 +45717,7 @@
         <v>45757.30554398148</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45774,7 +45774,7 @@
         <v>45755.70262731481</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45831,7 +45831,7 @@
         <v>45201.59743055556</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45888,7 +45888,7 @@
         <v>44295.31922453704</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45945,7 +45945,7 @@
         <v>44483.58045138889</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -46002,7 +46002,7 @@
         <v>45470.6672337963</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46059,7 +46059,7 @@
         <v>44992.67101851852</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46136,7 +46136,7 @@
         <v>45751.52445601852</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46198,7 +46198,7 @@
         <v>45748</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46260,7 +46260,7 @@
         <v>44658</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46317,7 +46317,7 @@
         <v>45092.42630787037</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46374,7 +46374,7 @@
         <v>45446.56622685185</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46431,7 +46431,7 @@
         <v>45049</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46488,7 +46488,7 @@
         <v>45051</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46545,7 +46545,7 @@
         <v>45048</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46602,7 +46602,7 @@
         <v>44959.36028935185</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46664,7 +46664,7 @@
         <v>45051.37461805555</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46721,7 +46721,7 @@
         <v>45764.4140162037</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46778,7 +46778,7 @@
         <v>44846.68375</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46835,7 +46835,7 @@
         <v>45130</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46892,7 +46892,7 @@
         <v>45764.31284722222</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46949,7 +46949,7 @@
         <v>45471.4034837963</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -47006,7 +47006,7 @@
         <v>44977.26482638889</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47063,7 +47063,7 @@
         <v>44998</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47120,7 +47120,7 @@
         <v>45673.71842592592</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47177,7 +47177,7 @@
         <v>45152</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47234,7 +47234,7 @@
         <v>45401</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47296,7 +47296,7 @@
         <v>45373.60802083334</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47353,7 +47353,7 @@
         <v>45127</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47410,7 +47410,7 @@
         <v>44967.6228125</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47467,7 +47467,7 @@
         <v>45605.84435185185</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47524,7 +47524,7 @@
         <v>45152</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47581,7 +47581,7 @@
         <v>45092</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47638,7 +47638,7 @@
         <v>45757.29700231482</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47695,7 +47695,7 @@
         <v>45615.90662037037</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47752,7 +47752,7 @@
         <v>44631</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47809,7 +47809,7 @@
         <v>45567</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47866,7 +47866,7 @@
         <v>45630.6993287037</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47923,7 +47923,7 @@
         <v>45240</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47980,7 +47980,7 @@
         <v>45642.92393518519</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48037,7 +48037,7 @@
         <v>44229</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48094,7 +48094,7 @@
         <v>44735</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48151,7 +48151,7 @@
         <v>45012</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48208,7 +48208,7 @@
         <v>45300</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48265,7 +48265,7 @@
         <v>45588</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48322,7 +48322,7 @@
         <v>44985</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48379,7 +48379,7 @@
         <v>45099</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48436,7 +48436,7 @@
         <v>45363.45982638889</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48493,7 +48493,7 @@
         <v>45177.5462962963</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48550,7 +48550,7 @@
         <v>45223.65527777778</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48607,7 +48607,7 @@
         <v>45181</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48664,7 +48664,7 @@
         <v>44840</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48721,7 +48721,7 @@
         <v>45252.58925925926</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48778,7 +48778,7 @@
         <v>44487</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48835,7 +48835,7 @@
         <v>45356.65395833334</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48897,7 +48897,7 @@
         <v>45107</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48954,7 +48954,7 @@
         <v>44588.50104166667</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -49011,7 +49011,7 @@
         <v>45747.44508101852</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49068,7 +49068,7 @@
         <v>45747.45177083334</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49125,7 +49125,7 @@
         <v>44979</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49182,7 +49182,7 @@
         <v>45201</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49244,7 +49244,7 @@
         <v>45545.53883101852</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49301,7 +49301,7 @@
         <v>45169</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49358,7 +49358,7 @@
         <v>45468.44574074074</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49415,7 +49415,7 @@
         <v>45775.32407407407</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49472,7 +49472,7 @@
         <v>45597.53744212963</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49529,7 +49529,7 @@
         <v>45447.55340277778</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49586,7 +49586,7 @@
         <v>45644.62243055556</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49643,7 +49643,7 @@
         <v>44904.49826388889</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49700,7 +49700,7 @@
         <v>44904</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49757,7 +49757,7 @@
         <v>44923.55936342593</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49814,7 +49814,7 @@
         <v>45414</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49871,7 +49871,7 @@
         <v>45377.42784722222</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49928,7 +49928,7 @@
         <v>45351.65180555556</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49990,7 +49990,7 @@
         <v>45617.48947916667</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50047,7 +50047,7 @@
         <v>45219</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50104,7 +50104,7 @@
         <v>45477.33712962963</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50161,7 +50161,7 @@
         <v>45406.89703703704</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50218,7 +50218,7 @@
         <v>45547.43793981482</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50280,7 +50280,7 @@
         <v>45492.70833333334</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -50337,7 +50337,7 @@
         <v>45566</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -50394,7 +50394,7 @@
         <v>45706.68554398148</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -50456,7 +50456,7 @@
         <v>45645.88440972222</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -50513,7 +50513,7 @@
         <v>45734.59972222222</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45900</v>
+        <v>45901</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>

--- a/Översikt JÖNKÖPING.xlsx
+++ b/Översikt JÖNKÖPING.xlsx
@@ -567,7 +567,7 @@
         <v>45856.56684027778</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -665,7 +665,7 @@
         <v>45856.57200231482</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
         <v>45777</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>45609</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         <v>45348</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         <v>44111</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>45698.48634259259</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>45275</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>44083</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>45846.47335648148</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>45788.88578703703</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>44992</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>44530</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>44512.62668981482</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>44602</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1960,7 +1960,7 @@
         <v>44974</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2047,7 +2047,7 @@
         <v>45604.53402777778</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2134,7 +2134,7 @@
         <v>45790.83706018519</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2220,7 +2220,7 @@
         <v>45539</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2306,7 +2306,7 @@
         <v>45302</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2392,7 +2392,7 @@
         <v>45679.98452546296</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2478,7 +2478,7 @@
         <v>45373.44148148148</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2564,7 +2564,7 @@
         <v>45898.45456018519</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2654,7 +2654,7 @@
         <v>44991</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2740,7 +2740,7 @@
         <v>45358.52763888889</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2826,7 +2826,7 @@
         <v>44278</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2911,7 +2911,7 @@
         <v>44419</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2996,7 +2996,7 @@
         <v>44463</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3081,7 +3081,7 @@
         <v>44095</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3166,7 +3166,7 @@
         <v>44347.63069444444</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3251,7 +3251,7 @@
         <v>44467</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3336,7 +3336,7 @@
         <v>44083</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3426,7 +3426,7 @@
         <v>44469</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3515,7 +3515,7 @@
         <v>45295.3942824074</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3605,7 +3605,7 @@
         <v>45580.46207175926</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3690,7 +3690,7 @@
         <v>44840</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3775,7 +3775,7 @@
         <v>45302</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3860,7 +3860,7 @@
         <v>44404.71972222222</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3945,7 +3945,7 @@
         <v>45783</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4030,7 +4030,7 @@
         <v>45740.58743055556</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4115,7 +4115,7 @@
         <v>45587</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4200,7 +4200,7 @@
         <v>45819.60131944445</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4285,7 +4285,7 @@
         <v>45876.69954861111</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         <v>45846</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4464,7 +4464,7 @@
         <v>45841.4303125</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4549,7 +4549,7 @@
         <v>45846</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4634,7 +4634,7 @@
         <v>45616</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4723,7 +4723,7 @@
         <v>45856.55965277777</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
         <v>44879</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4901,7 +4901,7 @@
         <v>45758</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         <v>45343</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5076,7 +5076,7 @@
         <v>44943</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5161,7 +5161,7 @@
         <v>45538.45523148148</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5246,7 +5246,7 @@
         <v>45205</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5331,7 +5331,7 @@
         <v>45569.41550925926</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5416,7 +5416,7 @@
         <v>44260</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5473,7 +5473,7 @@
         <v>44188</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5530,7 +5530,7 @@
         <v>44137</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5587,7 +5587,7 @@
         <v>44147</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5644,7 +5644,7 @@
         <v>44306</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5701,7 +5701,7 @@
         <v>44308</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5763,7 +5763,7 @@
         <v>44144</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5820,7 +5820,7 @@
         <v>44328.35063657408</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5877,7 +5877,7 @@
         <v>44239.33525462963</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5934,7 +5934,7 @@
         <v>44496</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5991,7 +5991,7 @@
         <v>44404.84280092592</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6048,7 +6048,7 @@
         <v>44404.84659722223</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6105,7 +6105,7 @@
         <v>44278.3859375</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6162,7 +6162,7 @@
         <v>44575.80925925926</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6219,7 +6219,7 @@
         <v>44662</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6276,7 +6276,7 @@
         <v>44487</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         <v>44749.55936342593</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6390,7 +6390,7 @@
         <v>44749.55703703704</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6447,7 +6447,7 @@
         <v>44273.62572916667</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6504,7 +6504,7 @@
         <v>44454.35472222222</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6561,7 +6561,7 @@
         <v>44308</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6623,7 +6623,7 @@
         <v>44225</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6680,7 +6680,7 @@
         <v>44308</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6742,7 +6742,7 @@
         <v>44349</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6799,7 +6799,7 @@
         <v>44792.53711805555</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6856,7 +6856,7 @@
         <v>44411</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6913,7 +6913,7 @@
         <v>44194</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6970,7 +6970,7 @@
         <v>44225</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -7027,7 +7027,7 @@
         <v>44809</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7084,7 +7084,7 @@
         <v>44442</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         <v>44487.49392361111</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7198,7 +7198,7 @@
         <v>44487</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7255,7 +7255,7 @@
         <v>44749.32716435185</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7312,7 +7312,7 @@
         <v>44420.68987268519</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7369,7 +7369,7 @@
         <v>44404.84138888889</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7426,7 +7426,7 @@
         <v>44266</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7483,7 +7483,7 @@
         <v>44881.81052083334</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7540,7 +7540,7 @@
         <v>44665.60081018518</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7597,7 +7597,7 @@
         <v>44869.49265046296</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7659,7 +7659,7 @@
         <v>44734</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7721,7 +7721,7 @@
         <v>44792</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7778,7 +7778,7 @@
         <v>44259</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7835,7 +7835,7 @@
         <v>44365</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7892,7 +7892,7 @@
         <v>44538</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7949,7 +7949,7 @@
         <v>44263</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -8011,7 +8011,7 @@
         <v>44113</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8068,7 +8068,7 @@
         <v>44487</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         <v>44487</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8182,7 +8182,7 @@
         <v>44272</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8239,7 +8239,7 @@
         <v>44875.59231481481</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8296,7 +8296,7 @@
         <v>44200</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8353,7 +8353,7 @@
         <v>44852.74376157407</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8415,7 +8415,7 @@
         <v>44498.56373842592</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8472,7 +8472,7 @@
         <v>44292</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8529,7 +8529,7 @@
         <v>44111</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8586,7 +8586,7 @@
         <v>44881.79847222222</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8643,7 +8643,7 @@
         <v>44286.34827546297</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8700,7 +8700,7 @@
         <v>44273</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8757,7 +8757,7 @@
         <v>44673</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8814,7 +8814,7 @@
         <v>44298.46462962963</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8876,7 +8876,7 @@
         <v>44298.46582175926</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8938,7 +8938,7 @@
         <v>44278.38752314815</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8995,7 +8995,7 @@
         <v>44279.37552083333</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9052,7 +9052,7 @@
         <v>44754.47359953704</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9114,7 +9114,7 @@
         <v>44347.61920138889</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9171,7 +9171,7 @@
         <v>44855.3080787037</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9228,7 +9228,7 @@
         <v>44476</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9285,7 +9285,7 @@
         <v>44373.75251157407</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9342,7 +9342,7 @@
         <v>44347.6287962963</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9399,7 +9399,7 @@
         <v>44511</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9456,7 +9456,7 @@
         <v>44466.4425</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9513,7 +9513,7 @@
         <v>44377</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9570,7 +9570,7 @@
         <v>44440.71997685185</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9627,7 +9627,7 @@
         <v>44840</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9684,7 +9684,7 @@
         <v>44104</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9741,7 +9741,7 @@
         <v>44280</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9798,7 +9798,7 @@
         <v>44613</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9855,7 +9855,7 @@
         <v>44456.46952546296</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9912,7 +9912,7 @@
         <v>44537</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9969,7 +9969,7 @@
         <v>44356</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -10026,7 +10026,7 @@
         <v>44476</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10083,7 +10083,7 @@
         <v>44360</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10140,7 +10140,7 @@
         <v>44575</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10197,7 +10197,7 @@
         <v>44298.44060185185</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10259,7 +10259,7 @@
         <v>44711</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10316,7 +10316,7 @@
         <v>44659.57226851852</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10378,7 +10378,7 @@
         <v>44659</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10440,7 +10440,7 @@
         <v>44454.4800925926</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10497,7 +10497,7 @@
         <v>44578</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10554,7 +10554,7 @@
         <v>44628</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10611,7 +10611,7 @@
         <v>44474.25150462963</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10668,7 +10668,7 @@
         <v>44711</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10725,7 +10725,7 @@
         <v>44711</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10782,7 +10782,7 @@
         <v>44082.79793981482</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10839,7 +10839,7 @@
         <v>44082</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10896,7 +10896,7 @@
         <v>44841.31997685185</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10953,7 +10953,7 @@
         <v>44579.41064814815</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -11010,7 +11010,7 @@
         <v>44557.71989583333</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11067,7 +11067,7 @@
         <v>44467.68283564815</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11124,7 +11124,7 @@
         <v>44792.53936342592</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11181,7 +11181,7 @@
         <v>44616.39256944445</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11238,7 +11238,7 @@
         <v>44373</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11295,7 +11295,7 @@
         <v>44239</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11352,7 +11352,7 @@
         <v>44239</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11409,7 +11409,7 @@
         <v>44464.40523148148</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11466,7 +11466,7 @@
         <v>44259</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11523,7 +11523,7 @@
         <v>44294</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11580,7 +11580,7 @@
         <v>44575</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11637,7 +11637,7 @@
         <v>44532.30398148148</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11694,7 +11694,7 @@
         <v>44412</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11751,7 +11751,7 @@
         <v>44830.90146990741</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11808,7 +11808,7 @@
         <v>44787.80010416666</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11865,7 +11865,7 @@
         <v>44428.58511574074</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11927,7 +11927,7 @@
         <v>44593</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11984,7 +11984,7 @@
         <v>44428.34821759259</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12046,7 +12046,7 @@
         <v>44272</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12103,7 +12103,7 @@
         <v>44088</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12160,7 +12160,7 @@
         <v>44825.40940972222</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12222,7 +12222,7 @@
         <v>44729</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12279,7 +12279,7 @@
         <v>44614</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12341,7 +12341,7 @@
         <v>44308</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12403,7 +12403,7 @@
         <v>44585.30171296297</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12460,7 +12460,7 @@
         <v>44272</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12517,7 +12517,7 @@
         <v>44161.31023148148</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12574,7 +12574,7 @@
         <v>44579</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12631,7 +12631,7 @@
         <v>44711</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12688,7 +12688,7 @@
         <v>44428</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12750,7 +12750,7 @@
         <v>44279.61517361111</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12807,7 +12807,7 @@
         <v>44805</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12869,7 +12869,7 @@
         <v>44811</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12926,7 +12926,7 @@
         <v>44151</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12983,7 +12983,7 @@
         <v>44464.42415509259</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13040,7 +13040,7 @@
         <v>44488</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13097,7 +13097,7 @@
         <v>44536</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13159,7 +13159,7 @@
         <v>45747.73295138889</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13216,7 +13216,7 @@
         <v>45404.58408564814</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13273,7 +13273,7 @@
         <v>44252</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13330,7 +13330,7 @@
         <v>44326</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13387,7 +13387,7 @@
         <v>44575.8194212963</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13444,7 +13444,7 @@
         <v>45697.26537037037</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13501,7 +13501,7 @@
         <v>45735.81920138889</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13558,7 +13558,7 @@
         <v>45169</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13615,7 +13615,7 @@
         <v>45048</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13672,7 +13672,7 @@
         <v>45605.84435185185</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13729,7 +13729,7 @@
         <v>45152</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13786,7 +13786,7 @@
         <v>44428.596875</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13848,7 +13848,7 @@
         <v>44819</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13905,7 +13905,7 @@
         <v>44819.28449074074</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13962,7 +13962,7 @@
         <v>44596</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -14019,7 +14019,7 @@
         <v>44498.57181712963</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14076,7 +14076,7 @@
         <v>44292</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14133,7 +14133,7 @@
         <v>44846.66688657407</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14190,7 +14190,7 @@
         <v>44605.44909722222</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14247,7 +14247,7 @@
         <v>44523.65311342593</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14304,7 +14304,7 @@
         <v>44589.73825231481</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14361,7 +14361,7 @@
         <v>45758</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14423,7 +14423,7 @@
         <v>45747.45038194444</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14480,7 +14480,7 @@
         <v>45547.43438657407</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14542,7 +14542,7 @@
         <v>45145.47684027778</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14599,7 +14599,7 @@
         <v>44344</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14656,7 +14656,7 @@
         <v>45111</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14713,7 +14713,7 @@
         <v>44628</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14770,7 +14770,7 @@
         <v>45772.45813657407</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14827,7 +14827,7 @@
         <v>45056.6438425926</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14884,7 +14884,7 @@
         <v>45406.89568287037</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14941,7 +14941,7 @@
         <v>45406.89640046296</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14998,7 +14998,7 @@
         <v>45477.38181712963</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15055,7 +15055,7 @@
         <v>44853</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15117,7 +15117,7 @@
         <v>45747.45177083334</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15174,7 +15174,7 @@
         <v>45440.3712037037</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15231,7 +15231,7 @@
         <v>45216.47443287037</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15288,7 +15288,7 @@
         <v>45777.50512731481</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15345,7 +15345,7 @@
         <v>45667.63950231481</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15402,7 +15402,7 @@
         <v>45198.41381944445</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15459,7 +15459,7 @@
         <v>45198.41887731481</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15516,7 +15516,7 @@
         <v>45642.60125</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15573,7 +15573,7 @@
         <v>45777.60824074074</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15630,7 +15630,7 @@
         <v>44557</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15687,7 +15687,7 @@
         <v>44886.3340625</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15744,7 +15744,7 @@
         <v>44658</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15801,7 +15801,7 @@
         <v>45303.63494212963</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15863,7 +15863,7 @@
         <v>45580.46572916667</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15920,7 +15920,7 @@
         <v>44550.30402777778</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15977,7 +15977,7 @@
         <v>45455.42533564815</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -16039,7 +16039,7 @@
         <v>45519.48550925926</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16096,7 +16096,7 @@
         <v>45130</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16153,7 +16153,7 @@
         <v>45477.33712962963</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16210,7 +16210,7 @@
         <v>45547.83519675926</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16272,7 +16272,7 @@
         <v>45112.3174074074</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16329,7 +16329,7 @@
         <v>45112</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16386,7 +16386,7 @@
         <v>45177</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16443,7 +16443,7 @@
         <v>45307.72520833334</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16500,7 +16500,7 @@
         <v>45174</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16557,7 +16557,7 @@
         <v>45012.47533564815</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16614,7 +16614,7 @@
         <v>45092.42630787037</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16671,7 +16671,7 @@
         <v>45435.51875</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16728,7 +16728,7 @@
         <v>45557.35435185185</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16785,7 +16785,7 @@
         <v>45268</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16842,7 +16842,7 @@
         <v>45785.65899305556</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16899,7 +16899,7 @@
         <v>45252.58925925926</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16956,7 +16956,7 @@
         <v>44614</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -17013,7 +17013,7 @@
         <v>45726.42344907407</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17075,7 +17075,7 @@
         <v>45405</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17132,7 +17132,7 @@
         <v>45405</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17189,7 +17189,7 @@
         <v>45272.42149305555</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17246,7 +17246,7 @@
         <v>45586.62837962963</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17303,7 +17303,7 @@
         <v>45621</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17360,7 +17360,7 @@
         <v>44943.44811342593</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17417,7 +17417,7 @@
         <v>45462.38087962963</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17474,7 +17474,7 @@
         <v>44861.62300925926</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17531,7 +17531,7 @@
         <v>44750</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17588,7 +17588,7 @@
         <v>44998</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17645,7 +17645,7 @@
         <v>45621.52488425926</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17702,7 +17702,7 @@
         <v>45621.5278125</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17759,7 +17759,7 @@
         <v>45436.68626157408</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17816,7 +17816,7 @@
         <v>45295.4037962963</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17878,7 +17878,7 @@
         <v>45392.58569444445</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17935,7 +17935,7 @@
         <v>45114.55280092593</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17992,7 +17992,7 @@
         <v>45764.30391203704</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18049,7 +18049,7 @@
         <v>45324.64302083333</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18111,7 +18111,7 @@
         <v>45270.42966435185</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18168,7 +18168,7 @@
         <v>44711</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18225,7 +18225,7 @@
         <v>45588</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18282,7 +18282,7 @@
         <v>45788.3231712963</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18339,7 +18339,7 @@
         <v>45179.9259375</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18396,7 +18396,7 @@
         <v>44507.43497685185</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18453,7 +18453,7 @@
         <v>45775.4233912037</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18510,7 +18510,7 @@
         <v>44118</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18572,7 +18572,7 @@
         <v>45755.70262731481</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18629,7 +18629,7 @@
         <v>45617.4922337963</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18686,7 +18686,7 @@
         <v>45469.43982638889</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18743,7 +18743,7 @@
         <v>44979</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18800,7 +18800,7 @@
         <v>45789.54226851852</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18857,7 +18857,7 @@
         <v>45456.66137731481</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18914,7 +18914,7 @@
         <v>45790.81799768518</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18971,7 +18971,7 @@
         <v>45618</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -19028,7 +19028,7 @@
         <v>45012</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19085,7 +19085,7 @@
         <v>44130</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19142,7 +19142,7 @@
         <v>45645.57626157408</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19199,7 +19199,7 @@
         <v>45275</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19256,7 +19256,7 @@
         <v>45541.38644675926</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19313,7 +19313,7 @@
         <v>45551.36004629629</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19370,7 +19370,7 @@
         <v>44151</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19427,7 +19427,7 @@
         <v>45350.56959490741</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19484,7 +19484,7 @@
         <v>45757.29700231482</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19541,7 +19541,7 @@
         <v>45646.5796412037</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19598,7 +19598,7 @@
         <v>44187</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19660,7 +19660,7 @@
         <v>45790.82361111111</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19717,7 +19717,7 @@
         <v>44936</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19774,7 +19774,7 @@
         <v>45538</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19831,7 +19831,7 @@
         <v>45791.85732638889</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19888,7 +19888,7 @@
         <v>44252</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19945,7 +19945,7 @@
         <v>44172</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -20002,7 +20002,7 @@
         <v>44103</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20059,7 +20059,7 @@
         <v>45630.70101851852</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20121,7 +20121,7 @@
         <v>44938.53719907408</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20183,7 +20183,7 @@
         <v>44943</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20240,7 +20240,7 @@
         <v>45302</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20297,7 +20297,7 @@
         <v>45300</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20354,7 +20354,7 @@
         <v>45412</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20416,7 +20416,7 @@
         <v>44273</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20473,7 +20473,7 @@
         <v>45764.4140162037</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20530,7 +20530,7 @@
         <v>45793</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20587,7 +20587,7 @@
         <v>45253.73424768518</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20644,7 +20644,7 @@
         <v>45331</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20701,7 +20701,7 @@
         <v>45182.36129629629</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20758,7 +20758,7 @@
         <v>45523.5090625</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20820,7 +20820,7 @@
         <v>45267.62943287037</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20877,7 +20877,7 @@
         <v>45570.58934027778</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20934,7 +20934,7 @@
         <v>45797.67148148148</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20991,7 +20991,7 @@
         <v>45149</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21048,7 +21048,7 @@
         <v>44943.44532407408</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21105,7 +21105,7 @@
         <v>44082</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21162,7 +21162,7 @@
         <v>45184</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21219,7 +21219,7 @@
         <v>45615.89965277778</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21276,7 +21276,7 @@
         <v>45615.90662037037</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21333,7 +21333,7 @@
         <v>45523.58461805555</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21395,7 +21395,7 @@
         <v>44231</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21452,7 +21452,7 @@
         <v>45706.67424768519</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21514,7 +21514,7 @@
         <v>44449</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21571,7 +21571,7 @@
         <v>45281.57759259259</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21633,7 +21633,7 @@
         <v>45741.65699074074</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21690,7 +21690,7 @@
         <v>45116.44680555556</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21747,7 +21747,7 @@
         <v>45741.69303240741</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21804,7 +21804,7 @@
         <v>45755</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21861,7 +21861,7 @@
         <v>44944.40825231482</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21918,7 +21918,7 @@
         <v>44614.68596064814</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21975,7 +21975,7 @@
         <v>44090</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -22032,7 +22032,7 @@
         <v>44729</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22089,7 +22089,7 @@
         <v>45727.35745370371</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22146,7 +22146,7 @@
         <v>45727.36243055556</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22203,7 +22203,7 @@
         <v>45734.3584837963</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22260,7 +22260,7 @@
         <v>45736</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22317,7 +22317,7 @@
         <v>45545.53883101852</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22374,7 +22374,7 @@
         <v>45740.91412037037</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22431,7 +22431,7 @@
         <v>45799.52318287037</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22488,7 +22488,7 @@
         <v>45730.3782175926</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22550,7 +22550,7 @@
         <v>45736</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22607,7 +22607,7 @@
         <v>45751.58130787037</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22664,7 +22664,7 @@
         <v>44137</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22721,7 +22721,7 @@
         <v>45799.5803125</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22778,7 +22778,7 @@
         <v>44949</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22835,7 +22835,7 @@
         <v>45743.59641203703</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22892,7 +22892,7 @@
         <v>45736.67693287037</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22949,7 +22949,7 @@
         <v>45740.59474537037</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -23006,7 +23006,7 @@
         <v>44648.61840277778</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23063,7 +23063,7 @@
         <v>45727.3134375</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23120,7 +23120,7 @@
         <v>45727.36650462963</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23177,7 +23177,7 @@
         <v>45470.6672337963</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23234,7 +23234,7 @@
         <v>45177.5462962963</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23291,7 +23291,7 @@
         <v>45519.49606481481</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23348,7 +23348,7 @@
         <v>44295.31922453704</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23405,7 +23405,7 @@
         <v>45799.58894675926</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23462,7 +23462,7 @@
         <v>44963</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23519,7 +23519,7 @@
         <v>44482</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23576,7 +23576,7 @@
         <v>45728</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23633,7 +23633,7 @@
         <v>44662</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23690,7 +23690,7 @@
         <v>45799.50469907407</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23747,7 +23747,7 @@
         <v>45735.65969907407</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23804,7 +23804,7 @@
         <v>44211</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23861,7 +23861,7 @@
         <v>44904.49826388889</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23918,7 +23918,7 @@
         <v>44938</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23980,7 +23980,7 @@
         <v>45799.51578703704</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24037,7 +24037,7 @@
         <v>45588</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24094,7 +24094,7 @@
         <v>45735</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24151,7 +24151,7 @@
         <v>45737.67416666666</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24208,7 +24208,7 @@
         <v>45730.65831018519</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24265,7 +24265,7 @@
         <v>45734.35039351852</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24322,7 +24322,7 @@
         <v>45734.35122685185</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24379,7 +24379,7 @@
         <v>45726.52925925926</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24436,7 +24436,7 @@
         <v>44904.59393518518</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24498,7 +24498,7 @@
         <v>44897</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24555,7 +24555,7 @@
         <v>44904.61212962963</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24617,7 +24617,7 @@
         <v>44861.6108912037</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24674,7 +24674,7 @@
         <v>44861</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24731,7 +24731,7 @@
         <v>44655.48328703704</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24788,7 +24788,7 @@
         <v>45687</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24845,7 +24845,7 @@
         <v>45687</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24902,7 +24902,7 @@
         <v>45769.43446759259</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24959,7 +24959,7 @@
         <v>45272</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -25016,7 +25016,7 @@
         <v>45406</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25073,7 +25073,7 @@
         <v>45622.35340277778</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25130,7 +25130,7 @@
         <v>44368.64017361111</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25187,7 +25187,7 @@
         <v>45587</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25244,7 +25244,7 @@
         <v>45730.44528935185</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25306,7 +25306,7 @@
         <v>44992.66236111111</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25363,7 +25363,7 @@
         <v>45205</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25420,7 +25420,7 @@
         <v>44839</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25482,7 +25482,7 @@
         <v>45092.39466435185</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25539,7 +25539,7 @@
         <v>44423.87825231482</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25596,7 +25596,7 @@
         <v>44893</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25653,7 +25653,7 @@
         <v>44882</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25710,7 +25710,7 @@
         <v>45733</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25767,7 +25767,7 @@
         <v>45805</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25824,7 +25824,7 @@
         <v>44225</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25881,7 +25881,7 @@
         <v>45363.91521990741</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25938,7 +25938,7 @@
         <v>45183</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25995,7 +25995,7 @@
         <v>45804.31922453704</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26052,7 +26052,7 @@
         <v>45769.60498842593</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26109,7 +26109,7 @@
         <v>45314</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26166,7 +26166,7 @@
         <v>45373.60802083334</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26223,7 +26223,7 @@
         <v>45805.60481481482</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26280,7 +26280,7 @@
         <v>45805.58372685185</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26337,7 +26337,7 @@
         <v>45455.4374537037</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26399,7 +26399,7 @@
         <v>45804</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26456,7 +26456,7 @@
         <v>45805.58325231481</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26513,7 +26513,7 @@
         <v>44484.49586805556</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26570,7 +26570,7 @@
         <v>45806.2833912037</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26627,7 +26627,7 @@
         <v>45806.28703703704</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26684,7 +26684,7 @@
         <v>44571</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26741,7 +26741,7 @@
         <v>45539.34539351852</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26798,7 +26798,7 @@
         <v>45806.26452546296</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26855,7 +26855,7 @@
         <v>45226.3731712963</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26912,7 +26912,7 @@
         <v>45624.41041666667</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26969,7 +26969,7 @@
         <v>44589.74348379629</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27026,7 +27026,7 @@
         <v>44592.28611111111</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27083,7 +27083,7 @@
         <v>44578.52657407407</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27140,7 +27140,7 @@
         <v>45547.83950231481</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27202,7 +27202,7 @@
         <v>45597.43615740741</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27259,7 +27259,7 @@
         <v>45811</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27316,7 +27316,7 @@
         <v>45587</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27373,7 +27373,7 @@
         <v>44804</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27430,7 +27430,7 @@
         <v>45043.67869212963</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27487,7 +27487,7 @@
         <v>45455.42981481482</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27549,7 +27549,7 @@
         <v>45113.31806712963</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27606,7 +27606,7 @@
         <v>45182.71081018518</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27663,7 +27663,7 @@
         <v>45810</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27720,7 +27720,7 @@
         <v>45751.52445601852</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27782,7 +27782,7 @@
         <v>45461.65380787037</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27839,7 +27839,7 @@
         <v>44622</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27896,7 +27896,7 @@
         <v>44893</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27958,7 +27958,7 @@
         <v>45701.38606481482</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28015,7 +28015,7 @@
         <v>45037.67510416666</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28072,7 +28072,7 @@
         <v>45600.48127314815</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28129,7 +28129,7 @@
         <v>45600.48347222222</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28186,7 +28186,7 @@
         <v>45558.63807870371</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28248,7 +28248,7 @@
         <v>44992.67101851852</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28325,7 +28325,7 @@
         <v>45637.51090277778</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28382,7 +28382,7 @@
         <v>45644.62803240741</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28439,7 +28439,7 @@
         <v>44433</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28496,7 +28496,7 @@
         <v>45643.89232638889</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28553,7 +28553,7 @@
         <v>45701.37818287037</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28610,7 +28610,7 @@
         <v>45726.44835648148</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28667,7 +28667,7 @@
         <v>44608</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28724,7 +28724,7 @@
         <v>45561.87885416667</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28781,7 +28781,7 @@
         <v>45215.71418981482</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28838,7 +28838,7 @@
         <v>44734</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28900,7 +28900,7 @@
         <v>44734</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28962,7 +28962,7 @@
         <v>44904</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -29019,7 +29019,7 @@
         <v>45819.53688657407</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29076,7 +29076,7 @@
         <v>45819.53980324074</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29133,7 +29133,7 @@
         <v>45819.5429050926</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29190,7 +29190,7 @@
         <v>45197.38018518518</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29247,7 +29247,7 @@
         <v>45321</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29304,7 +29304,7 @@
         <v>45468.44574074074</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29361,7 +29361,7 @@
         <v>45043</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29418,7 +29418,7 @@
         <v>45371.60959490741</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29475,7 +29475,7 @@
         <v>45597.53744212963</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29532,7 +29532,7 @@
         <v>44308.520625</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29589,7 +29589,7 @@
         <v>45372.34530092592</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29646,7 +29646,7 @@
         <v>45867.66349537037</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29703,7 +29703,7 @@
         <v>45682.47550925926</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29760,7 +29760,7 @@
         <v>44977.26300925926</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29817,7 +29817,7 @@
         <v>45446.56622685185</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29874,7 +29874,7 @@
         <v>45826</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29931,7 +29931,7 @@
         <v>45870.62930555556</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29993,7 +29993,7 @@
         <v>45545.59315972222</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30055,7 +30055,7 @@
         <v>45831.51019675926</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30112,7 +30112,7 @@
         <v>45617.92190972222</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30169,7 +30169,7 @@
         <v>45833.65434027778</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30226,7 +30226,7 @@
         <v>45875.57328703703</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30288,7 +30288,7 @@
         <v>45875.60922453704</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30345,7 +30345,7 @@
         <v>45833.63770833334</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30402,7 +30402,7 @@
         <v>44711</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30459,7 +30459,7 @@
         <v>45477.48771990741</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30516,7 +30516,7 @@
         <v>45477.48915509259</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30573,7 +30573,7 @@
         <v>44585</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30630,7 +30630,7 @@
         <v>45152</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30687,7 +30687,7 @@
         <v>45877.87582175926</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30744,7 +30744,7 @@
         <v>45876.6799537037</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30801,7 +30801,7 @@
         <v>45834.48820601852</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30858,7 +30858,7 @@
         <v>45880.49957175926</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30915,7 +30915,7 @@
         <v>45880.43709490741</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30972,7 +30972,7 @@
         <v>45880.46642361111</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -31029,7 +31029,7 @@
         <v>45299</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31086,7 +31086,7 @@
         <v>45839.71761574074</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31143,7 +31143,7 @@
         <v>45841.71503472222</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31200,7 +31200,7 @@
         <v>45882.43462962963</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31257,7 +31257,7 @@
         <v>45841.4390625</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31314,7 +31314,7 @@
         <v>45883.58956018519</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31371,7 +31371,7 @@
         <v>45883.59239583334</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31428,7 +31428,7 @@
         <v>45883.60604166667</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31485,7 +31485,7 @@
         <v>45883.60416666666</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31542,7 +31542,7 @@
         <v>45750.50650462963</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31599,7 +31599,7 @@
         <v>44998.8734837963</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31656,7 +31656,7 @@
         <v>45701.31962962963</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31713,7 +31713,7 @@
         <v>45756</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31770,7 +31770,7 @@
         <v>45175.44625</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31827,7 +31827,7 @@
         <v>45887.62158564815</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31884,7 +31884,7 @@
         <v>45887.62953703704</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31941,7 +31941,7 @@
         <v>45118</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31998,7 +31998,7 @@
         <v>45842.49056712963</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32055,7 +32055,7 @@
         <v>45887.68474537037</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32112,7 +32112,7 @@
         <v>45351.65180555556</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32174,7 +32174,7 @@
         <v>45797.56770833334</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32231,7 +32231,7 @@
         <v>45845.60700231481</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32288,7 +32288,7 @@
         <v>45842.49457175926</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32345,7 +32345,7 @@
         <v>45842.5059375</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32402,7 +32402,7 @@
         <v>45587.47273148148</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32459,7 +32459,7 @@
         <v>45846.73861111111</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32516,7 +32516,7 @@
         <v>44591</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32573,7 +32573,7 @@
         <v>45603.60537037037</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32630,7 +32630,7 @@
         <v>45846.48190972222</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32687,7 +32687,7 @@
         <v>45708.50255787037</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32744,7 +32744,7 @@
         <v>45846</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32806,7 +32806,7 @@
         <v>45211</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32863,7 +32863,7 @@
         <v>45112</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32920,7 +32920,7 @@
         <v>45846</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32982,7 +32982,7 @@
         <v>45846</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33044,7 +33044,7 @@
         <v>44846.68375</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33101,7 +33101,7 @@
         <v>45895.29351851852</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33158,7 +33158,7 @@
         <v>45892.42259259259</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33215,7 +33215,7 @@
         <v>45751</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33277,7 +33277,7 @@
         <v>45892.46936342592</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33334,7 +33334,7 @@
         <v>45892.38811342593</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33391,7 +33391,7 @@
         <v>45892.43763888889</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33448,7 +33448,7 @@
         <v>45764.53740740741</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33505,7 +33505,7 @@
         <v>45775.32407407407</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33562,7 +33562,7 @@
         <v>45502.32021990741</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33619,7 +33619,7 @@
         <v>45375</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33676,7 +33676,7 @@
         <v>45630.3944675926</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33738,7 +33738,7 @@
         <v>45701</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33795,7 +33795,7 @@
         <v>45898.46327546296</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33852,7 +33852,7 @@
         <v>45860.54674768518</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33909,7 +33909,7 @@
         <v>45788.32225694445</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33966,7 +33966,7 @@
         <v>44904</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -34028,7 +34028,7 @@
         <v>44158</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34085,7 +34085,7 @@
         <v>45541.36828703704</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34142,7 +34142,7 @@
         <v>45861.68065972222</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34199,7 +34199,7 @@
         <v>45861.46241898148</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34256,7 +34256,7 @@
         <v>44853</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34313,7 +34313,7 @@
         <v>45492.70833333334</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34370,7 +34370,7 @@
         <v>45902.67267361111</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34427,7 +34427,7 @@
         <v>45674.47359953704</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34484,7 +34484,7 @@
         <v>45189</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34541,7 +34541,7 @@
         <v>45905.30556712963</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34598,7 +34598,7 @@
         <v>44507.82581018518</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34655,7 +34655,7 @@
         <v>45358</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34712,7 +34712,7 @@
         <v>45358.61696759259</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34769,7 +34769,7 @@
         <v>45905.29668981482</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34826,7 +34826,7 @@
         <v>45905.2990162037</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34883,7 +34883,7 @@
         <v>44449</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34940,7 +34940,7 @@
         <v>45887</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34997,7 +34997,7 @@
         <v>45562.38306712963</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35054,7 +35054,7 @@
         <v>45477.38554398148</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35111,7 +35111,7 @@
         <v>45477.38663194444</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35168,7 +35168,7 @@
         <v>45434.58377314815</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35225,7 +35225,7 @@
         <v>45862.63645833333</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35282,7 +35282,7 @@
         <v>44097</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35339,7 +35339,7 @@
         <v>45359.54100694445</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35396,7 +35396,7 @@
         <v>45294</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35458,7 +35458,7 @@
         <v>45870.62511574074</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35520,7 +35520,7 @@
         <v>45243</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35582,7 +35582,7 @@
         <v>45897</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35639,7 +35639,7 @@
         <v>45079</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35696,7 +35696,7 @@
         <v>45184</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35753,7 +35753,7 @@
         <v>45757</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35810,7 +35810,7 @@
         <v>45884</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35867,7 +35867,7 @@
         <v>45905.30106481481</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35924,7 +35924,7 @@
         <v>44083</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35981,7 +35981,7 @@
         <v>44355.60153935185</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36038,7 +36038,7 @@
         <v>45035</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36095,7 +36095,7 @@
         <v>44950</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36152,7 +36152,7 @@
         <v>44950</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36209,7 +36209,7 @@
         <v>44950</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36266,7 +36266,7 @@
         <v>45240</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36323,7 +36323,7 @@
         <v>44360.54226851852</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36380,7 +36380,7 @@
         <v>44626</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36437,7 +36437,7 @@
         <v>44930</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36494,7 +36494,7 @@
         <v>44082</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36551,7 +36551,7 @@
         <v>45246.50074074074</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36613,7 +36613,7 @@
         <v>45058</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36670,7 +36670,7 @@
         <v>45531</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36727,7 +36727,7 @@
         <v>45757.30554398148</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36784,7 +36784,7 @@
         <v>45679.36950231482</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36841,7 +36841,7 @@
         <v>45462.37888888889</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36898,7 +36898,7 @@
         <v>45201</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36955,7 +36955,7 @@
         <v>45747.44508101852</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -37012,7 +37012,7 @@
         <v>45547.53320601852</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37069,7 +37069,7 @@
         <v>45547.42313657407</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37131,7 +37131,7 @@
         <v>44325.76335648148</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37188,7 +37188,7 @@
         <v>45201.45827546297</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37245,7 +37245,7 @@
         <v>45119.54038194445</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37302,7 +37302,7 @@
         <v>45566</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37359,7 +37359,7 @@
         <v>45566</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37416,7 +37416,7 @@
         <v>44109</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37473,7 +37473,7 @@
         <v>44719.43577546296</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37530,7 +37530,7 @@
         <v>45335.76891203703</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37592,7 +37592,7 @@
         <v>45092</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37649,7 +37649,7 @@
         <v>45502.33179398148</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37706,7 +37706,7 @@
         <v>45099.74195601852</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37763,7 +37763,7 @@
         <v>44321</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37825,7 +37825,7 @@
         <v>44837</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37882,7 +37882,7 @@
         <v>45271</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37939,7 +37939,7 @@
         <v>45681.57619212963</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37996,7 +37996,7 @@
         <v>44943.48144675926</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38053,7 +38053,7 @@
         <v>45201</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38115,7 +38115,7 @@
         <v>44985</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38172,7 +38172,7 @@
         <v>44959.36028935185</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38234,7 +38234,7 @@
         <v>45210.34773148148</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38291,7 +38291,7 @@
         <v>44614.56209490741</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38348,7 +38348,7 @@
         <v>45021</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38405,7 +38405,7 @@
         <v>45245.46393518519</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38462,7 +38462,7 @@
         <v>44963.66563657407</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38519,7 +38519,7 @@
         <v>44935.37284722222</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38576,7 +38576,7 @@
         <v>44867</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38633,7 +38633,7 @@
         <v>45180</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38690,7 +38690,7 @@
         <v>44904</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38747,7 +38747,7 @@
         <v>44575.80709490741</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38804,7 +38804,7 @@
         <v>45497</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38861,7 +38861,7 @@
         <v>45735.82282407407</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38918,7 +38918,7 @@
         <v>45260.85619212963</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38975,7 +38975,7 @@
         <v>45107</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39032,7 +39032,7 @@
         <v>45764.40184027778</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39089,7 +39089,7 @@
         <v>45314</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39146,7 +39146,7 @@
         <v>45295.40646990741</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39208,7 +39208,7 @@
         <v>45008</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39265,7 +39265,7 @@
         <v>45105.34402777778</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39322,7 +39322,7 @@
         <v>45617.91424768518</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39379,7 +39379,7 @@
         <v>45474.70864583334</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39436,7 +39436,7 @@
         <v>45775.4219212963</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39493,7 +39493,7 @@
         <v>44113</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39550,7 +39550,7 @@
         <v>45534.36645833333</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39607,7 +39607,7 @@
         <v>45617.45760416667</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39664,7 +39664,7 @@
         <v>45700.60138888889</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39721,7 +39721,7 @@
         <v>44564.8419212963</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39778,7 +39778,7 @@
         <v>45124.59594907407</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39835,7 +39835,7 @@
         <v>45759.5549537037</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39892,7 +39892,7 @@
         <v>45051</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39949,7 +39949,7 @@
         <v>45377.42784722222</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -40006,7 +40006,7 @@
         <v>45219</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40063,7 +40063,7 @@
         <v>44261</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40120,7 +40120,7 @@
         <v>44487</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40177,7 +40177,7 @@
         <v>45363.45982638889</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40234,7 +40234,7 @@
         <v>44229</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40291,7 +40291,7 @@
         <v>45240</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40348,7 +40348,7 @@
         <v>44966.57471064815</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40410,7 +40410,7 @@
         <v>45194</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40467,7 +40467,7 @@
         <v>45194</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40524,7 +40524,7 @@
         <v>45408.67427083333</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40586,7 +40586,7 @@
         <v>45112</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40643,7 +40643,7 @@
         <v>44148</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40700,7 +40700,7 @@
         <v>45316</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40757,7 +40757,7 @@
         <v>45107</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40814,7 +40814,7 @@
         <v>44631</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40871,7 +40871,7 @@
         <v>45552.48335648148</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40928,7 +40928,7 @@
         <v>45015</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40985,7 +40985,7 @@
         <v>44904</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41042,7 +41042,7 @@
         <v>45049</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41099,7 +41099,7 @@
         <v>45338</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41161,7 +41161,7 @@
         <v>44893</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41223,7 +41223,7 @@
         <v>45716.7125</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41280,7 +41280,7 @@
         <v>44894</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41337,7 +41337,7 @@
         <v>45338.69246527777</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41399,7 +41399,7 @@
         <v>45630.6993287037</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41456,7 +41456,7 @@
         <v>44483.58045138889</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41513,7 +41513,7 @@
         <v>44735</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41570,7 +41570,7 @@
         <v>45169</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41627,7 +41627,7 @@
         <v>44893.50922453704</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41689,7 +41689,7 @@
         <v>44605.45792824074</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41746,7 +41746,7 @@
         <v>45679.98971064815</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41803,7 +41803,7 @@
         <v>45679.99299768519</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41860,7 +41860,7 @@
         <v>45197.61039351852</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41922,7 +41922,7 @@
         <v>45406.89703703704</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41979,7 +41979,7 @@
         <v>44985.35407407407</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -42036,7 +42036,7 @@
         <v>45769.60440972223</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42093,7 +42093,7 @@
         <v>45736</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42150,7 +42150,7 @@
         <v>45645.88440972222</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42207,7 +42207,7 @@
         <v>45051.37461805555</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42264,7 +42264,7 @@
         <v>44484</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42321,7 +42321,7 @@
         <v>45681.48793981481</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42378,7 +42378,7 @@
         <v>44412.7071875</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42435,7 +42435,7 @@
         <v>45770.51686342592</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42492,7 +42492,7 @@
         <v>45558.51949074074</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42554,7 +42554,7 @@
         <v>45758</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42616,7 +42616,7 @@
         <v>44923.55936342593</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42673,7 +42673,7 @@
         <v>45706.66618055556</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42735,7 +42735,7 @@
         <v>45671.44716435186</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42792,7 +42792,7 @@
         <v>45705</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42849,7 +42849,7 @@
         <v>45764.31284722222</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42906,7 +42906,7 @@
         <v>45740.59871527777</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42963,7 +42963,7 @@
         <v>45693</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -43020,7 +43020,7 @@
         <v>45300</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43077,7 +43077,7 @@
         <v>45009</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43134,7 +43134,7 @@
         <v>44272</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43191,7 +43191,7 @@
         <v>44090</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43248,7 +43248,7 @@
         <v>45127</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43305,7 +43305,7 @@
         <v>45681.53460648148</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43362,7 +43362,7 @@
         <v>44677</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43419,7 +43419,7 @@
         <v>45706.69090277778</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43481,7 +43481,7 @@
         <v>45756</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43538,7 +43538,7 @@
         <v>44659</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43600,7 +43600,7 @@
         <v>45324.64579861111</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43662,7 +43662,7 @@
         <v>45324.64745370371</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43724,7 +43724,7 @@
         <v>45671.44894675926</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43781,7 +43781,7 @@
         <v>45414</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43838,7 +43838,7 @@
         <v>45761.49107638889</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43895,7 +43895,7 @@
         <v>45455.40401620371</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43957,7 +43957,7 @@
         <v>44889</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -44014,7 +44014,7 @@
         <v>44741.69432870371</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44071,7 +44071,7 @@
         <v>45644.62243055556</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44128,7 +44128,7 @@
         <v>44853</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44185,7 +44185,7 @@
         <v>45401.34349537037</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44242,7 +44242,7 @@
         <v>44988</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44299,7 +44299,7 @@
         <v>45223.65527777778</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44356,7 +44356,7 @@
         <v>45471.4034837963</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44413,7 +44413,7 @@
         <v>45198.59607638889</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44470,7 +44470,7 @@
         <v>45547.43793981482</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44532,7 +44532,7 @@
         <v>45541.37402777778</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44589,7 +44589,7 @@
         <v>45764.30016203703</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44646,7 +44646,7 @@
         <v>45600.47958333333</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44703,7 +44703,7 @@
         <v>45435</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44765,7 +44765,7 @@
         <v>44414</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44822,7 +44822,7 @@
         <v>44967.6228125</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44879,7 +44879,7 @@
         <v>45704</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44936,7 +44936,7 @@
         <v>45364.40862268519</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44993,7 +44993,7 @@
         <v>45567</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -45050,7 +45050,7 @@
         <v>44734</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45112,7 +45112,7 @@
         <v>45188.3012037037</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45169,7 +45169,7 @@
         <v>45356.65395833334</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45231,7 +45231,7 @@
         <v>45181</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45288,7 +45288,7 @@
         <v>44882</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45345,7 +45345,7 @@
         <v>45617.48947916667</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45402,7 +45402,7 @@
         <v>44965</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45459,7 +45459,7 @@
         <v>45708.52121527777</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45516,7 +45516,7 @@
         <v>45747.30204861111</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45573,7 +45573,7 @@
         <v>45749.67842592593</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45630,7 +45630,7 @@
         <v>44648</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45687,7 +45687,7 @@
         <v>45533.46368055556</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45744,7 +45744,7 @@
         <v>44175</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45801,7 +45801,7 @@
         <v>45706.66388888889</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45863,7 +45863,7 @@
         <v>45706.67943287037</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45925,7 +45925,7 @@
         <v>45447.55340277778</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45982,7 +45982,7 @@
         <v>45706.68554398148</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -46044,7 +46044,7 @@
         <v>44249.66673611111</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46101,7 +46101,7 @@
         <v>44249</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46158,7 +46158,7 @@
         <v>45586</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46215,7 +46215,7 @@
         <v>45630.39777777778</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46277,7 +46277,7 @@
         <v>45630.4022337963</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46339,7 +46339,7 @@
         <v>45635.28104166667</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46396,7 +46396,7 @@
         <v>45764.42304398148</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46453,7 +46453,7 @@
         <v>45541</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46510,7 +46510,7 @@
         <v>45201</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46567,7 +46567,7 @@
         <v>45201.59743055556</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46624,7 +46624,7 @@
         <v>45341</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46681,7 +46681,7 @@
         <v>45194</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46738,7 +46738,7 @@
         <v>44950</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46795,7 +46795,7 @@
         <v>45099</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46852,7 +46852,7 @@
         <v>45681.57949074074</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46909,7 +46909,7 @@
         <v>45763.49306712963</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46966,7 +46966,7 @@
         <v>45643.47644675926</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -47023,7 +47023,7 @@
         <v>44943.4652199074</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47080,7 +47080,7 @@
         <v>44943.46980324074</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47137,7 +47137,7 @@
         <v>45587.49814814814</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47194,7 +47194,7 @@
         <v>45715.65605324074</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47251,7 +47251,7 @@
         <v>45642.8053125</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47313,7 +47313,7 @@
         <v>45642.92393518519</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47370,7 +47370,7 @@
         <v>45720.70986111111</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47427,7 +47427,7 @@
         <v>45734.59972222222</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47484,7 +47484,7 @@
         <v>44627.41212962963</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47541,7 +47541,7 @@
         <v>45056</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47598,7 +47598,7 @@
         <v>45043.43777777778</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47655,7 +47655,7 @@
         <v>44411</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47712,7 +47712,7 @@
         <v>45392.63664351852</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47769,7 +47769,7 @@
         <v>45643</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47826,7 +47826,7 @@
         <v>45764.53915509259</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47883,7 +47883,7 @@
         <v>45748</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47945,7 +47945,7 @@
         <v>45355.56604166667</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -48002,7 +48002,7 @@
         <v>45271</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -48059,7 +48059,7 @@
         <v>44173</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48116,7 +48116,7 @@
         <v>44966.52741898148</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48178,7 +48178,7 @@
         <v>44588.50104166667</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48235,7 +48235,7 @@
         <v>44488</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48292,7 +48292,7 @@
         <v>44361</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48349,7 +48349,7 @@
         <v>45215.72212962963</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48406,7 +48406,7 @@
         <v>44803.44065972222</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48463,7 +48463,7 @@
         <v>45197</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48520,7 +48520,7 @@
         <v>45547.84315972222</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48582,7 +48582,7 @@
         <v>45673.71842592592</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48639,7 +48639,7 @@
         <v>44957.36059027778</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48696,7 +48696,7 @@
         <v>45460.42804398148</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48753,7 +48753,7 @@
         <v>45691.5603125</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48810,7 +48810,7 @@
         <v>45030</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48867,7 +48867,7 @@
         <v>44897.3564699074</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48929,7 +48929,7 @@
         <v>45764.3996412037</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48986,7 +48986,7 @@
         <v>45764.42006944444</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -49043,7 +49043,7 @@
         <v>44977.26482638889</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49100,7 +49100,7 @@
         <v>45764.42517361111</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49157,7 +49157,7 @@
         <v>45545.65415509259</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49219,7 +49219,7 @@
         <v>45706.69384259259</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49281,7 +49281,7 @@
         <v>44540.57753472222</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49338,7 +49338,7 @@
         <v>45034</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49395,7 +49395,7 @@
         <v>45198.60034722222</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49452,7 +49452,7 @@
         <v>44468</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49509,7 +49509,7 @@
         <v>45750.40476851852</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49566,7 +49566,7 @@
         <v>45349</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49623,7 +49623,7 @@
         <v>45182</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49680,7 +49680,7 @@
         <v>45763.49402777778</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49737,7 +49737,7 @@
         <v>44084.61673611111</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49794,7 +49794,7 @@
         <v>45758</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49856,7 +49856,7 @@
         <v>45646.67994212963</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49913,7 +49913,7 @@
         <v>45184</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49970,7 +49970,7 @@
         <v>45169</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -50027,7 +50027,7 @@
         <v>45169.38410879629</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -50084,7 +50084,7 @@
         <v>44704.65815972222</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -50141,7 +50141,7 @@
         <v>45401</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -50203,7 +50203,7 @@
         <v>45414</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -50260,7 +50260,7 @@
         <v>45693.67859953704</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45907</v>
+        <v>45908</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>

--- a/Översikt JÖNKÖPING.xlsx
+++ b/Översikt JÖNKÖPING.xlsx
@@ -567,7 +567,7 @@
         <v>45856.56684027778</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -665,7 +665,7 @@
         <v>45856.57200231482</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
         <v>45777</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>45609</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         <v>45348</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         <v>44111</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>45275</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>45698.48634259259</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>45846.47335648148</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>45788.88578703703</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>44992</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>44530</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>44512.62668981482</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>44602</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>45604.53402777778</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>44974</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>45373.44148148148</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>45790.83706018519</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         <v>45679.98452546296</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>45358.52763888889</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
         <v>44991</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>45302</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         <v>45898.45456018519</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         <v>45539</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>44278</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>44419</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         <v>44463</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>44095</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>44347.63069444444</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>44467</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>44404.71972222222</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
         <v>44840</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
         <v>45783</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
         <v>45740.58743055556</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3582,7 +3582,7 @@
         <v>44469</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         <v>45587</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>45758</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3846,7 +3846,7 @@
         <v>45819.60131944445</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>45302</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4016,7 +4016,7 @@
         <v>45846</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4110,7 +4110,7 @@
         <v>45876.69954861111</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         <v>45580.46207175926</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>45295.3942824074</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         <v>45343</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4455,7 +4455,7 @@
         <v>45538.45523148148</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
         <v>45205</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4625,7 +4625,7 @@
         <v>44879</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4714,7 +4714,7 @@
         <v>45841.4303125</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4799,7 +4799,7 @@
         <v>45846</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v>45616</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4973,7 +4973,7 @@
         <v>45856.55965277777</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5062,7 +5062,7 @@
         <v>45569.41550925926</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5147,7 +5147,7 @@
         <v>44943</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5232,7 +5232,7 @@
         <v>44260</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5289,7 +5289,7 @@
         <v>44188</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5346,7 +5346,7 @@
         <v>44137</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5403,7 +5403,7 @@
         <v>44147</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         <v>44306</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5517,7 +5517,7 @@
         <v>44308</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
         <v>44144</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
         <v>44328.35063657408</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5693,7 +5693,7 @@
         <v>44496</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5750,7 +5750,7 @@
         <v>44278.3859375</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5807,7 +5807,7 @@
         <v>44575.80925925926</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5864,7 +5864,7 @@
         <v>44662</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5921,7 +5921,7 @@
         <v>44239.33525462963</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         <v>44404.84280092592</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6035,7 +6035,7 @@
         <v>44404.84659722223</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6092,7 +6092,7 @@
         <v>44487</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6149,7 +6149,7 @@
         <v>44749.55703703704</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6206,7 +6206,7 @@
         <v>44749.55936342593</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6263,7 +6263,7 @@
         <v>44273.62572916667</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6320,7 +6320,7 @@
         <v>44454.35472222222</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6377,7 +6377,7 @@
         <v>44308</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6439,7 +6439,7 @@
         <v>44225</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6496,7 +6496,7 @@
         <v>44308</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6558,7 +6558,7 @@
         <v>44349</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6615,7 +6615,7 @@
         <v>44792.53711805555</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6672,7 +6672,7 @@
         <v>44411</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6729,7 +6729,7 @@
         <v>44194</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6786,7 +6786,7 @@
         <v>44225</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6843,7 +6843,7 @@
         <v>44809</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6900,7 +6900,7 @@
         <v>44442</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6957,7 +6957,7 @@
         <v>44487</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         <v>44487.49392361111</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         <v>44749.32716435185</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7128,7 +7128,7 @@
         <v>44420.68987268519</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7185,7 +7185,7 @@
         <v>44404.84138888889</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7242,7 +7242,7 @@
         <v>44266</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
         <v>44881.81052083334</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7356,7 +7356,7 @@
         <v>44665.60081018518</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7413,7 +7413,7 @@
         <v>44869.49265046296</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         <v>44734</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7537,7 +7537,7 @@
         <v>44792</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7594,7 +7594,7 @@
         <v>44259</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7651,7 +7651,7 @@
         <v>44365</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7708,7 +7708,7 @@
         <v>44538</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7765,7 +7765,7 @@
         <v>44263</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7827,7 +7827,7 @@
         <v>44113</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7884,7 +7884,7 @@
         <v>44487</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7941,7 +7941,7 @@
         <v>44487</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7998,7 +7998,7 @@
         <v>44272</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         <v>44875.59231481481</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8112,7 +8112,7 @@
         <v>44852.74376157407</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8174,7 +8174,7 @@
         <v>44292</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8231,7 +8231,7 @@
         <v>44200</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8288,7 +8288,7 @@
         <v>44111</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8345,7 +8345,7 @@
         <v>44498.56373842592</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8402,7 +8402,7 @@
         <v>44881.79847222222</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         <v>44286.34827546297</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8516,7 +8516,7 @@
         <v>44273</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8573,7 +8573,7 @@
         <v>44673</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8630,7 +8630,7 @@
         <v>44298.46462962963</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
         <v>44298.46582175926</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8754,7 +8754,7 @@
         <v>44278.38752314815</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8811,7 +8811,7 @@
         <v>44279.37552083333</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8868,7 +8868,7 @@
         <v>44347.61920138889</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8925,7 +8925,7 @@
         <v>44754.47359953704</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8987,7 +8987,7 @@
         <v>44855.3080787037</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9044,7 +9044,7 @@
         <v>44476</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9101,7 +9101,7 @@
         <v>44373.75251157407</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9158,7 +9158,7 @@
         <v>44347.6287962963</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9215,7 +9215,7 @@
         <v>44511</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9272,7 +9272,7 @@
         <v>44466.4425</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9329,7 +9329,7 @@
         <v>44377</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9386,7 +9386,7 @@
         <v>44440.71997685185</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         <v>44840</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9500,7 +9500,7 @@
         <v>44104</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9557,7 +9557,7 @@
         <v>44280</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9614,7 +9614,7 @@
         <v>44613</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9671,7 +9671,7 @@
         <v>44456.46952546296</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9728,7 +9728,7 @@
         <v>44537</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9785,7 +9785,7 @@
         <v>44360</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9842,7 +9842,7 @@
         <v>44476</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9899,7 +9899,7 @@
         <v>44356</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9956,7 +9956,7 @@
         <v>44575</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10013,7 +10013,7 @@
         <v>44298.44060185185</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10075,7 +10075,7 @@
         <v>44659.57226851852</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10137,7 +10137,7 @@
         <v>44659</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10199,7 +10199,7 @@
         <v>44454.4800925926</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10256,7 +10256,7 @@
         <v>44711</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10313,7 +10313,7 @@
         <v>44578</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10370,7 +10370,7 @@
         <v>44344</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10427,7 +10427,7 @@
         <v>44596</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10484,7 +10484,7 @@
         <v>44628</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10541,7 +10541,7 @@
         <v>44498.57181712963</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10598,7 +10598,7 @@
         <v>44474.25150462963</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10655,7 +10655,7 @@
         <v>44711</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10712,7 +10712,7 @@
         <v>44711</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10769,7 +10769,7 @@
         <v>44841.31997685185</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10826,7 +10826,7 @@
         <v>44467.68283564815</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10883,7 +10883,7 @@
         <v>44792.53936342592</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10940,7 +10940,7 @@
         <v>44532.30398148148</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10997,7 +10997,7 @@
         <v>44579.41064814815</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11054,7 +11054,7 @@
         <v>44593</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11111,7 +11111,7 @@
         <v>44557.71989583333</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11168,7 +11168,7 @@
         <v>44259</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11225,7 +11225,7 @@
         <v>44616.39256944445</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11282,7 +11282,7 @@
         <v>44373</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11339,7 +11339,7 @@
         <v>44239</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11396,7 +11396,7 @@
         <v>44239</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11453,7 +11453,7 @@
         <v>44464.40523148148</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11510,7 +11510,7 @@
         <v>44294</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11567,7 +11567,7 @@
         <v>44575</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11624,7 +11624,7 @@
         <v>44412</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11681,7 +11681,7 @@
         <v>44830.90146990741</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11738,7 +11738,7 @@
         <v>44787.80010416666</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11795,7 +11795,7 @@
         <v>44428.58511574074</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11857,7 +11857,7 @@
         <v>44729</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11914,7 +11914,7 @@
         <v>44272</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11971,7 +11971,7 @@
         <v>44161.31023148148</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12028,7 +12028,7 @@
         <v>44825.40940972222</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12090,7 +12090,7 @@
         <v>44614</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12152,7 +12152,7 @@
         <v>44279.61517361111</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12209,7 +12209,7 @@
         <v>44805</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12271,7 +12271,7 @@
         <v>44585.30171296297</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12328,7 +12328,7 @@
         <v>44811</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12385,7 +12385,7 @@
         <v>44579</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12442,7 +12442,7 @@
         <v>44711</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12499,7 +12499,7 @@
         <v>44536</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         <v>44151</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12618,7 +12618,7 @@
         <v>44273</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12675,7 +12675,7 @@
         <v>44252</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12732,7 +12732,7 @@
         <v>44428.34821759259</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12794,7 +12794,7 @@
         <v>44272</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12851,7 +12851,7 @@
         <v>45621.52488425926</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12908,7 +12908,7 @@
         <v>45621.5278125</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12965,7 +12965,7 @@
         <v>45008</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13022,7 +13022,7 @@
         <v>45750.50650462963</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13079,7 +13079,7 @@
         <v>45338.69246527777</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13141,7 +13141,7 @@
         <v>44326</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13198,7 +13198,7 @@
         <v>44575.8194212963</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13255,7 +13255,7 @@
         <v>44428.596875</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13317,7 +13317,7 @@
         <v>45531</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13374,7 +13374,7 @@
         <v>44088</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13431,7 +13431,7 @@
         <v>45341</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13488,7 +13488,7 @@
         <v>44325.76335648148</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13545,7 +13545,7 @@
         <v>44819</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13602,7 +13602,7 @@
         <v>44819.28449074074</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13659,7 +13659,7 @@
         <v>44292</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13716,7 +13716,7 @@
         <v>44846.66688657407</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13773,7 +13773,7 @@
         <v>45406</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13830,7 +13830,7 @@
         <v>44605.44909722222</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13887,7 +13887,7 @@
         <v>44523.65311342593</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13944,7 +13944,7 @@
         <v>45324.64579861111</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14006,7 +14006,7 @@
         <v>45324.64745370371</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14068,7 +14068,7 @@
         <v>45772.45813657407</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14125,7 +14125,7 @@
         <v>45092.39466435185</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14182,7 +14182,7 @@
         <v>45775.4219212963</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14239,7 +14239,7 @@
         <v>45197.61039351852</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14301,7 +14301,7 @@
         <v>44804</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14358,7 +14358,7 @@
         <v>45697.26537037037</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14415,7 +14415,7 @@
         <v>45716.7125</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14472,7 +14472,7 @@
         <v>45111</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14529,7 +14529,7 @@
         <v>45615.89965277778</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14586,7 +14586,7 @@
         <v>45747.45038194444</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14643,7 +14643,7 @@
         <v>45701.38606481482</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14700,7 +14700,7 @@
         <v>45112</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14757,7 +14757,7 @@
         <v>44950</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14814,7 +14814,7 @@
         <v>44950</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14871,7 +14871,7 @@
         <v>45764.53915509259</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14928,7 +14928,7 @@
         <v>45349</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14985,7 +14985,7 @@
         <v>45119.54038194445</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15042,7 +15042,7 @@
         <v>44449</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15099,7 +15099,7 @@
         <v>45758</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15161,7 +15161,7 @@
         <v>44893</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15223,7 +15223,7 @@
         <v>45331</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15280,7 +15280,7 @@
         <v>44944.40825231482</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15337,7 +15337,7 @@
         <v>45764.3996412037</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15394,7 +15394,7 @@
         <v>45643.47644675926</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15451,7 +15451,7 @@
         <v>45307.72520833334</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15508,7 +15508,7 @@
         <v>45099.74195601852</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15565,7 +15565,7 @@
         <v>45116.44680555556</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15622,7 +15622,7 @@
         <v>45587.49814814814</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15679,7 +15679,7 @@
         <v>44957.36059027778</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15736,7 +15736,7 @@
         <v>45118</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15793,7 +15793,7 @@
         <v>45321</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15850,7 +15850,7 @@
         <v>45107</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15907,7 +15907,7 @@
         <v>45299</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15964,7 +15964,7 @@
         <v>45270.42966435185</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16021,7 +16021,7 @@
         <v>45474.70864583334</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16078,7 +16078,7 @@
         <v>45338</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16140,7 +16140,7 @@
         <v>45562.38306712963</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16197,7 +16197,7 @@
         <v>45667.63950231481</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16254,7 +16254,7 @@
         <v>45704</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16311,7 +16311,7 @@
         <v>44414</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16368,7 +16368,7 @@
         <v>45358</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16425,7 +16425,7 @@
         <v>45358.61696759259</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16482,7 +16482,7 @@
         <v>44484.49586805556</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16539,7 +16539,7 @@
         <v>45558.51949074074</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16601,7 +16601,7 @@
         <v>45777.60824074074</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16658,7 +16658,7 @@
         <v>45777.50512731481</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16715,7 +16715,7 @@
         <v>45281.57759259259</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16777,7 +16777,7 @@
         <v>45275</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16834,7 +16834,7 @@
         <v>45455.4374537037</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16896,7 +16896,7 @@
         <v>44628</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16953,7 +16953,7 @@
         <v>44893</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17015,7 +17015,7 @@
         <v>45335.76891203703</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17077,7 +17077,7 @@
         <v>44368.64017361111</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17134,7 +17134,7 @@
         <v>45243</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17196,7 +17196,7 @@
         <v>45541.37402777778</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17253,7 +17253,7 @@
         <v>44507.82581018518</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17310,7 +17310,7 @@
         <v>45586.62837962963</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17367,7 +17367,7 @@
         <v>44308</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17429,7 +17429,7 @@
         <v>45114.55280092593</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17486,7 +17486,7 @@
         <v>45519.48550925926</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17543,7 +17543,7 @@
         <v>45785.65899305556</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17600,7 +17600,7 @@
         <v>44837</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17657,7 +17657,7 @@
         <v>45477.48771990741</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17714,7 +17714,7 @@
         <v>45436.68626157408</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17771,7 +17771,7 @@
         <v>45314</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17828,7 +17828,7 @@
         <v>45455.42533564815</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17890,7 +17890,7 @@
         <v>45455.42981481482</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17952,7 +17952,7 @@
         <v>44963.66563657407</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18009,7 +18009,7 @@
         <v>44449</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18066,7 +18066,7 @@
         <v>45359.54100694445</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18123,7 +18123,7 @@
         <v>45124.59594907407</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18180,7 +18180,7 @@
         <v>45477.38181712963</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18237,7 +18237,7 @@
         <v>45533.46368055556</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18294,7 +18294,7 @@
         <v>45267.62943287037</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18351,7 +18351,7 @@
         <v>45539.34539351852</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18408,7 +18408,7 @@
         <v>45747.73295138889</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18465,7 +18465,7 @@
         <v>45460.42804398148</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18522,7 +18522,7 @@
         <v>45588</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18579,7 +18579,7 @@
         <v>45462.37888888889</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18636,7 +18636,7 @@
         <v>45789.54226851852</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18693,7 +18693,7 @@
         <v>44605.45792824074</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18750,7 +18750,7 @@
         <v>45502.32021990741</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18807,7 +18807,7 @@
         <v>45502.33179398148</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18864,7 +18864,7 @@
         <v>45175.44625</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18921,7 +18921,7 @@
         <v>44853</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18983,7 +18983,7 @@
         <v>44355.60153935185</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19040,7 +19040,7 @@
         <v>45586</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19097,7 +19097,7 @@
         <v>44428</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19159,7 +19159,7 @@
         <v>45646.5796412037</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19216,7 +19216,7 @@
         <v>45764.42304398148</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19273,7 +19273,7 @@
         <v>45145.47684027778</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19330,7 +19330,7 @@
         <v>44488</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19387,7 +19387,7 @@
         <v>45790.82361111111</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19444,7 +19444,7 @@
         <v>45405</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19501,7 +19501,7 @@
         <v>45405</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19558,7 +19558,7 @@
         <v>44966.57471064815</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19620,7 +19620,7 @@
         <v>45184</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19677,7 +19677,7 @@
         <v>44936</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19734,7 +19734,7 @@
         <v>45547.83950231481</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19796,7 +19796,7 @@
         <v>44578.52657407407</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19853,7 +19853,7 @@
         <v>44592.28611111111</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19910,7 +19910,7 @@
         <v>44411</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19967,7 +19967,7 @@
         <v>45541</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20024,7 +20024,7 @@
         <v>45545.65415509259</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20086,7 +20086,7 @@
         <v>45412</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20148,7 +20148,7 @@
         <v>45552.48335648148</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20205,7 +20205,7 @@
         <v>45462.38087962963</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20262,7 +20262,7 @@
         <v>44187</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20324,7 +20324,7 @@
         <v>45551.36004629629</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20381,7 +20381,7 @@
         <v>44585</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20438,7 +20438,7 @@
         <v>45541.38644675926</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20495,7 +20495,7 @@
         <v>44464.42415509259</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20552,7 +20552,7 @@
         <v>45763.49402777778</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         <v>45177</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20666,7 +20666,7 @@
         <v>44488</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20723,7 +20723,7 @@
         <v>44853</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20780,7 +20780,7 @@
         <v>45497</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20837,7 +20837,7 @@
         <v>45790.81799768518</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20894,7 +20894,7 @@
         <v>45791.85732638889</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20951,7 +20951,7 @@
         <v>45350.56959490741</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21008,7 +21008,7 @@
         <v>45600.47958333333</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21065,7 +21065,7 @@
         <v>45169.38410879629</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21122,7 +21122,7 @@
         <v>45205</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21179,7 +21179,7 @@
         <v>44935.37284722222</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21236,7 +21236,7 @@
         <v>45645.57626157408</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21293,7 +21293,7 @@
         <v>45012.47533564815</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21350,7 +21350,7 @@
         <v>45570.58934027778</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21407,7 +21407,7 @@
         <v>44482</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21464,7 +21464,7 @@
         <v>45184</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21521,7 +21521,7 @@
         <v>45793</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21578,7 +21578,7 @@
         <v>45557.35435185185</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21635,7 +21635,7 @@
         <v>45701.31962962963</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21692,7 +21692,7 @@
         <v>45635.28104166667</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21749,7 +21749,7 @@
         <v>45295.40646990741</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21811,7 +21811,7 @@
         <v>45681.48793981481</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21868,7 +21868,7 @@
         <v>45681.53460648148</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21925,7 +21925,7 @@
         <v>45736</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21982,7 +21982,7 @@
         <v>45740.59474537037</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22039,7 +22039,7 @@
         <v>45736.67693287037</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22096,7 +22096,7 @@
         <v>45727.3134375</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22153,7 +22153,7 @@
         <v>45727.36650462963</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22210,7 +22210,7 @@
         <v>44090</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22267,7 +22267,7 @@
         <v>45558.63807870371</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22329,7 +22329,7 @@
         <v>44591</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22386,7 +22386,7 @@
         <v>45735</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22443,7 +22443,7 @@
         <v>45734.35039351852</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22500,7 +22500,7 @@
         <v>45740.91412037037</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22557,7 +22557,7 @@
         <v>45741.65699074074</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22614,7 +22614,7 @@
         <v>45741.69303240741</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22671,7 +22671,7 @@
         <v>45735.65969907407</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22728,7 +22728,7 @@
         <v>44608</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22785,7 +22785,7 @@
         <v>45169</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22842,7 +22842,7 @@
         <v>45755</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22899,7 +22899,7 @@
         <v>45728</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22956,7 +22956,7 @@
         <v>45727.35745370371</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23013,7 +23013,7 @@
         <v>45727.36243055556</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23070,7 +23070,7 @@
         <v>45734.3584837963</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23127,7 +23127,7 @@
         <v>45736</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23184,7 +23184,7 @@
         <v>45743.59641203703</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23241,7 +23241,7 @@
         <v>45797.67148148148</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23298,7 +23298,7 @@
         <v>45734.35122685185</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23355,7 +23355,7 @@
         <v>45726.52925925926</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23412,7 +23412,7 @@
         <v>44626</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23469,7 +23469,7 @@
         <v>45730.65831018519</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23526,7 +23526,7 @@
         <v>45737.67416666666</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23583,7 +23583,7 @@
         <v>45730.3782175926</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23645,7 +23645,7 @@
         <v>45618</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23702,7 +23702,7 @@
         <v>45414</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23759,7 +23759,7 @@
         <v>45799.52318287037</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23816,7 +23816,7 @@
         <v>45799.58894675926</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23873,7 +23873,7 @@
         <v>45799.5803125</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23930,7 +23930,7 @@
         <v>44589.74348379629</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23987,7 +23987,7 @@
         <v>45799.50469907407</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24044,7 +24044,7 @@
         <v>44893.50922453704</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24106,7 +24106,7 @@
         <v>45545.59315972222</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24168,7 +24168,7 @@
         <v>45435</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24230,7 +24230,7 @@
         <v>45030</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24287,7 +24287,7 @@
         <v>45799.51578703704</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24344,7 +24344,7 @@
         <v>45371.60959490741</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24401,7 +24401,7 @@
         <v>45538</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24458,7 +24458,7 @@
         <v>45617.92190972222</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24515,7 +24515,7 @@
         <v>45056</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24572,7 +24572,7 @@
         <v>44564.8419212963</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24629,7 +24629,7 @@
         <v>45174</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24686,7 +24686,7 @@
         <v>45726.44835648148</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24743,7 +24743,7 @@
         <v>45646.67994212963</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24800,7 +24800,7 @@
         <v>45804.31922453704</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24857,7 +24857,7 @@
         <v>44648.61840277778</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24914,7 +24914,7 @@
         <v>44571</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24971,7 +24971,7 @@
         <v>45804</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25028,7 +25028,7 @@
         <v>44992.66236111111</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25085,7 +25085,7 @@
         <v>45805</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25142,7 +25142,7 @@
         <v>45730.44528935185</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25204,7 +25204,7 @@
         <v>45372.34530092592</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25261,7 +25261,7 @@
         <v>45179.9259375</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25318,7 +25318,7 @@
         <v>45806.26452546296</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25375,7 +25375,7 @@
         <v>45806.28703703704</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25432,7 +25432,7 @@
         <v>44109</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25489,7 +25489,7 @@
         <v>44261</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25546,7 +25546,7 @@
         <v>45624.41041666667</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25603,7 +25603,7 @@
         <v>44097</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25660,7 +25660,7 @@
         <v>44550.30402777778</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25717,7 +25717,7 @@
         <v>45733</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25774,7 +25774,7 @@
         <v>45805.58325231481</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25831,7 +25831,7 @@
         <v>45805.60481481482</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25888,7 +25888,7 @@
         <v>45806.2833912037</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25945,7 +25945,7 @@
         <v>44118</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26007,7 +26007,7 @@
         <v>45182.71081018518</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26064,7 +26064,7 @@
         <v>44589.73825231481</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26121,7 +26121,7 @@
         <v>45805.58372685185</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26178,7 +26178,7 @@
         <v>44557</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26235,7 +26235,7 @@
         <v>44904</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26292,7 +26292,7 @@
         <v>45547.42313657407</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26354,7 +26354,7 @@
         <v>45547.53320601852</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26411,7 +26411,7 @@
         <v>44943</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26468,7 +26468,7 @@
         <v>45440.3712037037</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26525,7 +26525,7 @@
         <v>45720.70986111111</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26582,7 +26582,7 @@
         <v>45216.47443287037</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26639,7 +26639,7 @@
         <v>45810</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26696,7 +26696,7 @@
         <v>44614.68596064814</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26753,7 +26753,7 @@
         <v>45691.5603125</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26810,7 +26810,7 @@
         <v>45597.43615740741</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26867,7 +26867,7 @@
         <v>45009</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26924,7 +26924,7 @@
         <v>44839</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26986,7 +26986,7 @@
         <v>45693.67859953704</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27043,7 +27043,7 @@
         <v>45401.34349537037</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27100,7 +27100,7 @@
         <v>45700.60138888889</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27157,7 +27157,7 @@
         <v>44659</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27219,7 +27219,7 @@
         <v>45705</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27276,7 +27276,7 @@
         <v>44172</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27333,7 +27333,7 @@
         <v>45750.40476851852</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27390,7 +27390,7 @@
         <v>45811</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27447,7 +27447,7 @@
         <v>45434.58377314815</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27504,7 +27504,7 @@
         <v>45566</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27561,7 +27561,7 @@
         <v>45105.34402777778</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27618,7 +27618,7 @@
         <v>45687</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27675,7 +27675,7 @@
         <v>45687</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27732,7 +27732,7 @@
         <v>44360.54226851852</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27789,7 +27789,7 @@
         <v>45194</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27846,7 +27846,7 @@
         <v>45643.89232638889</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27903,7 +27903,7 @@
         <v>45561.87885416667</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27960,7 +27960,7 @@
         <v>45197</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28017,7 +28017,7 @@
         <v>45021</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28074,7 +28074,7 @@
         <v>45519.49606481481</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28131,7 +28131,7 @@
         <v>45456.66137731481</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28188,7 +28188,7 @@
         <v>45215.72212962963</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28245,7 +28245,7 @@
         <v>44950</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28302,7 +28302,7 @@
         <v>45404.58408564814</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28359,7 +28359,7 @@
         <v>45523.5090625</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28421,7 +28421,7 @@
         <v>45523.58461805555</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28483,7 +28483,7 @@
         <v>45392.63664351852</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28540,7 +28540,7 @@
         <v>45043</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28597,7 +28597,7 @@
         <v>44704.65815972222</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28654,7 +28654,7 @@
         <v>45198.59607638889</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28711,7 +28711,7 @@
         <v>45706.67424768519</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28773,7 +28773,7 @@
         <v>44938</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28835,7 +28835,7 @@
         <v>45819.53688657407</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28892,7 +28892,7 @@
         <v>45819.53980324074</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28949,7 +28949,7 @@
         <v>45819.5429050926</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29006,7 +29006,7 @@
         <v>45198.60034722222</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29063,7 +29063,7 @@
         <v>44977.26300925926</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29120,7 +29120,7 @@
         <v>45764.42006944444</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29177,7 +29177,7 @@
         <v>45764.42517361111</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29234,7 +29234,7 @@
         <v>44655.48328703704</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29291,7 +29291,7 @@
         <v>45211</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29348,7 +29348,7 @@
         <v>45587</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29405,7 +29405,7 @@
         <v>44734</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29467,7 +29467,7 @@
         <v>44734</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29529,7 +29529,7 @@
         <v>45194</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29586,7 +29586,7 @@
         <v>45194</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29643,7 +29643,7 @@
         <v>45681.57949074074</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29700,7 +29700,7 @@
         <v>44252</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29757,7 +29757,7 @@
         <v>44943.4652199074</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29814,7 +29814,7 @@
         <v>44943.46980324074</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29871,7 +29871,7 @@
         <v>45642.8053125</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29933,7 +29933,7 @@
         <v>45622.35340277778</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29990,7 +29990,7 @@
         <v>45756</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30047,7 +30047,7 @@
         <v>45169</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30104,7 +30104,7 @@
         <v>45826</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30161,7 +30161,7 @@
         <v>45197.38018518518</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30218,7 +30218,7 @@
         <v>45637.51090277778</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30275,7 +30275,7 @@
         <v>45112.3174074074</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30332,7 +30332,7 @@
         <v>45112</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30389,7 +30389,7 @@
         <v>44930</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30446,7 +30446,7 @@
         <v>45769.43446759259</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30503,7 +30503,7 @@
         <v>45701.37818287037</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30560,7 +30560,7 @@
         <v>44423.87825231482</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30617,7 +30617,7 @@
         <v>44575.80709490741</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30674,7 +30674,7 @@
         <v>44950</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30731,7 +30731,7 @@
         <v>44249</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30788,7 +30788,7 @@
         <v>45759.5549537037</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30845,7 +30845,7 @@
         <v>44225</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30902,7 +30902,7 @@
         <v>44249.66673611111</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30959,7 +30959,7 @@
         <v>45363.91521990741</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31016,7 +31016,7 @@
         <v>45314</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31073,7 +31073,7 @@
         <v>45364.40862268519</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31130,7 +31130,7 @@
         <v>45303.63494212963</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31192,7 +31192,7 @@
         <v>45831.51019675926</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31249,7 +31249,7 @@
         <v>44966.52741898148</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31311,7 +31311,7 @@
         <v>45245.46393518519</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31368,7 +31368,7 @@
         <v>45189</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31425,7 +31425,7 @@
         <v>45294</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31487,7 +31487,7 @@
         <v>44904.59393518518</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31549,7 +31549,7 @@
         <v>44897</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31606,7 +31606,7 @@
         <v>44904.61212962963</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31668,7 +31668,7 @@
         <v>45246.50074074074</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31730,7 +31730,7 @@
         <v>45268</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31787,7 +31787,7 @@
         <v>45630.70101851852</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31849,7 +31849,7 @@
         <v>45182.36129629629</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31906,7 +31906,7 @@
         <v>44988</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31963,7 +31963,7 @@
         <v>45761.49107638889</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32020,7 +32020,7 @@
         <v>45600.48127314815</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32077,7 +32077,7 @@
         <v>45600.48347222222</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32134,7 +32134,7 @@
         <v>45679.98971064815</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32191,7 +32191,7 @@
         <v>45679.99299768519</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32248,7 +32248,7 @@
         <v>45875.57328703703</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32310,7 +32310,7 @@
         <v>45875.60922453704</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32367,7 +32367,7 @@
         <v>45272</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32424,7 +32424,7 @@
         <v>45876.6799537037</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32481,7 +32481,7 @@
         <v>45833.65434027778</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32538,7 +32538,7 @@
         <v>45833.63770833334</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32595,7 +32595,7 @@
         <v>45764.40184027778</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32652,7 +32652,7 @@
         <v>45834.48820601852</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32709,7 +32709,7 @@
         <v>44711</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32766,7 +32766,7 @@
         <v>45201</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32823,7 +32823,7 @@
         <v>44998.8734837963</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32880,7 +32880,7 @@
         <v>45547.84315972222</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32942,7 +32942,7 @@
         <v>45226.3731712963</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32999,7 +32999,7 @@
         <v>45769.60498842593</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33056,7 +33056,7 @@
         <v>44894</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33113,7 +33113,7 @@
         <v>45763.49306712963</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33170,7 +33170,7 @@
         <v>45295.4037962963</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33232,7 +33232,7 @@
         <v>45671.44894675926</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33289,7 +33289,7 @@
         <v>45880.43709490741</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33346,7 +33346,7 @@
         <v>45877.87582175926</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33403,7 +33403,7 @@
         <v>45617.4922337963</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33460,7 +33460,7 @@
         <v>45113.31806712963</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33517,7 +33517,7 @@
         <v>45435.51875</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33574,7 +33574,7 @@
         <v>45240</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33631,7 +33631,7 @@
         <v>44090</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33688,7 +33688,7 @@
         <v>45316</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33745,7 +33745,7 @@
         <v>45880.49957175926</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33802,7 +33802,7 @@
         <v>45880.46642361111</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33859,7 +33859,7 @@
         <v>44272</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33916,7 +33916,7 @@
         <v>44965</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33973,7 +33973,7 @@
         <v>45706.66618055556</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34035,7 +34035,7 @@
         <v>44734</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34097,7 +34097,7 @@
         <v>45671.44716435186</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34154,7 +34154,7 @@
         <v>45643</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34211,7 +34211,7 @@
         <v>45015</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34268,7 +34268,7 @@
         <v>45617.91424768518</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34325,7 +34325,7 @@
         <v>45271</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34382,7 +34382,7 @@
         <v>45630.39777777778</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34444,7 +34444,7 @@
         <v>45630.4022337963</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34506,7 +34506,7 @@
         <v>45679.36950231482</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34563,7 +34563,7 @@
         <v>44321</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34625,7 +34625,7 @@
         <v>45644.62803240741</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34682,7 +34682,7 @@
         <v>45210.34773148148</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34739,7 +34739,7 @@
         <v>44750</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34796,7 +34796,7 @@
         <v>45708.52121527777</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34853,7 +34853,7 @@
         <v>45642.60125</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34910,7 +34910,7 @@
         <v>45617.45760416667</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34967,7 +34967,7 @@
         <v>45736</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35024,7 +35024,7 @@
         <v>44614</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35081,7 +35081,7 @@
         <v>45693</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35138,7 +35138,7 @@
         <v>44729</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35195,7 +35195,7 @@
         <v>45469.43982638889</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35252,7 +35252,7 @@
         <v>44889</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35309,7 +35309,7 @@
         <v>45198.41381944445</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35366,7 +35366,7 @@
         <v>45198.41887731481</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35423,7 +35423,7 @@
         <v>45735.82282407407</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35480,7 +35480,7 @@
         <v>45201.45827546297</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35537,7 +35537,7 @@
         <v>45706.66388888889</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35599,7 +35599,7 @@
         <v>45706.67943287037</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35661,7 +35661,7 @@
         <v>45882.43462962963</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35718,7 +35718,7 @@
         <v>45839.71761574074</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35775,7 +35775,7 @@
         <v>45534.36645833333</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35832,7 +35832,7 @@
         <v>45149</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35889,7 +35889,7 @@
         <v>45883.60416666666</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35946,7 +35946,7 @@
         <v>45201</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36003,7 +36003,7 @@
         <v>45726.42344907407</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36065,7 +36065,7 @@
         <v>44719.43577546296</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36122,7 +36122,7 @@
         <v>45253.73424768518</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36179,7 +36179,7 @@
         <v>45300</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36236,7 +36236,7 @@
         <v>45215.71418981482</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36293,7 +36293,7 @@
         <v>45392.58569444445</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36350,7 +36350,7 @@
         <v>45035</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36407,7 +36407,7 @@
         <v>45188.3012037037</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36464,7 +36464,7 @@
         <v>44540.57753472222</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36521,7 +36521,7 @@
         <v>44103</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36578,7 +36578,7 @@
         <v>44803.44065972222</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36635,7 +36635,7 @@
         <v>44882</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36692,7 +36692,7 @@
         <v>45883.58956018519</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36749,7 +36749,7 @@
         <v>45842.49457175926</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36806,7 +36806,7 @@
         <v>45842.5059375</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36863,7 +36863,7 @@
         <v>45621</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36920,7 +36920,7 @@
         <v>45182</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36977,7 +36977,7 @@
         <v>44137</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37034,7 +37034,7 @@
         <v>45708.50255787037</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37091,7 +37091,7 @@
         <v>45715.65605324074</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37148,7 +37148,7 @@
         <v>44627.41212962963</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37205,7 +37205,7 @@
         <v>44985.35407407407</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37262,7 +37262,7 @@
         <v>45674.47359953704</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37319,7 +37319,7 @@
         <v>45883.59239583334</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37376,7 +37376,7 @@
         <v>45883.60604166667</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37433,7 +37433,7 @@
         <v>45842.49056712963</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37490,7 +37490,7 @@
         <v>45681.57619212963</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37547,7 +37547,7 @@
         <v>45682.47550925926</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37604,7 +37604,7 @@
         <v>44412.7071875</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37661,7 +37661,7 @@
         <v>44361</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37718,7 +37718,7 @@
         <v>44867</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37775,7 +37775,7 @@
         <v>45758</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37837,7 +37837,7 @@
         <v>45747.30204861111</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37894,7 +37894,7 @@
         <v>45272.42149305555</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37951,7 +37951,7 @@
         <v>45477.38554398148</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38008,7 +38008,7 @@
         <v>45477.38663194444</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38065,7 +38065,7 @@
         <v>44904</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38122,7 +38122,7 @@
         <v>45260.85619212963</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38179,7 +38179,7 @@
         <v>45841.71503472222</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38236,7 +38236,7 @@
         <v>44886.3340625</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38293,7 +38293,7 @@
         <v>45043.67869212963</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38350,7 +38350,7 @@
         <v>45841.4390625</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38407,7 +38407,7 @@
         <v>44741.69432870371</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38464,7 +38464,7 @@
         <v>44308.520625</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38521,7 +38521,7 @@
         <v>45735.81920138889</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38578,7 +38578,7 @@
         <v>45112</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38635,7 +38635,7 @@
         <v>45775.4233912037</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38692,7 +38692,7 @@
         <v>45749.67842592593</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38749,7 +38749,7 @@
         <v>45587</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38806,7 +38806,7 @@
         <v>44468</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38863,7 +38863,7 @@
         <v>44148</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38920,7 +38920,7 @@
         <v>45706.69090277778</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38982,7 +38982,7 @@
         <v>44130</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39039,7 +39039,7 @@
         <v>45757</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39096,7 +39096,7 @@
         <v>44113</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39153,7 +39153,7 @@
         <v>45302</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39210,7 +39210,7 @@
         <v>45846</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39272,7 +39272,7 @@
         <v>45846</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39334,7 +39334,7 @@
         <v>45756</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39391,7 +39391,7 @@
         <v>45797.56770833334</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39448,7 +39448,7 @@
         <v>45587.47273148148</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39505,7 +39505,7 @@
         <v>44904</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39567,7 +39567,7 @@
         <v>45769.60440972223</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39624,7 +39624,7 @@
         <v>44175</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39681,7 +39681,7 @@
         <v>44433</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39738,7 +39738,7 @@
         <v>45846</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39800,7 +39800,7 @@
         <v>45037.67510416666</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39857,7 +39857,7 @@
         <v>45079</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39914,7 +39914,7 @@
         <v>44151</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39971,7 +39971,7 @@
         <v>45887.68474537037</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40028,7 +40028,7 @@
         <v>45764.30016203703</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40085,7 +40085,7 @@
         <v>44882</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40142,7 +40142,7 @@
         <v>45764.30391203704</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40199,7 +40199,7 @@
         <v>45355.56604166667</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40256,7 +40256,7 @@
         <v>45324.64302083333</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40318,7 +40318,7 @@
         <v>44893</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40375,7 +40375,7 @@
         <v>45740.59871527777</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40432,7 +40432,7 @@
         <v>45887.62953703704</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40489,7 +40489,7 @@
         <v>45846.48190972222</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40546,7 +40546,7 @@
         <v>45547.43438657407</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40608,7 +40608,7 @@
         <v>45406.89568287037</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40665,7 +40665,7 @@
         <v>45406.89640046296</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40722,7 +40722,7 @@
         <v>45887.62158564815</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40779,7 +40779,7 @@
         <v>45845.60700231481</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40836,7 +40836,7 @@
         <v>45846.73861111111</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40893,7 +40893,7 @@
         <v>45183</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40950,7 +40950,7 @@
         <v>45056.6438425926</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41007,7 +41007,7 @@
         <v>44853</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41064,7 +41064,7 @@
         <v>44484</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41121,7 +41121,7 @@
         <v>45757.30554398148</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41178,7 +41178,7 @@
         <v>45755.70262731481</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41235,7 +41235,7 @@
         <v>45603.60537037037</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41292,7 +41292,7 @@
         <v>45201.59743055556</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41349,7 +41349,7 @@
         <v>44949</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41406,7 +41406,7 @@
         <v>44648</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41463,7 +41463,7 @@
         <v>44861.62300925926</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41520,7 +41520,7 @@
         <v>44938.53719907408</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41582,7 +41582,7 @@
         <v>44483.58045138889</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41639,7 +41639,7 @@
         <v>45375</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41696,7 +41696,7 @@
         <v>45751.52445601852</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41758,7 +41758,7 @@
         <v>45180</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41815,7 +41815,7 @@
         <v>44943.44811342593</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41872,7 +41872,7 @@
         <v>45748</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41934,7 +41934,7 @@
         <v>45092.42630787037</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41991,7 +41991,7 @@
         <v>45446.56622685185</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42048,7 +42048,7 @@
         <v>45049</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42105,7 +42105,7 @@
         <v>45051</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42162,7 +42162,7 @@
         <v>45892.38811342593</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42219,7 +42219,7 @@
         <v>45892.46936342592</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42276,7 +42276,7 @@
         <v>44614.56209490741</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42333,7 +42333,7 @@
         <v>44711</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42390,7 +42390,7 @@
         <v>45892.43763888889</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42447,7 +42447,7 @@
         <v>45892.42259259259</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42504,7 +42504,7 @@
         <v>44622</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42561,7 +42561,7 @@
         <v>45895.29351851852</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42618,7 +42618,7 @@
         <v>45764.53740740741</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42675,7 +42675,7 @@
         <v>45058</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42732,7 +42732,7 @@
         <v>44173</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42789,7 +42789,7 @@
         <v>44662</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42846,7 +42846,7 @@
         <v>45751</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42908,7 +42908,7 @@
         <v>45184</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42965,7 +42965,7 @@
         <v>45630.3944675926</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43027,7 +43027,7 @@
         <v>45898.46327546296</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43084,7 +43084,7 @@
         <v>45751.58130787037</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43141,7 +43141,7 @@
         <v>45706.69384259259</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43203,7 +43203,7 @@
         <v>45271</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43260,7 +43260,7 @@
         <v>44861.6108912037</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43317,7 +43317,7 @@
         <v>44861</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43374,7 +43374,7 @@
         <v>44211</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43431,7 +43431,7 @@
         <v>45461.65380787037</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43488,7 +43488,7 @@
         <v>45701</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43545,7 +43545,7 @@
         <v>45788.32225694445</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43602,7 +43602,7 @@
         <v>45860.54674768518</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43659,7 +43659,7 @@
         <v>45541.36828703704</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43716,7 +43716,7 @@
         <v>45902.67267361111</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43773,7 +43773,7 @@
         <v>45043.43777777778</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43830,7 +43830,7 @@
         <v>45861.68065972222</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43887,7 +43887,7 @@
         <v>44897.3564699074</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43949,7 +43949,7 @@
         <v>45884</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44006,7 +44006,7 @@
         <v>45455.40401620371</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44068,7 +44068,7 @@
         <v>44507.43497685185</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44125,7 +44125,7 @@
         <v>45862.63645833333</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44182,7 +44182,7 @@
         <v>44943.44532407408</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44239,7 +44239,7 @@
         <v>44943.48144675926</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44296,7 +44296,7 @@
         <v>45580.46572916667</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44353,7 +44353,7 @@
         <v>45861.46241898148</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44410,7 +44410,7 @@
         <v>44963</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44467,7 +44467,7 @@
         <v>45770.51686342592</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44524,7 +44524,7 @@
         <v>45908.90319444444</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44581,7 +44581,7 @@
         <v>45477.48915509259</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44638,7 +44638,7 @@
         <v>45408.67427083333</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44700,7 +44700,7 @@
         <v>45547.83519675926</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44762,7 +44762,7 @@
         <v>45887</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44819,7 +44819,7 @@
         <v>44158</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44876,7 +44876,7 @@
         <v>45905.29668981482</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44933,7 +44933,7 @@
         <v>45905.2990162037</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44990,7 +44990,7 @@
         <v>45905.30106481481</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45047,7 +45047,7 @@
         <v>45034</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45104,7 +45104,7 @@
         <v>44677</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45161,7 +45161,7 @@
         <v>44231</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45218,7 +45218,7 @@
         <v>45758</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45280,7 +45280,7 @@
         <v>45905.30556712963</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45337,7 +45337,7 @@
         <v>44295.31922453704</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45394,7 +45394,7 @@
         <v>45470.6672337963</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45451,7 +45451,7 @@
         <v>44992.67101851852</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45528,7 +45528,7 @@
         <v>44658</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45585,7 +45585,7 @@
         <v>45867.66349537037</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45642,7 +45642,7 @@
         <v>45048</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45699,7 +45699,7 @@
         <v>45908.91429398148</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45756,7 +45756,7 @@
         <v>45908.92369212963</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45813,7 +45813,7 @@
         <v>45908.92039351852</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45870,7 +45870,7 @@
         <v>44959.36028935185</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45932,7 +45932,7 @@
         <v>45897</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45989,7 +45989,7 @@
         <v>45051.37461805555</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46046,7 +46046,7 @@
         <v>45870.62930555556</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46108,7 +46108,7 @@
         <v>45764.4140162037</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46165,7 +46165,7 @@
         <v>44846.68375</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46222,7 +46222,7 @@
         <v>45130</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46279,7 +46279,7 @@
         <v>45870.62511574074</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46341,7 +46341,7 @@
         <v>45788.3231712963</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46398,7 +46398,7 @@
         <v>45764.31284722222</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46455,7 +46455,7 @@
         <v>45471.4034837963</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46512,7 +46512,7 @@
         <v>44977.26482638889</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46569,7 +46569,7 @@
         <v>44998</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46626,7 +46626,7 @@
         <v>45673.71842592592</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46683,7 +46683,7 @@
         <v>45152</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46740,7 +46740,7 @@
         <v>45401</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46802,7 +46802,7 @@
         <v>45373.60802083334</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46859,7 +46859,7 @@
         <v>45127</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46916,7 +46916,7 @@
         <v>44967.6228125</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46973,7 +46973,7 @@
         <v>45605.84435185185</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47030,7 +47030,7 @@
         <v>45152</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47087,7 +47087,7 @@
         <v>45092</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47144,7 +47144,7 @@
         <v>45757.29700231482</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47201,7 +47201,7 @@
         <v>45615.90662037037</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47258,7 +47258,7 @@
         <v>44631</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47315,7 +47315,7 @@
         <v>45567</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47372,7 +47372,7 @@
         <v>45630.6993287037</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47429,7 +47429,7 @@
         <v>45240</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47486,7 +47486,7 @@
         <v>45642.92393518519</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47543,7 +47543,7 @@
         <v>44229</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47600,7 +47600,7 @@
         <v>44735</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47657,7 +47657,7 @@
         <v>45012</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47714,7 +47714,7 @@
         <v>45300</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47771,7 +47771,7 @@
         <v>45588</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47828,7 +47828,7 @@
         <v>44985</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47885,7 +47885,7 @@
         <v>45099</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47942,7 +47942,7 @@
         <v>45363.45982638889</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47999,7 +47999,7 @@
         <v>45177.5462962963</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48056,7 +48056,7 @@
         <v>45223.65527777778</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48113,7 +48113,7 @@
         <v>45181</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48170,7 +48170,7 @@
         <v>45252.58925925926</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48227,7 +48227,7 @@
         <v>44487</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48284,7 +48284,7 @@
         <v>45356.65395833334</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48346,7 +48346,7 @@
         <v>45107</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48403,7 +48403,7 @@
         <v>44588.50104166667</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48460,7 +48460,7 @@
         <v>45747.44508101852</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48517,7 +48517,7 @@
         <v>45747.45177083334</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48574,7 +48574,7 @@
         <v>44979</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48631,7 +48631,7 @@
         <v>45201</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48693,7 +48693,7 @@
         <v>45545.53883101852</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48750,7 +48750,7 @@
         <v>45169</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48807,7 +48807,7 @@
         <v>45468.44574074074</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48864,7 +48864,7 @@
         <v>45775.32407407407</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48921,7 +48921,7 @@
         <v>45597.53744212963</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48978,7 +48978,7 @@
         <v>45447.55340277778</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49035,7 +49035,7 @@
         <v>45644.62243055556</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49092,7 +49092,7 @@
         <v>44904.49826388889</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49149,7 +49149,7 @@
         <v>44904</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49206,7 +49206,7 @@
         <v>44923.55936342593</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49263,7 +49263,7 @@
         <v>45414</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49320,7 +49320,7 @@
         <v>45377.42784722222</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49377,7 +49377,7 @@
         <v>45351.65180555556</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49439,7 +49439,7 @@
         <v>45617.48947916667</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49496,7 +49496,7 @@
         <v>45219</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49553,7 +49553,7 @@
         <v>45477.33712962963</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49610,7 +49610,7 @@
         <v>45406.89703703704</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49667,7 +49667,7 @@
         <v>45547.43793981482</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49729,7 +49729,7 @@
         <v>45492.70833333334</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49786,7 +49786,7 @@
         <v>45566</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49843,7 +49843,7 @@
         <v>45706.68554398148</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49905,7 +49905,7 @@
         <v>45645.88440972222</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49962,7 +49962,7 @@
         <v>45734.59972222222</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45913</v>
+        <v>45914</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>

--- a/Översikt JÖNKÖPING.xlsx
+++ b/Översikt JÖNKÖPING.xlsx
@@ -567,7 +567,7 @@
         <v>45856.56684027778</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -665,7 +665,7 @@
         <v>45856.57200231482</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
         <v>45777</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>45609</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         <v>45348</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         <v>44111</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>45275</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>45698.48634259259</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>45846.47335648148</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1415,7 +1415,7 @@
         <v>45788.88578703703</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>44992</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1595,7 +1595,7 @@
         <v>44530</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1682,7 +1682,7 @@
         <v>44512.62668981482</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1774,7 +1774,7 @@
         <v>44602</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1866,7 +1866,7 @@
         <v>45604.53402777778</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
         <v>44974</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2040,7 +2040,7 @@
         <v>45373.44148148148</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2126,7 +2126,7 @@
         <v>45790.83706018519</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2212,7 +2212,7 @@
         <v>45679.98452546296</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>45358.52763888889</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
         <v>44991</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
         <v>45302</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2556,7 +2556,7 @@
         <v>45898.45456018519</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2646,7 +2646,7 @@
         <v>45539</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2732,7 +2732,7 @@
         <v>44278</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2817,7 +2817,7 @@
         <v>44419</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2902,7 +2902,7 @@
         <v>44463</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2987,7 +2987,7 @@
         <v>44095</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3072,7 +3072,7 @@
         <v>44347.63069444444</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3157,7 +3157,7 @@
         <v>44467</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3242,7 +3242,7 @@
         <v>44404.71972222222</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
         <v>44840</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3412,7 +3412,7 @@
         <v>45783</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3497,7 +3497,7 @@
         <v>45740.58743055556</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3582,7 +3582,7 @@
         <v>44469</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3671,7 +3671,7 @@
         <v>45587</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3756,7 +3756,7 @@
         <v>45758</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3846,7 +3846,7 @@
         <v>45819.60131944445</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3931,7 +3931,7 @@
         <v>45302</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4016,7 +4016,7 @@
         <v>45846</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4110,7 +4110,7 @@
         <v>45876.69954861111</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         <v>45580.46207175926</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4280,7 +4280,7 @@
         <v>45295.3942824074</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4370,7 +4370,7 @@
         <v>45343</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4455,7 +4455,7 @@
         <v>45538.45523148148</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4540,7 +4540,7 @@
         <v>45205</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4625,7 +4625,7 @@
         <v>44879</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4714,7 +4714,7 @@
         <v>45841.4303125</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4799,7 +4799,7 @@
         <v>45846</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4884,7 +4884,7 @@
         <v>45616</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4973,7 +4973,7 @@
         <v>45856.55965277777</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5062,7 +5062,7 @@
         <v>45569.41550925926</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5147,7 +5147,7 @@
         <v>44943</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5232,7 +5232,7 @@
         <v>44260</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5289,7 +5289,7 @@
         <v>44188</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5346,7 +5346,7 @@
         <v>44137</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5403,7 +5403,7 @@
         <v>44147</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5460,7 +5460,7 @@
         <v>44306</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5517,7 +5517,7 @@
         <v>44308</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5579,7 +5579,7 @@
         <v>44144</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5636,7 +5636,7 @@
         <v>44328.35063657408</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5693,7 +5693,7 @@
         <v>44496</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5750,7 +5750,7 @@
         <v>44278.3859375</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5807,7 +5807,7 @@
         <v>44575.80925925926</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5864,7 +5864,7 @@
         <v>44662</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5921,7 +5921,7 @@
         <v>44239.33525462963</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -5978,7 +5978,7 @@
         <v>44404.84280092592</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6035,7 +6035,7 @@
         <v>44404.84659722223</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6092,7 +6092,7 @@
         <v>44487</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6149,7 +6149,7 @@
         <v>44749.55703703704</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6206,7 +6206,7 @@
         <v>44749.55936342593</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6263,7 +6263,7 @@
         <v>44273.62572916667</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6320,7 +6320,7 @@
         <v>44454.35472222222</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6377,7 +6377,7 @@
         <v>44308</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6439,7 +6439,7 @@
         <v>44225</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6496,7 +6496,7 @@
         <v>44308</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6558,7 +6558,7 @@
         <v>44349</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6615,7 +6615,7 @@
         <v>44792.53711805555</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6672,7 +6672,7 @@
         <v>44411</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6729,7 +6729,7 @@
         <v>44194</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6786,7 +6786,7 @@
         <v>44225</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6843,7 +6843,7 @@
         <v>44809</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6900,7 +6900,7 @@
         <v>44442</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6957,7 +6957,7 @@
         <v>44487</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7014,7 +7014,7 @@
         <v>44487.49392361111</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7071,7 +7071,7 @@
         <v>44749.32716435185</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7128,7 +7128,7 @@
         <v>44420.68987268519</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7185,7 +7185,7 @@
         <v>44404.84138888889</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7242,7 +7242,7 @@
         <v>44266</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7299,7 +7299,7 @@
         <v>44881.81052083334</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7356,7 +7356,7 @@
         <v>44665.60081018518</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7413,7 +7413,7 @@
         <v>44869.49265046296</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7475,7 +7475,7 @@
         <v>44734</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7537,7 +7537,7 @@
         <v>44792</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7594,7 +7594,7 @@
         <v>44259</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7651,7 +7651,7 @@
         <v>44365</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7708,7 +7708,7 @@
         <v>44538</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7765,7 +7765,7 @@
         <v>44263</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7827,7 +7827,7 @@
         <v>44113</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7884,7 +7884,7 @@
         <v>44487</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7941,7 +7941,7 @@
         <v>44487</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -7998,7 +7998,7 @@
         <v>44272</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8055,7 +8055,7 @@
         <v>44875.59231481481</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8112,7 +8112,7 @@
         <v>44852.74376157407</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8174,7 +8174,7 @@
         <v>44292</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8231,7 +8231,7 @@
         <v>44200</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8288,7 +8288,7 @@
         <v>44111</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8345,7 +8345,7 @@
         <v>44498.56373842592</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8402,7 +8402,7 @@
         <v>44881.79847222222</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8459,7 +8459,7 @@
         <v>44286.34827546297</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8516,7 +8516,7 @@
         <v>44273</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8573,7 +8573,7 @@
         <v>44673</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8630,7 +8630,7 @@
         <v>44298.46462962963</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8692,7 +8692,7 @@
         <v>44298.46582175926</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8754,7 +8754,7 @@
         <v>44278.38752314815</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8811,7 +8811,7 @@
         <v>44279.37552083333</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8868,7 +8868,7 @@
         <v>44347.61920138889</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8925,7 +8925,7 @@
         <v>44754.47359953704</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -8987,7 +8987,7 @@
         <v>44855.3080787037</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9044,7 +9044,7 @@
         <v>44476</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9101,7 +9101,7 @@
         <v>44373.75251157407</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9158,7 +9158,7 @@
         <v>44347.6287962963</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9215,7 +9215,7 @@
         <v>44511</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9272,7 +9272,7 @@
         <v>44466.4425</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9329,7 +9329,7 @@
         <v>44377</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9386,7 +9386,7 @@
         <v>44440.71997685185</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9443,7 +9443,7 @@
         <v>44840</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9500,7 +9500,7 @@
         <v>44104</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9557,7 +9557,7 @@
         <v>44280</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9614,7 +9614,7 @@
         <v>44613</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9671,7 +9671,7 @@
         <v>44456.46952546296</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9728,7 +9728,7 @@
         <v>44537</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9785,7 +9785,7 @@
         <v>44360</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9842,7 +9842,7 @@
         <v>44476</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9899,7 +9899,7 @@
         <v>44356</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9956,7 +9956,7 @@
         <v>44575</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10013,7 +10013,7 @@
         <v>44298.44060185185</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10075,7 +10075,7 @@
         <v>44659.57226851852</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10137,7 +10137,7 @@
         <v>44659</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10199,7 +10199,7 @@
         <v>44454.4800925926</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10256,7 +10256,7 @@
         <v>44711</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10313,7 +10313,7 @@
         <v>44578</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10370,7 +10370,7 @@
         <v>44344</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10427,7 +10427,7 @@
         <v>44596</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10484,7 +10484,7 @@
         <v>44628</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10541,7 +10541,7 @@
         <v>44498.57181712963</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10598,7 +10598,7 @@
         <v>44474.25150462963</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10655,7 +10655,7 @@
         <v>44711</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10712,7 +10712,7 @@
         <v>44711</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10769,7 +10769,7 @@
         <v>44841.31997685185</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10826,7 +10826,7 @@
         <v>44467.68283564815</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10883,7 +10883,7 @@
         <v>44792.53936342592</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10940,7 +10940,7 @@
         <v>44532.30398148148</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -10997,7 +10997,7 @@
         <v>44579.41064814815</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11054,7 +11054,7 @@
         <v>44593</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11111,7 +11111,7 @@
         <v>44557.71989583333</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11168,7 +11168,7 @@
         <v>44259</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11225,7 +11225,7 @@
         <v>44616.39256944445</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11282,7 +11282,7 @@
         <v>44373</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11339,7 +11339,7 @@
         <v>44239</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11396,7 +11396,7 @@
         <v>44239</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11453,7 +11453,7 @@
         <v>44464.40523148148</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11510,7 +11510,7 @@
         <v>44294</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11567,7 +11567,7 @@
         <v>44575</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11624,7 +11624,7 @@
         <v>44412</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11681,7 +11681,7 @@
         <v>44830.90146990741</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11738,7 +11738,7 @@
         <v>44787.80010416666</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11795,7 +11795,7 @@
         <v>44428.58511574074</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11857,7 +11857,7 @@
         <v>44729</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11914,7 +11914,7 @@
         <v>44272</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -11971,7 +11971,7 @@
         <v>44161.31023148148</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12028,7 +12028,7 @@
         <v>44825.40940972222</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12090,7 +12090,7 @@
         <v>44614</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12152,7 +12152,7 @@
         <v>44279.61517361111</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12209,7 +12209,7 @@
         <v>44805</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12271,7 +12271,7 @@
         <v>44585.30171296297</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12328,7 +12328,7 @@
         <v>44811</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12385,7 +12385,7 @@
         <v>44579</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12442,7 +12442,7 @@
         <v>44711</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12499,7 +12499,7 @@
         <v>44536</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12561,7 +12561,7 @@
         <v>44151</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12618,7 +12618,7 @@
         <v>44273</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12675,7 +12675,7 @@
         <v>44252</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12732,7 +12732,7 @@
         <v>44428.34821759259</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12794,7 +12794,7 @@
         <v>44272</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12851,7 +12851,7 @@
         <v>45621.52488425926</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12908,7 +12908,7 @@
         <v>45621.5278125</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -12965,7 +12965,7 @@
         <v>45008</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13022,7 +13022,7 @@
         <v>45750.50650462963</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13079,7 +13079,7 @@
         <v>45338.69246527777</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13141,7 +13141,7 @@
         <v>44326</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13198,7 +13198,7 @@
         <v>44575.8194212963</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13255,7 +13255,7 @@
         <v>44428.596875</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13317,7 +13317,7 @@
         <v>45531</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13374,7 +13374,7 @@
         <v>44088</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13431,7 +13431,7 @@
         <v>45341</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13488,7 +13488,7 @@
         <v>44325.76335648148</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13545,7 +13545,7 @@
         <v>44819</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13602,7 +13602,7 @@
         <v>44819.28449074074</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13659,7 +13659,7 @@
         <v>44292</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13716,7 +13716,7 @@
         <v>44846.66688657407</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13773,7 +13773,7 @@
         <v>45406</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13830,7 +13830,7 @@
         <v>44605.44909722222</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13887,7 +13887,7 @@
         <v>44523.65311342593</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13944,7 +13944,7 @@
         <v>45324.64579861111</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14006,7 +14006,7 @@
         <v>45324.64745370371</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14068,7 +14068,7 @@
         <v>45772.45813657407</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14125,7 +14125,7 @@
         <v>45092.39466435185</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14182,7 +14182,7 @@
         <v>45775.4219212963</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14239,7 +14239,7 @@
         <v>45197.61039351852</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14301,7 +14301,7 @@
         <v>44804</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14358,7 +14358,7 @@
         <v>45697.26537037037</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14415,7 +14415,7 @@
         <v>45716.7125</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14472,7 +14472,7 @@
         <v>45111</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14529,7 +14529,7 @@
         <v>45615.89965277778</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14586,7 +14586,7 @@
         <v>45747.45038194444</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14643,7 +14643,7 @@
         <v>45701.38606481482</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14700,7 +14700,7 @@
         <v>45112</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14757,7 +14757,7 @@
         <v>44950</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14814,7 +14814,7 @@
         <v>44950</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14871,7 +14871,7 @@
         <v>45764.53915509259</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14928,7 +14928,7 @@
         <v>45349</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -14985,7 +14985,7 @@
         <v>45119.54038194445</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15042,7 +15042,7 @@
         <v>44449</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15099,7 +15099,7 @@
         <v>45758</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15161,7 +15161,7 @@
         <v>44893</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15223,7 +15223,7 @@
         <v>45331</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15280,7 +15280,7 @@
         <v>44944.40825231482</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15337,7 +15337,7 @@
         <v>45764.3996412037</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15394,7 +15394,7 @@
         <v>45643.47644675926</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15451,7 +15451,7 @@
         <v>45307.72520833334</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15508,7 +15508,7 @@
         <v>45099.74195601852</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15565,7 +15565,7 @@
         <v>45116.44680555556</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15622,7 +15622,7 @@
         <v>45587.49814814814</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15679,7 +15679,7 @@
         <v>44957.36059027778</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15736,7 +15736,7 @@
         <v>45118</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15793,7 +15793,7 @@
         <v>45321</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15850,7 +15850,7 @@
         <v>45107</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15907,7 +15907,7 @@
         <v>45299</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15964,7 +15964,7 @@
         <v>45270.42966435185</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16021,7 +16021,7 @@
         <v>45474.70864583334</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16078,7 +16078,7 @@
         <v>45338</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16140,7 +16140,7 @@
         <v>45562.38306712963</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16197,7 +16197,7 @@
         <v>45667.63950231481</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16254,7 +16254,7 @@
         <v>45704</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16311,7 +16311,7 @@
         <v>44414</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16368,7 +16368,7 @@
         <v>45358</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16425,7 +16425,7 @@
         <v>45358.61696759259</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16482,7 +16482,7 @@
         <v>44484.49586805556</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16539,7 +16539,7 @@
         <v>45558.51949074074</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16601,7 +16601,7 @@
         <v>45777.60824074074</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16658,7 +16658,7 @@
         <v>45777.50512731481</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16715,7 +16715,7 @@
         <v>45281.57759259259</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16777,7 +16777,7 @@
         <v>45275</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16834,7 +16834,7 @@
         <v>45455.4374537037</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16896,7 +16896,7 @@
         <v>44628</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16953,7 +16953,7 @@
         <v>44893</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17015,7 +17015,7 @@
         <v>45335.76891203703</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17077,7 +17077,7 @@
         <v>44368.64017361111</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17134,7 +17134,7 @@
         <v>45243</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17196,7 +17196,7 @@
         <v>45541.37402777778</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17253,7 +17253,7 @@
         <v>44507.82581018518</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17310,7 +17310,7 @@
         <v>45586.62837962963</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17367,7 +17367,7 @@
         <v>44308</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17429,7 +17429,7 @@
         <v>45114.55280092593</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17486,7 +17486,7 @@
         <v>45519.48550925926</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17543,7 +17543,7 @@
         <v>45785.65899305556</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17600,7 +17600,7 @@
         <v>44837</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17657,7 +17657,7 @@
         <v>45477.48771990741</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17714,7 +17714,7 @@
         <v>45436.68626157408</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17771,7 +17771,7 @@
         <v>45314</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17828,7 +17828,7 @@
         <v>45455.42533564815</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17890,7 +17890,7 @@
         <v>45455.42981481482</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17952,7 +17952,7 @@
         <v>44963.66563657407</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18009,7 +18009,7 @@
         <v>44449</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18066,7 +18066,7 @@
         <v>45359.54100694445</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18123,7 +18123,7 @@
         <v>45124.59594907407</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18180,7 +18180,7 @@
         <v>45477.38181712963</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18237,7 +18237,7 @@
         <v>45533.46368055556</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18294,7 +18294,7 @@
         <v>45267.62943287037</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18351,7 +18351,7 @@
         <v>45539.34539351852</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18408,7 +18408,7 @@
         <v>45747.73295138889</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18465,7 +18465,7 @@
         <v>45460.42804398148</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18522,7 +18522,7 @@
         <v>45588</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18579,7 +18579,7 @@
         <v>45462.37888888889</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18636,7 +18636,7 @@
         <v>45789.54226851852</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18693,7 +18693,7 @@
         <v>44605.45792824074</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18750,7 +18750,7 @@
         <v>45502.32021990741</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18807,7 +18807,7 @@
         <v>45502.33179398148</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18864,7 +18864,7 @@
         <v>45175.44625</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18921,7 +18921,7 @@
         <v>44853</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18983,7 +18983,7 @@
         <v>44355.60153935185</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19040,7 +19040,7 @@
         <v>45586</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19097,7 +19097,7 @@
         <v>44428</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19159,7 +19159,7 @@
         <v>45646.5796412037</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19216,7 +19216,7 @@
         <v>45764.42304398148</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19273,7 +19273,7 @@
         <v>45145.47684027778</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19330,7 +19330,7 @@
         <v>44488</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19387,7 +19387,7 @@
         <v>45790.82361111111</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19444,7 +19444,7 @@
         <v>45405</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19501,7 +19501,7 @@
         <v>45405</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19558,7 +19558,7 @@
         <v>44966.57471064815</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19620,7 +19620,7 @@
         <v>45184</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19677,7 +19677,7 @@
         <v>44936</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19734,7 +19734,7 @@
         <v>45547.83950231481</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19796,7 +19796,7 @@
         <v>44578.52657407407</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19853,7 +19853,7 @@
         <v>44592.28611111111</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19910,7 +19910,7 @@
         <v>44411</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19967,7 +19967,7 @@
         <v>45541</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20024,7 +20024,7 @@
         <v>45545.65415509259</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20086,7 +20086,7 @@
         <v>45412</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20148,7 +20148,7 @@
         <v>45552.48335648148</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20205,7 +20205,7 @@
         <v>45462.38087962963</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20262,7 +20262,7 @@
         <v>44187</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20324,7 +20324,7 @@
         <v>45551.36004629629</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20381,7 +20381,7 @@
         <v>44585</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20438,7 +20438,7 @@
         <v>45541.38644675926</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20495,7 +20495,7 @@
         <v>44464.42415509259</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20552,7 +20552,7 @@
         <v>45763.49402777778</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20609,7 +20609,7 @@
         <v>45177</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20666,7 +20666,7 @@
         <v>44488</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20723,7 +20723,7 @@
         <v>44853</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20780,7 +20780,7 @@
         <v>45497</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20837,7 +20837,7 @@
         <v>45790.81799768518</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20894,7 +20894,7 @@
         <v>45791.85732638889</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20951,7 +20951,7 @@
         <v>45350.56959490741</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21008,7 +21008,7 @@
         <v>45600.47958333333</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21065,7 +21065,7 @@
         <v>45169.38410879629</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21122,7 +21122,7 @@
         <v>45205</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21179,7 +21179,7 @@
         <v>44935.37284722222</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21236,7 +21236,7 @@
         <v>45645.57626157408</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21293,7 +21293,7 @@
         <v>45012.47533564815</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21350,7 +21350,7 @@
         <v>45570.58934027778</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21407,7 +21407,7 @@
         <v>44482</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21464,7 +21464,7 @@
         <v>45184</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21521,7 +21521,7 @@
         <v>45793</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21578,7 +21578,7 @@
         <v>45557.35435185185</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21635,7 +21635,7 @@
         <v>45701.31962962963</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21692,7 +21692,7 @@
         <v>45635.28104166667</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21749,7 +21749,7 @@
         <v>45295.40646990741</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21811,7 +21811,7 @@
         <v>45681.48793981481</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21868,7 +21868,7 @@
         <v>45681.53460648148</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21925,7 +21925,7 @@
         <v>45736</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21982,7 +21982,7 @@
         <v>45740.59474537037</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22039,7 +22039,7 @@
         <v>45736.67693287037</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22096,7 +22096,7 @@
         <v>45727.3134375</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22153,7 +22153,7 @@
         <v>45727.36650462963</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22210,7 +22210,7 @@
         <v>44090</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22267,7 +22267,7 @@
         <v>45558.63807870371</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22329,7 +22329,7 @@
         <v>44591</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22386,7 +22386,7 @@
         <v>45735</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22443,7 +22443,7 @@
         <v>45734.35039351852</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22500,7 +22500,7 @@
         <v>45740.91412037037</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22557,7 +22557,7 @@
         <v>45741.65699074074</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22614,7 +22614,7 @@
         <v>45741.69303240741</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22671,7 +22671,7 @@
         <v>45735.65969907407</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22728,7 +22728,7 @@
         <v>44608</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22785,7 +22785,7 @@
         <v>45169</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22842,7 +22842,7 @@
         <v>45755</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22899,7 +22899,7 @@
         <v>45728</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22956,7 +22956,7 @@
         <v>45727.35745370371</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23013,7 +23013,7 @@
         <v>45727.36243055556</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23070,7 +23070,7 @@
         <v>45734.3584837963</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23127,7 +23127,7 @@
         <v>45736</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23184,7 +23184,7 @@
         <v>45743.59641203703</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23241,7 +23241,7 @@
         <v>45797.67148148148</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23298,7 +23298,7 @@
         <v>45734.35122685185</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23355,7 +23355,7 @@
         <v>45726.52925925926</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23412,7 +23412,7 @@
         <v>44626</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23469,7 +23469,7 @@
         <v>45730.65831018519</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23526,7 +23526,7 @@
         <v>45737.67416666666</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23583,7 +23583,7 @@
         <v>45730.3782175926</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23645,7 +23645,7 @@
         <v>45618</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23702,7 +23702,7 @@
         <v>45414</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23759,7 +23759,7 @@
         <v>45799.52318287037</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23816,7 +23816,7 @@
         <v>45799.58894675926</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23873,7 +23873,7 @@
         <v>45799.5803125</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23930,7 +23930,7 @@
         <v>44589.74348379629</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -23987,7 +23987,7 @@
         <v>45799.50469907407</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24044,7 +24044,7 @@
         <v>44893.50922453704</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24106,7 +24106,7 @@
         <v>45545.59315972222</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24168,7 +24168,7 @@
         <v>45435</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24230,7 +24230,7 @@
         <v>45030</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24287,7 +24287,7 @@
         <v>45799.51578703704</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24344,7 +24344,7 @@
         <v>45371.60959490741</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24401,7 +24401,7 @@
         <v>45538</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24458,7 +24458,7 @@
         <v>45617.92190972222</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24515,7 +24515,7 @@
         <v>45056</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24572,7 +24572,7 @@
         <v>44564.8419212963</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24629,7 +24629,7 @@
         <v>45174</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24686,7 +24686,7 @@
         <v>45726.44835648148</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24743,7 +24743,7 @@
         <v>45646.67994212963</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24800,7 +24800,7 @@
         <v>45804.31922453704</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24857,7 +24857,7 @@
         <v>44648.61840277778</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24914,7 +24914,7 @@
         <v>44571</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24971,7 +24971,7 @@
         <v>45804</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25028,7 +25028,7 @@
         <v>44992.66236111111</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25085,7 +25085,7 @@
         <v>45805</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25142,7 +25142,7 @@
         <v>45730.44528935185</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25204,7 +25204,7 @@
         <v>45372.34530092592</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25261,7 +25261,7 @@
         <v>45179.9259375</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25318,7 +25318,7 @@
         <v>45806.26452546296</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25375,7 +25375,7 @@
         <v>45806.28703703704</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25432,7 +25432,7 @@
         <v>44109</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25489,7 +25489,7 @@
         <v>44261</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25546,7 +25546,7 @@
         <v>45624.41041666667</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25603,7 +25603,7 @@
         <v>44097</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25660,7 +25660,7 @@
         <v>44550.30402777778</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25717,7 +25717,7 @@
         <v>45733</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25774,7 +25774,7 @@
         <v>45805.58325231481</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25831,7 +25831,7 @@
         <v>45805.60481481482</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25888,7 +25888,7 @@
         <v>45806.2833912037</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25945,7 +25945,7 @@
         <v>44118</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26007,7 +26007,7 @@
         <v>45182.71081018518</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26064,7 +26064,7 @@
         <v>44589.73825231481</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26121,7 +26121,7 @@
         <v>45805.58372685185</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26178,7 +26178,7 @@
         <v>44557</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26235,7 +26235,7 @@
         <v>44904</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26292,7 +26292,7 @@
         <v>45547.42313657407</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26354,7 +26354,7 @@
         <v>45547.53320601852</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26411,7 +26411,7 @@
         <v>44943</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26468,7 +26468,7 @@
         <v>45440.3712037037</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26525,7 +26525,7 @@
         <v>45720.70986111111</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26582,7 +26582,7 @@
         <v>45216.47443287037</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26639,7 +26639,7 @@
         <v>45810</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26696,7 +26696,7 @@
         <v>44614.68596064814</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26753,7 +26753,7 @@
         <v>45691.5603125</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26810,7 +26810,7 @@
         <v>45597.43615740741</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26867,7 +26867,7 @@
         <v>45009</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26924,7 +26924,7 @@
         <v>44839</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -26986,7 +26986,7 @@
         <v>45693.67859953704</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27043,7 +27043,7 @@
         <v>45401.34349537037</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27100,7 +27100,7 @@
         <v>45700.60138888889</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27157,7 +27157,7 @@
         <v>44659</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27219,7 +27219,7 @@
         <v>45705</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27276,7 +27276,7 @@
         <v>44172</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27333,7 +27333,7 @@
         <v>45750.40476851852</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27390,7 +27390,7 @@
         <v>45811</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27447,7 +27447,7 @@
         <v>45434.58377314815</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27504,7 +27504,7 @@
         <v>45566</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27561,7 +27561,7 @@
         <v>45105.34402777778</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27618,7 +27618,7 @@
         <v>45687</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27675,7 +27675,7 @@
         <v>45687</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27732,7 +27732,7 @@
         <v>44360.54226851852</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27789,7 +27789,7 @@
         <v>45194</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27846,7 +27846,7 @@
         <v>45643.89232638889</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27903,7 +27903,7 @@
         <v>45561.87885416667</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -27960,7 +27960,7 @@
         <v>45197</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28017,7 +28017,7 @@
         <v>45021</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28074,7 +28074,7 @@
         <v>45519.49606481481</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28131,7 +28131,7 @@
         <v>45456.66137731481</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28188,7 +28188,7 @@
         <v>45215.72212962963</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28245,7 +28245,7 @@
         <v>44950</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28302,7 +28302,7 @@
         <v>45404.58408564814</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28359,7 +28359,7 @@
         <v>45523.5090625</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28421,7 +28421,7 @@
         <v>45523.58461805555</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28483,7 +28483,7 @@
         <v>45392.63664351852</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28540,7 +28540,7 @@
         <v>45043</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28597,7 +28597,7 @@
         <v>44704.65815972222</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28654,7 +28654,7 @@
         <v>45198.59607638889</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28711,7 +28711,7 @@
         <v>45706.67424768519</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28773,7 +28773,7 @@
         <v>44938</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28835,7 +28835,7 @@
         <v>45819.53688657407</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28892,7 +28892,7 @@
         <v>45819.53980324074</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28949,7 +28949,7 @@
         <v>45819.5429050926</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29006,7 +29006,7 @@
         <v>45198.60034722222</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29063,7 +29063,7 @@
         <v>44977.26300925926</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29120,7 +29120,7 @@
         <v>45764.42006944444</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29177,7 +29177,7 @@
         <v>45764.42517361111</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29234,7 +29234,7 @@
         <v>44655.48328703704</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29291,7 +29291,7 @@
         <v>45211</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29348,7 +29348,7 @@
         <v>45587</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29405,7 +29405,7 @@
         <v>44734</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29467,7 +29467,7 @@
         <v>44734</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29529,7 +29529,7 @@
         <v>45194</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29586,7 +29586,7 @@
         <v>45194</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29643,7 +29643,7 @@
         <v>45681.57949074074</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29700,7 +29700,7 @@
         <v>44252</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29757,7 +29757,7 @@
         <v>44943.4652199074</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29814,7 +29814,7 @@
         <v>44943.46980324074</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29871,7 +29871,7 @@
         <v>45642.8053125</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29933,7 +29933,7 @@
         <v>45622.35340277778</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -29990,7 +29990,7 @@
         <v>45756</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30047,7 +30047,7 @@
         <v>45169</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30104,7 +30104,7 @@
         <v>45826</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30161,7 +30161,7 @@
         <v>45197.38018518518</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30218,7 +30218,7 @@
         <v>45637.51090277778</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30275,7 +30275,7 @@
         <v>45112.3174074074</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30332,7 +30332,7 @@
         <v>45112</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30389,7 +30389,7 @@
         <v>44930</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30446,7 +30446,7 @@
         <v>45769.43446759259</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30503,7 +30503,7 @@
         <v>45701.37818287037</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30560,7 +30560,7 @@
         <v>44423.87825231482</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30617,7 +30617,7 @@
         <v>44575.80709490741</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30674,7 +30674,7 @@
         <v>44950</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30731,7 +30731,7 @@
         <v>44249</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30788,7 +30788,7 @@
         <v>45759.5549537037</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30845,7 +30845,7 @@
         <v>44225</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30902,7 +30902,7 @@
         <v>44249.66673611111</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30959,7 +30959,7 @@
         <v>45363.91521990741</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31016,7 +31016,7 @@
         <v>45314</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31073,7 +31073,7 @@
         <v>45364.40862268519</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31130,7 +31130,7 @@
         <v>45303.63494212963</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31192,7 +31192,7 @@
         <v>45831.51019675926</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31249,7 +31249,7 @@
         <v>44966.52741898148</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31311,7 +31311,7 @@
         <v>45245.46393518519</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31368,7 +31368,7 @@
         <v>45189</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31425,7 +31425,7 @@
         <v>45294</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31487,7 +31487,7 @@
         <v>44904.59393518518</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31549,7 +31549,7 @@
         <v>44897</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31606,7 +31606,7 @@
         <v>44904.61212962963</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31668,7 +31668,7 @@
         <v>45246.50074074074</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31730,7 +31730,7 @@
         <v>45268</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31787,7 +31787,7 @@
         <v>45630.70101851852</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31849,7 +31849,7 @@
         <v>45182.36129629629</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31906,7 +31906,7 @@
         <v>44988</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31963,7 +31963,7 @@
         <v>45761.49107638889</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32020,7 +32020,7 @@
         <v>45600.48127314815</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32077,7 +32077,7 @@
         <v>45600.48347222222</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32134,7 +32134,7 @@
         <v>45679.98971064815</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32191,7 +32191,7 @@
         <v>45679.99299768519</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32248,7 +32248,7 @@
         <v>45875.57328703703</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32310,7 +32310,7 @@
         <v>45875.60922453704</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32367,7 +32367,7 @@
         <v>45272</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32424,7 +32424,7 @@
         <v>45876.6799537037</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32481,7 +32481,7 @@
         <v>45833.65434027778</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32538,7 +32538,7 @@
         <v>45833.63770833334</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32595,7 +32595,7 @@
         <v>45764.40184027778</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32652,7 +32652,7 @@
         <v>45834.48820601852</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32709,7 +32709,7 @@
         <v>44711</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32766,7 +32766,7 @@
         <v>45201</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32823,7 +32823,7 @@
         <v>44998.8734837963</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32880,7 +32880,7 @@
         <v>45547.84315972222</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32942,7 +32942,7 @@
         <v>45226.3731712963</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -32999,7 +32999,7 @@
         <v>45769.60498842593</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33056,7 +33056,7 @@
         <v>44894</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33113,7 +33113,7 @@
         <v>45763.49306712963</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33170,7 +33170,7 @@
         <v>45295.4037962963</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33232,7 +33232,7 @@
         <v>45671.44894675926</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33289,7 +33289,7 @@
         <v>45880.43709490741</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33346,7 +33346,7 @@
         <v>45877.87582175926</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33403,7 +33403,7 @@
         <v>45617.4922337963</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33460,7 +33460,7 @@
         <v>45113.31806712963</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33517,7 +33517,7 @@
         <v>45435.51875</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33574,7 +33574,7 @@
         <v>45240</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33631,7 +33631,7 @@
         <v>44090</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33688,7 +33688,7 @@
         <v>45316</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33745,7 +33745,7 @@
         <v>45880.49957175926</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33802,7 +33802,7 @@
         <v>45880.46642361111</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33859,7 +33859,7 @@
         <v>44272</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33916,7 +33916,7 @@
         <v>44965</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33973,7 +33973,7 @@
         <v>45706.66618055556</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34035,7 +34035,7 @@
         <v>44734</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34097,7 +34097,7 @@
         <v>45671.44716435186</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34154,7 +34154,7 @@
         <v>45643</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34211,7 +34211,7 @@
         <v>45015</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34268,7 +34268,7 @@
         <v>45617.91424768518</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34325,7 +34325,7 @@
         <v>45271</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34382,7 +34382,7 @@
         <v>45630.39777777778</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34444,7 +34444,7 @@
         <v>45630.4022337963</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34506,7 +34506,7 @@
         <v>45679.36950231482</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34563,7 +34563,7 @@
         <v>44321</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34625,7 +34625,7 @@
         <v>45644.62803240741</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34682,7 +34682,7 @@
         <v>45210.34773148148</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34739,7 +34739,7 @@
         <v>44750</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34796,7 +34796,7 @@
         <v>45708.52121527777</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34853,7 +34853,7 @@
         <v>45642.60125</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34910,7 +34910,7 @@
         <v>45617.45760416667</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34967,7 +34967,7 @@
         <v>45736</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35024,7 +35024,7 @@
         <v>44614</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35081,7 +35081,7 @@
         <v>45693</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35138,7 +35138,7 @@
         <v>44729</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35195,7 +35195,7 @@
         <v>45469.43982638889</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35252,7 +35252,7 @@
         <v>44889</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35309,7 +35309,7 @@
         <v>45198.41381944445</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35366,7 +35366,7 @@
         <v>45198.41887731481</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35423,7 +35423,7 @@
         <v>45735.82282407407</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35480,7 +35480,7 @@
         <v>45201.45827546297</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35537,7 +35537,7 @@
         <v>45706.66388888889</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35599,7 +35599,7 @@
         <v>45706.67943287037</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35661,7 +35661,7 @@
         <v>45882.43462962963</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35718,7 +35718,7 @@
         <v>45839.71761574074</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35775,7 +35775,7 @@
         <v>45534.36645833333</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35832,7 +35832,7 @@
         <v>45149</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35889,7 +35889,7 @@
         <v>45883.60416666666</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35946,7 +35946,7 @@
         <v>45201</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -36003,7 +36003,7 @@
         <v>45726.42344907407</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36065,7 +36065,7 @@
         <v>44719.43577546296</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36122,7 +36122,7 @@
         <v>45253.73424768518</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36179,7 +36179,7 @@
         <v>45300</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36236,7 +36236,7 @@
         <v>45215.71418981482</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36293,7 +36293,7 @@
         <v>45392.58569444445</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36350,7 +36350,7 @@
         <v>45035</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36407,7 +36407,7 @@
         <v>45188.3012037037</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36464,7 +36464,7 @@
         <v>44540.57753472222</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36521,7 +36521,7 @@
         <v>44103</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36578,7 +36578,7 @@
         <v>44803.44065972222</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36635,7 +36635,7 @@
         <v>44882</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36692,7 +36692,7 @@
         <v>45883.58956018519</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36749,7 +36749,7 @@
         <v>45842.49457175926</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36806,7 +36806,7 @@
         <v>45842.5059375</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36863,7 +36863,7 @@
         <v>45621</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36920,7 +36920,7 @@
         <v>45182</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36977,7 +36977,7 @@
         <v>44137</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37034,7 +37034,7 @@
         <v>45708.50255787037</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37091,7 +37091,7 @@
         <v>45715.65605324074</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37148,7 +37148,7 @@
         <v>44627.41212962963</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37205,7 +37205,7 @@
         <v>44985.35407407407</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37262,7 +37262,7 @@
         <v>45674.47359953704</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37319,7 +37319,7 @@
         <v>45883.59239583334</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37376,7 +37376,7 @@
         <v>45883.60604166667</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37433,7 +37433,7 @@
         <v>45842.49056712963</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37490,7 +37490,7 @@
         <v>45681.57619212963</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37547,7 +37547,7 @@
         <v>45682.47550925926</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37604,7 +37604,7 @@
         <v>44412.7071875</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37661,7 +37661,7 @@
         <v>44361</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37718,7 +37718,7 @@
         <v>44867</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37775,7 +37775,7 @@
         <v>45758</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37837,7 +37837,7 @@
         <v>45747.30204861111</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37894,7 +37894,7 @@
         <v>45272.42149305555</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37951,7 +37951,7 @@
         <v>45477.38554398148</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38008,7 +38008,7 @@
         <v>45477.38663194444</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38065,7 +38065,7 @@
         <v>44904</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38122,7 +38122,7 @@
         <v>45260.85619212963</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38179,7 +38179,7 @@
         <v>45841.71503472222</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38236,7 +38236,7 @@
         <v>44886.3340625</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38293,7 +38293,7 @@
         <v>45043.67869212963</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38350,7 +38350,7 @@
         <v>45841.4390625</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38407,7 +38407,7 @@
         <v>44741.69432870371</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38464,7 +38464,7 @@
         <v>44308.520625</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38521,7 +38521,7 @@
         <v>45735.81920138889</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38578,7 +38578,7 @@
         <v>45112</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38635,7 +38635,7 @@
         <v>45775.4233912037</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38692,7 +38692,7 @@
         <v>45749.67842592593</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38749,7 +38749,7 @@
         <v>45587</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38806,7 +38806,7 @@
         <v>44468</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38863,7 +38863,7 @@
         <v>44148</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38920,7 +38920,7 @@
         <v>45706.69090277778</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -38982,7 +38982,7 @@
         <v>44130</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39039,7 +39039,7 @@
         <v>45757</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39096,7 +39096,7 @@
         <v>44113</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39153,7 +39153,7 @@
         <v>45302</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39210,7 +39210,7 @@
         <v>45846</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39272,7 +39272,7 @@
         <v>45846</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39334,7 +39334,7 @@
         <v>45756</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39391,7 +39391,7 @@
         <v>45797.56770833334</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39448,7 +39448,7 @@
         <v>45587.47273148148</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39505,7 +39505,7 @@
         <v>44904</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39567,7 +39567,7 @@
         <v>45769.60440972223</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39624,7 +39624,7 @@
         <v>44175</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39681,7 +39681,7 @@
         <v>44433</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39738,7 +39738,7 @@
         <v>45846</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39800,7 +39800,7 @@
         <v>45037.67510416666</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39857,7 +39857,7 @@
         <v>45079</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39914,7 +39914,7 @@
         <v>44151</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39971,7 +39971,7 @@
         <v>45887.68474537037</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40028,7 +40028,7 @@
         <v>45764.30016203703</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40085,7 +40085,7 @@
         <v>44882</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40142,7 +40142,7 @@
         <v>45764.30391203704</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40199,7 +40199,7 @@
         <v>45355.56604166667</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40256,7 +40256,7 @@
         <v>45324.64302083333</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40318,7 +40318,7 @@
         <v>44893</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40375,7 +40375,7 @@
         <v>45740.59871527777</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40432,7 +40432,7 @@
         <v>45887.62953703704</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40489,7 +40489,7 @@
         <v>45846.48190972222</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40546,7 +40546,7 @@
         <v>45547.43438657407</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40608,7 +40608,7 @@
         <v>45406.89568287037</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40665,7 +40665,7 @@
         <v>45406.89640046296</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40722,7 +40722,7 @@
         <v>45887.62158564815</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40779,7 +40779,7 @@
         <v>45845.60700231481</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40836,7 +40836,7 @@
         <v>45846.73861111111</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40893,7 +40893,7 @@
         <v>45183</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40950,7 +40950,7 @@
         <v>45056.6438425926</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41007,7 +41007,7 @@
         <v>44853</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41064,7 +41064,7 @@
         <v>44484</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41121,7 +41121,7 @@
         <v>45757.30554398148</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41178,7 +41178,7 @@
         <v>45755.70262731481</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41235,7 +41235,7 @@
         <v>45603.60537037037</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41292,7 +41292,7 @@
         <v>45201.59743055556</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41349,7 +41349,7 @@
         <v>44949</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41406,7 +41406,7 @@
         <v>44648</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41463,7 +41463,7 @@
         <v>44861.62300925926</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41520,7 +41520,7 @@
         <v>44938.53719907408</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41582,7 +41582,7 @@
         <v>44483.58045138889</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41639,7 +41639,7 @@
         <v>45375</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41696,7 +41696,7 @@
         <v>45751.52445601852</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41758,7 +41758,7 @@
         <v>45180</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -41815,7 +41815,7 @@
         <v>44943.44811342593</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -41872,7 +41872,7 @@
         <v>45748</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -41934,7 +41934,7 @@
         <v>45092.42630787037</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -41991,7 +41991,7 @@
         <v>45446.56622685185</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -42048,7 +42048,7 @@
         <v>45049</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -42105,7 +42105,7 @@
         <v>45051</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -42162,7 +42162,7 @@
         <v>45892.38811342593</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -42219,7 +42219,7 @@
         <v>45892.46936342592</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -42276,7 +42276,7 @@
         <v>44614.56209490741</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -42333,7 +42333,7 @@
         <v>44711</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -42390,7 +42390,7 @@
         <v>45892.43763888889</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -42447,7 +42447,7 @@
         <v>45892.42259259259</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -42504,7 +42504,7 @@
         <v>44622</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -42561,7 +42561,7 @@
         <v>45895.29351851852</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -42618,7 +42618,7 @@
         <v>45764.53740740741</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -42675,7 +42675,7 @@
         <v>45058</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -42732,7 +42732,7 @@
         <v>44173</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -42789,7 +42789,7 @@
         <v>44662</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -42846,7 +42846,7 @@
         <v>45751</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -42908,7 +42908,7 @@
         <v>45184</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -42965,7 +42965,7 @@
         <v>45630.3944675926</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -43027,7 +43027,7 @@
         <v>45898.46327546296</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -43084,7 +43084,7 @@
         <v>45751.58130787037</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -43141,7 +43141,7 @@
         <v>45706.69384259259</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -43203,7 +43203,7 @@
         <v>45271</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -43260,7 +43260,7 @@
         <v>44861.6108912037</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -43317,7 +43317,7 @@
         <v>44861</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -43374,7 +43374,7 @@
         <v>44211</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -43431,7 +43431,7 @@
         <v>45461.65380787037</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -43488,7 +43488,7 @@
         <v>45701</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -43545,7 +43545,7 @@
         <v>45788.32225694445</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -43602,7 +43602,7 @@
         <v>45860.54674768518</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -43659,7 +43659,7 @@
         <v>45541.36828703704</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -43716,7 +43716,7 @@
         <v>45902.67267361111</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -43773,7 +43773,7 @@
         <v>45043.43777777778</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -43830,7 +43830,7 @@
         <v>45861.68065972222</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -43887,7 +43887,7 @@
         <v>44897.3564699074</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -43949,7 +43949,7 @@
         <v>45884</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -44006,7 +44006,7 @@
         <v>45455.40401620371</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -44068,7 +44068,7 @@
         <v>44507.43497685185</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -44125,7 +44125,7 @@
         <v>45862.63645833333</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -44182,7 +44182,7 @@
         <v>44943.44532407408</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -44239,7 +44239,7 @@
         <v>44943.48144675926</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -44296,7 +44296,7 @@
         <v>45580.46572916667</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -44353,7 +44353,7 @@
         <v>45861.46241898148</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -44410,7 +44410,7 @@
         <v>44963</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -44467,7 +44467,7 @@
         <v>45770.51686342592</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -44524,7 +44524,7 @@
         <v>45908.90319444444</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -44581,7 +44581,7 @@
         <v>45477.48915509259</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -44638,7 +44638,7 @@
         <v>45408.67427083333</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -44700,7 +44700,7 @@
         <v>45547.83519675926</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -44762,7 +44762,7 @@
         <v>45887</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -44819,7 +44819,7 @@
         <v>44158</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -44876,7 +44876,7 @@
         <v>45905.29668981482</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -44933,7 +44933,7 @@
         <v>45905.2990162037</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -44990,7 +44990,7 @@
         <v>45905.30106481481</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -45047,7 +45047,7 @@
         <v>45034</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -45104,7 +45104,7 @@
         <v>44677</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -45161,7 +45161,7 @@
         <v>44231</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -45218,7 +45218,7 @@
         <v>45758</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -45280,7 +45280,7 @@
         <v>45905.30556712963</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -45337,7 +45337,7 @@
         <v>44295.31922453704</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -45394,7 +45394,7 @@
         <v>45470.6672337963</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -45451,7 +45451,7 @@
         <v>44992.67101851852</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -45528,7 +45528,7 @@
         <v>44658</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -45585,7 +45585,7 @@
         <v>45867.66349537037</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -45642,7 +45642,7 @@
         <v>45048</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -45699,7 +45699,7 @@
         <v>45908.91429398148</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -45756,7 +45756,7 @@
         <v>45908.92369212963</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -45813,7 +45813,7 @@
         <v>45908.92039351852</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -45870,7 +45870,7 @@
         <v>44959.36028935185</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -45932,7 +45932,7 @@
         <v>45897</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -45989,7 +45989,7 @@
         <v>45051.37461805555</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -46046,7 +46046,7 @@
         <v>45870.62930555556</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -46108,7 +46108,7 @@
         <v>45764.4140162037</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -46165,7 +46165,7 @@
         <v>44846.68375</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -46222,7 +46222,7 @@
         <v>45130</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -46279,7 +46279,7 @@
         <v>45870.62511574074</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -46341,7 +46341,7 @@
         <v>45788.3231712963</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -46398,7 +46398,7 @@
         <v>45764.31284722222</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -46455,7 +46455,7 @@
         <v>45471.4034837963</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -46512,7 +46512,7 @@
         <v>44977.26482638889</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -46569,7 +46569,7 @@
         <v>44998</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -46626,7 +46626,7 @@
         <v>45673.71842592592</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -46683,7 +46683,7 @@
         <v>45152</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -46740,7 +46740,7 @@
         <v>45401</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -46802,7 +46802,7 @@
         <v>45373.60802083334</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -46859,7 +46859,7 @@
         <v>45127</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -46916,7 +46916,7 @@
         <v>44967.6228125</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -46973,7 +46973,7 @@
         <v>45605.84435185185</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -47030,7 +47030,7 @@
         <v>45152</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -47087,7 +47087,7 @@
         <v>45092</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -47144,7 +47144,7 @@
         <v>45757.29700231482</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -47201,7 +47201,7 @@
         <v>45615.90662037037</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -47258,7 +47258,7 @@
         <v>44631</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -47315,7 +47315,7 @@
         <v>45567</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -47372,7 +47372,7 @@
         <v>45630.6993287037</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -47429,7 +47429,7 @@
         <v>45240</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -47486,7 +47486,7 @@
         <v>45642.92393518519</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -47543,7 +47543,7 @@
         <v>44229</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -47600,7 +47600,7 @@
         <v>44735</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -47657,7 +47657,7 @@
         <v>45012</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -47714,7 +47714,7 @@
         <v>45300</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -47771,7 +47771,7 @@
         <v>45588</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -47828,7 +47828,7 @@
         <v>44985</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -47885,7 +47885,7 @@
         <v>45099</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -47942,7 +47942,7 @@
         <v>45363.45982638889</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -47999,7 +47999,7 @@
         <v>45177.5462962963</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -48056,7 +48056,7 @@
         <v>45223.65527777778</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -48113,7 +48113,7 @@
         <v>45181</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -48170,7 +48170,7 @@
         <v>45252.58925925926</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -48227,7 +48227,7 @@
         <v>44487</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -48284,7 +48284,7 @@
         <v>45356.65395833334</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -48346,7 +48346,7 @@
         <v>45107</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -48403,7 +48403,7 @@
         <v>44588.50104166667</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -48460,7 +48460,7 @@
         <v>45747.44508101852</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -48517,7 +48517,7 @@
         <v>45747.45177083334</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -48574,7 +48574,7 @@
         <v>44979</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -48631,7 +48631,7 @@
         <v>45201</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -48693,7 +48693,7 @@
         <v>45545.53883101852</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -48750,7 +48750,7 @@
         <v>45169</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -48807,7 +48807,7 @@
         <v>45468.44574074074</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -48864,7 +48864,7 @@
         <v>45775.32407407407</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -48921,7 +48921,7 @@
         <v>45597.53744212963</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -48978,7 +48978,7 @@
         <v>45447.55340277778</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -49035,7 +49035,7 @@
         <v>45644.62243055556</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -49092,7 +49092,7 @@
         <v>44904.49826388889</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -49149,7 +49149,7 @@
         <v>44904</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -49206,7 +49206,7 @@
         <v>44923.55936342593</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -49263,7 +49263,7 @@
         <v>45414</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -49320,7 +49320,7 @@
         <v>45377.42784722222</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -49377,7 +49377,7 @@
         <v>45351.65180555556</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -49439,7 +49439,7 @@
         <v>45617.48947916667</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -49496,7 +49496,7 @@
         <v>45219</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -49553,7 +49553,7 @@
         <v>45477.33712962963</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -49610,7 +49610,7 @@
         <v>45406.89703703704</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -49667,7 +49667,7 @@
         <v>45547.43793981482</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -49729,7 +49729,7 @@
         <v>45492.70833333334</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -49786,7 +49786,7 @@
         <v>45566</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -49843,7 +49843,7 @@
         <v>45706.68554398148</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -49905,7 +49905,7 @@
         <v>45645.88440972222</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -49962,7 +49962,7 @@
         <v>45734.59972222222</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45914</v>
+        <v>45915</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>

--- a/Översikt JÖNKÖPING.xlsx
+++ b/Översikt JÖNKÖPING.xlsx
@@ -567,7 +567,7 @@
         <v>45856.56684027778</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -665,7 +665,7 @@
         <v>45856.57200231482</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -760,7 +760,7 @@
         <v>45777</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -857,7 +857,7 @@
         <v>45609</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -953,7 +953,7 @@
         <v>45348</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1049,7 +1049,7 @@
         <v>44111</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1139,7 +1139,7 @@
         <v>45275</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1233,7 +1233,7 @@
         <v>45698.48634259259</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
         <v>44512.62668981482</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1417,7 +1417,7 @@
         <v>45846.47335648148</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>45788.88578703703</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1597,7 +1597,7 @@
         <v>44992</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1689,7 +1689,7 @@
         <v>44530</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1776,7 +1776,7 @@
         <v>44602</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1868,7 +1868,7 @@
         <v>44974</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -1955,7 +1955,7 @@
         <v>45604.53402777778</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2042,7 +2042,7 @@
         <v>45790.83706018519</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2128,7 +2128,7 @@
         <v>45302</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2214,7 +2214,7 @@
         <v>45539</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>45679.98452546296</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2386,7 +2386,7 @@
         <v>45373.44148148148</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2472,7 +2472,7 @@
         <v>44991</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2558,7 +2558,7 @@
         <v>45898.45456018519</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
         <v>45358.52763888889</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2734,7 +2734,7 @@
         <v>44278</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -2819,7 +2819,7 @@
         <v>44419</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -2904,7 +2904,7 @@
         <v>44463</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -2989,7 +2989,7 @@
         <v>44347.63069444444</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3074,7 +3074,7 @@
         <v>44467</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3159,7 +3159,7 @@
         <v>44469</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3248,7 +3248,7 @@
         <v>45580.46207175926</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3333,7 +3333,7 @@
         <v>45295.3942824074</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3423,7 +3423,7 @@
         <v>45302</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
         <v>44840</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         <v>45783</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3678,7 +3678,7 @@
         <v>44404.71972222222</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -3763,7 +3763,7 @@
         <v>45740.58743055556</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -3848,7 +3848,7 @@
         <v>45726.52925925926</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -3933,7 +3933,7 @@
         <v>45587</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4018,7 +4018,7 @@
         <v>45819.60131944445</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4103,7 +4103,7 @@
         <v>44879</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4192,7 +4192,7 @@
         <v>45758</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4282,7 +4282,7 @@
         <v>45343</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4367,7 +4367,7 @@
         <v>44943</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4452,7 +4452,7 @@
         <v>45841.4303125</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4537,7 +4537,7 @@
         <v>45538.45523148148</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4622,7 +4622,7 @@
         <v>45846</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -4707,7 +4707,7 @@
         <v>45205</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -4792,7 +4792,7 @@
         <v>45616</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -4881,7 +4881,7 @@
         <v>45856.55965277777</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -4970,7 +4970,7 @@
         <v>45846</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5064,7 +5064,7 @@
         <v>45569.41550925926</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5149,7 +5149,7 @@
         <v>45876.69954861111</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5234,7 +5234,7 @@
         <v>45924.51141203703</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5319,7 +5319,7 @@
         <v>44260</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5376,7 +5376,7 @@
         <v>44188</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5433,7 +5433,7 @@
         <v>44137</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5490,7 +5490,7 @@
         <v>44147</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -5547,7 +5547,7 @@
         <v>44306</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -5604,7 +5604,7 @@
         <v>44308</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -5666,7 +5666,7 @@
         <v>44144</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -5723,7 +5723,7 @@
         <v>44239.33525462963</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -5780,7 +5780,7 @@
         <v>44328.35063657408</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -5837,7 +5837,7 @@
         <v>44404.84280092592</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -5894,7 +5894,7 @@
         <v>44404.84659722223</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -5951,7 +5951,7 @@
         <v>44496</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6008,7 +6008,7 @@
         <v>44278.3859375</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6065,7 +6065,7 @@
         <v>44575.80925925926</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6122,7 +6122,7 @@
         <v>44662</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -6179,7 +6179,7 @@
         <v>44487</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -6236,7 +6236,7 @@
         <v>44749.55936342593</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -6293,7 +6293,7 @@
         <v>44749.55703703704</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -6350,7 +6350,7 @@
         <v>44273.62572916667</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -6407,7 +6407,7 @@
         <v>44454.35472222222</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -6464,7 +6464,7 @@
         <v>44308</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -6526,7 +6526,7 @@
         <v>44225</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -6583,7 +6583,7 @@
         <v>44308</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -6645,7 +6645,7 @@
         <v>44349</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -6702,7 +6702,7 @@
         <v>44792.53711805555</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -6759,7 +6759,7 @@
         <v>44194</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -6816,7 +6816,7 @@
         <v>44225</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -6873,7 +6873,7 @@
         <v>44411</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -6930,7 +6930,7 @@
         <v>44442</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -6987,7 +6987,7 @@
         <v>44809</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -7044,7 +7044,7 @@
         <v>44487.49392361111</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -7101,7 +7101,7 @@
         <v>44487</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -7158,7 +7158,7 @@
         <v>44749.32716435185</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -7215,7 +7215,7 @@
         <v>44420.68987268519</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -7272,7 +7272,7 @@
         <v>44404.84138888889</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -7329,7 +7329,7 @@
         <v>44266</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -7386,7 +7386,7 @@
         <v>44881.81052083334</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -7443,7 +7443,7 @@
         <v>44665.60081018518</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -7500,7 +7500,7 @@
         <v>44869.49265046296</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -7562,7 +7562,7 @@
         <v>44734</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -7624,7 +7624,7 @@
         <v>44792</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -7681,7 +7681,7 @@
         <v>44259</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -7738,7 +7738,7 @@
         <v>44365</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -7795,7 +7795,7 @@
         <v>44538</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -7852,7 +7852,7 @@
         <v>44263</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -7914,7 +7914,7 @@
         <v>44113</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -7971,7 +7971,7 @@
         <v>44272</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -8028,7 +8028,7 @@
         <v>44487</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -8085,7 +8085,7 @@
         <v>44487</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -8142,7 +8142,7 @@
         <v>44852.74376157407</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -8204,7 +8204,7 @@
         <v>44292</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -8261,7 +8261,7 @@
         <v>44498.56373842592</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -8318,7 +8318,7 @@
         <v>44200</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -8375,7 +8375,7 @@
         <v>44875.59231481481</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -8432,7 +8432,7 @@
         <v>44111</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -8489,7 +8489,7 @@
         <v>44881.79847222222</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -8546,7 +8546,7 @@
         <v>44286.34827546297</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -8603,7 +8603,7 @@
         <v>44273</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -8660,7 +8660,7 @@
         <v>44673</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -8717,7 +8717,7 @@
         <v>44278.38752314815</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -8774,7 +8774,7 @@
         <v>44298.46462962963</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -8836,7 +8836,7 @@
         <v>44298.46582175926</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -8898,7 +8898,7 @@
         <v>44279.37552083333</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -8955,7 +8955,7 @@
         <v>44347.61920138889</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -9012,7 +9012,7 @@
         <v>44754.47359953704</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -9074,7 +9074,7 @@
         <v>44855.3080787037</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -9131,7 +9131,7 @@
         <v>44476</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -9188,7 +9188,7 @@
         <v>44373.75251157407</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -9245,7 +9245,7 @@
         <v>44347.6287962963</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -9302,7 +9302,7 @@
         <v>44511</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -9359,7 +9359,7 @@
         <v>44466.4425</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -9416,7 +9416,7 @@
         <v>44377</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -9473,7 +9473,7 @@
         <v>44440.71997685185</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -9530,7 +9530,7 @@
         <v>44104</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -9587,7 +9587,7 @@
         <v>44840</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -9644,7 +9644,7 @@
         <v>44280</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -9701,7 +9701,7 @@
         <v>44613</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -9758,7 +9758,7 @@
         <v>44456.46952546296</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -9815,7 +9815,7 @@
         <v>44537</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -9872,7 +9872,7 @@
         <v>44356</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -9929,7 +9929,7 @@
         <v>44360</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -9986,7 +9986,7 @@
         <v>44476</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -10043,7 +10043,7 @@
         <v>44575</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -10100,7 +10100,7 @@
         <v>44298.44060185185</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -10162,7 +10162,7 @@
         <v>44711</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -10219,7 +10219,7 @@
         <v>44659.57226851852</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -10281,7 +10281,7 @@
         <v>44659</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -10343,7 +10343,7 @@
         <v>44454.4800925926</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -10400,7 +10400,7 @@
         <v>44578</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -10457,7 +10457,7 @@
         <v>44344</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -10514,7 +10514,7 @@
         <v>44474.25150462963</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -10571,7 +10571,7 @@
         <v>44628</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -10628,7 +10628,7 @@
         <v>44711</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -10685,7 +10685,7 @@
         <v>44711</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -10742,7 +10742,7 @@
         <v>44579.41064814815</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -10799,7 +10799,7 @@
         <v>44841.31997685185</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -10856,7 +10856,7 @@
         <v>44557.71989583333</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -10913,7 +10913,7 @@
         <v>44467.68283564815</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -10970,7 +10970,7 @@
         <v>44792.53936342592</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -11027,7 +11027,7 @@
         <v>44616.39256944445</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -11084,7 +11084,7 @@
         <v>44373</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -11141,7 +11141,7 @@
         <v>44259</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -11198,7 +11198,7 @@
         <v>44239</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -11255,7 +11255,7 @@
         <v>44239</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -11312,7 +11312,7 @@
         <v>44464.40523148148</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -11369,7 +11369,7 @@
         <v>44428.34821759259</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -11431,7 +11431,7 @@
         <v>44412</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -11488,7 +11488,7 @@
         <v>44830.90146990741</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -11545,7 +11545,7 @@
         <v>44787.80010416666</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -11602,7 +11602,7 @@
         <v>44294</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -11659,7 +11659,7 @@
         <v>44575</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -11716,7 +11716,7 @@
         <v>44272</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -11773,7 +11773,7 @@
         <v>44596</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -11830,7 +11830,7 @@
         <v>44428.58511574074</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -11892,7 +11892,7 @@
         <v>44498.57181712963</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -11949,7 +11949,7 @@
         <v>44279.61517361111</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -12006,7 +12006,7 @@
         <v>44308</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -12068,7 +12068,7 @@
         <v>44536</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -12130,7 +12130,7 @@
         <v>44825.40940972222</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -12192,7 +12192,7 @@
         <v>44614</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -12254,7 +12254,7 @@
         <v>44428</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -12316,7 +12316,7 @@
         <v>44585.30171296297</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -12373,7 +12373,7 @@
         <v>44464.42415509259</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -12430,7 +12430,7 @@
         <v>44488</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -12487,7 +12487,7 @@
         <v>44252</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -12544,7 +12544,7 @@
         <v>44579</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -12601,7 +12601,7 @@
         <v>44326</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -12658,7 +12658,7 @@
         <v>44575.8194212963</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -12715,7 +12715,7 @@
         <v>44711</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -12772,7 +12772,7 @@
         <v>44428.596875</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -12834,7 +12834,7 @@
         <v>44819</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -12891,7 +12891,7 @@
         <v>44819.28449074074</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -12948,7 +12948,7 @@
         <v>44292</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -13005,7 +13005,7 @@
         <v>44846.66688657407</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -13062,7 +13062,7 @@
         <v>44605.44909722222</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -13119,7 +13119,7 @@
         <v>44151</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -13176,7 +13176,7 @@
         <v>44523.65311342593</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -13233,7 +13233,7 @@
         <v>44750</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -13290,7 +13290,7 @@
         <v>45056.6438425926</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -13347,7 +13347,7 @@
         <v>45114.55280092593</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -13404,7 +13404,7 @@
         <v>45406.89568287037</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -13461,7 +13461,7 @@
         <v>45406.89640046296</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -13518,7 +13518,7 @@
         <v>45764.30391203704</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -13575,7 +13575,7 @@
         <v>44711</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -13632,7 +13632,7 @@
         <v>45617.4922337963</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -13689,7 +13689,7 @@
         <v>45747.45177083334</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -13746,7 +13746,7 @@
         <v>45758</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -13808,7 +13808,7 @@
         <v>45440.3712037037</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -13865,7 +13865,7 @@
         <v>45747.45038194444</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -13922,7 +13922,7 @@
         <v>45216.47443287037</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -13979,7 +13979,7 @@
         <v>45547.43438657407</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -14041,7 +14041,7 @@
         <v>45469.43982638889</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -14098,7 +14098,7 @@
         <v>44979</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -14155,7 +14155,7 @@
         <v>45777.50512731481</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -14212,7 +14212,7 @@
         <v>45772.45813657407</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -14269,7 +14269,7 @@
         <v>45012</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -14326,7 +14326,7 @@
         <v>45667.63950231481</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -14383,7 +14383,7 @@
         <v>45747.73295138889</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -14440,7 +14440,7 @@
         <v>45404.58408564814</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -14497,7 +14497,7 @@
         <v>45777.60824074074</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -14554,7 +14554,7 @@
         <v>45198.41381944445</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -14611,7 +14611,7 @@
         <v>45198.41887731481</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -14668,7 +14668,7 @@
         <v>45697.26537037037</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -14725,7 +14725,7 @@
         <v>45169</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -14782,7 +14782,7 @@
         <v>44557</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -14839,7 +14839,7 @@
         <v>45048</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -14896,7 +14896,7 @@
         <v>44886.3340625</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -14953,7 +14953,7 @@
         <v>45605.84435185185</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -15010,7 +15010,7 @@
         <v>45152</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -15067,7 +15067,7 @@
         <v>44658</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -15124,7 +15124,7 @@
         <v>45303.63494212963</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -15186,7 +15186,7 @@
         <v>45580.46572916667</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -15243,7 +15243,7 @@
         <v>44550.30402777778</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -15300,7 +15300,7 @@
         <v>45455.42533564815</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -15362,7 +15362,7 @@
         <v>44589.73825231481</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -15419,7 +15419,7 @@
         <v>44532.30398148148</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -15476,7 +15476,7 @@
         <v>45519.48550925926</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -15533,7 +15533,7 @@
         <v>45130</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -15590,7 +15590,7 @@
         <v>45477.33712962963</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -15647,7 +15647,7 @@
         <v>45547.83519675926</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -15709,7 +15709,7 @@
         <v>45112.3174074074</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -15766,7 +15766,7 @@
         <v>45112</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -15823,7 +15823,7 @@
         <v>45145.47684027778</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -15880,7 +15880,7 @@
         <v>45111</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -15937,7 +15937,7 @@
         <v>44628</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -15994,7 +15994,7 @@
         <v>45174</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -16051,7 +16051,7 @@
         <v>45642.60125</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -16108,7 +16108,7 @@
         <v>45557.35435185185</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -16165,7 +16165,7 @@
         <v>45268</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -16222,7 +16222,7 @@
         <v>44614</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -16279,7 +16279,7 @@
         <v>45785.65899305556</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -16336,7 +16336,7 @@
         <v>45462.38087962963</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -16393,7 +16393,7 @@
         <v>44861.62300925926</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -16450,7 +16450,7 @@
         <v>45586.62837962963</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -16507,7 +16507,7 @@
         <v>45324.64302083333</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -16569,7 +16569,7 @@
         <v>45270.42966435185</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -16626,7 +16626,7 @@
         <v>45588</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -16683,7 +16683,7 @@
         <v>44593</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -16740,7 +16740,7 @@
         <v>45179.9259375</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -16797,7 +16797,7 @@
         <v>44507.43497685185</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -16854,7 +16854,7 @@
         <v>45775.4233912037</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -16911,7 +16911,7 @@
         <v>45755.70262731481</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -16968,7 +16968,7 @@
         <v>45177</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -17025,7 +17025,7 @@
         <v>45618</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -17082,7 +17082,7 @@
         <v>44130</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -17139,7 +17139,7 @@
         <v>45275</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -17196,7 +17196,7 @@
         <v>45307.72520833334</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -17253,7 +17253,7 @@
         <v>45012.47533564815</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -17310,7 +17310,7 @@
         <v>45092.42630787037</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -17367,7 +17367,7 @@
         <v>45726.42344907407</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -17429,7 +17429,7 @@
         <v>45405</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -17486,7 +17486,7 @@
         <v>45405</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -17543,7 +17543,7 @@
         <v>44936</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -17600,7 +17600,7 @@
         <v>45538</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -17657,7 +17657,7 @@
         <v>45621</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -17714,7 +17714,7 @@
         <v>44943.44811342593</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -17771,7 +17771,7 @@
         <v>44998</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -17828,7 +17828,7 @@
         <v>45630.70101851852</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -17890,7 +17890,7 @@
         <v>45789.54226851852</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -17947,7 +17947,7 @@
         <v>45621.52488425926</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -18004,7 +18004,7 @@
         <v>45621.5278125</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -18061,7 +18061,7 @@
         <v>45436.68626157408</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -18118,7 +18118,7 @@
         <v>45295.4037962963</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -18180,7 +18180,7 @@
         <v>45392.58569444445</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -18237,7 +18237,7 @@
         <v>44118</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -18299,7 +18299,7 @@
         <v>45790.81799768518</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -18356,7 +18356,7 @@
         <v>45302</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -18413,7 +18413,7 @@
         <v>45300</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -18470,7 +18470,7 @@
         <v>45412</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -18532,7 +18532,7 @@
         <v>45541.38644675926</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -18589,7 +18589,7 @@
         <v>45551.36004629629</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -18646,7 +18646,7 @@
         <v>45456.66137731481</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -18703,7 +18703,7 @@
         <v>44729</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -18760,7 +18760,7 @@
         <v>45350.56959490741</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -18817,7 +18817,7 @@
         <v>45764.4140162037</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -18874,7 +18874,7 @@
         <v>45646.5796412037</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -18931,7 +18931,7 @@
         <v>45645.57626157408</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -18988,7 +18988,7 @@
         <v>44187</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -19050,7 +19050,7 @@
         <v>45790.82361111111</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -19107,7 +19107,7 @@
         <v>45182.36129629629</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -19164,7 +19164,7 @@
         <v>45523.5090625</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -19226,7 +19226,7 @@
         <v>45791.85732638889</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -19283,7 +19283,7 @@
         <v>44151</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -19340,7 +19340,7 @@
         <v>45267.62943287037</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -19397,7 +19397,7 @@
         <v>45149</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -19454,7 +19454,7 @@
         <v>44272</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -19511,7 +19511,7 @@
         <v>44943.44532407408</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -19568,7 +19568,7 @@
         <v>44161.31023148148</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -19625,7 +19625,7 @@
         <v>45757.29700231482</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -19682,7 +19682,7 @@
         <v>45615.89965277778</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -19739,7 +19739,7 @@
         <v>45615.90662037037</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -19796,7 +19796,7 @@
         <v>45523.58461805555</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -19858,7 +19858,7 @@
         <v>44231</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -19915,7 +19915,7 @@
         <v>45793</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -19972,7 +19972,7 @@
         <v>44252</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -20029,7 +20029,7 @@
         <v>44172</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -20086,7 +20086,7 @@
         <v>44103</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -20143,7 +20143,7 @@
         <v>45570.58934027778</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -20200,7 +20200,7 @@
         <v>45797.67148148148</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -20257,7 +20257,7 @@
         <v>45706.67424768519</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -20319,7 +20319,7 @@
         <v>44449</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -20376,7 +20376,7 @@
         <v>44805</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -20438,7 +20438,7 @@
         <v>44811</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -20495,7 +20495,7 @@
         <v>44938.53719907408</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -20557,7 +20557,7 @@
         <v>45281.57759259259</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -20619,7 +20619,7 @@
         <v>44944.40825231482</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -20676,7 +20676,7 @@
         <v>44614.68596064814</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -20733,7 +20733,7 @@
         <v>44729</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -20790,7 +20790,7 @@
         <v>45751.58130787037</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -20847,7 +20847,7 @@
         <v>44137</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -20904,7 +20904,7 @@
         <v>44648.61840277778</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -20961,7 +20961,7 @@
         <v>45470.6672337963</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -21018,7 +21018,7 @@
         <v>45177.5462962963</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -21075,7 +21075,7 @@
         <v>44295.31922453704</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -21132,7 +21132,7 @@
         <v>44963</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -21189,7 +21189,7 @@
         <v>44211</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -21246,7 +21246,7 @@
         <v>44938</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -21308,7 +21308,7 @@
         <v>45588</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -21365,7 +21365,7 @@
         <v>44655.48328703704</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -21422,7 +21422,7 @@
         <v>45687</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -21479,7 +21479,7 @@
         <v>45687</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -21536,7 +21536,7 @@
         <v>44943</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -21593,7 +21593,7 @@
         <v>45769.43446759259</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -21650,7 +21650,7 @@
         <v>44273</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -21707,7 +21707,7 @@
         <v>45253.73424768518</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -21764,7 +21764,7 @@
         <v>44368.64017361111</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -21821,7 +21821,7 @@
         <v>45331</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -21878,7 +21878,7 @@
         <v>45730.44528935185</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -21940,7 +21940,7 @@
         <v>45741.65699074074</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -21997,7 +21997,7 @@
         <v>45184</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -22054,7 +22054,7 @@
         <v>45741.69303240741</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -22111,7 +22111,7 @@
         <v>45755</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -22168,7 +22168,7 @@
         <v>45727.35745370371</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -22225,7 +22225,7 @@
         <v>45727.36243055556</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -22282,7 +22282,7 @@
         <v>45736</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -22339,7 +22339,7 @@
         <v>45740.91412037037</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -22396,7 +22396,7 @@
         <v>45730.3782175926</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -22458,7 +22458,7 @@
         <v>45736</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -22515,7 +22515,7 @@
         <v>44839</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -22577,7 +22577,7 @@
         <v>45092.39466435185</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -22634,7 +22634,7 @@
         <v>45799.5803125</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -22691,7 +22691,7 @@
         <v>44893</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -22748,7 +22748,7 @@
         <v>45743.59641203703</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -22805,7 +22805,7 @@
         <v>45736.67693287037</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -22862,7 +22862,7 @@
         <v>45740.59474537037</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -22919,7 +22919,7 @@
         <v>45727.3134375</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -22976,7 +22976,7 @@
         <v>45727.36650462963</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -23033,7 +23033,7 @@
         <v>45728</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -23090,7 +23090,7 @@
         <v>45799.50469907407</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -23147,7 +23147,7 @@
         <v>45735.65969907407</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -23204,7 +23204,7 @@
         <v>45799.51578703704</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -23261,7 +23261,7 @@
         <v>45363.91521990741</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -23318,7 +23318,7 @@
         <v>45116.44680555556</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -23375,7 +23375,7 @@
         <v>45735</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -23432,7 +23432,7 @@
         <v>45737.67416666666</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -23489,7 +23489,7 @@
         <v>45730.65831018519</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -23546,7 +23546,7 @@
         <v>45734.35039351852</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -23603,7 +23603,7 @@
         <v>45734.35122685185</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -23660,7 +23660,7 @@
         <v>45314</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -23717,7 +23717,7 @@
         <v>44484.49586805556</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -23774,7 +23774,7 @@
         <v>45735.81920138889</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -23831,7 +23831,7 @@
         <v>45545.53883101852</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -23888,7 +23888,7 @@
         <v>44992.66236111111</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -23945,7 +23945,7 @@
         <v>45226.3731712963</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -24002,7 +24002,7 @@
         <v>45624.41041666667</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -24059,7 +24059,7 @@
         <v>44589.74348379629</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -24116,7 +24116,7 @@
         <v>44949</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -24173,7 +24173,7 @@
         <v>44578.52657407407</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -24230,7 +24230,7 @@
         <v>45733</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -24287,7 +24287,7 @@
         <v>45805</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -24344,7 +24344,7 @@
         <v>45519.49606481481</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -24401,7 +24401,7 @@
         <v>44482</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -24458,7 +24458,7 @@
         <v>44662</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -24515,7 +24515,7 @@
         <v>44904.49826388889</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -24572,7 +24572,7 @@
         <v>45587</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -24629,7 +24629,7 @@
         <v>44804</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -24686,7 +24686,7 @@
         <v>45804.31922453704</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -24743,7 +24743,7 @@
         <v>45805.60481481482</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -24800,7 +24800,7 @@
         <v>45805.58372685185</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -24857,7 +24857,7 @@
         <v>44904.59393518518</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -24919,7 +24919,7 @@
         <v>44897</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -24976,7 +24976,7 @@
         <v>44904.61212962963</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -25038,7 +25038,7 @@
         <v>45804</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -25095,7 +25095,7 @@
         <v>45805.58325231481</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -25152,7 +25152,7 @@
         <v>44861.6108912037</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -25209,7 +25209,7 @@
         <v>44861</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -25266,7 +25266,7 @@
         <v>45806.2833912037</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -25323,7 +25323,7 @@
         <v>45806.28703703704</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -25380,7 +25380,7 @@
         <v>45043.67869212963</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -25437,7 +25437,7 @@
         <v>45272</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -25494,7 +25494,7 @@
         <v>45806.26452546296</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -25551,7 +25551,7 @@
         <v>45406</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -25608,7 +25608,7 @@
         <v>45622.35340277778</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -25665,7 +25665,7 @@
         <v>45113.31806712963</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -25722,7 +25722,7 @@
         <v>45587</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -25779,7 +25779,7 @@
         <v>45597.43615740741</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -25836,7 +25836,7 @@
         <v>45811</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -25893,7 +25893,7 @@
         <v>45205</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -25950,7 +25950,7 @@
         <v>45751.52445601852</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -26012,7 +26012,7 @@
         <v>44423.87825231482</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -26069,7 +26069,7 @@
         <v>44882</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -26126,7 +26126,7 @@
         <v>44225</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -26183,7 +26183,7 @@
         <v>45183</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -26240,7 +26240,7 @@
         <v>45810</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -26297,7 +26297,7 @@
         <v>45769.60498842593</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -26354,7 +26354,7 @@
         <v>45373.60802083334</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -26411,7 +26411,7 @@
         <v>45455.4374537037</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -26473,7 +26473,7 @@
         <v>44571</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -26530,7 +26530,7 @@
         <v>45701.38606481482</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -26587,7 +26587,7 @@
         <v>45558.63807870371</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -26649,7 +26649,7 @@
         <v>45539.34539351852</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -26706,7 +26706,7 @@
         <v>44992.67101851852</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -26783,7 +26783,7 @@
         <v>45637.51090277778</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -26840,7 +26840,7 @@
         <v>45644.62803240741</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -26897,7 +26897,7 @@
         <v>44433</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -26954,7 +26954,7 @@
         <v>44592.28611111111</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -27011,7 +27011,7 @@
         <v>45547.83950231481</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -27073,7 +27073,7 @@
         <v>44608</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -27130,7 +27130,7 @@
         <v>45643.89232638889</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -27187,7 +27187,7 @@
         <v>45477.38181712963</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -27244,7 +27244,7 @@
         <v>44853</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -27306,7 +27306,7 @@
         <v>45455.42981481482</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -27368,7 +27368,7 @@
         <v>45561.87885416667</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -27425,7 +27425,7 @@
         <v>45182.71081018518</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -27482,7 +27482,7 @@
         <v>44734</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -27544,7 +27544,7 @@
         <v>44734</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -27606,7 +27606,7 @@
         <v>44904</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -27663,7 +27663,7 @@
         <v>45819.53688657407</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -27720,7 +27720,7 @@
         <v>45819.53980324074</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -27777,7 +27777,7 @@
         <v>45819.5429050926</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -27834,7 +27834,7 @@
         <v>45197.38018518518</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -27891,7 +27891,7 @@
         <v>45321</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -27948,7 +27948,7 @@
         <v>45461.65380787037</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -28005,7 +28005,7 @@
         <v>45043</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -28062,7 +28062,7 @@
         <v>44622</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -28119,7 +28119,7 @@
         <v>44893</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -28181,7 +28181,7 @@
         <v>45037.67510416666</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -28238,7 +28238,7 @@
         <v>45600.48127314815</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -28295,7 +28295,7 @@
         <v>45600.48347222222</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -28352,7 +28352,7 @@
         <v>44308.520625</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -28409,7 +28409,7 @@
         <v>45701.37818287037</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -28466,7 +28466,7 @@
         <v>45435.51875</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -28523,7 +28523,7 @@
         <v>45726.44835648148</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -28580,7 +28580,7 @@
         <v>45252.58925925926</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -28637,7 +28637,7 @@
         <v>45215.71418981482</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -28694,7 +28694,7 @@
         <v>45272.42149305555</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -28751,7 +28751,7 @@
         <v>45372.34530092592</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -28808,7 +28808,7 @@
         <v>45545.59315972222</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -28870,7 +28870,7 @@
         <v>44711</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -28927,7 +28927,7 @@
         <v>45477.48771990741</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -28984,7 +28984,7 @@
         <v>45477.48915509259</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -29041,7 +29041,7 @@
         <v>45299</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -29098,7 +29098,7 @@
         <v>44998.8734837963</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -29155,7 +29155,7 @@
         <v>45175.44625</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -29212,7 +29212,7 @@
         <v>45118</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -29269,7 +29269,7 @@
         <v>45468.44574074074</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -29326,7 +29326,7 @@
         <v>45371.60959490741</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -29383,7 +29383,7 @@
         <v>45597.53744212963</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -29440,7 +29440,7 @@
         <v>45682.47550925926</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -29497,7 +29497,7 @@
         <v>44977.26300925926</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -29554,7 +29554,7 @@
         <v>45446.56622685185</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -29611,7 +29611,7 @@
         <v>44591</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -29668,7 +29668,7 @@
         <v>45708.50255787037</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -29725,7 +29725,7 @@
         <v>45211</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -29782,7 +29782,7 @@
         <v>45617.92190972222</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -29839,7 +29839,7 @@
         <v>45112</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -29896,7 +29896,7 @@
         <v>44585</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -29953,7 +29953,7 @@
         <v>45152</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -30010,7 +30010,7 @@
         <v>45750.50650462963</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -30067,7 +30067,7 @@
         <v>45701.31962962963</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -30124,7 +30124,7 @@
         <v>45351.65180555556</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -30186,7 +30186,7 @@
         <v>45375</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -30243,7 +30243,7 @@
         <v>44846.68375</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -30300,7 +30300,7 @@
         <v>45541.36828703704</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -30357,7 +30357,7 @@
         <v>44853</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -30414,7 +30414,7 @@
         <v>45492.70833333334</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -30471,7 +30471,7 @@
         <v>45775.32407407407</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -30528,7 +30528,7 @@
         <v>45674.47359953704</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -30585,7 +30585,7 @@
         <v>45502.32021990741</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -30642,7 +30642,7 @@
         <v>44904</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -30704,7 +30704,7 @@
         <v>44158</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -30761,7 +30761,7 @@
         <v>45562.38306712963</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -30818,7 +30818,7 @@
         <v>45189</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -30875,7 +30875,7 @@
         <v>45477.38554398148</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -30932,7 +30932,7 @@
         <v>45477.38663194444</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -30989,7 +30989,7 @@
         <v>44507.82581018518</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -31046,7 +31046,7 @@
         <v>45358</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -31103,7 +31103,7 @@
         <v>45358.61696759259</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -31160,7 +31160,7 @@
         <v>45359.54100694445</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -31217,7 +31217,7 @@
         <v>44449</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -31274,7 +31274,7 @@
         <v>45243</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -31336,7 +31336,7 @@
         <v>45434.58377314815</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -31393,7 +31393,7 @@
         <v>45294</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -31455,7 +31455,7 @@
         <v>45184</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -31512,7 +31512,7 @@
         <v>45757</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -31569,7 +31569,7 @@
         <v>45079</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -31626,7 +31626,7 @@
         <v>44355.60153935185</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -31683,7 +31683,7 @@
         <v>45035</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -31740,7 +31740,7 @@
         <v>44950</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -31797,7 +31797,7 @@
         <v>44950</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -31854,7 +31854,7 @@
         <v>44950</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -31911,7 +31911,7 @@
         <v>45240</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -31968,7 +31968,7 @@
         <v>44626</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -32025,7 +32025,7 @@
         <v>44360.54226851852</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -32082,7 +32082,7 @@
         <v>45246.50074074074</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -32144,7 +32144,7 @@
         <v>45058</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -32201,7 +32201,7 @@
         <v>45679.36950231482</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -32258,7 +32258,7 @@
         <v>44930</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -32315,7 +32315,7 @@
         <v>45531</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -32372,7 +32372,7 @@
         <v>45757.30554398148</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -32429,7 +32429,7 @@
         <v>45547.42313657407</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -32491,7 +32491,7 @@
         <v>45462.37888888889</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -32548,7 +32548,7 @@
         <v>45201</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -32605,7 +32605,7 @@
         <v>45747.44508101852</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -32662,7 +32662,7 @@
         <v>45119.54038194445</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -32719,7 +32719,7 @@
         <v>45547.53320601852</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -32776,7 +32776,7 @@
         <v>45566</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -32833,7 +32833,7 @@
         <v>45566</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -32890,7 +32890,7 @@
         <v>44109</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -32947,7 +32947,7 @@
         <v>44325.76335648148</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -33004,7 +33004,7 @@
         <v>45502.33179398148</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -33061,7 +33061,7 @@
         <v>45201.45827546297</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -33118,7 +33118,7 @@
         <v>44837</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -33175,7 +33175,7 @@
         <v>45681.57619212963</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -33232,7 +33232,7 @@
         <v>44719.43577546296</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -33289,7 +33289,7 @@
         <v>45335.76891203703</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -33351,7 +33351,7 @@
         <v>45210.34773148148</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -33408,7 +33408,7 @@
         <v>45092</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -33465,7 +33465,7 @@
         <v>44614.56209490741</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -33522,7 +33522,7 @@
         <v>45099.74195601852</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -33579,7 +33579,7 @@
         <v>44321</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -33641,7 +33641,7 @@
         <v>45271</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -33698,7 +33698,7 @@
         <v>44943.48144675926</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -33755,7 +33755,7 @@
         <v>45021</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -33812,7 +33812,7 @@
         <v>44963.66563657407</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -33869,7 +33869,7 @@
         <v>45201</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -33931,7 +33931,7 @@
         <v>44935.37284722222</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -33988,7 +33988,7 @@
         <v>44867</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -34045,7 +34045,7 @@
         <v>44985</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -34102,7 +34102,7 @@
         <v>44959.36028935185</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -34164,7 +34164,7 @@
         <v>45180</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -34221,7 +34221,7 @@
         <v>44904</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -34278,7 +34278,7 @@
         <v>44575.80709490741</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -34335,7 +34335,7 @@
         <v>45497</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -34392,7 +34392,7 @@
         <v>45245.46393518519</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -34449,7 +34449,7 @@
         <v>45107</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -34506,7 +34506,7 @@
         <v>45764.40184027778</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -34563,7 +34563,7 @@
         <v>45735.82282407407</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -34620,7 +34620,7 @@
         <v>45314</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -34677,7 +34677,7 @@
         <v>45295.40646990741</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -34739,7 +34739,7 @@
         <v>45617.91424768518</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -34796,7 +34796,7 @@
         <v>45260.85619212963</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -34853,7 +34853,7 @@
         <v>44113</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -34910,7 +34910,7 @@
         <v>45008</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -34967,7 +34967,7 @@
         <v>45105.34402777778</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -35024,7 +35024,7 @@
         <v>45826</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -35081,7 +35081,7 @@
         <v>45534.36645833333</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -35138,7 +35138,7 @@
         <v>45617.45760416667</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -35195,7 +35195,7 @@
         <v>45700.60138888889</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -35252,7 +35252,7 @@
         <v>45474.70864583334</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -35309,7 +35309,7 @@
         <v>44564.8419212963</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -35366,7 +35366,7 @@
         <v>45377.42784722222</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -35423,7 +35423,7 @@
         <v>45219</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -35480,7 +35480,7 @@
         <v>45124.59594907407</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -35537,7 +35537,7 @@
         <v>44261</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -35594,7 +35594,7 @@
         <v>45363.45982638889</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -35651,7 +35651,7 @@
         <v>45240</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -35708,7 +35708,7 @@
         <v>45759.5549537037</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -35765,7 +35765,7 @@
         <v>45051</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -35822,7 +35822,7 @@
         <v>44487</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -35879,7 +35879,7 @@
         <v>44229</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -35936,7 +35936,7 @@
         <v>44966.57471064815</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -35998,7 +35998,7 @@
         <v>45194</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -36055,7 +36055,7 @@
         <v>45194</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -36112,7 +36112,7 @@
         <v>45112</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -36169,7 +36169,7 @@
         <v>44148</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -36226,7 +36226,7 @@
         <v>45831.51019675926</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -36283,7 +36283,7 @@
         <v>45408.67427083333</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -36345,7 +36345,7 @@
         <v>45107</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -36402,7 +36402,7 @@
         <v>45316</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -36459,7 +36459,7 @@
         <v>45015</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -36516,7 +36516,7 @@
         <v>44631</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -36573,7 +36573,7 @@
         <v>44904</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -36630,7 +36630,7 @@
         <v>45049</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -36687,7 +36687,7 @@
         <v>45552.48335648148</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -36744,7 +36744,7 @@
         <v>45833.65434027778</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -36801,7 +36801,7 @@
         <v>45338</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -36863,7 +36863,7 @@
         <v>45833.63770833334</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -36920,7 +36920,7 @@
         <v>44893</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -36982,7 +36982,7 @@
         <v>45834.48820601852</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -37039,7 +37039,7 @@
         <v>45716.7125</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -37096,7 +37096,7 @@
         <v>45338.69246527777</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -37158,7 +37158,7 @@
         <v>44483.58045138889</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -37215,7 +37215,7 @@
         <v>45169</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -37272,7 +37272,7 @@
         <v>44894</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -37329,7 +37329,7 @@
         <v>45679.98971064815</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -37386,7 +37386,7 @@
         <v>45679.99299768519</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -37443,7 +37443,7 @@
         <v>45630.6993287037</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -37500,7 +37500,7 @@
         <v>45769.60440972223</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -37557,7 +37557,7 @@
         <v>45839.71761574074</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -37614,7 +37614,7 @@
         <v>44735</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -37671,7 +37671,7 @@
         <v>44893.50922453704</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -37733,7 +37733,7 @@
         <v>45841.71503472222</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -37790,7 +37790,7 @@
         <v>44605.45792824074</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -37847,7 +37847,7 @@
         <v>45645.88440972222</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -37904,7 +37904,7 @@
         <v>45197.61039351852</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -37966,7 +37966,7 @@
         <v>45406.89703703704</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -38023,7 +38023,7 @@
         <v>45681.48793981481</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -38080,7 +38080,7 @@
         <v>44412.7071875</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -38137,7 +38137,7 @@
         <v>45841.4390625</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -38194,7 +38194,7 @@
         <v>44985.35407407407</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -38251,7 +38251,7 @@
         <v>44923.55936342593</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -38308,7 +38308,7 @@
         <v>45764.31284722222</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -38365,7 +38365,7 @@
         <v>45756</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -38422,7 +38422,7 @@
         <v>45736</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -38479,7 +38479,7 @@
         <v>45300</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -38536,7 +38536,7 @@
         <v>45887.62158564815</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -38593,7 +38593,7 @@
         <v>45887.62953703704</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -38650,7 +38650,7 @@
         <v>45051.37461805555</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -38707,7 +38707,7 @@
         <v>44484</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -38764,7 +38764,7 @@
         <v>45842.49056712963</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -38821,7 +38821,7 @@
         <v>45770.51686342592</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -38878,7 +38878,7 @@
         <v>45558.51949074074</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -38940,7 +38940,7 @@
         <v>45758</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -39002,7 +39002,7 @@
         <v>45706.66618055556</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -39064,7 +39064,7 @@
         <v>45887.68474537037</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -39121,7 +39121,7 @@
         <v>45671.44716435186</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -39178,7 +39178,7 @@
         <v>45705</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -39235,7 +39235,7 @@
         <v>45740.59871527777</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -39292,7 +39292,7 @@
         <v>45681.53460648148</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -39349,7 +39349,7 @@
         <v>45693</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -39406,7 +39406,7 @@
         <v>44659</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -39468,7 +39468,7 @@
         <v>45797.56770833334</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -39525,7 +39525,7 @@
         <v>45845.60700231481</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -39582,7 +39582,7 @@
         <v>45842.49457175926</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -39639,7 +39639,7 @@
         <v>45842.5059375</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -39696,7 +39696,7 @@
         <v>45587.47273148148</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -39753,7 +39753,7 @@
         <v>45009</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -39810,7 +39810,7 @@
         <v>45846.73861111111</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -39867,7 +39867,7 @@
         <v>44272</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -39924,7 +39924,7 @@
         <v>45603.60537037037</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -39981,7 +39981,7 @@
         <v>45455.40401620371</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -40043,7 +40043,7 @@
         <v>45846.48190972222</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -40100,7 +40100,7 @@
         <v>44889</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -40157,7 +40157,7 @@
         <v>45846</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -40219,7 +40219,7 @@
         <v>45846</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -40281,7 +40281,7 @@
         <v>45846</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -40343,7 +40343,7 @@
         <v>45127</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -40400,7 +40400,7 @@
         <v>45644.62243055556</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -40457,7 +40457,7 @@
         <v>44853</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -40514,7 +40514,7 @@
         <v>45401.34349537037</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -40571,7 +40571,7 @@
         <v>44988</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -40628,7 +40628,7 @@
         <v>44677</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -40685,7 +40685,7 @@
         <v>45471.4034837963</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -40742,7 +40742,7 @@
         <v>45706.69090277778</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -40804,7 +40804,7 @@
         <v>45198.59607638889</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -40861,7 +40861,7 @@
         <v>45756</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -40918,7 +40918,7 @@
         <v>45764.30016203703</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -40975,7 +40975,7 @@
         <v>44414</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -41032,7 +41032,7 @@
         <v>45324.64579861111</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -41094,7 +41094,7 @@
         <v>45324.64745370371</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -41156,7 +41156,7 @@
         <v>45671.44894675926</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -41213,7 +41213,7 @@
         <v>45414</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -41270,7 +41270,7 @@
         <v>45761.49107638889</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -41327,7 +41327,7 @@
         <v>45895.29351851852</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -41384,7 +41384,7 @@
         <v>45892.42259259259</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -41441,7 +41441,7 @@
         <v>45751</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -41503,7 +41503,7 @@
         <v>45892.46936342592</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -41560,7 +41560,7 @@
         <v>45704</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -41617,7 +41617,7 @@
         <v>45364.40862268519</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -41674,7 +41674,7 @@
         <v>45892.38811342593</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -41731,7 +41731,7 @@
         <v>45892.43763888889</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45926</v>
+        <v>45927</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -41788,7 +41788,7 @@
         <v>45567</v>
       </c>
       <c 